--- a/GICS_SubIndustry_Leaderboard.xlsx
+++ b/GICS_SubIndustry_Leaderboard.xlsx
@@ -616,16 +616,16 @@
         <v>0.9924480510984311</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>1.689503449180924</v>
+        <v>1.689503462302694</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>4.934172798556512</v>
+        <v>4.934172800529265</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>4.970235288947002</v>
+        <v>4.970235416896228</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.6480084033035107</v>
+        <v>0.6480084076784873</v>
       </c>
     </row>
     <row r="3">
@@ -669,19 +669,19 @@
         <v>0.3738133925399351</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>0.7078721412131196</v>
+        <v>0.7078721889299694</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.8922790072008017</v>
+        <v>0.8922791281767735</v>
       </c>
       <c r="N3" s="5" t="n">
         <v>1.113930953823824</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>1.562774775517577</v>
+        <v>1.562774391459258</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>0.3675338244448547</v>
+        <v>0.3675337563907899</v>
       </c>
     </row>
     <row r="4">
@@ -725,19 +725,19 @@
         <v>0.5134525521977806</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0.3920259175515631</v>
+        <v>0.3920258970050808</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.8622476679172718</v>
+        <v>0.8622476484620613</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>1.066662337782509</v>
+        <v>1.066662313809357</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0.6138773627099472</v>
+        <v>0.6138774269104439</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.1608024481217933</v>
+        <v>0.1608024603148983</v>
       </c>
     </row>
     <row r="5">
@@ -781,19 +781,19 @@
         <v>-0.00960838641158949</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.2641861062389021</v>
+        <v>0.2641861292245408</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0.8233405176788805</v>
+        <v>0.823340492710642</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>1.808284640813201</v>
+        <v>1.808284608159607</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>5.187059083265262</v>
+        <v>5.18705899600372</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0.6926308282493475</v>
+        <v>0.6926308099618188</v>
       </c>
     </row>
     <row r="6">
@@ -840,16 +840,16 @@
         <v>0.1594072533706812</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.8969335208759361</v>
+        <v>0.8969335527453479</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>1.834387778650562</v>
+        <v>1.83438783780921</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>2.942185012669034</v>
+        <v>2.942185369605466</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.5761466976302484</v>
+        <v>0.5761467406934807</v>
       </c>
     </row>
     <row r="7">
@@ -902,10 +902,10 @@
         <v>0.8486851151037247</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>1.167472935984003</v>
+        <v>1.167473160251502</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0.2941498344971634</v>
+        <v>0.2941498791322055</v>
       </c>
     </row>
     <row r="8">
@@ -952,16 +952,16 @@
         <v>0.08714200806174643</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.5778851096088218</v>
+        <v>0.5778852501672704</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>0.9209122567446928</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>2.768441232451782</v>
+        <v>2.768440831585422</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.5561588095723902</v>
+        <v>0.5561587543938071</v>
       </c>
     </row>
     <row r="9">
@@ -1005,19 +1005,19 @@
         <v>-0.1268820605514715</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.398789254115313</v>
+        <v>0.3987892392351556</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.7000071157167725</v>
+        <v>0.7000071160932095</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>1.070058616777526</v>
+        <v>1.070058627172328</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>2.246841256561231</v>
+        <v>2.24684124466884</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.3628366123567088</v>
+        <v>0.362836602658243</v>
       </c>
     </row>
     <row r="10">
@@ -1064,16 +1064,16 @@
         <v>0.6921625349636423</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.3490394272723993</v>
+        <v>0.3490394384046352</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0.376077694296597</v>
+        <v>0.3760776842985303</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>1.456578666995776</v>
+        <v>1.456578641316315</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.3117113499025544</v>
+        <v>0.3117113434802579</v>
       </c>
     </row>
     <row r="11">
@@ -1120,16 +1120,16 @@
         <v>0.5965390418073115</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.4349437768362868</v>
+        <v>0.4349438064262685</v>
       </c>
       <c r="N11" s="5" t="n">
         <v>0.5495272889178864</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>-0.08624864265311097</v>
+        <v>-0.08624859804347576</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-0.03024678784375082</v>
+        <v>-0.03024677163121486</v>
       </c>
     </row>
     <row r="12">
@@ -1182,10 +1182,10 @@
         <v>1.289493331989727</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>4.591970713902266</v>
+        <v>4.591970839325541</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.7541536829942324</v>
+        <v>0.7541537024514261</v>
       </c>
     </row>
     <row r="13">
@@ -1235,13 +1235,13 @@
         <v>0.1017917554135765</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.3238683441397184</v>
+        <v>0.3238683433157796</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>0.2198970616528984</v>
+        <v>0.2198971276122894</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>0.06517598889768512</v>
+        <v>0.06517600877150605</v>
       </c>
     </row>
     <row r="14">
@@ -1288,16 +1288,16 @@
         <v>0.3159818698378061</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.5088216904754849</v>
+        <v>0.5088216116698036</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.71600629254255</v>
+        <v>0.7160062058179317</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>0.9651403842670784</v>
+        <v>0.9651407198518716</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2466195474212831</v>
+        <v>0.24661961940513</v>
       </c>
     </row>
     <row r="15">
@@ -1347,13 +1347,13 @@
         <v>0.1159874636315039</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.2116188540381096</v>
+        <v>0.2116187227202022</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>0.3614006223594555</v>
+        <v>0.3614002078793204</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0.1083118624864872</v>
+        <v>0.1083117500108282</v>
       </c>
     </row>
     <row r="16">
@@ -1459,13 +1459,13 @@
         <v>0.5139438593681176</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.2597938131963313</v>
+        <v>0.2597938971517011</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1.946497695888449</v>
+        <v>1.946497466256829</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.4336243492325234</v>
+        <v>0.4336243119899477</v>
       </c>
     </row>
     <row r="18">
@@ -1512,16 +1512,16 @@
         <v>0.1824298735983613</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.3648968793585052</v>
+        <v>0.3648969103409923</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.4328197089235284</v>
+        <v>0.4328196573631661</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.6644180018849647</v>
+        <v>0.6644179561744801</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.1842247374355078</v>
+        <v>0.1842247270485688</v>
       </c>
     </row>
     <row r="19">
@@ -1565,19 +1565,19 @@
         <v>0.2147084261378599</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.2500090062146806</v>
+        <v>0.2500090241968267</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>0.2654522087090681</v>
+        <v>0.265452229522232</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.303880623331356</v>
+        <v>0.303880618620078</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3.190330955499822</v>
+        <v>3.190331014246819</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>0.540878093383948</v>
+        <v>0.5408781039678922</v>
       </c>
     </row>
     <row r="20">
@@ -1630,10 +1630,10 @@
         <v>0.02616451406140885</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>-0.009824766617435476</v>
+        <v>-0.009824983513860297</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-0.003285706247341369</v>
+        <v>-0.003285779023612156</v>
       </c>
     </row>
     <row r="21">
@@ -1739,13 +1739,13 @@
         <v>0.5079479523714554</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0.5678751524086375</v>
+        <v>0.5678752521826655</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0.2122242763243365</v>
+        <v>0.2122240811135779</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.06208781869321589</v>
+        <v>0.06208776202385313</v>
       </c>
     </row>
     <row r="23">
@@ -1795,13 +1795,13 @@
         <v>0.3209028104532512</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>0.2024936551015688</v>
+        <v>0.2024935611079193</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>2.504647315145934</v>
+        <v>2.504647714346963</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0.5189661880587382</v>
+        <v>0.5189662457319539</v>
       </c>
     </row>
     <row r="24">
@@ -1904,16 +1904,16 @@
         <v>0.1750336364463755</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0.3189620503500854</v>
+        <v>0.318962066401958</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>0.2523629235696113</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>0.5519780981493372</v>
+        <v>0.5519781115622402</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0.1395335053304501</v>
+        <v>0.1395335103033644</v>
       </c>
     </row>
     <row r="26">
@@ -1957,19 +1957,19 @@
         <v>0.1613182616914495</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.2430394218612707</v>
+        <v>0.2430394363568895</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.2650371376133618</v>
+        <v>0.2650371470431486</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0.2159734333342437</v>
+        <v>0.2159734496368819</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>1.118726144080619</v>
+        <v>1.118726135380642</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.2672614286984203</v>
+        <v>0.2672614282354466</v>
       </c>
     </row>
     <row r="27">
@@ -2013,19 +2013,19 @@
         <v>0.1245314426068547</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.07407374581808328</v>
+        <v>0.0740737755011812</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>0.2584372607949403</v>
+        <v>0.2584372845292666</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>0.4474709953397901</v>
+        <v>0.4474710130955589</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.4289149193724729</v>
+        <v>0.4289148045211007</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>0.1018782785020975</v>
+        <v>0.1018782502493215</v>
       </c>
     </row>
     <row r="28">
@@ -2069,19 +2069,19 @@
         <v>0.2832830719512477</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.3714928770010811</v>
+        <v>0.3714928284935299</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.1404615049915731</v>
+        <v>0.1404614706582005</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>-0.05062305249176741</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>0.1674470302172996</v>
+        <v>0.1674471083820381</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.05287541545154884</v>
+        <v>0.05287543896413527</v>
       </c>
     </row>
     <row r="29">
@@ -2125,19 +2125,19 @@
         <v>0.04165178379950152</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.05198584999332206</v>
+        <v>0.05198583392931733</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>0.3282773698949228</v>
+        <v>0.3282773967521531</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>0.5552711198338985</v>
+        <v>0.5552711822209948</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>1.531569292515065</v>
+        <v>1.531569291312114</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>0.3559345805908664</v>
+        <v>0.3559345825770047</v>
       </c>
     </row>
     <row r="30">
@@ -2181,19 +2181,19 @@
         <v>0.1012734151096499</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.1807301125125367</v>
+        <v>0.1807300646733794</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.2171995916937184</v>
+        <v>0.2171994689685293</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>0.4056428921771173</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>1.280616455428267</v>
+        <v>1.280616560437043</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.2979574043033275</v>
+        <v>0.2979574205734065</v>
       </c>
     </row>
     <row r="31">
@@ -2243,13 +2243,13 @@
         <v>0.4071790573364185</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>0.3963027016444427</v>
+        <v>0.3963027674765286</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0.5309066273906299</v>
+        <v>0.53090667735507</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>0.1518989958108562</v>
+        <v>0.1518990059853352</v>
       </c>
     </row>
     <row r="32">
@@ -2299,13 +2299,13 @@
         <v>0.2774527776568936</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0.3087925952825756</v>
+        <v>0.3087925123936657</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>0.6842389999016294</v>
+        <v>0.6842387253701432</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>0.1897834033444941</v>
+        <v>0.1897833386994676</v>
       </c>
     </row>
     <row r="33">
@@ -2358,10 +2358,10 @@
         <v>0.02661618948331068</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0.6106606052615311</v>
+        <v>0.6106603056529997</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>0.171843046721088</v>
+        <v>0.1718429740306899</v>
       </c>
     </row>
     <row r="34">
@@ -2408,16 +2408,16 @@
         <v>0.2045201696434528</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.4451480846117312</v>
+        <v>0.4451481058027044</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>0.5114714162979613</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>2.396909137132595</v>
+        <v>2.396909143997499</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.4640370470474306</v>
+        <v>0.4640370427313346</v>
       </c>
     </row>
     <row r="35">
@@ -2461,19 +2461,19 @@
         <v>-0.02995402024293878</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.05303361444645976</v>
+        <v>0.05303363716423115</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.3355039291985868</v>
+        <v>0.3355039417574501</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>0.5288410804669745</v>
+        <v>0.5288410532999305</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>3.101966371738689</v>
+        <v>3.101966500553108</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>0.5269735382120195</v>
+        <v>0.5269735438084799</v>
       </c>
     </row>
     <row r="36">
@@ -2520,16 +2520,16 @@
         <v>0.190909276328784</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>0.2269910130597115</v>
+        <v>0.2269910567715943</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0.2341583772990316</v>
+        <v>0.2341583043334485</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>0.6087291044695615</v>
+        <v>0.6087292048697104</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>0.1714748702373786</v>
+        <v>0.1714748945861246</v>
       </c>
     </row>
     <row r="37">
@@ -2573,19 +2573,19 @@
         <v>0.1268723034502179</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.1200738097450045</v>
+        <v>0.1200738209856105</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>0.2117140383769836</v>
+        <v>0.2117140515613812</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>0.2550732453875596</v>
+        <v>0.2550732474161733</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>1.43631794484072</v>
+        <v>1.436317973845096</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>0.3402842600280976</v>
+        <v>0.3402842678868589</v>
       </c>
     </row>
     <row r="38">
@@ -2632,16 +2632,16 @@
         <v>0.01844220923599498</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.2951958430688199</v>
+        <v>0.2951958464679045</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0.2397786634624456</v>
+        <v>0.2397786060394941</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>0.4740699659745725</v>
+        <v>0.4740701349073714</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.1249078540259412</v>
+        <v>0.1249078965668085</v>
       </c>
     </row>
     <row r="39">
@@ -2685,19 +2685,19 @@
         <v>-0.03743029821209776</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.09786162788248687</v>
+        <v>0.09786170394295768</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>0.4476347751241054</v>
+        <v>0.4476346428783498</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>0.3620155031430621</v>
+        <v>0.3620152690126712</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>1.180945954352449</v>
+        <v>1.180946404593328</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>0.2968257773463623</v>
+        <v>0.2968258665865284</v>
       </c>
     </row>
     <row r="40">
@@ -2747,13 +2747,13 @@
         <v>0.2918005264117119</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>0.07632940276097055</v>
+        <v>0.07632940539106325</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>1.150824613327903</v>
+        <v>1.150824629647193</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.288734285397038</v>
+        <v>0.2887342862194544</v>
       </c>
     </row>
     <row r="41">
@@ -2797,19 +2797,19 @@
         <v>0.08794888804276131</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.1614030714693465</v>
+        <v>0.1614030463104778</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0.2493578723734266</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.2436960767851274</v>
+        <v>0.2436961285986553</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.595368212242397</v>
+        <v>0.5953681089350089</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>0.1632999105462765</v>
+        <v>0.1632998773973725</v>
       </c>
     </row>
     <row r="42">
@@ -2853,19 +2853,19 @@
         <v>0.1953360161450693</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.1237167768352853</v>
+        <v>0.1237167948016672</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>0.1807063615379979</v>
+        <v>0.1807063456020605</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0.123488831354806</v>
+        <v>0.1234888474842231</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>1.039022604066907</v>
+        <v>1.039022652547081</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>0.2516006116521289</v>
+        <v>0.2516006213088123</v>
       </c>
     </row>
     <row r="43">
@@ -2915,13 +2915,13 @@
         <v>0.2285101971377285</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>0.4576827694308768</v>
+        <v>0.4576827614816577</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>0.4490707775346967</v>
+        <v>0.4490707935404323</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>0.1186045374516035</v>
+        <v>0.1186045379470988</v>
       </c>
     </row>
     <row r="44">
@@ -2974,10 +2974,10 @@
         <v>0.3601448855908318</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>1.013077447515236</v>
+        <v>1.013077673258502</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.24914963762138</v>
+        <v>0.2491496820666074</v>
       </c>
     </row>
     <row r="45">
@@ -3030,10 +3030,10 @@
         <v>0.2264861979864474</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.2697922244654278</v>
+        <v>0.269792320450329</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>0.08287307270745892</v>
+        <v>0.08287309999262149</v>
       </c>
     </row>
     <row r="46">
@@ -3077,19 +3077,19 @@
         <v>-0.03371517808564595</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.08421785048765301</v>
+        <v>0.08421785207208468</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>0.3674495725937222</v>
+        <v>0.3674495889168815</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>0.4057671154033901</v>
+        <v>0.4057671370221822</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>1.409693808625617</v>
+        <v>1.409694123195389</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>0.3276902250931676</v>
+        <v>0.3276902769656833</v>
       </c>
     </row>
     <row r="47">
@@ -3133,19 +3133,19 @@
         <v>0.006485540591164931</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.1085706252324621</v>
+        <v>0.1085706030564114</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>0.3309803833889677</v>
+        <v>0.3309804112303972</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>0.3240794623428721</v>
+        <v>0.3240794228627281</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>0.2780013004606607</v>
+        <v>0.2780013682846774</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>0.08114666481944269</v>
+        <v>0.08114668278457041</v>
       </c>
     </row>
     <row r="48">
@@ -3195,13 +3195,13 @@
         <v>0.3526010194574228</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>0.2971928117490823</v>
+        <v>0.2971928675811089</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>0.579908535191905</v>
+        <v>0.5799086466354431</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>0.1642106459815188</v>
+        <v>0.1642106723086705</v>
       </c>
     </row>
     <row r="49">
@@ -3245,7 +3245,7 @@
         <v>0.2343439741636805</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.01412065786687773</v>
+        <v>0.01412067298072322</v>
       </c>
       <c r="M49" s="5" t="n">
         <v>0.2014837995758512</v>
@@ -3254,10 +3254,10 @@
         <v>0.07160839327506148</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>0.3644352408674707</v>
+        <v>0.3644353237793464</v>
       </c>
       <c r="P49" s="5" t="n">
-        <v>0.1042951990878256</v>
+        <v>0.1042952186423045</v>
       </c>
     </row>
     <row r="50">
@@ -3304,16 +3304,16 @@
         <v>0.02675515394764698</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.2488808106173878</v>
+        <v>0.2488807375310662</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>0.2751386960018943</v>
+        <v>0.2751386916959467</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>0.9558498787494777</v>
+        <v>0.955849944103495</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.2437459955904825</v>
+        <v>0.2437460089894033</v>
       </c>
     </row>
     <row r="51">
@@ -3357,19 +3357,19 @@
         <v>0.09686429092038358</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0.06935783429579571</v>
+        <v>0.06935784576915371</v>
       </c>
       <c r="M51" s="5" t="n">
         <v>0.2408226074062879</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>0.2268999555599559</v>
+        <v>0.2268999181086121</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>1.245740793805259</v>
+        <v>1.245740746577388</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>0.3054227523628895</v>
+        <v>0.3054227404877848</v>
       </c>
     </row>
     <row r="52">
@@ -3413,19 +3413,19 @@
         <v>-2.512670074936718e-05</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.04934476091578126</v>
+        <v>0.04934474271456361</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>0.2542694649157024</v>
+        <v>0.2542693920714105</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>0.3975964974643605</v>
+        <v>0.3975965435684915</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>1.692672829373481</v>
+        <v>1.69267272263871</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>0.3250766069777097</v>
+        <v>0.3250765837855257</v>
       </c>
     </row>
     <row r="53">
@@ -3472,16 +3472,16 @@
         <v>0.1088183026757145</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>0.3204840441641727</v>
+        <v>0.3204840721020337</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>0.1349978485547435</v>
+        <v>0.1349978939636685</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0.4174402704055697</v>
+        <v>0.4174401565940745</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>0.1019442612276698</v>
+        <v>0.1019442355645885</v>
       </c>
     </row>
     <row r="54">
@@ -3531,13 +3531,13 @@
         <v>0.2129657636891578</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>0.2319380785197356</v>
+        <v>0.2319381982108197</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>0.5720063979156129</v>
+        <v>0.5720063004699318</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.1627457740135008</v>
+        <v>0.1627457499880354</v>
       </c>
     </row>
     <row r="55">
@@ -3584,16 +3584,16 @@
         <v>-0.01180082124522197</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>0.3710582456088989</v>
+        <v>0.3710583338003769</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>0.4989614463329564</v>
+        <v>0.4989615476821325</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>0.2757343075558614</v>
+        <v>0.2757342918646234</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>0.07282136811019076</v>
+        <v>0.07282136348828357</v>
       </c>
     </row>
     <row r="56">
@@ -3646,10 +3646,10 @@
         <v>-0.1290201168825313</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>-0.2715126875723733</v>
+        <v>-0.2715126305821204</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>-0.1002110320189961</v>
+        <v>-0.1002110085552154</v>
       </c>
     </row>
     <row r="57">
@@ -3702,10 +3702,10 @@
         <v>0.113306811159297</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>0.1211436471279215</v>
+        <v>0.1211437493135707</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>0.03885217518322714</v>
+        <v>0.03885220674498147</v>
       </c>
     </row>
     <row r="58">
@@ -3752,16 +3752,16 @@
         <v>0.06027523665098233</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>0.2659161272362649</v>
+        <v>0.265916171364121</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>0.2843142824788842</v>
+        <v>0.2843143013774205</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>0.0820443891981969</v>
+        <v>0.08204437264535347</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>0.02663250171762976</v>
+        <v>0.02663249649446497</v>
       </c>
     </row>
     <row r="59">
@@ -3805,19 +3805,19 @@
         <v>0.1749429121034725</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.1779215661653644</v>
+        <v>0.1779215795666712</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0.08664425742858299</v>
+        <v>0.08664426456030057</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>-0.05717412930099632</v>
+        <v>-0.05717411123654829</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>0.1518264892297862</v>
+        <v>0.1518265011838162</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>0.03178368610511552</v>
+        <v>0.03178368762394652</v>
       </c>
     </row>
     <row r="60">
@@ -3867,13 +3867,13 @@
         <v>0.1513104674627346</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0.3256882795891123</v>
+        <v>0.3256883731373974</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>0.2858402240058917</v>
+        <v>0.2858404000238735</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>0.08741587553949559</v>
+        <v>0.08741592515808616</v>
       </c>
     </row>
     <row r="61">
@@ -3920,16 +3920,16 @@
         <v>0.07618803462892498</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>0.0920571588149071</v>
+        <v>0.09205717937687079</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>0.1492248440863462</v>
+        <v>0.1492248591140973</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>0.9587102975745706</v>
+        <v>0.9587102351391922</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>0.2465796639029449</v>
+        <v>0.2465796482393595</v>
       </c>
     </row>
     <row r="62">
@@ -3982,10 +3982,10 @@
         <v>0.1173537029289581</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>1.260644951241952</v>
+        <v>1.260645069375013</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>0.309820779039593</v>
+        <v>0.3098208000693597</v>
       </c>
     </row>
     <row r="63">
@@ -4029,19 +4029,19 @@
         <v>0.2294473894113705</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.1021293255434761</v>
+        <v>0.1021293071016641</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>0.01260948386710633</v>
+        <v>0.01260951596972278</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>-0.1069377347642857</v>
+        <v>-0.1069376746667833</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>0.1824468031295097</v>
+        <v>0.1824468368893142</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>0.052305536378907</v>
+        <v>0.05230554603526624</v>
       </c>
     </row>
     <row r="64">
@@ -4094,10 +4094,10 @@
         <v>0.1697078731518049</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>-0.2909128944043769</v>
+        <v>-0.290912847881739</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>-0.1162939382921433</v>
+        <v>-0.1162939215652503</v>
       </c>
     </row>
     <row r="65">
@@ -4147,13 +4147,13 @@
         <v>0.1495064612439951</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>0.346256954456084</v>
+        <v>0.3462571268156541</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0.8609341294160948</v>
+        <v>0.8609340603905382</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>0.2279491542128054</v>
+        <v>0.2279491401333578</v>
       </c>
     </row>
     <row r="66">
@@ -4194,22 +4194,22 @@
         <v>-0.05909332897725861</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>0.01857109579349212</v>
+        <v>0.01857110858202631</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>0.0523170695510772</v>
+        <v>0.05231709272884884</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.1858614164601857</v>
+        <v>0.1858614200881896</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>0.1846118048324459</v>
+        <v>0.1846117330869547</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>0.57954028555482</v>
+        <v>0.5795402155719966</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>0.1585968416520502</v>
+        <v>0.1585968220109647</v>
       </c>
     </row>
     <row r="67">
@@ -4256,16 +4256,16 @@
         <v>0.08505035862360322</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.1097737397254764</v>
+        <v>0.1097737883134355</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>0.1529874876449071</v>
+        <v>0.1529874567010876</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0.7856129132311481</v>
+        <v>0.7856129091426315</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>0.2092933445779971</v>
+        <v>0.2092933449764599</v>
       </c>
     </row>
     <row r="68">
@@ -4309,19 +4309,19 @@
         <v>0.04441844090030811</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>0.05382826626435766</v>
+        <v>0.05382820914957287</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.1770791136615124</v>
+        <v>0.1770791166225629</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>0.1204947223471378</v>
+        <v>0.1204946587731858</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>0.300649190812128</v>
+        <v>0.3006490241358402</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>0.09155100530785543</v>
+        <v>0.09155095888285847</v>
       </c>
     </row>
     <row r="69">
@@ -4374,10 +4374,10 @@
         <v>0.02425842543823986</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>-0.0007646272820528432</v>
+        <v>-0.0007645642422281496</v>
       </c>
       <c r="P69" s="5" t="n">
-        <v>-0.0002549407499470302</v>
+        <v>-0.0002549197259541502</v>
       </c>
     </row>
     <row r="70">
@@ -4421,19 +4421,19 @@
         <v>0.03360040203442818</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.03363326406064554</v>
+        <v>-0.03363328714419026</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.1712663093985841</v>
+        <v>0.1712663033657935</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>0.2018002461312752</v>
+        <v>0.2018002599383924</v>
       </c>
       <c r="O70" s="5" t="n">
-        <v>0.1399892712411628</v>
+        <v>0.1399891993690169</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.03330687975313146</v>
+        <v>0.03330685658303365</v>
       </c>
     </row>
     <row r="71">
@@ -4477,7 +4477,7 @@
         <v>0.002527711703117164</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>0.06147176963382717</v>
+        <v>0.06147183181220306</v>
       </c>
       <c r="M71" s="5" t="n">
         <v>0.1716986171763727</v>
@@ -4486,10 +4486,10 @@
         <v>0.1542642840540748</v>
       </c>
       <c r="O71" s="5" t="n">
-        <v>0.4116068213983733</v>
+        <v>0.4116067833861907</v>
       </c>
       <c r="P71" s="5" t="n">
-        <v>0.1120826711062289</v>
+        <v>0.1120826586315193</v>
       </c>
     </row>
     <row r="72">
@@ -4536,16 +4536,16 @@
         <v>0.07026931896600479</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>0.007652174501927418</v>
+        <v>0.007652138529400314</v>
       </c>
       <c r="N72" s="5" t="n">
         <v>0.05935838989456288</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>1.379610193235914</v>
+        <v>1.379610414636162</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.3337862541812983</v>
+        <v>0.333786299114709</v>
       </c>
     </row>
     <row r="73">
@@ -4592,16 +4592,16 @@
         <v>0.02360106458533473</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0.245391840149416</v>
+        <v>0.2453919030746957</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>0.1423333812579526</v>
+        <v>0.1423333245481213</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>1.139239740668071</v>
+        <v>1.139239529014914</v>
       </c>
       <c r="P73" s="5" t="n">
-        <v>0.2874878458354113</v>
+        <v>0.2874878055713352</v>
       </c>
     </row>
     <row r="74">
@@ -4707,13 +4707,13 @@
         <v>0.1806010094877126</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>0.2595543504511</v>
+        <v>0.2595544018460034</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>1.382691774411905</v>
+        <v>1.38269149889729</v>
       </c>
       <c r="P75" s="5" t="n">
-        <v>0.3051345762746616</v>
+        <v>0.3051345283578984</v>
       </c>
     </row>
     <row r="76">
@@ -4763,13 +4763,13 @@
         <v>0.03992159805432804</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>-0.1104310779219834</v>
+        <v>-0.1104310428022987</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>-0.06919549956481369</v>
+        <v>-0.06919563396313605</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>-0.04436059798456971</v>
+        <v>-0.04436064463963696</v>
       </c>
     </row>
     <row r="77">
@@ -4813,19 +4813,19 @@
         <v>0.1012344717073557</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.05030251709222444</v>
+        <v>-0.05030243464380968</v>
       </c>
       <c r="M77" s="5" t="n">
         <v>0.1233223358820625</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>0.08191087326822122</v>
+        <v>0.08191098027091526</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>0.3002016873561912</v>
+        <v>0.3002019964307427</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>0.09144932120538352</v>
+        <v>0.0914494076891923</v>
       </c>
     </row>
     <row r="78">
@@ -4869,19 +4869,19 @@
         <v>0.06427523947843496</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.02738184041960029</v>
+        <v>-0.02738184045222918</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>0.1165332161649811</v>
+        <v>0.1165332052377312</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>0.1341318798972569</v>
+        <v>0.1341318805531005</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>0.3747705010457331</v>
+        <v>0.3747705457557699</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.1017752129250307</v>
+        <v>0.1017752213654469</v>
       </c>
     </row>
     <row r="79">
@@ -4928,16 +4928,16 @@
         <v>-0.1761984211464461</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>0.05487903791809068</v>
+        <v>0.0548790712813233</v>
       </c>
       <c r="N79" s="5" t="n">
         <v>0.8152977251799061</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>2.205445824378558</v>
+        <v>2.205445866980643</v>
       </c>
       <c r="P79" s="5" t="n">
-        <v>0.4167738560094937</v>
+        <v>0.4167738672281133</v>
       </c>
     </row>
     <row r="80">
@@ -4984,16 +4984,16 @@
         <v>0.02690002819140358</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>0.3485131244117188</v>
+        <v>0.3485130094087463</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>0.2735796901563909</v>
+        <v>0.2735797927336361</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>-0.3350535076568909</v>
+        <v>-0.3350536195058804</v>
       </c>
       <c r="P80" s="5" t="n">
-        <v>-0.1271715377652405</v>
+        <v>-0.1271715867040089</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +5037,19 @@
         <v>0.04543201262346608</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0.0002858090561356774</v>
+        <v>0.0002857758791358633</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0.1663004184042515</v>
+        <v>0.166300378960511</v>
       </c>
       <c r="N81" s="5" t="n">
         <v>0.07632736520282785</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>0.9910186876656425</v>
+        <v>0.9910187521039439</v>
       </c>
       <c r="P81" s="5" t="n">
-        <v>0.2572543175130214</v>
+        <v>0.2572543318040276</v>
       </c>
     </row>
     <row r="82">
@@ -5093,13 +5093,13 @@
         <v>0.1069611948925845</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-0.03593369791772927</v>
+        <v>-0.03593366138821741</v>
       </c>
       <c r="M82" s="5" t="n">
         <v>0.1095288952922114</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>0.03811217738180946</v>
+        <v>0.03811211517344903</v>
       </c>
       <c r="O82" s="5" t="n">
         <v>-0.09941654545361674</v>
@@ -5205,19 +5205,19 @@
         <v>0.009726090187758754</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.04821845539039715</v>
+        <v>-0.04821840758375121</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>0.1120766172273392</v>
+        <v>0.1120765853427247</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0.2049693832396312</v>
+        <v>0.2049694216981407</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>0.7107987885507195</v>
+        <v>0.7107987904665757</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>0.1864038038042173</v>
+        <v>0.1864038105495115</v>
       </c>
     </row>
     <row r="85">
@@ -5267,13 +5267,13 @@
         <v>0.2018182966755485</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>0.04686211351156611</v>
+        <v>0.04686209047970458</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>0.2328299132277744</v>
+        <v>0.2328300334973382</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>0.07156958373301414</v>
+        <v>0.07156961886239366</v>
       </c>
     </row>
     <row r="86">
@@ -5317,19 +5317,19 @@
         <v>0.08347028514301225</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.03830362246025323</v>
+        <v>-0.03830364090669788</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.1249813616656421</v>
+        <v>0.1249813710075522</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>0.0110661137344745</v>
+        <v>0.01106610753345488</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>0.04952529029990227</v>
+        <v>0.04952528983491922</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>0.011625448855692</v>
+        <v>0.01162544508198335</v>
       </c>
     </row>
     <row r="87">
@@ -5373,19 +5373,19 @@
         <v>0.02863540224278327</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>0.05859267163869926</v>
+        <v>0.05859269514076164</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>0.09010655615605345</v>
+        <v>0.09010657171796024</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0.05329299786871931</v>
+        <v>0.05329301179695663</v>
       </c>
       <c r="O87" s="5" t="n">
-        <v>0.1700028568474506</v>
+        <v>0.1700028575973385</v>
       </c>
       <c r="P87" s="5" t="n">
-        <v>0.05263821744316725</v>
+        <v>0.05263821892022431</v>
       </c>
     </row>
     <row r="88">
@@ -5429,19 +5429,19 @@
         <v>0.05779766317824369</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>-0.06805455468806322</v>
+        <v>-0.06805456228961823</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>0.095245168414752</v>
+        <v>0.09524517411672186</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>0.1137341911162867</v>
+        <v>0.1137341837924983</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>1.191023859298386</v>
+        <v>1.191023852694354</v>
       </c>
       <c r="P88" s="5" t="n">
-        <v>0.2556015378711989</v>
+        <v>0.2556015394589993</v>
       </c>
     </row>
     <row r="89">
@@ -5485,19 +5485,19 @@
         <v>0.04139833598797971</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0.02023592220296022</v>
+        <v>0.02023584093716346</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>0.1332269030923281</v>
+        <v>0.1332268028294139</v>
       </c>
       <c r="N89" s="5" t="n">
         <v>-0.04549681970287811</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>-0.1798158863351699</v>
+        <v>-0.1798157287734712</v>
       </c>
       <c r="P89" s="5" t="n">
-        <v>-0.06393979066025124</v>
+        <v>-0.06393973071955217</v>
       </c>
     </row>
     <row r="90">
@@ -5544,7 +5544,7 @@
         <v>0.2317878109481263</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>0.03826783802271116</v>
+        <v>0.03826781473847988</v>
       </c>
       <c r="N90" s="5" t="n">
         <v>0.06069392837182493</v>
@@ -5597,19 +5597,19 @@
         <v>0.05251976017568865</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0.09731855092697801</v>
+        <v>0.09731854271512347</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>0.0252993635716742</v>
+        <v>0.02529936176742029</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>-0.05235045072262322</v>
+        <v>-0.0523504530890068</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>0.5744672959942558</v>
+        <v>0.5744672737533507</v>
       </c>
       <c r="P91" s="5" t="n">
-        <v>0.1483487912266572</v>
+        <v>0.1483487907997014</v>
       </c>
     </row>
     <row r="92">
@@ -5656,16 +5656,16 @@
         <v>-0.0272492899883716</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>0.04071980716100219</v>
+        <v>0.04071983047498494</v>
       </c>
       <c r="N92" s="5" t="n">
         <v>-0.02300631762255526</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>-0.1220216306592279</v>
+        <v>-0.1220216298322494</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>-0.04621303783153169</v>
+        <v>-0.04621303917795579</v>
       </c>
     </row>
     <row r="93">
@@ -5715,13 +5715,13 @@
         <v>0.03926921800685616</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>0.2438682078081124</v>
+        <v>0.2438682425776661</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>0.855998146563639</v>
+        <v>0.855998344620633</v>
       </c>
       <c r="P93" s="5" t="n">
-        <v>0.2163438560025351</v>
+        <v>0.216343898562661</v>
       </c>
     </row>
     <row r="94">
@@ -5821,19 +5821,19 @@
         <v>0.05702427335096175</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.03533717440495695</v>
+        <v>-0.03533718700844466</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>0.06530552145166706</v>
+        <v>0.06530553971804702</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>-0.002980049939430074</v>
+        <v>-0.002980058579072279</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>0.1665371794779401</v>
+        <v>0.166537221950389</v>
       </c>
       <c r="P95" s="5" t="n">
-        <v>0.04917182050724443</v>
+        <v>0.04917183381586904</v>
       </c>
     </row>
     <row r="96">
@@ -5933,19 +5933,19 @@
         <v>-0.02657124632104835</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>0.04188748736566106</v>
+        <v>0.04188746025823903</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>-0.05509041615341861</v>
+        <v>-0.05509039104664884</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>0.2034108804646525</v>
+        <v>0.2034109110873447</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>1.453192949251129</v>
+        <v>1.453192842772679</v>
       </c>
       <c r="P97" s="5" t="n">
-        <v>0.3461353069059347</v>
+        <v>0.3461352885788651</v>
       </c>
     </row>
     <row r="98">
@@ -6045,19 +6045,19 @@
         <v>0.1241736877818252</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.03917327541189437</v>
+        <v>-0.03917326914120819</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>-0.05509746757946826</v>
+        <v>-0.05509745991543288</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>-0.05767294205246248</v>
+        <v>-0.05767294128867025</v>
       </c>
       <c r="O99" s="5" t="n">
-        <v>0.06811876617320312</v>
+        <v>0.06811874177669755</v>
       </c>
       <c r="P99" s="5" t="n">
-        <v>0.01805582847807258</v>
+        <v>0.01805582200056771</v>
       </c>
     </row>
     <row r="100">
@@ -6104,16 +6104,16 @@
         <v>0.05512836472126836</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>-0.1767299994120648</v>
+        <v>-0.1767299434549007</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>-0.2651760072616289</v>
+        <v>-0.2651759626818645</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>0.06016277981171814</v>
+        <v>0.06016305819141721</v>
       </c>
       <c r="P100" s="5" t="n">
-        <v>0.01966501232413043</v>
+        <v>0.01966510157269363</v>
       </c>
     </row>
     <row r="101">
@@ -6163,13 +6163,13 @@
         <v>0.01148192321179389</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>-0.09823580779687471</v>
+        <v>-0.09823581605349188</v>
       </c>
       <c r="O101" s="5" t="n">
-        <v>0.6271117645956348</v>
+        <v>0.6271117905824125</v>
       </c>
       <c r="P101" s="5" t="n">
-        <v>0.160981087828263</v>
+        <v>0.1609810948286231</v>
       </c>
     </row>
     <row r="102">
@@ -6213,19 +6213,19 @@
         <v>-0.0410442120530449</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>-0.04939222504642402</v>
+        <v>-0.04939221672768287</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>0.0350987820875058</v>
+        <v>0.03509879086332202</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>0.08844957030881044</v>
+        <v>0.08844960331836323</v>
       </c>
       <c r="O102" s="5" t="n">
-        <v>0.4121522914828625</v>
+        <v>0.4121523385390282</v>
       </c>
       <c r="P102" s="5" t="n">
-        <v>0.1206499327819525</v>
+        <v>0.1206499467330266</v>
       </c>
     </row>
     <row r="103">
@@ -6275,13 +6275,13 @@
         <v>-0.1945258301025207</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>-0.1367312163167648</v>
+        <v>-0.1367312327212805</v>
       </c>
       <c r="O103" s="5" t="n">
-        <v>-0.02286949549024181</v>
+        <v>-0.02286952279817075</v>
       </c>
       <c r="P103" s="5" t="n">
-        <v>-0.03137602176055954</v>
+        <v>-0.03137603117865936</v>
       </c>
     </row>
     <row r="104">
@@ -6328,16 +6328,16 @@
         <v>0.1250878525597503</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>-0.1233290330649388</v>
+        <v>-0.1233290289219497</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>-0.1528267579845216</v>
+        <v>-0.1528267616954102</v>
       </c>
       <c r="O104" s="5" t="n">
-        <v>0.8993955405505317</v>
+        <v>0.8993955375183325</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.1163182371701537</v>
+        <v>0.1163182358943552</v>
       </c>
     </row>
     <row r="105">
@@ -6381,19 +6381,19 @@
         <v>-0.03425844859203211</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>-0.06074868147498536</v>
+        <v>-0.06074867762316829</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>0.01874804653262325</v>
+        <v>0.01874803128012431</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>0.06174548438319918</v>
+        <v>0.06174549914502424</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>0.8083471441494494</v>
+        <v>0.8083471788491533</v>
       </c>
       <c r="P105" s="5" t="n">
-        <v>0.1960664978966488</v>
+        <v>0.19606650448459</v>
       </c>
     </row>
     <row r="106">
@@ -6446,10 +6446,10 @@
         <v>-0.05400066635832593</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>0.01606318053732399</v>
+        <v>0.01606322950268054</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>0.005088224528448222</v>
+        <v>0.00508824137065896</v>
       </c>
     </row>
     <row r="107">
@@ -6499,13 +6499,13 @@
         <v>0.03688680396464872</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>0.05138802183134347</v>
+        <v>0.05138804853700285</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>0.1078817343870956</v>
+        <v>0.107881762277615</v>
       </c>
       <c r="P107" s="5" t="n">
-        <v>0.02586962767819995</v>
+        <v>0.02586962772293633</v>
       </c>
     </row>
     <row r="108">
@@ -6549,19 +6549,19 @@
         <v>-0.002429362093111564</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>-0.04800245332588066</v>
+        <v>-0.04800244453218971</v>
       </c>
       <c r="M108" s="5" t="n">
         <v>0.02349596867843906</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>-0.1061347743960682</v>
+        <v>-0.106134763494653</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>-0.4994282264032168</v>
+        <v>-0.4994282169964016</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>-0.2070724909848137</v>
+        <v>-0.207072484241113</v>
       </c>
     </row>
     <row r="109">
@@ -6605,19 +6605,19 @@
         <v>0.1371763483166538</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>-0.02892324286964687</v>
+        <v>-0.02892320497079104</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>-0.1250532555753184</v>
+        <v>-0.1250532262356954</v>
       </c>
       <c r="N109" s="5" t="n">
         <v>-0.2572489232353794</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>-0.09807362412433746</v>
+        <v>-0.09807357243760884</v>
       </c>
       <c r="P109" s="5" t="n">
-        <v>-0.03490915114932314</v>
+        <v>-0.03490913511748422</v>
       </c>
     </row>
     <row r="110">
@@ -6661,19 +6661,19 @@
         <v>0.01896637256498071</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>-0.09669765702797378</v>
+        <v>-0.09669764515112171</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>-0.006806144916893155</v>
+        <v>-0.006806138303930164</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>-0.07155971876842722</v>
+        <v>-0.07155973997638841</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>0.4442138876781276</v>
+        <v>0.4442138240854539</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>0.1077170416435207</v>
+        <v>0.1077170261873681</v>
       </c>
     </row>
     <row r="111">
@@ -6717,19 +6717,19 @@
         <v>-0.04660195388563193</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>-0.06885806265503536</v>
+        <v>-0.06885798369969054</v>
       </c>
       <c r="M111" s="5" t="n">
         <v>-0.01658201817188087</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>0.03623125222934975</v>
+        <v>0.03623135001230038</v>
       </c>
       <c r="O111" s="5" t="n">
-        <v>0.5311061543883204</v>
+        <v>0.5311062611290982</v>
       </c>
       <c r="P111" s="5" t="n">
-        <v>0.1525729798556268</v>
+        <v>0.1525730066394291</v>
       </c>
     </row>
     <row r="112">
@@ -6779,7 +6779,7 @@
         <v>-0.104988357631029</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>-0.1954720661303073</v>
+        <v>-0.1954720898023594</v>
       </c>
       <c r="O112" s="5" t="n">
         <v>0.3031610281371109</v>
@@ -6832,16 +6832,16 @@
         <v>-0.2202587356462219</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>-0.2206483270095429</v>
+        <v>-0.2206482773459073</v>
       </c>
       <c r="N113" s="5" t="n">
         <v>0.01584235982637228</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>0.4816714063494746</v>
+        <v>0.4816715781140507</v>
       </c>
       <c r="P113" s="5" t="n">
-        <v>0.1391391758573666</v>
+        <v>0.1391392199135874</v>
       </c>
     </row>
     <row r="114">
@@ -6941,19 +6941,19 @@
         <v>0.05924040866546232</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>-0.09402479651578705</v>
+        <v>-0.09402480616240477</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>-0.1063093239087353</v>
+        <v>-0.1063093038218489</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>-0.161099215313759</v>
+        <v>-0.1610992551069052</v>
       </c>
       <c r="O115" s="5" t="n">
-        <v>0.2451673790340111</v>
+        <v>0.2451674022083817</v>
       </c>
       <c r="P115" s="5" t="n">
-        <v>0.06701590152885523</v>
+        <v>0.06701590784172684</v>
       </c>
     </row>
     <row r="116">
@@ -6997,19 +6997,19 @@
         <v>0.04575530748513401</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>-0.1313278146998479</v>
+        <v>-0.1313278522990941</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>-0.0511191586961246</v>
+        <v>-0.0511191151074914</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>-0.1528489317359277</v>
+        <v>-0.1528489642327064</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>0.07533524654137269</v>
+        <v>0.0753351889599243</v>
       </c>
       <c r="P116" s="5" t="n">
-        <v>0.02422062632430577</v>
+        <v>0.0242206086237734</v>
       </c>
     </row>
     <row r="117">
@@ -7053,19 +7053,19 @@
         <v>-0.0008698762875879451</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>-0.09596497495748535</v>
+        <v>-0.09596504917012716</v>
       </c>
       <c r="M117" s="5" t="n">
         <v>-0.0644901101238583</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>-0.1511167778683411</v>
+        <v>-0.1511167124343595</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>-0.2591741423621774</v>
+        <v>-0.2591742420333611</v>
       </c>
       <c r="P117" s="5" t="n">
-        <v>-0.09515947270830794</v>
+        <v>-0.09515951328758376</v>
       </c>
     </row>
     <row r="118">
@@ -7109,19 +7109,19 @@
         <v>-0.02311845278043959</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>-0.08634502704717112</v>
+        <v>-0.08634501048872759</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>-0.0946543963188857</v>
+        <v>-0.09465438685546784</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>-0.1130442714425244</v>
+        <v>-0.1130442594742077</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>0.3322511427884814</v>
+        <v>0.3322511598436149</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>0.09504167496742992</v>
+        <v>0.0950416766448338</v>
       </c>
     </row>
     <row r="119">
@@ -7165,7 +7165,7 @@
         <v>0.07922116659714806</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>-0.2051288223378934</v>
+        <v>-0.2051288510025233</v>
       </c>
       <c r="M119" s="5" t="n">
         <v>-0.05143528597077635</v>
@@ -7174,10 +7174,10 @@
         <v>-0.2706183788187086</v>
       </c>
       <c r="O119" s="5" t="n">
-        <v>-0.4589510448815113</v>
+        <v>-0.4589510803473322</v>
       </c>
       <c r="P119" s="5" t="n">
-        <v>-0.1942986450392403</v>
+        <v>-0.1942986598953702</v>
       </c>
     </row>
     <row r="120">
@@ -7221,19 +7221,19 @@
         <v>0.002797761151220768</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>-0.1654355471326854</v>
+        <v>-0.1654355773458233</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>-0.1192144885388072</v>
+        <v>-0.1192145170978509</v>
       </c>
       <c r="N120" s="5" t="n">
         <v>-0.1001464324089965</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>0.438877163830854</v>
+        <v>0.4388772223810295</v>
       </c>
       <c r="P120" s="5" t="n">
-        <v>0.1256468322230134</v>
+        <v>0.125646849159268</v>
       </c>
     </row>
     <row r="121">
@@ -7283,13 +7283,13 @@
         <v>-0.03430144526028204</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>-0.1588574489834924</v>
+        <v>-0.1588574690848341</v>
       </c>
       <c r="O121" s="5" t="n">
-        <v>-0.02789357462019989</v>
+        <v>-0.02789356091602506</v>
       </c>
       <c r="P121" s="5" t="n">
-        <v>-0.01057155137499421</v>
+        <v>-0.01057154819457314</v>
       </c>
     </row>
     <row r="122">
@@ -7398,10 +7398,10 @@
         <v>-0.02963197186517585</v>
       </c>
       <c r="O123" s="5" t="n">
-        <v>1.087985579335044</v>
+        <v>1.087985404053214</v>
       </c>
       <c r="P123" s="5" t="n">
-        <v>0.2298150490501721</v>
+        <v>0.2298150223175731</v>
       </c>
     </row>
     <row r="124">
@@ -7445,19 +7445,19 @@
         <v>-0.06836345351685272</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>-0.2297270377247633</v>
+        <v>-0.2297270384473181</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>-0.1194685480259435</v>
+        <v>-0.1194685262322229</v>
       </c>
       <c r="N124" s="5" t="n">
-        <v>-0.072343635753294</v>
+        <v>-0.07234372249295939</v>
       </c>
       <c r="O124" s="5" t="n">
-        <v>1.096249206528853</v>
+        <v>1.096249201201084</v>
       </c>
       <c r="P124" s="5" t="n">
-        <v>0.1400430520307049</v>
+        <v>0.1400430525878615</v>
       </c>
     </row>
     <row r="125">
@@ -7619,7 +7619,7 @@
         <v>-0.2848189783016568</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>-0.2996140759389979</v>
+        <v>-0.2996140372003843</v>
       </c>
       <c r="O127" s="5" t="n">
         <v>2.07047402212948</v>
@@ -7939,13 +7939,13 @@
         <v>3.159277647751241</v>
       </c>
       <c r="N4" t="n">
-        <v>7.026691786103124</v>
+        <v>7.026692312963588</v>
       </c>
       <c r="O4" t="n">
-        <v>13.80534112838111</v>
+        <v>13.80534202463133</v>
       </c>
       <c r="P4" t="n">
-        <v>1.455497367072949</v>
+        <v>1.455497416621284</v>
       </c>
     </row>
     <row r="5">
@@ -8000,10 +8000,10 @@
         <v>4.705270291684745</v>
       </c>
       <c r="O5" t="n">
-        <v>14.17023306045598</v>
+        <v>14.17023403427641</v>
       </c>
       <c r="P5" t="n">
-        <v>1.47550657578776</v>
+        <v>1.475506628757696</v>
       </c>
     </row>
     <row r="6">
@@ -8055,13 +8055,13 @@
         <v>1.885445998296779</v>
       </c>
       <c r="N6" t="n">
-        <v>2.302154522205557</v>
+        <v>2.302154176117611</v>
       </c>
       <c r="O6" t="n">
-        <v>3.534941709602184</v>
+        <v>3.534941383236021</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6552257593533106</v>
+        <v>0.6552257196460973</v>
       </c>
     </row>
     <row r="7">
@@ -8113,7 +8113,7 @@
         <v>2.618408629248262</v>
       </c>
       <c r="N7" t="n">
-        <v>2.490218142880296</v>
+        <v>2.490217731193055</v>
       </c>
       <c r="O7" t="n">
         <v>7.428266212632144</v>
@@ -8171,7 +8171,7 @@
         <v>2.15342796805355</v>
       </c>
       <c r="N8" t="n">
-        <v>4.051550635428815</v>
+        <v>4.051551109312885</v>
       </c>
       <c r="O8" t="n">
         <v>12.67403817732864</v>
@@ -8348,10 +8348,10 @@
         <v>1.363043658099382</v>
       </c>
       <c r="O11" t="n">
-        <v>1.776952811888919</v>
+        <v>1.776952293392295</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4055819344219573</v>
+        <v>0.4055818469412327</v>
       </c>
     </row>
     <row r="12">
@@ -8406,10 +8406,10 @@
         <v>2.56334036967603</v>
       </c>
       <c r="O12" t="n">
-        <v>1.674981001189212</v>
+        <v>1.674980689161878</v>
       </c>
       <c r="P12" t="n">
-        <v>0.388162262848226</v>
+        <v>0.3881622088734393</v>
       </c>
     </row>
     <row r="13">
@@ -8522,10 +8522,10 @@
         <v>1.418135548399391</v>
       </c>
       <c r="O14" t="n">
-        <v>2.474548557764628</v>
+        <v>2.474548988648728</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5146052637743268</v>
+        <v>0.5146053263838322</v>
       </c>
     </row>
     <row r="15">
@@ -8571,19 +8571,19 @@
         <v>0.3974149517540857</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8246401329075577</v>
+        <v>0.8246402760581069</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8894735046234687</v>
+        <v>0.8894736581276421</v>
       </c>
       <c r="N15" t="n">
         <v>1.095525492926681</v>
       </c>
       <c r="O15" t="n">
-        <v>1.615014504486271</v>
+        <v>1.615014210459623</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3777107084191904</v>
+        <v>0.3777106567835715</v>
       </c>
     </row>
     <row r="16">
@@ -8693,13 +8693,13 @@
         <v>1.078443732151377</v>
       </c>
       <c r="N17" t="n">
-        <v>2.124027394226258</v>
+        <v>2.124027630860849</v>
       </c>
       <c r="O17" t="n">
-        <v>3.895461891221892</v>
+        <v>3.895463053382036</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6979747382855035</v>
+        <v>0.6979748726492914</v>
       </c>
     </row>
     <row r="18">
@@ -8812,10 +8812,10 @@
         <v>2.138020274911799</v>
       </c>
       <c r="O19" t="n">
-        <v>2.571516839264865</v>
+        <v>2.571517104850448</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5285661362912937</v>
+        <v>0.5285661741804351</v>
       </c>
     </row>
     <row r="20">
@@ -8867,7 +8867,7 @@
         <v>0.940080655223638</v>
       </c>
       <c r="N20" t="n">
-        <v>0.751153052974032</v>
+        <v>0.7511529098540795</v>
       </c>
       <c r="O20" t="n">
         <v>0.4981212601750507</v>
@@ -8980,10 +8980,10 @@
         <v>0.8547527975130265</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7033032130240431</v>
+        <v>0.7033033311199777</v>
       </c>
       <c r="N22" t="n">
-        <v>0.717954914811427</v>
+        <v>0.7179550349478068</v>
       </c>
       <c r="O22" t="n">
         <v>1.659564052248948</v>
@@ -9096,16 +9096,16 @@
         <v>0.5791349048250876</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8031648081381377</v>
+        <v>0.8031650175618801</v>
       </c>
       <c r="N24" t="n">
         <v>0.8832237104454077</v>
       </c>
       <c r="O24" t="n">
-        <v>1.29635701017754</v>
+        <v>1.296356670525857</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3193088304934164</v>
+        <v>0.3193087654475655</v>
       </c>
     </row>
     <row r="25">
@@ -9160,10 +9160,10 @@
         <v>0.330192645388196</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1562255275995157</v>
+        <v>-0.1562254718474045</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.05505007687679575</v>
+        <v>-0.05505005606438129</v>
       </c>
     </row>
     <row r="26">
@@ -9218,10 +9218,10 @@
         <v>0.5965832895788876</v>
       </c>
       <c r="O26" t="n">
-        <v>2.199570852029468</v>
+        <v>2.199571083127057</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4735467217344316</v>
+        <v>0.4735467572113858</v>
       </c>
     </row>
     <row r="27">
@@ -9392,10 +9392,10 @@
         <v>0.8486851151037247</v>
       </c>
       <c r="O29" t="n">
-        <v>1.167472935984003</v>
+        <v>1.167473160251502</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2941498344971634</v>
+        <v>0.2941498791322055</v>
       </c>
     </row>
     <row r="30">
@@ -9499,7 +9499,7 @@
         <v>0.2595675035380967</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4831030576726352</v>
+        <v>0.4831032316200605</v>
       </c>
       <c r="M31" t="n">
         <v>0.6925262757972082</v>
@@ -9563,7 +9563,7 @@
         <v>0.7574078768270673</v>
       </c>
       <c r="N32" t="n">
-        <v>0.9137820718799943</v>
+        <v>0.9137819029372634</v>
       </c>
       <c r="O32" t="n">
         <v>0.08481426716405593</v>
@@ -9618,10 +9618,10 @@
         <v>0.2962778074005148</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5152275603317475</v>
+        <v>0.5152274483698618</v>
       </c>
       <c r="N33" t="n">
-        <v>0.8952105352125537</v>
+        <v>0.8952107103703524</v>
       </c>
       <c r="O33" t="n">
         <v>0.5569618801914165</v>
@@ -9798,10 +9798,10 @@
         <v>0.5717326605107964</v>
       </c>
       <c r="O36" t="n">
-        <v>3.308619290789687</v>
+        <v>3.308619651400787</v>
       </c>
       <c r="P36" t="n">
-        <v>0.6272191271385765</v>
+        <v>0.6272191725354288</v>
       </c>
     </row>
     <row r="37">
@@ -9908,16 +9908,16 @@
         <v>0.08714200806174643</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5778851096088218</v>
+        <v>0.5778852501672704</v>
       </c>
       <c r="N38" t="n">
         <v>0.9209122567446928</v>
       </c>
       <c r="O38" t="n">
-        <v>2.768441232451782</v>
+        <v>2.768440831585422</v>
       </c>
       <c r="P38" t="n">
-        <v>0.5561588095723902</v>
+        <v>0.5561587543938071</v>
       </c>
     </row>
     <row r="39">
@@ -10082,16 +10082,16 @@
         <v>0.2588009595922336</v>
       </c>
       <c r="M41" t="n">
-        <v>0.702006207370492</v>
+        <v>0.7020063614329055</v>
       </c>
       <c r="N41" t="n">
-        <v>0.8183363174861362</v>
+        <v>0.81833649332823</v>
       </c>
       <c r="O41" t="n">
-        <v>2.623755251216178</v>
+        <v>2.623755949596795</v>
       </c>
       <c r="P41" t="n">
-        <v>0.5359825645468499</v>
+        <v>0.5359826632198477</v>
       </c>
     </row>
     <row r="42">
@@ -10198,16 +10198,16 @@
         <v>0.4189899526707046</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5990616817264001</v>
+        <v>0.5990615241150374</v>
       </c>
       <c r="N43" t="n">
-        <v>0.6774811638715259</v>
+        <v>0.6774809904222894</v>
       </c>
       <c r="O43" t="n">
-        <v>0.56240454931289</v>
+        <v>0.5624048502489303</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1603735789703757</v>
+        <v>0.1603736534705444</v>
       </c>
     </row>
     <row r="44">
@@ -10320,10 +10320,10 @@
         <v>0.6146371955176024</v>
       </c>
       <c r="O45" t="n">
-        <v>3.025727577494329</v>
+        <v>3.025726821945104</v>
       </c>
       <c r="P45" t="n">
-        <v>0.5907971132707857</v>
+        <v>0.5907970137504233</v>
       </c>
     </row>
     <row r="46">
@@ -10427,7 +10427,7 @@
         <v>-0.1452105352885564</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0783078332103524</v>
+        <v>0.07830792408143794</v>
       </c>
       <c r="M47" t="n">
         <v>0.6344075912803331</v>
@@ -10436,10 +10436,10 @@
         <v>1.264473061195271</v>
       </c>
       <c r="O47" t="n">
-        <v>7.676978662171161</v>
+        <v>7.676979397678936</v>
       </c>
       <c r="P47" t="n">
-        <v>1.054894405742462</v>
+        <v>1.054894463803792</v>
       </c>
     </row>
     <row r="48">
@@ -10494,10 +10494,10 @@
         <v>0.4549078421984405</v>
       </c>
       <c r="O48" t="n">
-        <v>0.5960151865482826</v>
+        <v>0.5960150478522745</v>
       </c>
       <c r="P48" t="n">
-        <v>0.1686353159952467</v>
+        <v>0.1686352821432175</v>
       </c>
     </row>
     <row r="49">
@@ -10552,10 +10552,10 @@
         <v>0.5755810445183418</v>
       </c>
       <c r="O49" t="n">
-        <v>0.8871718578374082</v>
+        <v>0.8871719807184795</v>
       </c>
       <c r="P49" t="n">
-        <v>0.2357685846911755</v>
+        <v>0.2357686115130684</v>
       </c>
     </row>
     <row r="50">
@@ -10665,13 +10665,13 @@
         <v>0.6622501364013462</v>
       </c>
       <c r="N51" t="n">
-        <v>0.5074126114526041</v>
+        <v>0.5074127476793791</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8525824965725461</v>
+        <v>0.8525822908162126</v>
       </c>
       <c r="P51" t="n">
-        <v>0.2281719814011227</v>
+        <v>0.2281719359323113</v>
       </c>
     </row>
     <row r="52">
@@ -10726,10 +10726,10 @@
         <v>0.5615073379822848</v>
       </c>
       <c r="O52" t="n">
-        <v>1.455907292660154</v>
+        <v>1.455907468456864</v>
       </c>
       <c r="P52" t="n">
-        <v>0.3491823659220021</v>
+        <v>0.3491823981140174</v>
       </c>
     </row>
     <row r="53">
@@ -10839,13 +10839,13 @@
         <v>0.103139473673187</v>
       </c>
       <c r="N54" t="n">
-        <v>0.2826614374019782</v>
+        <v>0.2826613506327673</v>
       </c>
       <c r="O54" t="n">
-        <v>-0.08345740246039712</v>
+        <v>-0.08345731385157817</v>
       </c>
       <c r="P54" t="n">
-        <v>-0.02863104773939995</v>
+        <v>-0.02863101643630761</v>
       </c>
     </row>
     <row r="55">
@@ -10897,13 +10897,13 @@
         <v>0.5325104278360566</v>
       </c>
       <c r="N55" t="n">
-        <v>0.8516694709319663</v>
+        <v>0.8516696704800224</v>
       </c>
       <c r="O55" t="n">
-        <v>0.4380916136400785</v>
+        <v>0.4380913729137721</v>
       </c>
       <c r="P55" t="n">
-        <v>0.1287441640354059</v>
+        <v>0.1287441010541543</v>
       </c>
     </row>
     <row r="56">
@@ -10952,16 +10952,16 @@
         <v>0.1801173391720967</v>
       </c>
       <c r="M56" t="n">
-        <v>0.4392504947464038</v>
+        <v>0.4392503342360794</v>
       </c>
       <c r="N56" t="n">
         <v>0.3462582803598591</v>
       </c>
       <c r="O56" t="n">
-        <v>0.2447688568701136</v>
+        <v>0.2447690969953216</v>
       </c>
       <c r="P56" t="n">
-        <v>0.0757125564254828</v>
+        <v>0.07571262559647352</v>
       </c>
     </row>
     <row r="57">
@@ -11013,7 +11013,7 @@
         <v>0.5317975913605846</v>
       </c>
       <c r="N57" t="n">
-        <v>0.8120246753313467</v>
+        <v>0.8120245251973526</v>
       </c>
       <c r="O57" t="n">
         <v>0.7015723153245095</v>
@@ -11071,13 +11071,13 @@
         <v>0.1159874636315039</v>
       </c>
       <c r="N58" t="n">
-        <v>0.2116188540381096</v>
+        <v>0.2116187227202022</v>
       </c>
       <c r="O58" t="n">
-        <v>0.3614006223594555</v>
+        <v>0.3614002078793204</v>
       </c>
       <c r="P58" t="n">
-        <v>0.1083118624864872</v>
+        <v>0.1083117500108282</v>
       </c>
     </row>
     <row r="59">
@@ -11129,7 +11129,7 @@
         <v>0.4908215306145318</v>
       </c>
       <c r="N59" t="n">
-        <v>0.5921241068129237</v>
+        <v>0.5921242945380607</v>
       </c>
       <c r="O59" t="n">
         <v>0.7394416772072447</v>
@@ -11248,10 +11248,10 @@
         <v>1.227742962276834</v>
       </c>
       <c r="O61" t="n">
-        <v>3.864093324956918</v>
+        <v>3.864093018306145</v>
       </c>
       <c r="P61" t="n">
-        <v>0.6943402699279797</v>
+        <v>0.6943402343221137</v>
       </c>
     </row>
     <row r="62">
@@ -11306,10 +11306,10 @@
         <v>0.4628325561428475</v>
       </c>
       <c r="O62" t="n">
-        <v>1.738063859939927</v>
+        <v>1.738064472267657</v>
       </c>
       <c r="P62" t="n">
-        <v>0.3989897235042454</v>
+        <v>0.398989827792066</v>
       </c>
     </row>
     <row r="63">
@@ -11358,16 +11358,16 @@
         <v>0.1324077740093426</v>
       </c>
       <c r="M63" t="n">
-        <v>0.4458888527545337</v>
+        <v>0.4458889601834546</v>
       </c>
       <c r="N63" t="n">
         <v>0.5432593773562939</v>
       </c>
       <c r="O63" t="n">
-        <v>1.69791903938729</v>
+        <v>1.69791941341971</v>
       </c>
       <c r="P63" t="n">
-        <v>0.3921188187476059</v>
+        <v>0.3921188830808371</v>
       </c>
     </row>
     <row r="64">
@@ -11535,13 +11535,13 @@
         <v>0.2633977087063688</v>
       </c>
       <c r="N66" t="n">
-        <v>0.1285339461466213</v>
+        <v>0.1285337815681935</v>
       </c>
       <c r="O66" t="n">
-        <v>0.08228826928778821</v>
+        <v>0.08228834497101767</v>
       </c>
       <c r="P66" t="n">
-        <v>0.0267096652636678</v>
+        <v>0.02670968919589356</v>
       </c>
     </row>
     <row r="67">
@@ -11587,7 +11587,7 @@
         <v>0.160026129488581</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2028755531798325</v>
+        <v>0.2028756963511462</v>
       </c>
       <c r="M67" t="n">
         <v>0.1168352744324703</v>
@@ -11645,19 +11645,19 @@
         <v>0.2884815786742529</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2812956293900823</v>
+        <v>0.2812957297210612</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1849194617492822</v>
+        <v>0.1849195475545642</v>
       </c>
       <c r="N68" t="n">
-        <v>0.3586410059456115</v>
+        <v>0.358640780326603</v>
       </c>
       <c r="O68" t="n">
-        <v>0.09496508972468387</v>
+        <v>0.09496494318109949</v>
       </c>
       <c r="P68" t="n">
-        <v>0.03070272519104456</v>
+        <v>0.03070267921001135</v>
       </c>
     </row>
     <row r="69">
@@ -11712,10 +11712,10 @@
         <v>0.5769603245310591</v>
       </c>
       <c r="O69" t="n">
-        <v>0.789156716220248</v>
+        <v>0.7891561797413653</v>
       </c>
       <c r="P69" t="n">
-        <v>0.2139928465979197</v>
+        <v>0.2139927252592679</v>
       </c>
     </row>
     <row r="70">
@@ -11761,19 +11761,19 @@
         <v>-0.07378412228427422</v>
       </c>
       <c r="L70" t="n">
-        <v>0.4172139892978688</v>
+        <v>0.4172141272117011</v>
       </c>
       <c r="M70" t="n">
-        <v>0.4770702032321601</v>
+        <v>0.4770700534227292</v>
       </c>
       <c r="N70" t="n">
-        <v>0.6891673867531156</v>
+        <v>0.6891671908315473</v>
       </c>
       <c r="O70" t="n">
-        <v>1.159128621985294</v>
+        <v>1.15912830187924</v>
       </c>
       <c r="P70" t="n">
-        <v>0.2924869640628924</v>
+        <v>0.2924869001894514</v>
       </c>
     </row>
     <row r="71">
@@ -11883,13 +11883,13 @@
         <v>0.2877634319770095</v>
       </c>
       <c r="N72" t="n">
-        <v>0.3925959072427001</v>
+        <v>0.392596028267318</v>
       </c>
       <c r="O72" t="n">
-        <v>0.9587116161380644</v>
+        <v>0.9587117358491812</v>
       </c>
       <c r="P72" t="n">
-        <v>0.2511906769134629</v>
+        <v>0.2511907024032507</v>
       </c>
     </row>
     <row r="73">
@@ -12060,10 +12060,10 @@
         <v>0.509971638027517</v>
       </c>
       <c r="O75" t="n">
-        <v>0.2599533249977195</v>
+        <v>0.2599530575169964</v>
       </c>
       <c r="P75" t="n">
-        <v>0.08006896135946029</v>
+        <v>0.08006888492868014</v>
       </c>
     </row>
     <row r="76">
@@ -12118,10 +12118,10 @@
         <v>0.4967910205265413</v>
       </c>
       <c r="O76" t="n">
-        <v>0.4478504569655279</v>
+        <v>0.4478503610768196</v>
       </c>
       <c r="P76" t="n">
-        <v>0.1312916175517407</v>
+        <v>0.1312915925772242</v>
       </c>
     </row>
     <row r="77">
@@ -12173,13 +12173,13 @@
         <v>0.05368963016262973</v>
       </c>
       <c r="N77" t="n">
-        <v>0.2846459210291037</v>
+        <v>0.2846460012068042</v>
       </c>
       <c r="O77" t="n">
-        <v>0.1710110753035761</v>
+        <v>0.1710113417861285</v>
       </c>
       <c r="P77" t="n">
-        <v>0.05403168800295921</v>
+        <v>0.05403176795695219</v>
       </c>
     </row>
     <row r="78">
@@ -12234,10 +12234,10 @@
         <v>0.3851746785359442</v>
       </c>
       <c r="O78" t="n">
-        <v>0.2423388407940745</v>
+        <v>0.2423389301087961</v>
       </c>
       <c r="P78" t="n">
-        <v>0.07501210465376951</v>
+        <v>0.07501213041550248</v>
       </c>
     </row>
     <row r="79">
@@ -12405,13 +12405,13 @@
         <v>0.4623696087418299</v>
       </c>
       <c r="N81" t="n">
-        <v>0.6668859706866848</v>
+        <v>0.6668860734764916</v>
       </c>
       <c r="O81" t="n">
-        <v>2.422493209388612</v>
+        <v>2.422492776054002</v>
       </c>
       <c r="P81" t="n">
-        <v>0.5070032828206832</v>
+        <v>0.5070032192182481</v>
       </c>
     </row>
     <row r="82">
@@ -12515,10 +12515,10 @@
         <v>0.01173570693545045</v>
       </c>
       <c r="L83" t="n">
-        <v>0.06431256940615326</v>
+        <v>0.06431263401652498</v>
       </c>
       <c r="M83" t="n">
-        <v>0.6206576330372451</v>
+        <v>0.6206577828491857</v>
       </c>
       <c r="N83" t="n">
         <v>0.6410201546016676</v>
@@ -12637,13 +12637,13 @@
         <v>0.5139438593681176</v>
       </c>
       <c r="N85" t="n">
-        <v>0.2597938131963313</v>
+        <v>0.2597938971517011</v>
       </c>
       <c r="O85" t="n">
-        <v>1.946497695888449</v>
+        <v>1.946497466256829</v>
       </c>
       <c r="P85" t="n">
-        <v>0.4336243492325234</v>
+        <v>0.4336243119899477</v>
       </c>
     </row>
     <row r="86">
@@ -12698,10 +12698,10 @@
         <v>0.7545314212135741</v>
       </c>
       <c r="O86" t="n">
-        <v>1.367876219221267</v>
+        <v>1.367876589454813</v>
       </c>
       <c r="P86" t="n">
-        <v>0.3328655158721905</v>
+        <v>0.3328655853397156</v>
       </c>
     </row>
     <row r="87">
@@ -12750,10 +12750,10 @@
         <v>0.1838211208780258</v>
       </c>
       <c r="M87" t="n">
-        <v>0.373258121187197</v>
+        <v>0.3732582141346583</v>
       </c>
       <c r="N87" t="n">
-        <v>0.4177849845795638</v>
+        <v>0.4177847864342388</v>
       </c>
       <c r="O87" t="n">
         <v>0.4771270627811162</v>
@@ -12811,13 +12811,13 @@
         <v>0.2735134122420477</v>
       </c>
       <c r="N88" t="n">
-        <v>0.3789419400668352</v>
+        <v>0.378942097045132</v>
       </c>
       <c r="O88" t="n">
-        <v>1.413176003987621</v>
+        <v>1.413176244366135</v>
       </c>
       <c r="P88" t="n">
-        <v>0.3413115553979569</v>
+        <v>0.3413115999343503</v>
       </c>
     </row>
     <row r="89">
@@ -12927,13 +12927,13 @@
         <v>0.261408348522729</v>
       </c>
       <c r="N90" t="n">
-        <v>0.2359042818761632</v>
+        <v>0.2359044199191849</v>
       </c>
       <c r="O90" t="n">
-        <v>0.6444507523685676</v>
+        <v>0.644450507976889</v>
       </c>
       <c r="P90" t="n">
-        <v>0.1803395442405895</v>
+        <v>0.1803394857681426</v>
       </c>
     </row>
     <row r="91">
@@ -13043,13 +13043,13 @@
         <v>0.3752302218455943</v>
       </c>
       <c r="N92" t="n">
-        <v>0.6505826358630018</v>
+        <v>0.6505829805821421</v>
       </c>
       <c r="O92" t="n">
-        <v>1.0890776611454</v>
+        <v>1.089077523094287</v>
       </c>
       <c r="P92" t="n">
-        <v>0.2783551587861055</v>
+        <v>0.2783551306272103</v>
       </c>
     </row>
     <row r="93">
@@ -13104,10 +13104,10 @@
         <v>0.4140493611140521</v>
       </c>
       <c r="O93" t="n">
-        <v>-0.1073285098763814</v>
+        <v>-0.1073283703084679</v>
       </c>
       <c r="P93" t="n">
-        <v>-0.03713835275691568</v>
+        <v>-0.03713830257623674</v>
       </c>
     </row>
     <row r="94">
@@ -13156,16 +13156,16 @@
         <v>0.2613516408260852</v>
       </c>
       <c r="M94" t="n">
-        <v>0.3319386309708869</v>
+        <v>0.3319387558498701</v>
       </c>
       <c r="N94" t="n">
         <v>0.5014158368910244</v>
       </c>
       <c r="O94" t="n">
-        <v>1.855470900555668</v>
+        <v>1.855470613579176</v>
       </c>
       <c r="P94" t="n">
-        <v>0.4187065687845624</v>
+        <v>0.4187065212576149</v>
       </c>
     </row>
     <row r="95">
@@ -13327,7 +13327,7 @@
         <v>0.06709869922107958</v>
       </c>
       <c r="L97" t="n">
-        <v>0.2245697852381476</v>
+        <v>0.2245699095948994</v>
       </c>
       <c r="M97" t="n">
         <v>0.3832015662473154</v>
@@ -13394,10 +13394,10 @@
         <v>0.6460857452177993</v>
       </c>
       <c r="O98" t="n">
-        <v>1.843901133815964</v>
+        <v>1.8439013931671</v>
       </c>
       <c r="P98" t="n">
-        <v>0.416787874984319</v>
+        <v>0.4167879180525689</v>
       </c>
     </row>
     <row r="99">
@@ -13452,10 +13452,10 @@
         <v>0.3093743678558432</v>
       </c>
       <c r="O99" t="n">
-        <v>0.3230714385036351</v>
+        <v>0.3230716110873924</v>
       </c>
       <c r="P99" t="n">
-        <v>0.0978114719350216</v>
+        <v>0.09781151966850365</v>
       </c>
     </row>
     <row r="100">
@@ -13501,19 +13501,19 @@
         <v>0.3062443275839459</v>
       </c>
       <c r="L100" t="n">
-        <v>0.06566509422368116</v>
+        <v>0.06566501106939437</v>
       </c>
       <c r="M100" t="n">
-        <v>0.06282729765669059</v>
+        <v>0.06282721494468291</v>
       </c>
       <c r="N100" t="n">
         <v>0.4637729499505414</v>
       </c>
       <c r="O100" t="n">
-        <v>0.01333912382268454</v>
+        <v>0.01333904863394841</v>
       </c>
       <c r="P100" t="n">
-        <v>0.00442674958002387</v>
+        <v>0.004426724737541132</v>
       </c>
     </row>
     <row r="101">
@@ -13565,7 +13565,7 @@
         <v>0.4405811972814861</v>
       </c>
       <c r="N101" t="n">
-        <v>0.8935759373145153</v>
+        <v>0.8935760721919934</v>
       </c>
       <c r="O101" t="n">
         <v>2.104686491988697</v>
@@ -13617,19 +13617,19 @@
         <v>0.2409915299767238</v>
       </c>
       <c r="L102" t="n">
-        <v>0.1894174516764553</v>
+        <v>0.1894173704588835</v>
       </c>
       <c r="M102" t="n">
         <v>0.1737453428550193</v>
       </c>
       <c r="N102" t="n">
-        <v>0.320335306138537</v>
+        <v>0.3203352060579467</v>
       </c>
       <c r="O102" t="n">
-        <v>1.00969681278688</v>
+        <v>1.009697044655809</v>
       </c>
       <c r="P102" t="n">
-        <v>0.2619539710413861</v>
+        <v>0.2619540195740639</v>
       </c>
     </row>
     <row r="103">
@@ -13681,7 +13681,7 @@
         <v>0.2583057043920634</v>
       </c>
       <c r="N103" t="n">
-        <v>0.2706041698144646</v>
+        <v>0.2706042996191074</v>
       </c>
       <c r="O103" t="n">
         <v>-0.08538542265459548</v>
@@ -13736,16 +13736,16 @@
         <v>0.2147194381203827</v>
       </c>
       <c r="M104" t="n">
-        <v>0.35602954372032</v>
+        <v>0.356029459834573</v>
       </c>
       <c r="N104" t="n">
-        <v>0.399351256637037</v>
+        <v>0.3993511673057981</v>
       </c>
       <c r="O104" t="n">
-        <v>1.073107394815757</v>
+        <v>1.073107590877808</v>
       </c>
       <c r="P104" t="n">
-        <v>0.2750892967965775</v>
+        <v>0.2750893369933398</v>
       </c>
     </row>
     <row r="105">
@@ -13858,10 +13858,10 @@
         <v>0.02616451406140885</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.009824766617435476</v>
+        <v>-0.009824983513860297</v>
       </c>
       <c r="P106" t="n">
-        <v>-0.003285706247341369</v>
+        <v>-0.003285779023612156</v>
       </c>
     </row>
     <row r="107">
@@ -13910,16 +13910,16 @@
         <v>0.2434317907411474</v>
       </c>
       <c r="M107" t="n">
-        <v>0.2297929000978975</v>
+        <v>0.229792989676544</v>
       </c>
       <c r="N107" t="n">
         <v>0.3005009314280398</v>
       </c>
       <c r="O107" t="n">
-        <v>1.615788822966732</v>
+        <v>1.615789025602404</v>
       </c>
       <c r="P107" t="n">
-        <v>0.3778466772744502</v>
+        <v>0.3778467128533771</v>
       </c>
     </row>
     <row r="108">
@@ -13971,13 +13971,13 @@
         <v>0.2804407519017611</v>
       </c>
       <c r="N108" t="n">
-        <v>0.07016853456877148</v>
+        <v>0.07016862770079491</v>
       </c>
       <c r="O108" t="n">
-        <v>-0.2041798697454421</v>
+        <v>-0.2041799727495219</v>
       </c>
       <c r="P108" t="n">
-        <v>-0.07330182699360011</v>
+        <v>-0.07330186697486929</v>
       </c>
     </row>
     <row r="109">
@@ -14087,13 +14087,13 @@
         <v>0.2087861115585867</v>
       </c>
       <c r="N110" t="n">
-        <v>0.2892065908335026</v>
+        <v>0.2892066923909578</v>
       </c>
       <c r="O110" t="n">
-        <v>1.361354736135401</v>
+        <v>1.361354906492112</v>
       </c>
       <c r="P110" t="n">
-        <v>0.331640754205375</v>
+        <v>0.3316407862285082</v>
       </c>
     </row>
     <row r="111">
@@ -14145,13 +14145,13 @@
         <v>0.3527610150791685</v>
       </c>
       <c r="N111" t="n">
-        <v>0.4410912561217435</v>
+        <v>0.4410911141350211</v>
       </c>
       <c r="O111" t="n">
-        <v>0.6273987076341623</v>
+        <v>0.6273992508521515</v>
       </c>
       <c r="P111" t="n">
-        <v>0.1762455378643162</v>
+        <v>0.1762456687393668</v>
       </c>
     </row>
     <row r="112">
@@ -14206,10 +14206,10 @@
         <v>-0.05779696867464834</v>
       </c>
       <c r="O112" t="n">
-        <v>0.1358271346856008</v>
+        <v>0.1358272134335627</v>
       </c>
       <c r="P112" t="n">
-        <v>0.04336776073548188</v>
+        <v>0.04336778484803694</v>
       </c>
     </row>
     <row r="113">
@@ -14261,13 +14261,13 @@
         <v>0.3209028104532512</v>
       </c>
       <c r="N113" t="n">
-        <v>0.2024936551015688</v>
+        <v>0.2024935611079193</v>
       </c>
       <c r="O113" t="n">
-        <v>2.504647315145934</v>
+        <v>2.504647714346963</v>
       </c>
       <c r="P113" t="n">
-        <v>0.5189661880587382</v>
+        <v>0.5189662457319539</v>
       </c>
     </row>
     <row r="114">
@@ -14435,13 +14435,13 @@
         <v>0.2495371590212319</v>
       </c>
       <c r="N116" t="n">
-        <v>0.1820869574717243</v>
+        <v>0.1820870524283449</v>
       </c>
       <c r="O116" t="n">
-        <v>1.012113466306033</v>
+        <v>1.012113328743149</v>
       </c>
       <c r="P116" t="n">
-        <v>0.2624596001959238</v>
+        <v>0.2624595714255802</v>
       </c>
     </row>
     <row r="117">
@@ -14490,16 +14490,16 @@
         <v>0.2010431403072359</v>
       </c>
       <c r="M117" t="n">
-        <v>0.2882303113567461</v>
+        <v>0.2882304122835408</v>
       </c>
       <c r="N117" t="n">
         <v>0.17091137637461</v>
       </c>
       <c r="O117" t="n">
-        <v>-0.008152903986466065</v>
+        <v>-0.008152963815066583</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.002725053835217706</v>
+        <v>-0.002725073887221652</v>
       </c>
     </row>
     <row r="118">
@@ -14545,7 +14545,7 @@
         <v>0.1479868383355476</v>
       </c>
       <c r="L118" t="n">
-        <v>0.1345951437345796</v>
+        <v>0.134595222418822</v>
       </c>
       <c r="M118" t="n">
         <v>0.3127956274401162</v>
@@ -14554,10 +14554,10 @@
         <v>0.3475433849167686</v>
       </c>
       <c r="O118" t="n">
-        <v>1.008098720881529</v>
+        <v>1.008098597643145</v>
       </c>
       <c r="P118" t="n">
-        <v>0.2616193843833445</v>
+        <v>0.261619358574531</v>
       </c>
     </row>
     <row r="119">
@@ -14606,10 +14606,10 @@
         <v>-0.02412719905454497</v>
       </c>
       <c r="M119" t="n">
-        <v>0.508899544687857</v>
+        <v>0.5088994088486796</v>
       </c>
       <c r="N119" t="n">
-        <v>1.047926055455842</v>
+        <v>1.047926180569005</v>
       </c>
       <c r="O119" t="n">
         <v>5.844741026090502</v>
@@ -14661,7 +14661,7 @@
         <v>0.1175605107922595</v>
       </c>
       <c r="L120" t="n">
-        <v>0.122565969358523</v>
+        <v>0.1225660381986711</v>
       </c>
       <c r="M120" t="n">
         <v>0.315484072276069</v>
@@ -14728,10 +14728,10 @@
         <v>0.2199280947736242</v>
       </c>
       <c r="O121" t="n">
-        <v>0.6789672817196881</v>
+        <v>0.6789675060520135</v>
       </c>
       <c r="P121" t="n">
-        <v>0.1885407534466046</v>
+        <v>0.188540806381545</v>
       </c>
     </row>
     <row r="122">
@@ -14783,7 +14783,7 @@
         <v>0.339171636256298</v>
       </c>
       <c r="N122" t="n">
-        <v>0.4621149627709837</v>
+        <v>0.462114839546695</v>
       </c>
       <c r="O122" t="n">
         <v>2.548211305700259</v>
@@ -14838,16 +14838,16 @@
         <v>0.166322774760826</v>
       </c>
       <c r="M123" t="n">
-        <v>0.1914000309534718</v>
+        <v>0.1913999411386536</v>
       </c>
       <c r="N123" t="n">
         <v>0.4839315457492335</v>
       </c>
       <c r="O123" t="n">
-        <v>2.155527682137611</v>
+        <v>2.155527997163939</v>
       </c>
       <c r="P123" t="n">
-        <v>0.4667541695826118</v>
+        <v>0.466754218392849</v>
       </c>
     </row>
     <row r="124">
@@ -14896,16 +14896,16 @@
         <v>0.3242693672598134</v>
       </c>
       <c r="M124" t="n">
-        <v>0.02359393768681683</v>
+        <v>0.02359400187227512</v>
       </c>
       <c r="N124" t="n">
-        <v>-0.09600911095629594</v>
+        <v>-0.09600921108054317</v>
       </c>
       <c r="O124" t="n">
-        <v>0.02646321738484114</v>
+        <v>0.02646328193064584</v>
       </c>
       <c r="P124" t="n">
-        <v>0.008744385309480407</v>
+        <v>0.008744406453351061</v>
       </c>
     </row>
     <row r="125">
@@ -14960,10 +14960,10 @@
         <v>0.4792892607075678</v>
       </c>
       <c r="O125" t="n">
-        <v>0.637668527658992</v>
+        <v>0.6376687824114886</v>
       </c>
       <c r="P125" t="n">
-        <v>0.1787146128803425</v>
+        <v>0.1787146739998486</v>
       </c>
     </row>
     <row r="126">
@@ -15015,13 +15015,13 @@
         <v>0.3369812209318526</v>
       </c>
       <c r="N126" t="n">
-        <v>0.4323039563859938</v>
+        <v>0.4323040738468806</v>
       </c>
       <c r="O126" t="n">
-        <v>2.541771702683602</v>
+        <v>2.541770984453017</v>
       </c>
       <c r="P126" t="n">
-        <v>0.5243107809414933</v>
+        <v>0.5243106779039186</v>
       </c>
     </row>
     <row r="127">
@@ -15070,16 +15070,16 @@
         <v>0.1244867206251294</v>
       </c>
       <c r="M127" t="n">
-        <v>0.3400092382739452</v>
+        <v>0.3400091192872927</v>
       </c>
       <c r="N127" t="n">
         <v>0.4079590167651055</v>
       </c>
       <c r="O127" t="n">
-        <v>0.06132456140906095</v>
+        <v>0.06132448676777735</v>
       </c>
       <c r="P127" t="n">
-        <v>0.02003734369527144</v>
+        <v>0.02003731978273127</v>
       </c>
     </row>
     <row r="128">
@@ -15134,10 +15134,10 @@
         <v>0.4568694685162413</v>
       </c>
       <c r="O128" t="n">
-        <v>2.7699702827621</v>
+        <v>2.769970965682698</v>
       </c>
       <c r="P128" t="n">
-        <v>0.5563692523182886</v>
+        <v>0.5563693462957362</v>
       </c>
     </row>
     <row r="129">
@@ -15192,10 +15192,10 @@
         <v>0.36559255073862</v>
       </c>
       <c r="O129" t="n">
-        <v>1.635984280012563</v>
+        <v>1.635983775806978</v>
       </c>
       <c r="P129" t="n">
-        <v>0.3813835246137411</v>
+        <v>0.3813834365376805</v>
       </c>
     </row>
     <row r="130">
@@ -15244,16 +15244,16 @@
         <v>0.4143417106843821</v>
       </c>
       <c r="M130" t="n">
-        <v>0.2402183928504114</v>
+        <v>0.2402185112103379</v>
       </c>
       <c r="N130" t="n">
         <v>0.3357325644775169</v>
       </c>
       <c r="O130" t="n">
-        <v>-0.1385261756446688</v>
+        <v>-0.1385261185372527</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.04848852818348881</v>
+        <v>-0.0484885071581409</v>
       </c>
     </row>
     <row r="131">
@@ -15308,10 +15308,10 @@
         <v>0.3671160650710314</v>
       </c>
       <c r="O131" t="n">
-        <v>0.6575270490587899</v>
+        <v>0.6575273921563216</v>
       </c>
       <c r="P131" t="n">
-        <v>0.1834598848506019</v>
+        <v>0.1834599665068133</v>
       </c>
     </row>
     <row r="132">
@@ -15357,10 +15357,10 @@
         <v>0.1137457505389459</v>
       </c>
       <c r="L132" t="n">
-        <v>0.2766345554136083</v>
+        <v>0.2766344118961364</v>
       </c>
       <c r="M132" t="n">
-        <v>0.2571966986746275</v>
+        <v>0.2571964203138786</v>
       </c>
       <c r="N132" t="n">
         <v>0.3119397131104691</v>
@@ -15421,13 +15421,13 @@
         <v>0.249348312410711</v>
       </c>
       <c r="N133" t="n">
-        <v>0.1098915076909981</v>
+        <v>0.1098915747908442</v>
       </c>
       <c r="O133" t="n">
-        <v>0.7454598420447549</v>
+        <v>0.7454595101425967</v>
       </c>
       <c r="P133" t="n">
-        <v>0.2040280936914654</v>
+        <v>0.2040280173754638</v>
       </c>
     </row>
     <row r="134">
@@ -15482,10 +15482,10 @@
         <v>0.3295904459540913</v>
       </c>
       <c r="O134" t="n">
-        <v>0.4202378090847718</v>
+        <v>0.4202378973653167</v>
       </c>
       <c r="P134" t="n">
-        <v>0.1240536064730944</v>
+        <v>0.1240536297631054</v>
       </c>
     </row>
     <row r="135">
@@ -15644,16 +15644,16 @@
         <v>0.1765248233778627</v>
       </c>
       <c r="M137" t="n">
-        <v>0.09227582300103809</v>
+        <v>0.09227592798201401</v>
       </c>
       <c r="N137" t="n">
         <v>0.04365919028834564</v>
       </c>
       <c r="O137" t="n">
-        <v>0.7522604612609152</v>
+        <v>0.7522605963478297</v>
       </c>
       <c r="P137" t="n">
-        <v>0.2055897691520032</v>
+        <v>0.2055898001328234</v>
       </c>
     </row>
     <row r="138">
@@ -15702,16 +15702,16 @@
         <v>0.2899732545480527</v>
       </c>
       <c r="M138" t="n">
-        <v>0.09665102451023722</v>
+        <v>0.0966509386702068</v>
       </c>
       <c r="N138" t="n">
         <v>-0.05503604582813004</v>
       </c>
       <c r="O138" t="n">
-        <v>0.7939229252459663</v>
+        <v>0.7939230400958583</v>
       </c>
       <c r="P138" t="n">
-        <v>0.2150698927872996</v>
+        <v>0.2150699187175558</v>
       </c>
     </row>
     <row r="139">
@@ -15763,13 +15763,13 @@
         <v>0.2774527776568936</v>
       </c>
       <c r="N139" t="n">
-        <v>0.3087925952825756</v>
+        <v>0.3087925123936657</v>
       </c>
       <c r="O139" t="n">
-        <v>0.6842389999016294</v>
+        <v>0.6842387253701432</v>
       </c>
       <c r="P139" t="n">
-        <v>0.1897834033444941</v>
+        <v>0.1897833386994676</v>
       </c>
     </row>
     <row r="140">
@@ -15815,7 +15815,7 @@
         <v>0.001399131365921624</v>
       </c>
       <c r="L140" t="n">
-        <v>0.2118036229253053</v>
+        <v>0.2118035108284431</v>
       </c>
       <c r="M140" t="n">
         <v>0.382834223080448</v>
@@ -15824,10 +15824,10 @@
         <v>0.4091330168698077</v>
       </c>
       <c r="O140" t="n">
-        <v>0.4918808599070523</v>
+        <v>0.4918810298086007</v>
       </c>
       <c r="P140" t="n">
-        <v>0.1426451503727606</v>
+        <v>0.1426451937491404</v>
       </c>
     </row>
     <row r="141">
@@ -15934,16 +15934,16 @@
         <v>0.2168831814271321</v>
       </c>
       <c r="M142" t="n">
-        <v>0.4268436948214209</v>
+        <v>0.4268438006073982</v>
       </c>
       <c r="N142" t="n">
         <v>0.2512079216829597</v>
       </c>
       <c r="O142" t="n">
-        <v>0.2849653138254022</v>
+        <v>0.2849652280311783</v>
       </c>
       <c r="P142" t="n">
-        <v>0.08716918675568364</v>
+        <v>0.08716916255974172</v>
       </c>
     </row>
     <row r="143">
@@ -15992,16 +15992,16 @@
         <v>0.0369609655065728</v>
       </c>
       <c r="M143" t="n">
-        <v>0.5128414942522512</v>
+        <v>0.5128416580852018</v>
       </c>
       <c r="N143" t="n">
-        <v>0.5356413374107434</v>
+        <v>0.5356415062191173</v>
       </c>
       <c r="O143" t="n">
-        <v>0.01852626317154038</v>
+        <v>0.0185261146502389</v>
       </c>
       <c r="P143" t="n">
-        <v>0.006137672957033269</v>
+        <v>0.006137624052097612</v>
       </c>
     </row>
     <row r="144">
@@ -16053,7 +16053,7 @@
         <v>0.4566745254401043</v>
       </c>
       <c r="N144" t="n">
-        <v>0.4013787300432552</v>
+        <v>0.4013788417073083</v>
       </c>
       <c r="O144" t="n">
         <v>0.4837375739623007</v>
@@ -16114,10 +16114,10 @@
         <v>0.03367984690990267</v>
       </c>
       <c r="O145" t="n">
-        <v>0.5265017944016477</v>
+        <v>0.526501506916675</v>
       </c>
       <c r="P145" t="n">
-        <v>0.1514164762350683</v>
+        <v>0.1514164039532544</v>
       </c>
     </row>
     <row r="146">
@@ -16163,7 +16163,7 @@
         <v>0.1848391507108282</v>
       </c>
       <c r="L146" t="n">
-        <v>0.04322204132119478</v>
+        <v>0.04322197706517583</v>
       </c>
       <c r="M146" t="n">
         <v>0.2577191511493784</v>
@@ -16172,10 +16172,10 @@
         <v>0.3173381020670165</v>
       </c>
       <c r="O146" t="n">
-        <v>0.7012403887200864</v>
+        <v>0.7012405596002873</v>
       </c>
       <c r="P146" t="n">
-        <v>0.1937733925519727</v>
+        <v>0.1937734325212859</v>
       </c>
     </row>
     <row r="147">
@@ -16288,10 +16288,10 @@
         <v>0.0195525320567187</v>
       </c>
       <c r="O148" t="n">
-        <v>0.6948194161214145</v>
+        <v>0.6948191043893244</v>
       </c>
       <c r="P148" t="n">
-        <v>0.1922696172071077</v>
+        <v>0.1922695441081255</v>
       </c>
     </row>
     <row r="149">
@@ -16343,13 +16343,13 @@
         <v>0.3903163712817588</v>
       </c>
       <c r="N149" t="n">
-        <v>0.2950182660219203</v>
+        <v>0.295018187384805</v>
       </c>
       <c r="O149" t="n">
-        <v>0.8679227550984032</v>
+        <v>0.8679232459102142</v>
       </c>
       <c r="P149" t="n">
-        <v>0.231552615547657</v>
+        <v>0.231552723414451</v>
       </c>
     </row>
     <row r="150">
@@ -16398,10 +16398,10 @@
         <v>0.136882375856564</v>
       </c>
       <c r="M150" t="n">
-        <v>0.1418102896255997</v>
+        <v>0.1418101577680357</v>
       </c>
       <c r="N150" t="n">
-        <v>0.03655563082769375</v>
+        <v>0.03655552215951752</v>
       </c>
       <c r="O150" t="n">
         <v>0.3934110089353813</v>
@@ -16462,10 +16462,10 @@
         <v>0.2326679278080408</v>
       </c>
       <c r="O151" t="n">
-        <v>1.591126690559029</v>
+        <v>1.591127552202948</v>
       </c>
       <c r="P151" t="n">
-        <v>0.3735028006242258</v>
+        <v>0.3735029528707638</v>
       </c>
     </row>
     <row r="152">
@@ -16511,19 +16511,19 @@
         <v>0.2645928973658473</v>
       </c>
       <c r="L152" t="n">
-        <v>0.3408617392862134</v>
+        <v>0.340861642271111</v>
       </c>
       <c r="M152" t="n">
-        <v>0.1280739063908303</v>
+        <v>0.1280738377240851</v>
       </c>
       <c r="N152" t="n">
         <v>-0.04344913630888647</v>
       </c>
       <c r="O152" t="n">
-        <v>0.1990669257489983</v>
+        <v>0.1990670033305135</v>
       </c>
       <c r="P152" t="n">
-        <v>0.0623830701676158</v>
+        <v>0.0623830930802336</v>
       </c>
     </row>
     <row r="153">
@@ -16630,16 +16630,16 @@
         <v>0.01836970480302891</v>
       </c>
       <c r="M154" t="n">
-        <v>0.3283582059210792</v>
+        <v>0.3283581159081281</v>
       </c>
       <c r="N154" t="n">
         <v>0.4477267559323508</v>
       </c>
       <c r="O154" t="n">
-        <v>0.2412602784171112</v>
+        <v>0.2412601212251688</v>
       </c>
       <c r="P154" t="n">
-        <v>0.07470091652125443</v>
+        <v>0.07470087115490798</v>
       </c>
     </row>
     <row r="155">
@@ -16691,13 +16691,13 @@
         <v>0.3080462452162089</v>
       </c>
       <c r="N155" t="n">
-        <v>0.1301240601045774</v>
+        <v>0.1301239860850751</v>
       </c>
       <c r="O155" t="n">
-        <v>1.409981536830176</v>
+        <v>1.409981705133003</v>
       </c>
       <c r="P155" t="n">
-        <v>0.3407194356121728</v>
+        <v>0.3407194668222135</v>
       </c>
     </row>
     <row r="156">
@@ -16746,16 +16746,16 @@
         <v>0.1998748456298334</v>
       </c>
       <c r="M156" t="n">
-        <v>0.2801948568197279</v>
+        <v>0.2801950020102424</v>
       </c>
       <c r="N156" t="n">
-        <v>0.2456863064480388</v>
+        <v>0.2456861689794825</v>
       </c>
       <c r="O156" t="n">
-        <v>0.5856797005730288</v>
+        <v>0.5856794778234402</v>
       </c>
       <c r="P156" t="n">
-        <v>0.1661072321525612</v>
+        <v>0.1661071775492853</v>
       </c>
     </row>
     <row r="157">
@@ -16856,16 +16856,16 @@
         <v>0.006727772871809812</v>
       </c>
       <c r="M158" t="n">
-        <v>0.1977202404385248</v>
+        <v>0.1977203265903875</v>
       </c>
       <c r="N158" t="n">
-        <v>0.3663102486255847</v>
+        <v>0.3663101365134869</v>
       </c>
       <c r="O158" t="n">
-        <v>1.593080549649096</v>
+        <v>1.593080751558206</v>
       </c>
       <c r="P158" t="n">
-        <v>0.3738479473496381</v>
+        <v>0.3738479830076653</v>
       </c>
     </row>
     <row r="159">
@@ -16920,10 +16920,10 @@
         <v>0.2563162745800649</v>
       </c>
       <c r="O159" t="n">
-        <v>1.316706753135079</v>
+        <v>1.31670692087895</v>
       </c>
       <c r="P159" t="n">
-        <v>0.3231945036188189</v>
+        <v>0.3231945355546351</v>
       </c>
     </row>
     <row r="160">
@@ -16975,13 +16975,13 @@
         <v>0.2825617060717704</v>
       </c>
       <c r="N160" t="n">
-        <v>0.2509704532804855</v>
+        <v>0.2509703539547923</v>
       </c>
       <c r="O160" t="n">
-        <v>1.108676645806991</v>
+        <v>1.108676363587209</v>
       </c>
       <c r="P160" t="n">
-        <v>0.2823404132600631</v>
+        <v>0.2823403560516951</v>
       </c>
     </row>
     <row r="161">
@@ -17033,13 +17033,13 @@
         <v>0.3833691249540108</v>
       </c>
       <c r="N161" t="n">
-        <v>0.3133161425813176</v>
+        <v>0.3133162742454894</v>
       </c>
       <c r="O161" t="n">
-        <v>0.4241447271222678</v>
+        <v>0.4241445722986514</v>
       </c>
       <c r="P161" t="n">
-        <v>0.1250833787413699</v>
+        <v>0.1250833379708218</v>
       </c>
     </row>
     <row r="162">
@@ -17094,10 +17094,10 @@
         <v>0.487979435800648</v>
       </c>
       <c r="O162" t="n">
-        <v>1.201517946490242</v>
+        <v>1.201517748571065</v>
       </c>
       <c r="P162" t="n">
-        <v>0.3008905035694887</v>
+        <v>0.3008904645856008</v>
       </c>
     </row>
     <row r="163">
@@ -17152,10 +17152,10 @@
         <v>0.4858454943883257</v>
       </c>
       <c r="O163" t="n">
-        <v>1.685497057627054</v>
+        <v>1.685497378233022</v>
       </c>
       <c r="P163" t="n">
-        <v>0.3899789617137452</v>
+        <v>0.3899790170275939</v>
       </c>
     </row>
     <row r="164">
@@ -17265,13 +17265,13 @@
         <v>0.1524190715125007</v>
       </c>
       <c r="N165" t="n">
-        <v>0.1595145858742635</v>
+        <v>0.159514500501627</v>
       </c>
       <c r="O165" t="n">
-        <v>0.4839426211025459</v>
+        <v>0.4839427609326084</v>
       </c>
       <c r="P165" t="n">
-        <v>0.1406148886347058</v>
+        <v>0.140614924460944</v>
       </c>
     </row>
     <row r="166">
@@ -17323,13 +17323,13 @@
         <v>0.2306109862737868</v>
       </c>
       <c r="N166" t="n">
-        <v>0.2885500353780979</v>
+        <v>0.2885498911171989</v>
       </c>
       <c r="O166" t="n">
-        <v>0.7766852656665333</v>
+        <v>0.7766851285350793</v>
       </c>
       <c r="P166" t="n">
-        <v>0.2111655244222777</v>
+        <v>0.2111654932614606</v>
       </c>
     </row>
     <row r="167">
@@ -17378,16 +17378,16 @@
         <v>0.4473910423000838</v>
       </c>
       <c r="M167" t="n">
-        <v>0.07720892833469639</v>
+        <v>0.07720904793738703</v>
       </c>
       <c r="N167" t="n">
-        <v>-0.2130353407553798</v>
+        <v>-0.2130354684231863</v>
       </c>
       <c r="O167" t="n">
-        <v>-0.2859819308763289</v>
+        <v>-0.2859818783279348</v>
       </c>
       <c r="P167" t="n">
-        <v>-0.1062081283645145</v>
+        <v>-0.106208106438213</v>
       </c>
     </row>
     <row r="168">
@@ -17442,10 +17442,10 @@
         <v>0.2793556118385359</v>
       </c>
       <c r="O168" t="n">
-        <v>1.417721497718393</v>
+        <v>1.417721700836872</v>
       </c>
       <c r="P168" t="n">
-        <v>0.3421531985509609</v>
+        <v>0.3421532361367774</v>
       </c>
     </row>
     <row r="169">
@@ -17497,13 +17497,13 @@
         <v>0.08274095702415241</v>
       </c>
       <c r="N169" t="n">
-        <v>-0.09070732211947574</v>
+        <v>-0.09070722814779009</v>
       </c>
       <c r="O169" t="n">
-        <v>0.2139374376028915</v>
+        <v>0.2139372701154936</v>
       </c>
       <c r="P169" t="n">
-        <v>0.06675683716107028</v>
+        <v>0.06675678810078933</v>
       </c>
     </row>
     <row r="170">
@@ -17552,16 +17552,16 @@
         <v>0.188845795254017</v>
       </c>
       <c r="M170" t="n">
-        <v>0.3533005618481297</v>
+        <v>0.353300650103842</v>
       </c>
       <c r="N170" t="n">
-        <v>0.2688504017199993</v>
+        <v>0.2688503241354772</v>
       </c>
       <c r="O170" t="n">
-        <v>0.08267737692567367</v>
+        <v>0.08267726395067432</v>
       </c>
       <c r="P170" t="n">
-        <v>0.02683269246969</v>
+        <v>0.02683265675377888</v>
       </c>
     </row>
     <row r="171">
@@ -17613,7 +17613,7 @@
         <v>0.2480866640511354</v>
       </c>
       <c r="N171" t="n">
-        <v>0.1591026285412234</v>
+        <v>0.1591027447570643</v>
       </c>
       <c r="O171" t="n">
         <v>0.2265105493455508</v>
@@ -17723,19 +17723,19 @@
         <v>-0.00221402497763723</v>
       </c>
       <c r="L173" t="n">
-        <v>0.1574088932948987</v>
+        <v>0.1574088058073053</v>
       </c>
       <c r="M173" t="n">
         <v>0.4320438499060819</v>
       </c>
       <c r="N173" t="n">
-        <v>0.2848688575130833</v>
+        <v>0.2848687496952893</v>
       </c>
       <c r="O173" t="n">
-        <v>-0.003922100019763008</v>
+        <v>-0.003922035222075126</v>
       </c>
       <c r="P173" t="n">
-        <v>-0.001309079614907227</v>
+        <v>-0.001309057959016924</v>
       </c>
     </row>
     <row r="174">
@@ -17781,7 +17781,7 @@
         <v>0.1701946971564012</v>
       </c>
       <c r="L174" t="n">
-        <v>0.2321527507228955</v>
+        <v>0.2321528713346572</v>
       </c>
       <c r="M174" t="n">
         <v>0.1551930643080264</v>
@@ -17790,10 +17790,10 @@
         <v>0.1100630489355476</v>
       </c>
       <c r="O174" t="n">
-        <v>0.6201557022723367</v>
+        <v>0.6201559108049952</v>
       </c>
       <c r="P174" t="n">
-        <v>0.1744979179222694</v>
+        <v>0.1744979683127272</v>
       </c>
     </row>
     <row r="175">
@@ -17839,10 +17839,10 @@
         <v>0.1556455802565748</v>
       </c>
       <c r="L175" t="n">
-        <v>0.02215151691471728</v>
+        <v>0.0221514256960571</v>
       </c>
       <c r="M175" t="n">
-        <v>0.1957687319381531</v>
+        <v>0.1957686070999487</v>
       </c>
       <c r="N175" t="n">
         <v>0.3177117379920742</v>
@@ -17897,19 +17897,19 @@
         <v>-0.03743029821209776</v>
       </c>
       <c r="L176" t="n">
-        <v>0.09786162788248687</v>
+        <v>0.09786170394295768</v>
       </c>
       <c r="M176" t="n">
-        <v>0.4476347751241054</v>
+        <v>0.4476346428783498</v>
       </c>
       <c r="N176" t="n">
-        <v>0.3620155031430621</v>
+        <v>0.3620152690126712</v>
       </c>
       <c r="O176" t="n">
-        <v>1.180945954352449</v>
+        <v>1.180946404593328</v>
       </c>
       <c r="P176" t="n">
-        <v>0.2968257773463623</v>
+        <v>0.2968258665865284</v>
       </c>
     </row>
     <row r="177">
@@ -17964,10 +17964,10 @@
         <v>0.2952591120760886</v>
       </c>
       <c r="O177" t="n">
-        <v>0.6885862585992866</v>
+        <v>0.6885860912939901</v>
       </c>
       <c r="P177" t="n">
-        <v>0.1908061901890528</v>
+        <v>0.1908061508606522</v>
       </c>
     </row>
     <row r="178">
@@ -18022,10 +18022,10 @@
         <v>0.06552649714409409</v>
       </c>
       <c r="O178" t="n">
-        <v>0.798926203948864</v>
+        <v>0.7989260004856624</v>
       </c>
       <c r="P178" t="n">
-        <v>0.2161984604620446</v>
+        <v>0.2161984146103133</v>
       </c>
     </row>
     <row r="179">
@@ -18071,7 +18071,7 @@
         <v>0.002306857007955854</v>
       </c>
       <c r="L179" t="n">
-        <v>0.2376373369479485</v>
+        <v>0.2376372111536049</v>
       </c>
       <c r="M179" t="n">
         <v>0.2115638855609088</v>
@@ -18080,10 +18080,10 @@
         <v>0.3459998512131928</v>
       </c>
       <c r="O179" t="n">
-        <v>0.5473935285963261</v>
+        <v>0.5473936269172468</v>
       </c>
       <c r="P179" t="n">
-        <v>0.1566454632865169</v>
+        <v>0.1566454877841517</v>
       </c>
     </row>
     <row r="180">
@@ -18132,7 +18132,7 @@
         <v>0.05760908347696514</v>
       </c>
       <c r="M180" t="n">
-        <v>0.6262156195054116</v>
+        <v>0.6262157788524711</v>
       </c>
     </row>
     <row r="181">
@@ -18187,10 +18187,10 @@
         <v>0.1903480350419828</v>
       </c>
       <c r="O181" t="n">
-        <v>0.8257289753947852</v>
+        <v>0.8257293880006527</v>
       </c>
       <c r="P181" t="n">
-        <v>0.2222088835589899</v>
+        <v>0.2222089756300705</v>
       </c>
     </row>
     <row r="182">
@@ -18245,10 +18245,10 @@
         <v>0.4797738211292075</v>
       </c>
       <c r="O182" t="n">
-        <v>2.007723499965023</v>
+        <v>2.007723723557632</v>
       </c>
       <c r="P182" t="n">
-        <v>0.4434862001798885</v>
+        <v>0.4434862359492266</v>
       </c>
     </row>
     <row r="183">
@@ -18361,10 +18361,10 @@
         <v>-0.03967653340479205</v>
       </c>
       <c r="O184" t="n">
-        <v>0.5387266050063124</v>
+        <v>0.5387264509295464</v>
       </c>
       <c r="P184" t="n">
-        <v>0.1544819688013521</v>
+        <v>0.1544819302675728</v>
       </c>
     </row>
     <row r="185">
@@ -18471,7 +18471,7 @@
         <v>0.1142753430604433</v>
       </c>
       <c r="M186" t="n">
-        <v>0.3343423495918525</v>
+        <v>0.3343424943787403</v>
       </c>
       <c r="N186" t="n">
         <v>0.3454949155962055</v>
@@ -18535,10 +18535,10 @@
         <v>0.2264861979864474</v>
       </c>
       <c r="O187" t="n">
-        <v>0.2697922244654278</v>
+        <v>0.269792320450329</v>
       </c>
       <c r="P187" t="n">
-        <v>0.08287307270745892</v>
+        <v>0.08287309999262149</v>
       </c>
     </row>
     <row r="188">
@@ -18587,16 +18587,16 @@
         <v>0.02364169546836181</v>
       </c>
       <c r="M188" t="n">
-        <v>0.1925176293048592</v>
+        <v>0.1925175563751826</v>
       </c>
       <c r="N188" t="n">
-        <v>0.3372367310183921</v>
+        <v>0.337236639313762</v>
       </c>
       <c r="O188" t="n">
-        <v>1.136289890454184</v>
+        <v>1.136290124496893</v>
       </c>
       <c r="P188" t="n">
-        <v>0.2879135975674081</v>
+        <v>0.28791364460016</v>
       </c>
     </row>
     <row r="189">
@@ -18648,13 +18648,13 @@
         <v>0.2315934189361433</v>
       </c>
       <c r="N189" t="n">
-        <v>0.3110520023310697</v>
+        <v>0.3110521108130297</v>
       </c>
       <c r="O189" t="n">
-        <v>0.564107355588487</v>
+        <v>0.5641070467860791</v>
       </c>
       <c r="P189" t="n">
-        <v>0.1607949751725246</v>
+        <v>0.1607948987804309</v>
       </c>
     </row>
     <row r="190">
@@ -18700,7 +18700,7 @@
         <v>-0.01315146459454752</v>
       </c>
       <c r="L190" t="n">
-        <v>0.1412900364911174</v>
+        <v>0.1412901448620587</v>
       </c>
       <c r="M190" t="n">
         <v>0.3429960921237085</v>
@@ -18825,10 +18825,10 @@
         <v>0.2969707349896964</v>
       </c>
       <c r="O192" t="n">
-        <v>-0.07418742421647329</v>
+        <v>-0.07418735863745973</v>
       </c>
       <c r="P192" t="n">
-        <v>-0.02536719475802252</v>
+        <v>-0.02536717174564107</v>
       </c>
     </row>
     <row r="193">
@@ -18883,10 +18883,10 @@
         <v>0.08127016397199927</v>
       </c>
       <c r="O193" t="n">
-        <v>0.3236091284315077</v>
+        <v>0.3236089431237483</v>
       </c>
       <c r="P193" t="n">
-        <v>0.09796016691082188</v>
+        <v>0.09796011567199225</v>
       </c>
     </row>
     <row r="194">
@@ -18935,7 +18935,7 @@
         <v>0.09079538252606278</v>
       </c>
       <c r="M194" t="n">
-        <v>0.1681428738206883</v>
+        <v>0.1681429649193105</v>
       </c>
       <c r="N194" t="n">
         <v>0.216136729064929</v>
@@ -19057,10 +19057,10 @@
         <v>0.1953716712174673</v>
       </c>
       <c r="O196" t="n">
-        <v>0.8893158496170119</v>
+        <v>0.8893154050654639</v>
       </c>
       <c r="P196" t="n">
-        <v>0.2362363878685372</v>
+        <v>0.2362362909073643</v>
       </c>
     </row>
     <row r="197">
@@ -19170,13 +19170,13 @@
         <v>0.275554807607215</v>
       </c>
       <c r="N198" t="n">
-        <v>0.02253474541736367</v>
+        <v>0.02253482469705137</v>
       </c>
       <c r="O198" t="n">
-        <v>0.8916676898256308</v>
+        <v>0.8916675541613821</v>
       </c>
       <c r="P198" t="n">
-        <v>0.2367491351819033</v>
+        <v>0.2367491056166953</v>
       </c>
     </row>
     <row r="199">
@@ -19286,13 +19286,13 @@
         <v>0.01151389627483423</v>
       </c>
       <c r="N200" t="n">
-        <v>0.09011982028633669</v>
+        <v>0.09011992472681274</v>
       </c>
       <c r="O200" t="n">
-        <v>0.1421367158033575</v>
+        <v>0.1421368304487378</v>
       </c>
       <c r="P200" t="n">
-        <v>0.04529618240198641</v>
+        <v>0.04529621737689271</v>
       </c>
     </row>
     <row r="201">
@@ -19341,16 +19341,16 @@
         <v>0.05169703919499269</v>
       </c>
       <c r="M201" t="n">
-        <v>0.1972027393307001</v>
+        <v>0.1972025981953531</v>
       </c>
       <c r="N201" t="n">
         <v>0.188954566895311</v>
       </c>
       <c r="O201" t="n">
-        <v>0.6730827161562649</v>
+        <v>0.6730825783384891</v>
       </c>
       <c r="P201" t="n">
-        <v>0.187150566933115</v>
+        <v>0.1871505343365087</v>
       </c>
     </row>
     <row r="202">
@@ -19396,10 +19396,10 @@
         <v>-0.1784301795417707</v>
       </c>
       <c r="L202" t="n">
-        <v>0.06234132393166236</v>
+        <v>0.06234121829598771</v>
       </c>
       <c r="M202" t="n">
-        <v>0.4428246342833682</v>
+        <v>0.4428245368563133</v>
       </c>
       <c r="N202" t="n">
         <v>0.5674164894502758</v>
@@ -19463,10 +19463,10 @@
         <v>0.01668046732143691</v>
       </c>
       <c r="O203" t="n">
-        <v>0.5144523798342859</v>
+        <v>0.5144522630548758</v>
       </c>
       <c r="P203" t="n">
-        <v>0.1483789080540723</v>
+        <v>0.1483788785369089</v>
       </c>
     </row>
     <row r="204">
@@ -19515,16 +19515,16 @@
         <v>0.07324650729223303</v>
       </c>
       <c r="M204" t="n">
-        <v>0.342134247451835</v>
+        <v>0.3421344295448523</v>
       </c>
       <c r="N204" t="n">
         <v>0.5973518306883263</v>
       </c>
       <c r="O204" t="n">
-        <v>1.952143134147453</v>
+        <v>1.952142913897354</v>
       </c>
       <c r="P204" t="n">
-        <v>0.4345393648565046</v>
+        <v>0.434539329181016</v>
       </c>
     </row>
     <row r="205">
@@ -19573,16 +19573,16 @@
         <v>0.09391642577788928</v>
       </c>
       <c r="M205" t="n">
-        <v>0.06039115391134509</v>
+        <v>0.06039105825750157</v>
       </c>
       <c r="N205" t="n">
         <v>0.172159673160754</v>
       </c>
       <c r="O205" t="n">
-        <v>1.354233565795498</v>
+        <v>1.354233330052214</v>
       </c>
       <c r="P205" t="n">
-        <v>0.3303007904674113</v>
+        <v>0.3303007460637899</v>
       </c>
     </row>
     <row r="206">
@@ -19637,10 +19637,10 @@
         <v>0.2840808338853087</v>
       </c>
       <c r="O206" t="n">
-        <v>-0.01364306099140544</v>
+        <v>-0.01364321068661634</v>
       </c>
       <c r="P206" t="n">
-        <v>-0.004568526648974114</v>
+        <v>-0.004568577006448082</v>
       </c>
     </row>
     <row r="207">
@@ -19695,10 +19695,10 @@
         <v>0.2137129368102011</v>
       </c>
       <c r="O207" t="n">
-        <v>0.8426379696360804</v>
+        <v>0.8426380985126831</v>
       </c>
       <c r="P207" t="n">
-        <v>0.2259704584523792</v>
+        <v>0.2259704870343915</v>
       </c>
     </row>
     <row r="208">
@@ -19750,13 +19750,13 @@
         <v>0.2534158360246803</v>
       </c>
       <c r="N208" t="n">
-        <v>0.2639422135322353</v>
+        <v>0.2639423287775027</v>
       </c>
       <c r="O208" t="n">
-        <v>0.1944521491466047</v>
+        <v>0.1944522520681202</v>
       </c>
       <c r="P208" t="n">
-        <v>0.06101840807447423</v>
+        <v>0.06101843854914835</v>
       </c>
     </row>
     <row r="209">
@@ -19811,10 +19811,10 @@
         <v>0.1052876317750255</v>
       </c>
       <c r="O209" t="n">
-        <v>0.1894869946844093</v>
+        <v>0.1894868990463181</v>
       </c>
       <c r="P209" t="n">
-        <v>0.05954620265634514</v>
+        <v>0.05954617425951536</v>
       </c>
     </row>
     <row r="210">
@@ -19869,10 +19869,10 @@
         <v>0.3385779114620997</v>
       </c>
       <c r="O210" t="n">
-        <v>1.167606355302945</v>
+        <v>1.167606672149636</v>
       </c>
       <c r="P210" t="n">
-        <v>0.2941763878539903</v>
+        <v>0.2941764509121012</v>
       </c>
     </row>
     <row r="211">
@@ -19924,13 +19924,13 @@
         <v>0.1776112479964953</v>
       </c>
       <c r="N211" t="n">
-        <v>0.2444416634842197</v>
+        <v>0.2444417439250433</v>
       </c>
       <c r="O211" t="n">
-        <v>0.1185826129871597</v>
+        <v>0.1185830029425483</v>
       </c>
       <c r="P211" t="n">
-        <v>0.03806055367106076</v>
+        <v>0.03806067429909343</v>
       </c>
     </row>
     <row r="212">
@@ -19982,13 +19982,13 @@
         <v>0.2129657636891578</v>
       </c>
       <c r="N212" t="n">
-        <v>0.2319380785197356</v>
+        <v>0.2319381982108197</v>
       </c>
       <c r="O212" t="n">
-        <v>0.5720063979156129</v>
+        <v>0.5720063004699318</v>
       </c>
       <c r="P212" t="n">
-        <v>0.1627457740135008</v>
+        <v>0.1627457499880354</v>
       </c>
     </row>
     <row r="213">
@@ -20092,19 +20092,19 @@
         <v>-0.09348715123265083</v>
       </c>
       <c r="L214" t="n">
-        <v>0.1102960435275062</v>
+        <v>0.1102959350978181</v>
       </c>
       <c r="M214" t="n">
         <v>0.07481717580760061</v>
       </c>
       <c r="N214" t="n">
-        <v>0.6689038970525147</v>
+        <v>0.6689040195432836</v>
       </c>
       <c r="O214" t="n">
-        <v>1.695076995359252</v>
+        <v>1.695076675923903</v>
       </c>
       <c r="P214" t="n">
-        <v>0.3916298180271196</v>
+        <v>0.3916297630459107</v>
       </c>
     </row>
     <row r="215">
@@ -20153,16 +20153,16 @@
         <v>0.1074029182847251</v>
       </c>
       <c r="M215" t="n">
-        <v>0.118675018385046</v>
+        <v>0.1186751197997082</v>
       </c>
       <c r="N215" t="n">
-        <v>0.1979852701409397</v>
+        <v>0.1979853864452548</v>
       </c>
       <c r="O215" t="n">
-        <v>0.7874585746320053</v>
+        <v>0.7874587040917769</v>
       </c>
       <c r="P215" t="n">
-        <v>0.2136086461742726</v>
+        <v>0.2136086754735054</v>
       </c>
     </row>
     <row r="216">
@@ -20217,10 +20217,10 @@
         <v>-0.1290201168825313</v>
       </c>
       <c r="O216" t="n">
-        <v>-0.2715126875723733</v>
+        <v>-0.2715126305821204</v>
       </c>
       <c r="P216" t="n">
-        <v>-0.1002110320189961</v>
+        <v>-0.1002110085552154</v>
       </c>
     </row>
     <row r="217">
@@ -20272,13 +20272,13 @@
         <v>0.2442286700485761</v>
       </c>
       <c r="N217" t="n">
-        <v>0.3407031513819347</v>
+        <v>0.3407030546838661</v>
       </c>
       <c r="O217" t="n">
-        <v>1.542714941225312</v>
+        <v>1.542714767317979</v>
       </c>
       <c r="P217" t="n">
-        <v>0.3648949439870681</v>
+        <v>0.3648949128700338</v>
       </c>
     </row>
     <row r="218">
@@ -20324,7 +20324,7 @@
         <v>0.1576176752073082</v>
       </c>
       <c r="L218" t="n">
-        <v>0.1114635392661374</v>
+        <v>0.111463647159014</v>
       </c>
       <c r="M218" t="n">
         <v>0.14263572559965</v>
@@ -20333,10 +20333,10 @@
         <v>0.06748609422966356</v>
       </c>
       <c r="O218" t="n">
-        <v>0.7828462209211797</v>
+        <v>0.7828466373314371</v>
       </c>
       <c r="P218" t="n">
-        <v>0.2125638827678469</v>
+        <v>0.2125639771719507</v>
       </c>
     </row>
     <row r="219">
@@ -20391,10 +20391,10 @@
         <v>0.3692760319862614</v>
       </c>
       <c r="O219" t="n">
-        <v>0.7585322940676307</v>
+        <v>0.7585318372736842</v>
       </c>
       <c r="P219" t="n">
-        <v>0.2070264380034466</v>
+        <v>0.2070263334915912</v>
       </c>
     </row>
     <row r="220">
@@ -20443,10 +20443,10 @@
         <v>0.2324079945974717</v>
       </c>
       <c r="M220" t="n">
-        <v>0.03740012055520303</v>
+        <v>0.03740018734861783</v>
       </c>
       <c r="N220" t="n">
-        <v>-0.01686504461902216</v>
+        <v>-0.01686510460742252</v>
       </c>
       <c r="O220" t="n">
         <v>0.5580736705533527</v>
@@ -20498,19 +20498,19 @@
         <v>0.04818397153971654</v>
       </c>
       <c r="L221" t="n">
-        <v>0.1046584729267077</v>
+        <v>0.1046583819206195</v>
       </c>
       <c r="M221" t="n">
         <v>0.2256737374327378</v>
       </c>
       <c r="N221" t="n">
-        <v>0.1966747160939222</v>
+        <v>0.1966748228928017</v>
       </c>
       <c r="O221" t="n">
-        <v>0.8942799063587314</v>
+        <v>0.8942795049434524</v>
       </c>
       <c r="P221" t="n">
-        <v>0.2373181517198841</v>
+        <v>0.2373180643201911</v>
       </c>
     </row>
     <row r="222">
@@ -20556,19 +20556,19 @@
         <v>0.06688782898879242</v>
       </c>
       <c r="L222" t="n">
-        <v>0.09898955231140927</v>
+        <v>0.09898943808183969</v>
       </c>
       <c r="M222" t="n">
-        <v>0.2213541889270982</v>
+        <v>0.2213543300101224</v>
       </c>
       <c r="N222" t="n">
-        <v>0.1594683481866699</v>
+        <v>0.1594682210387659</v>
       </c>
       <c r="O222" t="n">
-        <v>0.318760788421373</v>
+        <v>0.3187605416955044</v>
       </c>
       <c r="P222" t="n">
-        <v>0.09661792847413953</v>
+        <v>0.09661786008568729</v>
       </c>
     </row>
     <row r="223">
@@ -20617,7 +20617,7 @@
         <v>0.0982611250705292</v>
       </c>
       <c r="M223" t="n">
-        <v>0.0629493274514088</v>
+        <v>0.0629494278784879</v>
       </c>
       <c r="N223" t="n">
         <v>0.6462059638242093</v>
@@ -20675,16 +20675,16 @@
         <v>0.03430518243700487</v>
       </c>
       <c r="M224" t="n">
-        <v>0.1821226845688639</v>
+        <v>0.1821227926530498</v>
       </c>
       <c r="N224" t="n">
-        <v>0.2319496507761061</v>
+        <v>0.2319497681639082</v>
       </c>
       <c r="O224" t="n">
-        <v>0.6139701609545798</v>
+        <v>0.6139699594764267</v>
       </c>
       <c r="P224" t="n">
-        <v>0.1730013188540152</v>
+        <v>0.1730012700439123</v>
       </c>
     </row>
     <row r="225">
@@ -20791,16 +20791,16 @@
         <v>0.2368066695973079</v>
       </c>
       <c r="M226" t="n">
-        <v>0.03126724764696842</v>
+        <v>0.03126736080441006</v>
       </c>
       <c r="N226" t="n">
         <v>-0.1196021697921971</v>
       </c>
       <c r="O226" t="n">
-        <v>0.5829242906033576</v>
+        <v>0.5829241573031343</v>
       </c>
       <c r="P226" t="n">
-        <v>0.1654313986471958</v>
+        <v>0.1654313659330033</v>
       </c>
     </row>
     <row r="227">
@@ -20849,16 +20849,16 @@
         <v>0.03937384403186139</v>
       </c>
       <c r="M227" t="n">
-        <v>0.2646746647931839</v>
+        <v>0.2646747906437434</v>
       </c>
       <c r="N227" t="n">
-        <v>0.2005920421486398</v>
+        <v>0.2005919287289772</v>
       </c>
       <c r="O227" t="n">
-        <v>1.319416157346821</v>
+        <v>1.319415734040506</v>
       </c>
       <c r="P227" t="n">
-        <v>0.3237101309673047</v>
+        <v>0.3237100504391526</v>
       </c>
     </row>
     <row r="228">
@@ -20907,7 +20907,7 @@
         <v>0.05584850996009649</v>
       </c>
       <c r="M228" t="n">
-        <v>0.2582225538430394</v>
+        <v>0.2582226634413192</v>
       </c>
       <c r="N228" t="n">
         <v>0.1079773148605887</v>
@@ -20971,10 +20971,10 @@
         <v>0.113306811159297</v>
       </c>
       <c r="O229" t="n">
-        <v>0.1211436471279215</v>
+        <v>0.1211437493135707</v>
       </c>
       <c r="P229" t="n">
-        <v>0.03885217518322714</v>
+        <v>0.03885220674498147</v>
       </c>
     </row>
     <row r="230">
@@ -21029,10 +21029,10 @@
         <v>-0.1289590585061453</v>
       </c>
       <c r="O230" t="n">
-        <v>0.3795977946018512</v>
+        <v>0.3795977060378759</v>
       </c>
       <c r="P230" t="n">
-        <v>0.1132281092087082</v>
+        <v>0.1132280853872947</v>
       </c>
     </row>
     <row r="231">
@@ -21084,13 +21084,13 @@
         <v>0.1514405227024649</v>
       </c>
       <c r="N231" t="n">
-        <v>0.1438312587999608</v>
+        <v>0.1438313955385793</v>
       </c>
       <c r="O231" t="n">
-        <v>0.3782177419180597</v>
+        <v>0.3782176426583823</v>
       </c>
       <c r="P231" t="n">
-        <v>0.1128567869764814</v>
+        <v>0.1128567602603816</v>
       </c>
     </row>
     <row r="232">
@@ -21145,10 +21145,10 @@
         <v>0.1393404685962396</v>
       </c>
       <c r="O232" t="n">
-        <v>0.7186789757140459</v>
+        <v>0.7186788400358939</v>
       </c>
       <c r="P232" t="n">
-        <v>0.1978384642966442</v>
+        <v>0.1978384327762119</v>
       </c>
     </row>
     <row r="233">
@@ -21197,16 +21197,16 @@
         <v>0.1186360032726386</v>
       </c>
       <c r="M233" t="n">
-        <v>0.06887303082528895</v>
+        <v>0.06887292290770763</v>
       </c>
       <c r="N233" t="n">
         <v>0.1096696959968002</v>
       </c>
       <c r="O233" t="n">
-        <v>1.695604387979722</v>
+        <v>1.695604216389593</v>
       </c>
       <c r="P233" t="n">
-        <v>0.3917205869153499</v>
+        <v>0.3917205573851117</v>
       </c>
     </row>
     <row r="234">
@@ -21255,16 +21255,16 @@
         <v>0.1122865653536447</v>
       </c>
       <c r="M234" t="n">
-        <v>0.2347797354625405</v>
+        <v>0.2347798342514473</v>
       </c>
       <c r="N234" t="n">
         <v>0.2390100942487934</v>
       </c>
       <c r="O234" t="n">
-        <v>0.3717319581049998</v>
+        <v>0.3717318361870552</v>
       </c>
       <c r="P234" t="n">
-        <v>0.1111083694223256</v>
+        <v>0.1111083365043171</v>
       </c>
     </row>
     <row r="235">
@@ -21319,10 +21319,10 @@
         <v>0.1930068934549094</v>
       </c>
       <c r="O235" t="n">
-        <v>0.6760794964215093</v>
+        <v>0.6760797193085855</v>
       </c>
       <c r="P235" t="n">
-        <v>0.1878589414320808</v>
+        <v>0.1878589940863842</v>
       </c>
     </row>
     <row r="236">
@@ -21377,10 +21377,10 @@
         <v>0.257959063565208</v>
       </c>
       <c r="O236" t="n">
-        <v>0.7600748299985323</v>
+        <v>0.7600745544621803</v>
       </c>
       <c r="P236" t="n">
-        <v>0.2073792582738019</v>
+        <v>0.2073791952694932</v>
       </c>
     </row>
     <row r="237">
@@ -21487,16 +21487,16 @@
         <v>0.138891879393408</v>
       </c>
       <c r="M238" t="n">
-        <v>0.4144127171927097</v>
+        <v>0.4144128391998116</v>
       </c>
       <c r="N238" t="n">
-        <v>0.1654958474727948</v>
+        <v>0.1654959303154979</v>
       </c>
       <c r="O238" t="n">
-        <v>-0.2115543534446488</v>
+        <v>-0.2115542776207127</v>
       </c>
       <c r="P238" t="n">
-        <v>-0.07617313695631922</v>
+        <v>-0.07617310734185478</v>
       </c>
     </row>
     <row r="239">
@@ -21545,7 +21545,7 @@
         <v>0.377137550869542</v>
       </c>
       <c r="M239" t="n">
-        <v>0.1596328126595337</v>
+        <v>0.1596327428068398</v>
       </c>
       <c r="N239" t="n">
         <v>0.1164466524288479</v>
@@ -21606,7 +21606,7 @@
         <v>0.1233382938023548</v>
       </c>
       <c r="N240" t="n">
-        <v>-0.0237947977046814</v>
+        <v>-0.02379486872083791</v>
       </c>
       <c r="O240" t="n">
         <v>0.6952794975186967</v>
@@ -21664,13 +21664,13 @@
         <v>-0.07623434945956153</v>
       </c>
       <c r="N241" t="n">
-        <v>-0.09900503019418749</v>
+        <v>-0.09900513685879386</v>
       </c>
       <c r="O241" t="n">
-        <v>0.1862142548258805</v>
+        <v>0.1862141623833338</v>
       </c>
       <c r="P241" t="n">
-        <v>0.05857356929148128</v>
+        <v>0.05857354179300911</v>
       </c>
     </row>
     <row r="242">
@@ -21725,10 +21725,10 @@
         <v>0.05825827051825416</v>
       </c>
       <c r="O242" t="n">
-        <v>0.04371434166329258</v>
+        <v>0.04371427640731551</v>
       </c>
       <c r="P242" t="n">
-        <v>0.01436413105150636</v>
+        <v>0.01436410991119974</v>
       </c>
     </row>
     <row r="243">
@@ -21780,13 +21780,13 @@
         <v>0.2288650070953318</v>
       </c>
       <c r="N243" t="n">
-        <v>0.1995713735029221</v>
+        <v>0.1995712481205523</v>
       </c>
       <c r="O243" t="n">
-        <v>1.348479117271772</v>
+        <v>1.348479357557395</v>
       </c>
       <c r="P243" t="n">
-        <v>0.3292160222766596</v>
+        <v>0.3292160676097557</v>
       </c>
     </row>
     <row r="244">
@@ -21841,10 +21841,10 @@
         <v>0.05998266445748524</v>
       </c>
       <c r="O244" t="n">
-        <v>0.9512851924684391</v>
+        <v>0.9512848982415538</v>
       </c>
       <c r="P244" t="n">
-        <v>0.2496073844219175</v>
+        <v>0.2496073216140635</v>
       </c>
     </row>
     <row r="245">
@@ -21896,13 +21896,13 @@
         <v>0.1649212457883227</v>
       </c>
       <c r="N245" t="n">
-        <v>0.2770250653829798</v>
+        <v>0.2770251837200974</v>
       </c>
       <c r="O245" t="n">
-        <v>-0.2608311656770254</v>
+        <v>-0.2608312449708466</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.09583460263129429</v>
+        <v>-0.09583463496253297</v>
       </c>
     </row>
     <row r="246">
@@ -21951,16 +21951,16 @@
         <v>0.03585856510780805</v>
       </c>
       <c r="M246" t="n">
-        <v>0.1834102006761043</v>
+        <v>0.183410081217694</v>
       </c>
       <c r="N246" t="n">
-        <v>0.3430720144807993</v>
+        <v>0.3430721683475584</v>
       </c>
       <c r="O246" t="n">
-        <v>0.8417095900912772</v>
+        <v>0.8417097347546194</v>
       </c>
       <c r="P246" t="n">
-        <v>0.2257645295764079</v>
+        <v>0.2257645616703547</v>
       </c>
     </row>
     <row r="247">
@@ -22070,13 +22070,13 @@
         <v>0.1610840117541412</v>
       </c>
       <c r="N248" t="n">
-        <v>0.05645439890713977</v>
+        <v>0.05645451469632601</v>
       </c>
       <c r="O248" t="n">
-        <v>0.8649328407018615</v>
+        <v>0.8649332015237874</v>
       </c>
       <c r="P248" t="n">
-        <v>0.2308951644998922</v>
+        <v>0.2308952438832574</v>
       </c>
     </row>
     <row r="249">
@@ -22186,13 +22186,13 @@
         <v>0.07948206304360395</v>
       </c>
       <c r="N250" t="n">
-        <v>-0.04656885017123857</v>
+        <v>-0.04656870673055447</v>
       </c>
       <c r="O250" t="n">
-        <v>0.04680512337846188</v>
+        <v>0.0468050369224382</v>
       </c>
       <c r="P250" t="n">
-        <v>0.01536443298610957</v>
+        <v>0.01536440503300018</v>
       </c>
     </row>
     <row r="251">
@@ -22299,16 +22299,16 @@
         <v>-0.03293912945533983</v>
       </c>
       <c r="M252" t="n">
-        <v>0.3361261321036393</v>
+        <v>0.3361262328451227</v>
       </c>
       <c r="N252" t="n">
-        <v>0.5480839496004677</v>
+        <v>0.5480840848396218</v>
       </c>
       <c r="O252" t="n">
-        <v>-0.05191091942031367</v>
+        <v>-0.05191081797272623</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.01761200142210051</v>
+        <v>-0.01761196638288642</v>
       </c>
     </row>
     <row r="253">
@@ -22354,19 +22354,19 @@
         <v>0.144892977393223</v>
       </c>
       <c r="L253" t="n">
-        <v>0.1147361735249306</v>
+        <v>0.1147360996182396</v>
       </c>
       <c r="M253" t="n">
-        <v>0.06355198251921501</v>
+        <v>0.06355191524370252</v>
       </c>
       <c r="N253" t="n">
-        <v>0.01482456365367524</v>
+        <v>0.01482462490585745</v>
       </c>
       <c r="O253" t="n">
-        <v>0.5720381655415263</v>
+        <v>0.5720378715764867</v>
       </c>
       <c r="P253" t="n">
-        <v>0.1627536063446364</v>
+        <v>0.1627535338678272</v>
       </c>
     </row>
     <row r="254">
@@ -22412,13 +22412,13 @@
         <v>0.06880744959383267</v>
       </c>
       <c r="L254" t="n">
-        <v>-0.004066564856223365</v>
+        <v>-0.004066638642001963</v>
       </c>
       <c r="M254" t="n">
-        <v>0.2301263056214264</v>
+        <v>0.2301264181885383</v>
       </c>
       <c r="N254" t="n">
-        <v>0.1200890289010637</v>
+        <v>0.1200889355719541</v>
       </c>
       <c r="O254" t="n">
         <v>0.1395556250301466</v>
@@ -22476,13 +22476,13 @@
         <v>0.1513104674627346</v>
       </c>
       <c r="N255" t="n">
-        <v>0.3256882795891123</v>
+        <v>0.3256883731373974</v>
       </c>
       <c r="O255" t="n">
-        <v>0.2858402240058917</v>
+        <v>0.2858404000238735</v>
       </c>
       <c r="P255" t="n">
-        <v>0.08741587553949559</v>
+        <v>0.08741592515808616</v>
       </c>
     </row>
     <row r="256">
@@ -22592,13 +22592,13 @@
         <v>0.1968490108456871</v>
       </c>
       <c r="N257" t="n">
-        <v>0.06043310453713446</v>
+        <v>0.06043299159465354</v>
       </c>
       <c r="O257" t="n">
-        <v>0.1389229864147907</v>
+        <v>0.1389231166953402</v>
       </c>
       <c r="P257" t="n">
-        <v>0.04431484781708561</v>
+        <v>0.04431488763654912</v>
       </c>
     </row>
     <row r="258">
@@ -22647,7 +22647,7 @@
         <v>-0.01585007909684044</v>
       </c>
       <c r="M258" t="n">
-        <v>0.1555856813212364</v>
+        <v>0.1555856089752239</v>
       </c>
       <c r="N258" t="n">
         <v>0.08258392626080746</v>
@@ -22711,10 +22711,10 @@
         <v>0.2045653421969427</v>
       </c>
       <c r="O259" t="n">
-        <v>1.25644666261346</v>
+        <v>1.256446898533778</v>
       </c>
       <c r="P259" t="n">
-        <v>0.3116209878755118</v>
+        <v>0.3116210335872105</v>
       </c>
     </row>
     <row r="260">
@@ -22769,10 +22769,10 @@
         <v>0.08940603373170819</v>
       </c>
       <c r="O260" t="n">
-        <v>1.562262374944858</v>
+        <v>1.56226261121098</v>
       </c>
       <c r="P260" t="n">
-        <v>0.3683836185583167</v>
+        <v>0.3683836606178501</v>
       </c>
     </row>
     <row r="261">
@@ -22821,16 +22821,16 @@
         <v>-0.2002750167318603</v>
       </c>
       <c r="M261" t="n">
-        <v>0.1918068980987235</v>
+        <v>0.1918069865048315</v>
       </c>
       <c r="N261" t="n">
-        <v>0.1132118298563318</v>
+        <v>0.1132117527258496</v>
       </c>
       <c r="O261" t="n">
-        <v>-0.1562598169281731</v>
+        <v>-0.1562596396937816</v>
       </c>
       <c r="P261" t="n">
-        <v>-0.05506287734993254</v>
+        <v>-0.05506281118606371</v>
       </c>
     </row>
     <row r="262">
@@ -22885,10 +22885,10 @@
         <v>0.02425842543823986</v>
       </c>
       <c r="O262" t="n">
-        <v>-0.0007646272820528432</v>
+        <v>-0.0007645642422281496</v>
       </c>
       <c r="P262" t="n">
-        <v>-0.0002549407499470302</v>
+        <v>-0.0002549197259541502</v>
       </c>
     </row>
     <row r="263">
@@ -22943,10 +22943,10 @@
         <v>-0.04816498847383921</v>
       </c>
       <c r="O263" t="n">
-        <v>0.5168985034746836</v>
+        <v>0.5168983940085012</v>
       </c>
       <c r="P263" t="n">
-        <v>0.1489968576604741</v>
+        <v>0.1489968300215556</v>
       </c>
     </row>
     <row r="264">
@@ -22995,16 +22995,16 @@
         <v>0.206899584228315</v>
       </c>
       <c r="M264" t="n">
-        <v>-0.0674174709047064</v>
+        <v>-0.06741740669721596</v>
       </c>
       <c r="N264" t="n">
         <v>-0.2136272711692879</v>
       </c>
       <c r="O264" t="n">
-        <v>-0.1475168286861837</v>
+        <v>-0.1475167750345722</v>
       </c>
       <c r="P264" t="n">
-        <v>-0.05181021675928033</v>
+        <v>-0.05181019686762323</v>
       </c>
     </row>
     <row r="265">
@@ -23053,10 +23053,10 @@
         <v>0.09076428953720717</v>
       </c>
       <c r="M265" t="n">
-        <v>0.1996497395600634</v>
+        <v>0.1996498426336741</v>
       </c>
       <c r="N265" t="n">
-        <v>0.1864398210285125</v>
+        <v>0.1864399218446351</v>
       </c>
       <c r="O265" t="n">
         <v>3.638729197480907</v>
@@ -23108,19 +23108,19 @@
         <v>-0.05763374403603427</v>
       </c>
       <c r="L266" t="n">
-        <v>-0.09914662859893542</v>
+        <v>-0.09914653757371739</v>
       </c>
       <c r="M266" t="n">
         <v>0.1846899627565173</v>
       </c>
       <c r="N266" t="n">
-        <v>0.4343168438557927</v>
+        <v>0.4343169592313214</v>
       </c>
       <c r="O266" t="n">
-        <v>0.5320148917302885</v>
+        <v>0.5320150233586523</v>
       </c>
       <c r="P266" t="n">
-        <v>0.1528009585967172</v>
+        <v>0.1528009916123449</v>
       </c>
     </row>
     <row r="267">
@@ -23172,13 +23172,13 @@
         <v>0.1689202783942931</v>
       </c>
       <c r="N267" t="n">
-        <v>0.4669110625977684</v>
+        <v>0.4669111772686751</v>
       </c>
       <c r="O267" t="n">
-        <v>1.622431249964189</v>
+        <v>1.622430700239761</v>
       </c>
       <c r="P267" t="n">
-        <v>0.3790119739339242</v>
+        <v>0.379011877575933</v>
       </c>
     </row>
     <row r="268">
@@ -23224,13 +23224,13 @@
         <v>0.1149721550900809</v>
       </c>
       <c r="L268" t="n">
-        <v>0.05386122165284379</v>
+        <v>0.05386133124137937</v>
       </c>
       <c r="M268" t="n">
         <v>0.1748763593056946</v>
       </c>
       <c r="N268" t="n">
-        <v>-0.04387987995014153</v>
+        <v>-0.04387997015358225</v>
       </c>
       <c r="O268" t="n">
         <v>-0.04675770223022013</v>
@@ -23404,13 +23404,13 @@
         <v>0.1443284074641018</v>
       </c>
       <c r="N271" t="n">
-        <v>0.09058749874183181</v>
+        <v>0.09058743164439997</v>
       </c>
       <c r="O271" t="n">
-        <v>0.1905651447050036</v>
+        <v>0.1905650647416146</v>
       </c>
       <c r="P271" t="n">
-        <v>0.05986622991666479</v>
+        <v>0.05986620618829841</v>
       </c>
     </row>
     <row r="272">
@@ -23465,10 +23465,10 @@
         <v>-0.00677967337104457</v>
       </c>
       <c r="O272" t="n">
-        <v>1.246054764950052</v>
+        <v>1.246054942939701</v>
       </c>
       <c r="P272" t="n">
-        <v>0.3096043645201656</v>
+        <v>0.309604399113566</v>
       </c>
     </row>
     <row r="273">
@@ -23520,13 +23520,13 @@
         <v>0.1203267727015391</v>
       </c>
       <c r="N273" t="n">
-        <v>0.2319800160640488</v>
+        <v>0.2319799187556326</v>
       </c>
       <c r="O273" t="n">
-        <v>0.03830180297933894</v>
+        <v>0.03830173386147639</v>
       </c>
       <c r="P273" t="n">
-        <v>0.01260764689284732</v>
+        <v>0.01260762442369701</v>
       </c>
     </row>
     <row r="274">
@@ -23578,13 +23578,13 @@
         <v>0.1194517456727489</v>
       </c>
       <c r="N274" t="n">
-        <v>0.147053166538601</v>
+        <v>0.1470530667550034</v>
       </c>
       <c r="O274" t="n">
-        <v>1.02338086938588</v>
+        <v>1.023380714140977</v>
       </c>
       <c r="P274" t="n">
-        <v>0.2648117160308847</v>
+        <v>0.2648116836831147</v>
       </c>
     </row>
     <row r="275">
@@ -23813,10 +23813,10 @@
         <v>0.05125117727227391</v>
       </c>
       <c r="O278" t="n">
-        <v>0.6552085268741512</v>
+        <v>0.6552083824908794</v>
       </c>
       <c r="P278" t="n">
-        <v>0.1829078258141232</v>
+        <v>0.182907791419241</v>
       </c>
     </row>
     <row r="279">
@@ -23920,19 +23920,19 @@
         <v>0.1012344717073557</v>
       </c>
       <c r="L280" t="n">
-        <v>-0.05030251709222444</v>
+        <v>-0.05030243464380968</v>
       </c>
       <c r="M280" t="n">
         <v>0.1233223358820625</v>
       </c>
       <c r="N280" t="n">
-        <v>0.08191087326822122</v>
+        <v>0.08191098027091526</v>
       </c>
       <c r="O280" t="n">
-        <v>0.3002016873561912</v>
+        <v>0.3002019964307427</v>
       </c>
       <c r="P280" t="n">
-        <v>0.09144932120538352</v>
+        <v>0.0914494076891923</v>
       </c>
     </row>
     <row r="281">
@@ -23981,16 +23981,16 @@
         <v>0.02690002819140358</v>
       </c>
       <c r="M281" t="n">
-        <v>0.3485131244117188</v>
+        <v>0.3485130094087463</v>
       </c>
       <c r="N281" t="n">
-        <v>0.2735796901563909</v>
+        <v>0.2735797927336361</v>
       </c>
       <c r="O281" t="n">
-        <v>-0.3350535076568909</v>
+        <v>-0.3350536195058804</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.1271715377652405</v>
+        <v>-0.1271715867040089</v>
       </c>
     </row>
     <row r="282">
@@ -24036,7 +24036,7 @@
         <v>0.1343054996759114</v>
       </c>
       <c r="L282" t="n">
-        <v>-0.0559644242478724</v>
+        <v>-0.05596434867864497</v>
       </c>
       <c r="M282" t="n">
         <v>0.0733736025813676</v>
@@ -24045,10 +24045,10 @@
         <v>0.04694267020027043</v>
       </c>
       <c r="O282" t="n">
-        <v>0.03319456016176181</v>
+        <v>0.03319465067924821</v>
       </c>
       <c r="P282" t="n">
-        <v>0.01094463142939306</v>
+        <v>0.01094466095212066</v>
       </c>
     </row>
     <row r="283">
@@ -24097,16 +24097,16 @@
         <v>0.009306930115020595</v>
       </c>
       <c r="M283" t="n">
-        <v>0.0409721455234493</v>
+        <v>0.04097222799938982</v>
       </c>
       <c r="N283" t="n">
-        <v>-0.0561449306138142</v>
+        <v>-0.05614486280913245</v>
       </c>
       <c r="O283" t="n">
-        <v>-0.1055312142286542</v>
+        <v>-0.1055310924392632</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.03649258069610506</v>
+        <v>-0.03649253696624799</v>
       </c>
     </row>
     <row r="284">
@@ -24155,7 +24155,7 @@
         <v>0.07473011531912488</v>
       </c>
       <c r="M284" t="n">
-        <v>0.1227149826697216</v>
+        <v>0.122714910827747</v>
       </c>
       <c r="N284" t="n">
         <v>0.1610891327410391</v>
@@ -24216,7 +24216,7 @@
         <v>-0.03767678187936685</v>
       </c>
       <c r="N285" t="n">
-        <v>-0.1689673041407034</v>
+        <v>-0.1689673779565711</v>
       </c>
       <c r="O285" t="n">
         <v>0.5628586663067405</v>
@@ -24271,16 +24271,16 @@
         <v>0.07373976412121452</v>
       </c>
       <c r="M286" t="n">
-        <v>0.1079778841910739</v>
+        <v>0.1079777969441387</v>
       </c>
       <c r="N286" t="n">
-        <v>0.2433751465456579</v>
+        <v>0.2433750366723104</v>
       </c>
       <c r="O286" t="n">
-        <v>0.4871531426734192</v>
+        <v>0.4871534570350298</v>
       </c>
       <c r="P286" t="n">
-        <v>0.1414368725672923</v>
+        <v>0.1414369529947654</v>
       </c>
     </row>
     <row r="287">
@@ -24387,16 +24387,16 @@
         <v>0.08684660741123729</v>
       </c>
       <c r="M288" t="n">
-        <v>0.04422676342930254</v>
+        <v>0.04422683834636554</v>
       </c>
       <c r="N288" t="n">
-        <v>-0.03101584925195588</v>
+        <v>-0.03101578474234112</v>
       </c>
       <c r="O288" t="n">
-        <v>0.8325871459691561</v>
+        <v>0.8325872613384875</v>
       </c>
       <c r="P288" t="n">
-        <v>0.2237373403070528</v>
+        <v>0.2237373659869148</v>
       </c>
     </row>
     <row r="289">
@@ -24439,22 +24439,22 @@
         <v>-0.03817998198351191</v>
       </c>
       <c r="K289" t="n">
-        <v>0.02623983799992202</v>
+        <v>0.02623990194259296</v>
       </c>
       <c r="L289" t="n">
-        <v>-0.02307929196014902</v>
+        <v>-0.02307917607129084</v>
       </c>
       <c r="M289" t="n">
-        <v>0.1525312289942442</v>
+        <v>0.1525311483453571</v>
       </c>
       <c r="N289" t="n">
-        <v>0.1385365452391873</v>
+        <v>0.1385363091325906</v>
       </c>
       <c r="O289" t="n">
-        <v>0.3259137050811278</v>
+        <v>0.3259132781248768</v>
       </c>
       <c r="P289" t="n">
-        <v>0.09859702819670302</v>
+        <v>0.09859691027728479</v>
       </c>
     </row>
     <row r="290">
@@ -24509,10 +24509,10 @@
         <v>0.146583332337838</v>
       </c>
       <c r="O290" t="n">
-        <v>0.8742440276055947</v>
+        <v>0.8742443543808289</v>
       </c>
       <c r="P290" t="n">
-        <v>0.2329402914881049</v>
+        <v>0.2329403631426537</v>
       </c>
     </row>
     <row r="291">
@@ -24619,10 +24619,10 @@
         <v>-0.174677249113898</v>
       </c>
       <c r="M292" t="n">
-        <v>0.2035741729863194</v>
+        <v>0.2035740376131017</v>
       </c>
       <c r="N292" t="n">
-        <v>0.2788105039944013</v>
+        <v>0.2788105804077974</v>
       </c>
       <c r="O292" t="n">
         <v>0.3953820257253364</v>
@@ -24677,10 +24677,10 @@
         <v>-0.01147606571281989</v>
       </c>
       <c r="M293" t="n">
-        <v>0.01275974329240936</v>
+        <v>0.01275983558319282</v>
       </c>
       <c r="N293" t="n">
-        <v>0.08042141664994551</v>
+        <v>0.08042131161549682</v>
       </c>
       <c r="O293" t="n">
         <v>1.211786141104521</v>
@@ -24732,19 +24732,19 @@
         <v>-0.08748709331579207</v>
       </c>
       <c r="L294" t="n">
-        <v>-0.02501151680930902</v>
+        <v>-0.02501161884252368</v>
       </c>
       <c r="M294" t="n">
         <v>0.2248058000218758</v>
       </c>
       <c r="N294" t="n">
-        <v>0.2904230123224303</v>
+        <v>0.2904229229555049</v>
       </c>
       <c r="O294" t="n">
-        <v>1.307308803281736</v>
+        <v>1.307309231845486</v>
       </c>
       <c r="P294" t="n">
-        <v>0.3214028556827377</v>
+        <v>0.3214029374959924</v>
       </c>
     </row>
     <row r="295">
@@ -24799,10 +24799,10 @@
         <v>-0.04119509745555472</v>
       </c>
       <c r="O295" t="n">
-        <v>0.3764681616881127</v>
+        <v>0.3764682916220015</v>
       </c>
       <c r="P295" t="n">
-        <v>0.1123856817601694</v>
+        <v>0.1123857167619702</v>
       </c>
     </row>
     <row r="296">
@@ -24851,16 +24851,16 @@
         <v>-0.03052498958418048</v>
       </c>
       <c r="M296" t="n">
-        <v>0.1138566037835174</v>
+        <v>0.1138565371524434</v>
       </c>
       <c r="N296" t="n">
         <v>0.1718340507059386</v>
       </c>
       <c r="O296" t="n">
-        <v>0.2506466793405429</v>
+        <v>0.250646763342145</v>
       </c>
       <c r="P296" t="n">
-        <v>0.07740307677786396</v>
+        <v>0.07740310089967339</v>
       </c>
     </row>
     <row r="297">
@@ -24909,16 +24909,16 @@
         <v>0.05246631316654216</v>
       </c>
       <c r="M297" t="n">
-        <v>-0.08216737062523494</v>
+        <v>-0.08216728299051212</v>
       </c>
       <c r="N297" t="n">
-        <v>-0.2343943299040916</v>
+        <v>-0.2343942689280109</v>
       </c>
       <c r="O297" t="n">
-        <v>0.02583349598500262</v>
+        <v>0.02583371492899333</v>
       </c>
       <c r="P297" t="n">
-        <v>0.008538059399567866</v>
+        <v>0.008538131150436001</v>
       </c>
     </row>
     <row r="298">
@@ -24970,13 +24970,13 @@
         <v>0.03505885201531944</v>
       </c>
       <c r="N298" t="n">
-        <v>0.143173510062085</v>
+        <v>0.1431733937344646</v>
       </c>
       <c r="O298" t="n">
-        <v>0.7710416186498366</v>
+        <v>0.7710414790496216</v>
       </c>
       <c r="P298" t="n">
-        <v>0.2098817402920199</v>
+        <v>0.2098817085028637</v>
       </c>
     </row>
     <row r="299">
@@ -25028,13 +25028,13 @@
         <v>0.08781848616971555</v>
       </c>
       <c r="N299" t="n">
-        <v>-0.1093260365331712</v>
+        <v>-0.1093260910494684</v>
       </c>
       <c r="O299" t="n">
-        <v>-0.03025696075035267</v>
+        <v>-0.03025702537559383</v>
       </c>
       <c r="P299" t="n">
-        <v>-0.01018911912687137</v>
+        <v>-0.01018914111440328</v>
       </c>
     </row>
     <row r="300">
@@ -25080,19 +25080,19 @@
         <v>-0.05775451601483095</v>
       </c>
       <c r="L300" t="n">
-        <v>-0.1661901761038329</v>
+        <v>-0.1661902576324364</v>
       </c>
       <c r="M300" t="n">
-        <v>0.2193339103840313</v>
+        <v>0.2193339975589137</v>
       </c>
       <c r="N300" t="n">
-        <v>0.3384388633240059</v>
+        <v>0.3384386532496504</v>
       </c>
       <c r="O300" t="n">
-        <v>3.241757807200356</v>
+        <v>3.241757543459292</v>
       </c>
       <c r="P300" t="n">
-        <v>0.6187581051572579</v>
+        <v>0.6187580716072525</v>
       </c>
     </row>
     <row r="301">
@@ -25138,7 +25138,7 @@
         <v>0.12632104212041</v>
       </c>
       <c r="L301" t="n">
-        <v>-0.02371865108524829</v>
+        <v>-0.0237185399470925</v>
       </c>
       <c r="M301" t="n">
         <v>0.04755294767909679</v>
@@ -25202,13 +25202,13 @@
         <v>0.1785316926244001</v>
       </c>
       <c r="N302" t="n">
-        <v>0.2997781632377692</v>
+        <v>0.2997782786193639</v>
       </c>
       <c r="O302" t="n">
-        <v>0.08141140147072012</v>
+        <v>0.08141148134003262</v>
       </c>
       <c r="P302" t="n">
-        <v>0.02643231096556953</v>
+        <v>0.02643233623515107</v>
       </c>
     </row>
     <row r="303">
@@ -25437,10 +25437,10 @@
         <v>0.01115726228793901</v>
       </c>
       <c r="O306" t="n">
-        <v>0.6775021602821745</v>
+        <v>0.6775024826913123</v>
       </c>
       <c r="P306" t="n">
-        <v>0.1881949330677435</v>
+        <v>0.1881950091898272</v>
       </c>
     </row>
     <row r="307">
@@ -25489,16 +25489,16 @@
         <v>0.008666980217306053</v>
       </c>
       <c r="M307" t="n">
-        <v>0.1328040383959266</v>
+        <v>0.1328039032350035</v>
       </c>
       <c r="N307" t="n">
         <v>0.08152109650760564</v>
       </c>
       <c r="O307" t="n">
-        <v>0.2825375932028831</v>
+        <v>0.2825375065761759</v>
       </c>
       <c r="P307" t="n">
-        <v>0.08648408214157133</v>
+        <v>0.08648405768002965</v>
       </c>
     </row>
     <row r="308">
@@ -25553,10 +25553,10 @@
         <v>-0.03872055597949964</v>
       </c>
       <c r="O308" t="n">
-        <v>0.09153161620823291</v>
+        <v>0.09153171867957655</v>
       </c>
       <c r="P308" t="n">
-        <v>0.0296242750017961</v>
+        <v>0.02962430722165355</v>
       </c>
     </row>
     <row r="309">
@@ -25611,10 +25611,10 @@
         <v>-0.02424407606487355</v>
       </c>
       <c r="O309" t="n">
-        <v>-0.119448242119808</v>
+        <v>-0.1194481837112893</v>
       </c>
       <c r="P309" t="n">
-        <v>-0.0415157898507853</v>
+        <v>-0.04151576865814821</v>
       </c>
     </row>
     <row r="310">
@@ -25669,10 +25669,10 @@
         <v>0.1136551347394772</v>
       </c>
       <c r="O310" t="n">
-        <v>0.3271265244020738</v>
+        <v>0.3271266715321006</v>
       </c>
       <c r="P310" t="n">
-        <v>0.09893189002374547</v>
+        <v>0.09893193063425976</v>
       </c>
     </row>
     <row r="311">
@@ -25727,10 +25727,10 @@
         <v>0.03998781029722709</v>
       </c>
       <c r="O311" t="n">
-        <v>-0.1189137589873697</v>
+        <v>-0.1189138632160912</v>
       </c>
       <c r="P311" t="n">
-        <v>-0.04132190004567415</v>
+        <v>-0.0413219378481775</v>
       </c>
     </row>
     <row r="312">
@@ -25834,19 +25834,19 @@
         <v>0.136469627925085</v>
       </c>
       <c r="L313" t="n">
-        <v>-0.01203771749321592</v>
+        <v>-0.0120378024904273</v>
       </c>
       <c r="M313" t="n">
-        <v>0.03005846288283709</v>
+        <v>0.03005837048800175</v>
       </c>
       <c r="N313" t="n">
         <v>-0.03603729518025611</v>
       </c>
       <c r="O313" t="n">
-        <v>0.360012534780344</v>
+        <v>0.3600123737121621</v>
       </c>
       <c r="P313" t="n">
-        <v>0.1079350551835447</v>
+        <v>0.1079350114454449</v>
       </c>
     </row>
     <row r="314">
@@ -25895,16 +25895,16 @@
         <v>0.008156941308097965</v>
       </c>
       <c r="M314" t="n">
-        <v>0.09018425987046608</v>
+        <v>0.09018414848922074</v>
       </c>
       <c r="N314" t="n">
-        <v>0.1758365430187099</v>
+        <v>0.1758364134482029</v>
       </c>
       <c r="O314" t="n">
-        <v>0.6172725758466999</v>
+        <v>0.6172726984067081</v>
       </c>
       <c r="P314" t="n">
-        <v>0.1738008168956713</v>
+        <v>0.1738008465466272</v>
       </c>
     </row>
     <row r="315">
@@ -26011,16 +26011,16 @@
         <v>0.01357861917568304</v>
       </c>
       <c r="M316" t="n">
-        <v>0.02885545199767403</v>
+        <v>0.02885559776155144</v>
       </c>
       <c r="N316" t="n">
-        <v>0.1611599313029839</v>
+        <v>0.1611598384715252</v>
       </c>
       <c r="O316" t="n">
-        <v>0.8008864513501979</v>
+        <v>0.8008863397014729</v>
       </c>
       <c r="P316" t="n">
-        <v>0.2166400543496694</v>
+        <v>0.2166400292071784</v>
       </c>
     </row>
     <row r="317">
@@ -26072,7 +26072,7 @@
         <v>-0.04585848467128795</v>
       </c>
       <c r="N317" t="n">
-        <v>-0.07329445592905948</v>
+        <v>-0.07329452226494426</v>
       </c>
     </row>
     <row r="318">
@@ -26124,13 +26124,13 @@
         <v>0.09593564656347264</v>
       </c>
       <c r="N318" t="n">
-        <v>0.2352282755097301</v>
+        <v>0.2352283798183912</v>
       </c>
       <c r="O318" t="n">
-        <v>0.414497862486451</v>
+        <v>0.4144981360514655</v>
       </c>
       <c r="P318" t="n">
-        <v>0.1225372596528418</v>
+        <v>0.1225373320193708</v>
       </c>
     </row>
     <row r="319">
@@ -26237,16 +26237,16 @@
         <v>-0.0382080773234299</v>
       </c>
       <c r="M320" t="n">
-        <v>0.1999901908588124</v>
+        <v>0.1999901020890362</v>
       </c>
       <c r="N320" t="n">
         <v>0.2154001814243602</v>
       </c>
       <c r="O320" t="n">
-        <v>1.064191028518438</v>
+        <v>1.064191159853163</v>
       </c>
       <c r="P320" t="n">
-        <v>0.2732586307822282</v>
+        <v>0.2732586577860385</v>
       </c>
     </row>
     <row r="321">
@@ -26292,19 +26292,19 @@
         <v>0.1472296306517573</v>
       </c>
       <c r="L321" t="n">
-        <v>-0.05632356954739237</v>
+        <v>-0.05632347656893122</v>
       </c>
       <c r="M321" t="n">
         <v>0.1124898656104445</v>
       </c>
       <c r="N321" t="n">
-        <v>-0.1382221844718811</v>
+        <v>-0.138222262012038</v>
       </c>
       <c r="O321" t="n">
-        <v>2.012539879099059</v>
+        <v>2.012539642211812</v>
       </c>
       <c r="P321" t="n">
-        <v>0.444256291920915</v>
+        <v>0.4442562540651611</v>
       </c>
     </row>
     <row r="322">
@@ -26359,10 +26359,10 @@
         <v>0.075185147057933</v>
       </c>
       <c r="O322" t="n">
-        <v>1.197171426777968</v>
+        <v>1.197172084579193</v>
       </c>
       <c r="P322" t="n">
-        <v>0.3000338111083793</v>
+        <v>0.3000339408454493</v>
       </c>
     </row>
     <row r="323">
@@ -26472,13 +26472,13 @@
         <v>-0.1134801473508119</v>
       </c>
       <c r="N324" t="n">
-        <v>0.02241841511692177</v>
+        <v>0.02241850262303946</v>
       </c>
       <c r="O324" t="n">
-        <v>0.223794714691937</v>
+        <v>0.2237945893206297</v>
       </c>
       <c r="P324" t="n">
-        <v>0.06963644290978155</v>
+        <v>0.06963640638357838</v>
       </c>
     </row>
     <row r="325">
@@ -26591,10 +26591,10 @@
         <v>0.09245448164912418</v>
       </c>
       <c r="O326" t="n">
-        <v>1.313387716395986</v>
+        <v>1.313387895773086</v>
       </c>
       <c r="P326" t="n">
-        <v>0.3225623087858001</v>
+        <v>0.3225623429690576</v>
       </c>
     </row>
     <row r="327">
@@ -26698,19 +26698,19 @@
         <v>0.04139833598797971</v>
       </c>
       <c r="L328" t="n">
-        <v>0.02023592220296022</v>
+        <v>0.02023584093716346</v>
       </c>
       <c r="M328" t="n">
-        <v>0.1332269030923281</v>
+        <v>0.1332268028294139</v>
       </c>
       <c r="N328" t="n">
         <v>-0.04549681970287811</v>
       </c>
       <c r="O328" t="n">
-        <v>-0.1798158863351699</v>
+        <v>-0.1798157287734712</v>
       </c>
       <c r="P328" t="n">
-        <v>-0.06393979066025124</v>
+        <v>-0.06393973071955217</v>
       </c>
     </row>
     <row r="329">
@@ -26814,19 +26814,19 @@
         <v>-0.005267162286199611</v>
       </c>
       <c r="L330" t="n">
-        <v>-0.01916494331365237</v>
+        <v>-0.01916501185191621</v>
       </c>
       <c r="M330" t="n">
         <v>0.1100456023008665</v>
       </c>
       <c r="N330" t="n">
-        <v>0.1069721620140687</v>
+        <v>0.106972249314141</v>
       </c>
       <c r="O330" t="n">
-        <v>0.3195852911905872</v>
+        <v>0.3195854152461213</v>
       </c>
       <c r="P330" t="n">
-        <v>0.0968464197873935</v>
+        <v>0.09684645415926885</v>
       </c>
     </row>
     <row r="331">
@@ -26878,13 +26878,13 @@
         <v>0.1127220651361927</v>
       </c>
       <c r="N331" t="n">
-        <v>0.1104307126754607</v>
+        <v>0.1104305900546014</v>
       </c>
       <c r="O331" t="n">
-        <v>0.4144649997823271</v>
+        <v>0.4144651987424062</v>
       </c>
       <c r="P331" t="n">
-        <v>0.1225285663686979</v>
+        <v>0.1225286190006971</v>
       </c>
     </row>
     <row r="332">
@@ -26939,10 +26939,10 @@
         <v>-0.1063894759512031</v>
       </c>
       <c r="O332" t="n">
-        <v>-0.04981897428186344</v>
+        <v>-0.04981908351357922</v>
       </c>
       <c r="P332" t="n">
-        <v>-0.01688999045912942</v>
+        <v>-0.01689002813152873</v>
       </c>
     </row>
     <row r="333">
@@ -26997,10 +26997,10 @@
         <v>0.02359832697618924</v>
       </c>
       <c r="O333" t="n">
-        <v>0.1090133108827109</v>
+        <v>0.1090131879658647</v>
       </c>
       <c r="P333" t="n">
-        <v>0.03509192268831329</v>
+        <v>0.03509188444704114</v>
       </c>
     </row>
     <row r="334">
@@ -27049,16 +27049,16 @@
         <v>0.04384343333875784</v>
       </c>
       <c r="M334" t="n">
-        <v>0.05700401306197356</v>
+        <v>0.05700408643087274</v>
       </c>
       <c r="N334" t="n">
         <v>0.1045716432774879</v>
       </c>
       <c r="O334" t="n">
-        <v>0.6676572113183825</v>
+        <v>0.6676570286883383</v>
       </c>
       <c r="P334" t="n">
-        <v>0.1858659390887052</v>
+        <v>0.1858658957994819</v>
       </c>
     </row>
     <row r="335">
@@ -27104,19 +27104,19 @@
         <v>-0.03783597094804314</v>
       </c>
       <c r="L335" t="n">
-        <v>-0.03337918168222465</v>
+        <v>-0.03337910304384029</v>
       </c>
       <c r="M335" t="n">
         <v>0.002487133400308261</v>
       </c>
       <c r="N335" t="n">
-        <v>0.2753098791009432</v>
+        <v>0.2753097422166371</v>
       </c>
       <c r="O335" t="n">
-        <v>2.394392201370464</v>
+        <v>2.394392443800452</v>
       </c>
       <c r="P335" t="n">
-        <v>0.5028674337777486</v>
+        <v>0.5028674695563804</v>
       </c>
     </row>
     <row r="336">
@@ -27226,13 +27226,13 @@
         <v>0.121883749242397</v>
       </c>
       <c r="N337" t="n">
-        <v>0.1274897833419395</v>
+        <v>0.1274898826430633</v>
       </c>
       <c r="O337" t="n">
-        <v>0.3979838232358508</v>
+        <v>0.3979839758986543</v>
       </c>
       <c r="P337" t="n">
-        <v>0.1181516663096873</v>
+        <v>0.1181517070111981</v>
       </c>
     </row>
     <row r="338">
@@ -27461,10 +27461,10 @@
         <v>0.2495247889692735</v>
       </c>
       <c r="O341" t="n">
-        <v>0.8224404139658961</v>
+        <v>0.8224406858554618</v>
       </c>
       <c r="P341" t="n">
-        <v>0.2214746152748355</v>
+        <v>0.2214746760186936</v>
       </c>
     </row>
     <row r="342">
@@ -27513,16 +27513,16 @@
         <v>0.01496711622557023</v>
       </c>
       <c r="M342" t="n">
-        <v>0.05086148574480021</v>
+        <v>0.05086156355433413</v>
       </c>
       <c r="N342" t="n">
         <v>0.03509693825939908</v>
       </c>
       <c r="O342" t="n">
-        <v>0.1346564685321674</v>
+        <v>0.134656649958651</v>
       </c>
       <c r="P342" t="n">
-        <v>0.0430091805843289</v>
+        <v>0.04300923617515684</v>
       </c>
     </row>
     <row r="343">
@@ -27574,13 +27574,13 @@
         <v>0.01826709970588647</v>
       </c>
       <c r="N343" t="n">
-        <v>0.06036134797579473</v>
+        <v>0.06036147210014975</v>
       </c>
       <c r="O343" t="n">
-        <v>1.035273804897728</v>
+        <v>1.035273347604505</v>
       </c>
       <c r="P343" t="n">
-        <v>0.267284960781377</v>
+        <v>0.2672848658685343</v>
       </c>
     </row>
     <row r="344">
@@ -27684,19 +27684,19 @@
         <v>0.08494858542638495</v>
       </c>
       <c r="L345" t="n">
-        <v>0.02092538136041799</v>
+        <v>0.02092531081365978</v>
       </c>
       <c r="M345" t="n">
         <v>0.003919410223245601</v>
       </c>
       <c r="N345" t="n">
-        <v>-0.06121523353504055</v>
+        <v>-0.06121529318650754</v>
       </c>
       <c r="O345" t="n">
-        <v>-0.5545712233885716</v>
+        <v>-0.5545711696723231</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.2362941975164593</v>
+        <v>-0.2362941668168943</v>
       </c>
     </row>
     <row r="346">
@@ -27806,7 +27806,7 @@
         <v>0.4422321457042218</v>
       </c>
       <c r="N347" t="n">
-        <v>0.1002936959028193</v>
+        <v>0.1002935702361993</v>
       </c>
       <c r="O347" t="n">
         <v>-0.001224599309695873</v>
@@ -27861,10 +27861,10 @@
         <v>0.01606317630681486</v>
       </c>
       <c r="M348" t="n">
-        <v>0.04764887011103935</v>
+        <v>0.04764897363163967</v>
       </c>
       <c r="N348" t="n">
-        <v>-0.08536351498622796</v>
+        <v>-0.08536359388899739</v>
       </c>
       <c r="O348" t="n">
         <v>0.4506627677351376</v>
@@ -27983,10 +27983,10 @@
         <v>0.111205238429235</v>
       </c>
       <c r="O350" t="n">
-        <v>0.4558881306754325</v>
+        <v>0.455887957237624</v>
       </c>
       <c r="P350" t="n">
-        <v>0.1333811929830988</v>
+        <v>0.1333811479770861</v>
       </c>
     </row>
     <row r="351">
@@ -28032,7 +28032,7 @@
         <v>0.08961693937245019</v>
       </c>
       <c r="L351" t="n">
-        <v>-0.09747801849482751</v>
+        <v>-0.0974780758240873</v>
       </c>
       <c r="M351" t="n">
         <v>0.1243659112494953</v>
@@ -28041,10 +28041,10 @@
         <v>-0.1086007058691409</v>
       </c>
       <c r="O351" t="n">
-        <v>-0.290136841536228</v>
+        <v>-0.2901369124678698</v>
       </c>
       <c r="P351" t="n">
-        <v>-0.1079451768499093</v>
+        <v>-0.107945206562169</v>
       </c>
     </row>
     <row r="352">
@@ -28154,7 +28154,7 @@
         <v>-0.1155375025063959</v>
       </c>
       <c r="N353" t="n">
-        <v>-0.1631462784621276</v>
+        <v>-0.1631463304145692</v>
       </c>
       <c r="O353" t="n">
         <v>-0.001057255964655446</v>
@@ -28212,13 +28212,13 @@
         <v>0.20678758250541</v>
       </c>
       <c r="N354" t="n">
-        <v>0.03329112248599775</v>
+        <v>0.03329118936475561</v>
       </c>
       <c r="O354" t="n">
-        <v>0.326736840040758</v>
+        <v>0.3267369502993362</v>
       </c>
       <c r="P354" t="n">
-        <v>0.09882431964894267</v>
+        <v>0.0988243500882382</v>
       </c>
     </row>
     <row r="355">
@@ -28270,7 +28270,7 @@
         <v>0.02925690229914002</v>
       </c>
       <c r="N355" t="n">
-        <v>0.08431480024110205</v>
+        <v>0.08431468543759091</v>
       </c>
       <c r="O355" t="n">
         <v>0.2760963974890285</v>
@@ -28328,13 +28328,13 @@
         <v>-0.1044392944945477</v>
       </c>
       <c r="N356" t="n">
-        <v>-0.2188030085505087</v>
+        <v>-0.2188029219920142</v>
       </c>
       <c r="O356" t="n">
-        <v>0.8447373660966242</v>
+        <v>0.8447372454271025</v>
       </c>
       <c r="P356" t="n">
-        <v>0.2264358819778447</v>
+        <v>0.2264358552362902</v>
       </c>
     </row>
     <row r="357">
@@ -28383,16 +28383,16 @@
         <v>0.05512836472126836</v>
       </c>
       <c r="M357" t="n">
-        <v>-0.1767299994120648</v>
+        <v>-0.1767299434549007</v>
       </c>
       <c r="N357" t="n">
-        <v>-0.2651760072616289</v>
+        <v>-0.2651759626818645</v>
       </c>
       <c r="O357" t="n">
-        <v>0.06016277981171814</v>
+        <v>0.06016305819141721</v>
       </c>
       <c r="P357" t="n">
-        <v>0.01966501232413043</v>
+        <v>0.01966510157269363</v>
       </c>
     </row>
     <row r="358">
@@ -28441,16 +28441,16 @@
         <v>0.08292005083571263</v>
       </c>
       <c r="M358" t="n">
-        <v>-0.06958436406161028</v>
+        <v>-0.06958442507514428</v>
       </c>
       <c r="N358" t="n">
         <v>-0.1634629183520871</v>
       </c>
       <c r="O358" t="n">
-        <v>0.2048907220325962</v>
+        <v>0.2048909266759282</v>
       </c>
       <c r="P358" t="n">
-        <v>0.06410027004157492</v>
+        <v>0.06410033028521611</v>
       </c>
     </row>
     <row r="359">
@@ -28505,10 +28505,10 @@
         <v>-0.1434211968115298</v>
       </c>
       <c r="O359" t="n">
-        <v>-0.3322426551314074</v>
+        <v>-0.3322426123719006</v>
       </c>
       <c r="P359" t="n">
-        <v>-0.1259433972408008</v>
+        <v>-0.1259433785842091</v>
       </c>
     </row>
     <row r="360">
@@ -28554,19 +28554,19 @@
         <v>0.0238303481983837</v>
       </c>
       <c r="L360" t="n">
-        <v>-0.01806370078417241</v>
+        <v>-0.01806363455039828</v>
       </c>
       <c r="M360" t="n">
         <v>0.0398452365841504</v>
       </c>
       <c r="N360" t="n">
-        <v>0.007365404121520758</v>
+        <v>0.007365473830213132</v>
       </c>
       <c r="O360" t="n">
-        <v>0.4689053947000787</v>
+        <v>0.4689055429179387</v>
       </c>
       <c r="P360" t="n">
-        <v>0.1367490727123861</v>
+        <v>0.1367491109464141</v>
       </c>
     </row>
     <row r="361">
@@ -28673,16 +28673,16 @@
         <v>-0.1045718469608249</v>
       </c>
       <c r="M362" t="n">
-        <v>0.09444695328249675</v>
+        <v>0.09444686282821646</v>
       </c>
       <c r="N362" t="n">
-        <v>0.1310935315891142</v>
+        <v>0.1310936282023882</v>
       </c>
       <c r="O362" t="n">
-        <v>0.4656563880084548</v>
+        <v>0.465656712448272</v>
       </c>
       <c r="P362" t="n">
-        <v>0.1359103457420143</v>
+        <v>0.1359104295575937</v>
       </c>
     </row>
     <row r="363">
@@ -28731,16 +28731,16 @@
         <v>-0.1484952289392818</v>
       </c>
       <c r="M363" t="n">
-        <v>0.01697952595720809</v>
+        <v>0.01697945075773677</v>
       </c>
       <c r="N363" t="n">
-        <v>-0.08015367216947167</v>
+        <v>-0.08015354912814332</v>
       </c>
       <c r="O363" t="n">
-        <v>-0.2383240274822587</v>
+        <v>-0.2383241118469765</v>
       </c>
       <c r="P363" t="n">
-        <v>-0.08674914968128433</v>
+        <v>-0.08674918339910132</v>
       </c>
     </row>
     <row r="364">
@@ -28853,10 +28853,10 @@
         <v>0.09077605341198436</v>
       </c>
       <c r="O365" t="n">
-        <v>0.4567754297810565</v>
+        <v>0.4567755813401848</v>
       </c>
       <c r="P365" t="n">
-        <v>0.1336113947107243</v>
+        <v>0.1336114340233836</v>
       </c>
     </row>
     <row r="366">
@@ -28902,19 +28902,19 @@
         <v>0.1082856953141924</v>
       </c>
       <c r="L366" t="n">
-        <v>-0.1547221403482766</v>
+        <v>-0.1547220709685881</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.01047386592452326</v>
+        <v>-0.01047377084480161</v>
       </c>
       <c r="N366" t="n">
-        <v>-0.01295198208916482</v>
+        <v>-0.01295188748507203</v>
       </c>
       <c r="O366" t="n">
-        <v>0.1436177484105294</v>
+        <v>0.1436176214130658</v>
       </c>
       <c r="P366" t="n">
-        <v>0.04574780640100107</v>
+        <v>0.04574776769129407</v>
       </c>
     </row>
     <row r="367">
@@ -28960,7 +28960,7 @@
         <v>0.0180572658322844</v>
       </c>
       <c r="L367" t="n">
-        <v>0.008165855283532641</v>
+        <v>0.008165972793844567</v>
       </c>
       <c r="M367" t="n">
         <v>0.01198916107111647</v>
@@ -28969,10 +28969,10 @@
         <v>-0.02664903343378444</v>
       </c>
       <c r="O367" t="n">
-        <v>0.03756161819931125</v>
+        <v>0.03756174266217993</v>
       </c>
       <c r="P367" t="n">
-        <v>0.01236696705004792</v>
+        <v>0.01236700753024356</v>
       </c>
     </row>
     <row r="368">
@@ -29085,10 +29085,10 @@
         <v>-0.2266799385363293</v>
       </c>
       <c r="O369" t="n">
-        <v>-0.007491344348261375</v>
+        <v>-0.007491187685276013</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.00250337644692411</v>
+        <v>-0.002503323963489068</v>
       </c>
     </row>
     <row r="370">
@@ -29137,16 +29137,16 @@
         <v>-0.05763872318643992</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.06753036328168394</v>
+        <v>-0.06753030720360642</v>
       </c>
       <c r="N370" t="n">
         <v>-0.1634251460820866</v>
       </c>
       <c r="O370" t="n">
-        <v>0.5137013188540196</v>
+        <v>0.5137011710779782</v>
       </c>
       <c r="P370" t="n">
-        <v>0.1481890384969917</v>
+        <v>0.1481890011327653</v>
       </c>
     </row>
     <row r="371">
@@ -29250,10 +29250,10 @@
         <v>0.03385017289626302</v>
       </c>
       <c r="L372" t="n">
-        <v>-0.05316186732606865</v>
+        <v>-0.05316193368006827</v>
       </c>
       <c r="M372" t="n">
-        <v>0.03239580834022315</v>
+        <v>0.03239572945274216</v>
       </c>
       <c r="N372" t="n">
         <v>-0.0610582064045454</v>
@@ -29314,13 +29314,13 @@
         <v>0.006900152473229726</v>
       </c>
       <c r="N373" t="n">
-        <v>0.1505405168783847</v>
+        <v>0.1505406367948201</v>
       </c>
       <c r="O373" t="n">
-        <v>0.3539622485993537</v>
+        <v>0.3539619994962604</v>
       </c>
       <c r="P373" t="n">
-        <v>0.1062896563411069</v>
+        <v>0.1062895884957409</v>
       </c>
     </row>
     <row r="374">
@@ -29369,10 +29369,10 @@
         <v>-0.05753293014002281</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.1121898675503898</v>
+        <v>-0.1121899692851239</v>
       </c>
       <c r="N374" t="n">
-        <v>-0.0407034517282352</v>
+        <v>-0.04070339233938669</v>
       </c>
       <c r="O374" t="n">
         <v>0.07340573223094382</v>
@@ -29430,13 +29430,13 @@
         <v>0.04928740346763627</v>
       </c>
       <c r="N375" t="n">
-        <v>-0.3021323198159661</v>
+        <v>-0.3021322495765967</v>
       </c>
       <c r="O375" t="n">
-        <v>-0.4620001275611351</v>
+        <v>-0.4620002110500204</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.1866813628799613</v>
+        <v>-0.1866814049512662</v>
       </c>
     </row>
     <row r="376">
@@ -29485,7 +29485,7 @@
         <v>-0.05931535485590755</v>
       </c>
       <c r="M376" t="n">
-        <v>0.03296847976925599</v>
+        <v>0.03296841346033785</v>
       </c>
       <c r="N376" t="n">
         <v>0.1200653536403027</v>
@@ -29540,19 +29540,19 @@
         <v>-0.2218209713306911</v>
       </c>
       <c r="L377" t="n">
-        <v>-0.3166348410623658</v>
+        <v>-0.3166348945664228</v>
       </c>
       <c r="M377" t="n">
-        <v>0.07180838293940139</v>
+        <v>0.07180831713039093</v>
       </c>
       <c r="N377" t="n">
         <v>0.6605134909715205</v>
       </c>
       <c r="O377" t="n">
-        <v>-0.2650551308602721</v>
+        <v>-0.2650553165174533</v>
       </c>
       <c r="P377" t="n">
-        <v>-0.09756017194998023</v>
+        <v>-0.09756024793955709</v>
       </c>
     </row>
     <row r="378">
@@ -29656,19 +29656,19 @@
         <v>0.05231623784100115</v>
       </c>
       <c r="L379" t="n">
-        <v>-0.03653584040475744</v>
+        <v>-0.0365359343316175</v>
       </c>
       <c r="M379" t="n">
         <v>-0.01546767588870201</v>
       </c>
       <c r="N379" t="n">
-        <v>-0.09676812321381734</v>
+        <v>-0.09676820576383904</v>
       </c>
       <c r="O379" t="n">
-        <v>0.3535976558235907</v>
+        <v>0.3535977485210733</v>
       </c>
       <c r="P379" t="n">
-        <v>0.1061903474604522</v>
+        <v>0.1061903727119387</v>
       </c>
     </row>
     <row r="380">
@@ -29714,7 +29714,7 @@
         <v>-0.02395926276760585</v>
       </c>
       <c r="L380" t="n">
-        <v>-0.04041747775661697</v>
+        <v>-0.04041741997936088</v>
       </c>
       <c r="M380" t="n">
         <v>0.02331405670185704</v>
@@ -29775,16 +29775,16 @@
         <v>0.02007853371352741</v>
       </c>
       <c r="M381" t="n">
-        <v>0.01309231874541794</v>
+        <v>0.01309220767288832</v>
       </c>
       <c r="N381" t="n">
         <v>-0.002848015345959576</v>
       </c>
       <c r="O381" t="n">
-        <v>0.1030174119172733</v>
+        <v>0.10301767524919</v>
       </c>
       <c r="P381" t="n">
-        <v>0.03322313684138134</v>
+        <v>0.03322321906450387</v>
       </c>
     </row>
     <row r="382">
@@ -29830,19 +29830,19 @@
         <v>0.04580209686315495</v>
       </c>
       <c r="L382" t="n">
-        <v>-0.09725090134236636</v>
+        <v>-0.09725079445069762</v>
       </c>
       <c r="M382" t="n">
-        <v>-0.04735861142649045</v>
+        <v>-0.04735855190982352</v>
       </c>
       <c r="N382" t="n">
         <v>0.01995090968257851</v>
       </c>
       <c r="O382" t="n">
-        <v>0.5699594513019743</v>
+        <v>0.5699589663735125</v>
       </c>
       <c r="P382" t="n">
-        <v>0.1622408752361828</v>
+        <v>0.1622407555720013</v>
       </c>
     </row>
     <row r="383">
@@ -29894,13 +29894,13 @@
         <v>0.07817818040135682</v>
       </c>
       <c r="N383" t="n">
-        <v>0.02552225415586507</v>
+        <v>0.02552218729154254</v>
       </c>
       <c r="O383" t="n">
-        <v>0.8706385416044757</v>
+        <v>0.8706392090340787</v>
       </c>
       <c r="P383" t="n">
-        <v>0.2321491809649476</v>
+        <v>0.2321493275054154</v>
       </c>
     </row>
     <row r="384">
@@ -30010,13 +30010,13 @@
         <v>0.03522822824225447</v>
       </c>
       <c r="N385" t="n">
-        <v>0.06160524530227507</v>
+        <v>0.06160536932321659</v>
       </c>
       <c r="O385" t="n">
-        <v>0.5518091275295689</v>
+        <v>0.5518089950297047</v>
       </c>
       <c r="P385" t="n">
-        <v>0.157744608842548</v>
+        <v>0.1577445758915437</v>
       </c>
     </row>
     <row r="386">
@@ -30129,10 +30129,10 @@
         <v>-0.05540105698534614</v>
       </c>
       <c r="O387" t="n">
-        <v>0.4106400098689913</v>
+        <v>0.4106401092521661</v>
       </c>
       <c r="P387" t="n">
-        <v>0.1215158073470808</v>
+        <v>0.12151583368496</v>
       </c>
     </row>
     <row r="388">
@@ -30187,10 +30187,10 @@
         <v>-0.05071128009466375</v>
       </c>
       <c r="O388" t="n">
-        <v>0.05906518624268853</v>
+        <v>0.05906469606538911</v>
       </c>
       <c r="P388" t="n">
-        <v>0.01931300216291243</v>
+        <v>0.01931284490341656</v>
       </c>
     </row>
     <row r="389">
@@ -30300,7 +30300,7 @@
         <v>0.02130957841588965</v>
       </c>
       <c r="N390" t="n">
-        <v>0.06475068140781892</v>
+        <v>0.06475080797206223</v>
       </c>
       <c r="O390" t="n">
         <v>0.4886106443573219</v>
@@ -30468,19 +30468,19 @@
         <v>-0.04079716588354676</v>
       </c>
       <c r="L393" t="n">
-        <v>-0.06227394939617736</v>
+        <v>-0.06227386248392164</v>
       </c>
       <c r="M393" t="n">
         <v>-0.01789112110767888</v>
       </c>
       <c r="N393" t="n">
-        <v>0.08955316944488456</v>
+        <v>0.0895532867794373</v>
       </c>
       <c r="O393" t="n">
-        <v>0.484618183368273</v>
+        <v>0.4846184012188093</v>
       </c>
       <c r="P393" t="n">
-        <v>0.1407879500153859</v>
+        <v>0.1407880058145261</v>
       </c>
     </row>
     <row r="394">
@@ -30526,7 +30526,7 @@
         <v>0.05351725056916967</v>
       </c>
       <c r="L394" t="n">
-        <v>-0.09774327851777798</v>
+        <v>-0.09774336915719184</v>
       </c>
       <c r="M394" t="n">
         <v>-0.05825891087717772</v>
@@ -30593,10 +30593,10 @@
         <v>-0.002031641201686973</v>
       </c>
       <c r="O395" t="n">
-        <v>0.4652211285207097</v>
+        <v>0.4652213105740899</v>
       </c>
       <c r="P395" t="n">
-        <v>0.1357978899372423</v>
+        <v>0.1357979369781137</v>
       </c>
     </row>
     <row r="396">
@@ -30648,13 +30648,13 @@
         <v>-0.09791841497229681</v>
       </c>
       <c r="N396" t="n">
-        <v>-0.01059324649533633</v>
+        <v>-0.01059335555797325</v>
       </c>
       <c r="O396" t="n">
-        <v>0.8245248253721618</v>
+        <v>0.8245246399354085</v>
       </c>
       <c r="P396" t="n">
-        <v>0.2219401239659826</v>
+        <v>0.2219400825684246</v>
       </c>
     </row>
     <row r="397">
@@ -30758,19 +30758,19 @@
         <v>0.08734251108589963</v>
       </c>
       <c r="L398" t="n">
-        <v>-0.08754638025886741</v>
+        <v>-0.08754645545735984</v>
       </c>
       <c r="M398" t="n">
-        <v>-0.01755597121043273</v>
+        <v>-0.01755588403316632</v>
       </c>
       <c r="N398" t="n">
-        <v>-0.1517157876614746</v>
+        <v>-0.1517158526550321</v>
       </c>
       <c r="O398" t="n">
-        <v>0.1291783052246944</v>
+        <v>0.1291781900617976</v>
       </c>
       <c r="P398" t="n">
-        <v>0.04132790965535271</v>
+        <v>0.04132787425428797</v>
       </c>
     </row>
     <row r="399">
@@ -30819,16 +30819,16 @@
         <v>-0.2040655088791944</v>
       </c>
       <c r="M399" t="n">
-        <v>-0.1646829761564736</v>
+        <v>-0.1646828768292024</v>
       </c>
       <c r="N399" t="n">
         <v>0.07175120642122756</v>
       </c>
       <c r="O399" t="n">
-        <v>0.6059495633181284</v>
+        <v>0.6059497468872568</v>
       </c>
       <c r="P399" t="n">
-        <v>0.1710550211287853</v>
+        <v>0.1710550657481902</v>
       </c>
     </row>
     <row r="400">
@@ -30883,10 +30883,10 @@
         <v>0.02025946890578689</v>
       </c>
       <c r="O400" t="n">
-        <v>0.2197116841073439</v>
+        <v>0.2197118121848103</v>
       </c>
       <c r="P400" t="n">
-        <v>0.06844555026509225</v>
+        <v>0.06844558766294506</v>
       </c>
     </row>
     <row r="401">
@@ -30938,7 +30938,7 @@
         <v>0.0009854454300533</v>
       </c>
       <c r="N401" t="n">
-        <v>-0.04146176835383575</v>
+        <v>-0.04146186477547631</v>
       </c>
       <c r="O401" t="n">
         <v>0.02480366845473503</v>
@@ -30990,13 +30990,13 @@
         <v>0.1570987970112634</v>
       </c>
       <c r="L402" t="n">
-        <v>-0.03284642471340027</v>
+        <v>-0.0328465353642724</v>
       </c>
       <c r="M402" t="n">
         <v>-0.1126793235592002</v>
       </c>
       <c r="N402" t="n">
-        <v>-0.2748945406997545</v>
+        <v>-0.2748944785031902</v>
       </c>
       <c r="O402" t="n">
         <v>-0.03568731565844618</v>
@@ -31054,13 +31054,13 @@
         <v>0.02559825514042258</v>
       </c>
       <c r="N403" t="n">
-        <v>0.01628156219982091</v>
+        <v>0.01628144643879459</v>
       </c>
       <c r="O403" t="n">
-        <v>0.4378899189763052</v>
+        <v>0.4378900348422061</v>
       </c>
       <c r="P403" t="n">
-        <v>0.1286913921728841</v>
+        <v>0.1286914224897255</v>
       </c>
     </row>
     <row r="404">
@@ -31158,19 +31158,19 @@
         <v>-0.04660195388563193</v>
       </c>
       <c r="L405" t="n">
-        <v>-0.06885806265503536</v>
+        <v>-0.06885798369969054</v>
       </c>
       <c r="M405" t="n">
         <v>-0.01658201817188087</v>
       </c>
       <c r="N405" t="n">
-        <v>0.03623125222934975</v>
+        <v>0.03623135001230038</v>
       </c>
       <c r="O405" t="n">
-        <v>0.5311061543883204</v>
+        <v>0.5311062611290982</v>
       </c>
       <c r="P405" t="n">
-        <v>0.1525729798556268</v>
+        <v>0.1525730066394291</v>
       </c>
     </row>
     <row r="406">
@@ -31219,16 +31219,16 @@
         <v>-0.1721734853717916</v>
       </c>
       <c r="M406" t="n">
-        <v>0.02463375294747538</v>
+        <v>0.02463383853254264</v>
       </c>
       <c r="N406" t="n">
         <v>0.06721564014131021</v>
       </c>
       <c r="O406" t="n">
-        <v>-0.05821278876091962</v>
+        <v>-0.05821286106556289</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.01979345904056784</v>
+        <v>-0.01979348412531645</v>
       </c>
     </row>
     <row r="407">
@@ -31283,10 +31283,10 @@
         <v>-0.1215038104217587</v>
       </c>
       <c r="O407" t="n">
-        <v>0.1174192299095134</v>
+        <v>0.1174193366044662</v>
       </c>
       <c r="P407" t="n">
-        <v>0.03770055016110452</v>
+        <v>0.03770058318881842</v>
       </c>
     </row>
     <row r="408">
@@ -31335,7 +31335,7 @@
         <v>-0.08363706598685672</v>
       </c>
       <c r="M408" t="n">
-        <v>0.03270680115057667</v>
+        <v>0.03270688496415963</v>
       </c>
       <c r="N408" t="n">
         <v>-0.2417595343846132</v>
@@ -31393,16 +31393,16 @@
         <v>-0.0716941799138856</v>
       </c>
       <c r="M409" t="n">
-        <v>-0.01606987429826312</v>
+        <v>-0.01606976875155874</v>
       </c>
       <c r="N409" t="n">
         <v>-0.01120962390167568</v>
       </c>
       <c r="O409" t="n">
-        <v>0.5317935770313604</v>
+        <v>0.5317937049361017</v>
       </c>
       <c r="P409" t="n">
-        <v>0.1527454447578558</v>
+        <v>0.1527454768425975</v>
       </c>
     </row>
     <row r="410">
@@ -31454,13 +31454,13 @@
         <v>-0.01603838882087805</v>
       </c>
       <c r="N410" t="n">
-        <v>0.03139345246684022</v>
+        <v>0.03139352855140465</v>
       </c>
       <c r="O410" t="n">
-        <v>0.3955098587337531</v>
+        <v>0.3955095801578719</v>
       </c>
       <c r="P410" t="n">
-        <v>0.1174916918329925</v>
+        <v>0.1174916174739684</v>
       </c>
     </row>
     <row r="411">
@@ -31512,7 +31512,7 @@
         <v>-0.03389773823347364</v>
       </c>
       <c r="N411" t="n">
-        <v>-0.1241290884459068</v>
+        <v>-0.1241291826194888</v>
       </c>
       <c r="O411" t="n">
         <v>-0.05597508999156575</v>
@@ -31564,19 +31564,19 @@
         <v>-0.08562575749742696</v>
       </c>
       <c r="L412" t="n">
-        <v>-0.08828291384868858</v>
+        <v>-0.08828283239778667</v>
       </c>
       <c r="M412" t="n">
-        <v>0.004675137089542369</v>
+        <v>0.004675235996540961</v>
       </c>
       <c r="N412" t="n">
-        <v>0.05611110185478485</v>
+        <v>0.05611121114843542</v>
       </c>
       <c r="O412" t="n">
-        <v>0.4892282934034524</v>
+        <v>0.4892281847438278</v>
       </c>
       <c r="P412" t="n">
-        <v>0.1419675403281973</v>
+        <v>0.1419675125541329</v>
       </c>
     </row>
     <row r="413">
@@ -31631,10 +31631,10 @@
         <v>-0.09969610489363734</v>
       </c>
       <c r="O413" t="n">
-        <v>0.1078819993757421</v>
+        <v>0.1078819193660245</v>
       </c>
       <c r="P413" t="n">
-        <v>0.03473983499540267</v>
+        <v>0.03473981008623839</v>
       </c>
     </row>
     <row r="414">
@@ -31744,13 +31744,13 @@
         <v>0.002463957750279855</v>
       </c>
       <c r="N415" t="n">
-        <v>-0.002005236048736592</v>
+        <v>-0.002005129226099078</v>
       </c>
       <c r="O415" t="n">
-        <v>-0.1195574844356562</v>
+        <v>-0.1195576507151335</v>
       </c>
       <c r="P415" t="n">
-        <v>-0.04155542839340332</v>
+        <v>-0.04155548873036252</v>
       </c>
     </row>
     <row r="416">
@@ -31796,7 +31796,7 @@
         <v>-0.09499855396242785</v>
       </c>
       <c r="L416" t="n">
-        <v>-0.1394251633501453</v>
+        <v>-0.1394251109554255</v>
       </c>
       <c r="M416" t="n">
         <v>0.09114873501415532</v>
@@ -31805,10 +31805,10 @@
         <v>0.008431632702346814</v>
       </c>
       <c r="O416" t="n">
-        <v>0.2461479081263724</v>
+        <v>0.2461480179888611</v>
       </c>
       <c r="P416" t="n">
-        <v>0.07610966234852334</v>
+        <v>0.07610969397239975</v>
       </c>
     </row>
     <row r="417">
@@ -31860,13 +31860,13 @@
         <v>-0.0402546850190918</v>
       </c>
       <c r="N417" t="n">
-        <v>0.05455619288164804</v>
+        <v>0.05455611432087659</v>
       </c>
       <c r="O417" t="n">
-        <v>0.3399023283206413</v>
+        <v>0.3399020746661741</v>
       </c>
       <c r="P417" t="n">
-        <v>0.1024469846136475</v>
+        <v>0.1024469150462335</v>
       </c>
     </row>
     <row r="418">
@@ -31921,10 +31921,10 @@
         <v>0.02958619719331645</v>
       </c>
       <c r="O418" t="n">
-        <v>0.1743786441789363</v>
+        <v>0.174378828229967</v>
       </c>
       <c r="P418" t="n">
-        <v>0.05504110833998843</v>
+        <v>0.05504116345605481</v>
       </c>
     </row>
     <row r="419">
@@ -31979,10 +31979,10 @@
         <v>-0.2029500370575419</v>
       </c>
       <c r="O419" t="n">
-        <v>-0.2768425328407234</v>
+        <v>-0.2768426793107081</v>
       </c>
       <c r="P419" t="n">
-        <v>-0.1024107863931215</v>
+        <v>-0.1024108469930569</v>
       </c>
     </row>
     <row r="420">
@@ -32028,19 +32028,19 @@
         <v>0.01142831080719064</v>
       </c>
       <c r="L420" t="n">
-        <v>-0.1659984558826617</v>
+        <v>-0.1659984051300676</v>
       </c>
       <c r="M420" t="n">
-        <v>0.03266168709439632</v>
+        <v>0.03266176490533801</v>
       </c>
       <c r="N420" t="n">
-        <v>-0.1500780874076636</v>
+        <v>-0.1500780346989292</v>
       </c>
       <c r="O420" t="n">
-        <v>0.6704442010095271</v>
+        <v>0.6704440992070293</v>
       </c>
       <c r="P420" t="n">
-        <v>0.1865261780411991</v>
+        <v>0.1865261539375644</v>
       </c>
     </row>
     <row r="421">
@@ -32086,19 +32086,19 @@
         <v>0.1045769880051244</v>
       </c>
       <c r="L421" t="n">
-        <v>-0.03236368498696973</v>
+        <v>-0.03236360918925807</v>
       </c>
       <c r="M421" t="n">
-        <v>-0.1486142500313767</v>
+        <v>-0.1486141913521306</v>
       </c>
       <c r="N421" t="n">
         <v>-0.2878179079344295</v>
       </c>
       <c r="O421" t="n">
-        <v>-0.1886559039004135</v>
+        <v>-0.1886559571899417</v>
       </c>
       <c r="P421" t="n">
-        <v>-0.06731492585172216</v>
+        <v>-0.06731494627147938</v>
       </c>
     </row>
     <row r="422">
@@ -32147,16 +32147,16 @@
         <v>-0.162631944121523</v>
       </c>
       <c r="M422" t="n">
-        <v>-0.08395555080863804</v>
+        <v>-0.08395548723571844</v>
       </c>
       <c r="N422" t="n">
         <v>-0.007458495299762169</v>
       </c>
       <c r="O422" t="n">
-        <v>0.6369155819917045</v>
+        <v>0.6369153789938051</v>
       </c>
       <c r="P422" t="n">
-        <v>0.1785339405615172</v>
+        <v>0.178533891843891</v>
       </c>
     </row>
     <row r="423">
@@ -32266,13 +32266,13 @@
         <v>-0.1492663049950351</v>
       </c>
       <c r="N424" t="n">
-        <v>-0.2257711884418142</v>
+        <v>-0.2257712407214236</v>
       </c>
       <c r="O424" t="n">
-        <v>-0.03739305592553732</v>
+        <v>-0.0373931367404764</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.0126230222112359</v>
+        <v>-0.01262304984273277</v>
       </c>
     </row>
     <row r="425">
@@ -32321,10 +32321,10 @@
         <v>-0.09819535577133909</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.07167555954322036</v>
+        <v>-0.07167548129844969</v>
       </c>
       <c r="N425" t="n">
-        <v>0.05841533007934574</v>
+        <v>0.05841522836834723</v>
       </c>
       <c r="O425" t="n">
         <v>0.2900705616232946</v>
@@ -32385,10 +32385,10 @@
         <v>0.02297271715693294</v>
       </c>
       <c r="O426" t="n">
-        <v>0.2099165900673001</v>
+        <v>0.2099169440286168</v>
       </c>
       <c r="P426" t="n">
-        <v>0.06557775085662376</v>
+        <v>0.06557785476826794</v>
       </c>
     </row>
     <row r="427">
@@ -32437,7 +32437,7 @@
         <v>-0.1566515388593984</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.006848122265165957</v>
+        <v>-0.006848193675850434</v>
       </c>
       <c r="N427" t="n">
         <v>0.1061439973501941</v>
@@ -32550,19 +32550,19 @@
         <v>-0.0008698762875879451</v>
       </c>
       <c r="L429" t="n">
-        <v>-0.09596497495748535</v>
+        <v>-0.09596504917012716</v>
       </c>
       <c r="M429" t="n">
         <v>-0.0644901101238583</v>
       </c>
       <c r="N429" t="n">
-        <v>-0.1511167778683411</v>
+        <v>-0.1511167124343595</v>
       </c>
       <c r="O429" t="n">
-        <v>-0.2591741423621774</v>
+        <v>-0.2591742420333611</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.09515947270830794</v>
+        <v>-0.09515951328758376</v>
       </c>
     </row>
     <row r="430">
@@ -32733,10 +32733,10 @@
         <v>-0.04006648676848301</v>
       </c>
       <c r="O432" t="n">
-        <v>0.3573932493808207</v>
+        <v>0.3573934093408446</v>
       </c>
       <c r="P432" t="n">
-        <v>0.1072233305859478</v>
+        <v>0.1072233740789845</v>
       </c>
     </row>
     <row r="433">
@@ -32791,10 +32791,10 @@
         <v>-0.01844988340544351</v>
       </c>
       <c r="O433" t="n">
-        <v>0.3237843862189262</v>
+        <v>0.3237842889699494</v>
       </c>
       <c r="P433" t="n">
-        <v>0.09800862471532912</v>
+        <v>0.09800859782771343</v>
       </c>
     </row>
     <row r="434">
@@ -32907,10 +32907,10 @@
         <v>-0.1080877210081099</v>
       </c>
       <c r="O435" t="n">
-        <v>-0.3084716227339342</v>
+        <v>-0.3084716782661117</v>
       </c>
       <c r="P435" t="n">
-        <v>-0.115692444879008</v>
+        <v>-0.115692468550018</v>
       </c>
     </row>
     <row r="436">
@@ -32965,10 +32965,10 @@
         <v>-0.0608686648518636</v>
       </c>
       <c r="O436" t="n">
-        <v>0.3217046278370881</v>
+        <v>0.3217045295711316</v>
       </c>
       <c r="P436" t="n">
-        <v>0.09743330706185382</v>
+        <v>0.09743327986456785</v>
       </c>
     </row>
     <row r="437">
@@ -33020,7 +33020,7 @@
         <v>-0.2151843922497964</v>
       </c>
       <c r="N437" t="n">
-        <v>0.00354270174735416</v>
+        <v>0.003542636129291399</v>
       </c>
       <c r="O437" t="n">
         <v>0.7672997392440322</v>
@@ -33081,10 +33081,10 @@
         <v>-0.1316051548024864</v>
       </c>
       <c r="O438" t="n">
-        <v>-0.1020063034070605</v>
+        <v>-0.1020063689894889</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.03522858050994326</v>
+        <v>-0.03522860399639394</v>
       </c>
     </row>
     <row r="439">
@@ -33188,19 +33188,19 @@
         <v>-0.08980730961260808</v>
       </c>
       <c r="L440" t="n">
-        <v>-0.1169302880121793</v>
+        <v>-0.1169301998780392</v>
       </c>
       <c r="M440" t="n">
         <v>0.04307252713363252</v>
       </c>
       <c r="N440" t="n">
-        <v>-0.1510543152570959</v>
+        <v>-0.1510542338027985</v>
       </c>
       <c r="O440" t="n">
-        <v>-0.4442852294178621</v>
+        <v>-0.44428526432048</v>
       </c>
       <c r="P440" t="n">
-        <v>-0.1778507844531682</v>
+        <v>-0.1778508016653317</v>
       </c>
     </row>
     <row r="441">
@@ -33252,13 +33252,13 @@
         <v>-0.01285353055473304</v>
       </c>
       <c r="N441" t="n">
-        <v>0.01379518040960503</v>
+        <v>0.01379508454966416</v>
       </c>
       <c r="O441" t="n">
-        <v>0.09061877977367527</v>
+        <v>0.09061889071229068</v>
       </c>
       <c r="P441" t="n">
-        <v>0.02933717362867783</v>
+        <v>0.02933720853034383</v>
       </c>
     </row>
     <row r="442">
@@ -33487,10 +33487,10 @@
         <v>-0.08350732143124651</v>
       </c>
       <c r="O445" t="n">
-        <v>0.3235909427931176</v>
+        <v>0.3235910339904695</v>
       </c>
       <c r="P445" t="n">
-        <v>0.09795513843789383</v>
+        <v>0.09795516365479839</v>
       </c>
     </row>
     <row r="446">
@@ -33545,10 +33545,10 @@
         <v>0.1544314966523284</v>
       </c>
       <c r="O446" t="n">
-        <v>0.6427496233326964</v>
+        <v>0.6427497666494597</v>
       </c>
       <c r="P446" t="n">
-        <v>0.1799323966184134</v>
+        <v>0.1799324309316332</v>
       </c>
     </row>
     <row r="447">
@@ -33661,10 +33661,10 @@
         <v>-0.03348664726493988</v>
       </c>
       <c r="O448" t="n">
-        <v>0.2086080779195736</v>
+        <v>0.2086081770921029</v>
       </c>
       <c r="P448" t="n">
-        <v>0.06519347522610075</v>
+        <v>0.06519350436097371</v>
       </c>
     </row>
     <row r="449">
@@ -33719,10 +33719,10 @@
         <v>-0.1644173753254936</v>
       </c>
       <c r="O449" t="n">
-        <v>0.0236622239623816</v>
+        <v>0.02366214793801635</v>
       </c>
       <c r="P449" t="n">
-        <v>0.007826001910324454</v>
+        <v>0.007825976960905257</v>
       </c>
     </row>
     <row r="450">
@@ -33774,13 +33774,13 @@
         <v>-0.1969734640444074</v>
       </c>
       <c r="N450" t="n">
-        <v>-0.1990345663218875</v>
+        <v>-0.1990346530979582</v>
       </c>
       <c r="O450" t="n">
-        <v>0.1566799566216619</v>
+        <v>0.1566798661382707</v>
       </c>
       <c r="P450" t="n">
-        <v>0.04971419481133776</v>
+        <v>0.04971416743940349</v>
       </c>
     </row>
     <row r="451">
@@ -33829,16 +33829,16 @@
         <v>-0.20813624666513</v>
       </c>
       <c r="M451" t="n">
-        <v>-0.1360430342800997</v>
+        <v>-0.1360431199572307</v>
       </c>
       <c r="N451" t="n">
         <v>-0.1156580003053366</v>
       </c>
       <c r="O451" t="n">
-        <v>0.2370416680925069</v>
+        <v>0.2370418437430335</v>
       </c>
       <c r="P451" t="n">
-        <v>0.07348202354452726</v>
+        <v>0.07348207435329113</v>
       </c>
     </row>
     <row r="452">
@@ -33884,7 +33884,7 @@
         <v>-0.3233413617388068</v>
       </c>
       <c r="L452" t="n">
-        <v>0.1122458816356593</v>
+        <v>0.1122457640689714</v>
       </c>
       <c r="M452" t="n">
         <v>-0.00173659122464076</v>
@@ -33893,10 +33893,10 @@
         <v>0.0481021186534798</v>
       </c>
       <c r="O452" t="n">
-        <v>0.5533765308235141</v>
+        <v>0.5533764161650374</v>
       </c>
       <c r="P452" t="n">
-        <v>0.1581342706166962</v>
+        <v>0.1581342421217988</v>
       </c>
     </row>
     <row r="453">
@@ -33945,7 +33945,7 @@
         <v>-0.3265962629506515</v>
       </c>
       <c r="M453" t="n">
-        <v>-0.06391291421820899</v>
+        <v>-0.06391282237102824</v>
       </c>
       <c r="N453" t="n">
         <v>0.09362702589001026</v>
@@ -34009,10 +34009,10 @@
         <v>-0.02182574833930329</v>
       </c>
       <c r="O454" t="n">
-        <v>0.6789410408890129</v>
+        <v>0.6789409086254028</v>
       </c>
       <c r="P454" t="n">
-        <v>0.1885345614539662</v>
+        <v>0.1885345302438419</v>
       </c>
     </row>
     <row r="455">
@@ -34122,7 +34122,7 @@
         <v>-0.3083168665360698</v>
       </c>
       <c r="N456" t="n">
-        <v>-0.320376703165149</v>
+        <v>-0.3203767444482348</v>
       </c>
       <c r="O456" t="n">
         <v>-0.2229695530183071</v>
@@ -34174,7 +34174,7 @@
         <v>-0.04375845953816837</v>
       </c>
       <c r="L457" t="n">
-        <v>-0.1849309616163956</v>
+        <v>-0.1849310372373218</v>
       </c>
       <c r="M457" t="n">
         <v>-0.1204544990362655</v>
@@ -34183,10 +34183,10 @@
         <v>-0.1238990025228627</v>
       </c>
       <c r="O457" t="n">
-        <v>0.01107357400559161</v>
+        <v>0.01107380673370861</v>
       </c>
       <c r="P457" t="n">
-        <v>0.00367764964806172</v>
+        <v>0.00367772665663213</v>
       </c>
     </row>
     <row r="458">
@@ -34296,13 +34296,13 @@
         <v>-0.204608982991179</v>
       </c>
       <c r="N459" t="n">
-        <v>-0.09882711677566758</v>
+        <v>-0.09882702776011587</v>
       </c>
       <c r="O459" t="n">
-        <v>1.680938236273138</v>
+        <v>1.680938630179777</v>
       </c>
       <c r="P459" t="n">
-        <v>0.3891919870038161</v>
+        <v>0.3891920550411809</v>
       </c>
     </row>
     <row r="460">
@@ -34522,19 +34522,19 @@
         <v>-0.01204960465234273</v>
       </c>
       <c r="L463" t="n">
-        <v>-0.1912250416156563</v>
+        <v>-0.1912251114521493</v>
       </c>
       <c r="M463" t="n">
         <v>-0.1784106784801062</v>
       </c>
       <c r="N463" t="n">
-        <v>-0.1595693153953497</v>
+        <v>-0.1595692399850082</v>
       </c>
       <c r="O463" t="n">
-        <v>-0.1003588611877054</v>
+        <v>-0.1003589475980305</v>
       </c>
       <c r="P463" t="n">
-        <v>-0.0346389571455672</v>
+        <v>-0.03463898805313703</v>
       </c>
     </row>
     <row r="464">
@@ -34760,13 +34760,13 @@
         <v>-0.04408096638010273</v>
       </c>
       <c r="N467" t="n">
-        <v>-0.03530385818401749</v>
+        <v>-0.03530396651385292</v>
       </c>
       <c r="O467" t="n">
-        <v>0.5587452977697378</v>
+        <v>0.5587455805945063</v>
       </c>
       <c r="P467" t="n">
-        <v>0.1594669810793854</v>
+        <v>0.1594670512054372</v>
       </c>
     </row>
     <row r="468">
@@ -34879,10 +34879,10 @@
         <v>-0.1477772697844848</v>
       </c>
       <c r="O469" t="n">
-        <v>0.3428903394351985</v>
+        <v>0.3428902217405765</v>
       </c>
       <c r="P469" t="n">
-        <v>0.1032658697286399</v>
+        <v>0.1032658374975488</v>
       </c>
     </row>
     <row r="470">
@@ -34989,16 +34989,16 @@
         <v>-0.1609193627664551</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.1088334261788384</v>
+        <v>-0.1088333594523732</v>
       </c>
       <c r="N471" t="n">
         <v>-0.2649868479379046</v>
       </c>
       <c r="O471" t="n">
-        <v>0.4241484360323406</v>
+        <v>0.4241485212365115</v>
       </c>
       <c r="P471" t="n">
-        <v>0.1250843554280261</v>
+        <v>0.1250843778652653</v>
       </c>
     </row>
     <row r="472">
@@ -35053,10 +35053,10 @@
         <v>-0.4497751656158925</v>
       </c>
       <c r="O472" t="n">
-        <v>-0.2948499009782733</v>
+        <v>-0.2948499434290599</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.1099237960205066</v>
+        <v>-0.1099238138816854</v>
       </c>
     </row>
     <row r="473">
@@ -35111,10 +35111,10 @@
         <v>-0.140984072269783</v>
       </c>
       <c r="O473" t="n">
-        <v>-0.04599023320663553</v>
+        <v>-0.04599008631056589</v>
       </c>
       <c r="P473" t="n">
-        <v>-0.01557128412839093</v>
+        <v>-0.01557123360175872</v>
       </c>
     </row>
     <row r="474">
@@ -35282,7 +35282,7 @@
         <v>-0.115560161956383</v>
       </c>
       <c r="N476" t="n">
-        <v>-0.2234633817262323</v>
+        <v>-0.2234634420302573</v>
       </c>
       <c r="O476" t="n">
         <v>-0.09909365036305251</v>
@@ -35566,13 +35566,13 @@
         <v>-0.007395479951749939</v>
       </c>
       <c r="L481" t="n">
-        <v>-0.1992191887612459</v>
+        <v>-0.1992192445590125</v>
       </c>
       <c r="M481" t="n">
-        <v>-0.3205202489511644</v>
+        <v>-0.3205201686036185</v>
       </c>
       <c r="N481" t="n">
-        <v>-0.3364577222779068</v>
+        <v>-0.3364577989004699</v>
       </c>
       <c r="O481" t="n">
         <v>-0.1661238288438439</v>
@@ -35688,7 +35688,7 @@
         <v>-0.1828084539400754</v>
       </c>
       <c r="N483" t="n">
-        <v>-0.26473435167739</v>
+        <v>-0.2647342923438668</v>
       </c>
       <c r="O483" t="n">
         <v>3.756875620658086</v>
@@ -35804,13 +35804,13 @@
         <v>-0.367307777635178</v>
       </c>
       <c r="N485" t="n">
-        <v>-0.4122156462029481</v>
+        <v>-0.4122155810711682</v>
       </c>
       <c r="O485" t="n">
-        <v>-0.1998159020419049</v>
+        <v>-0.1998159623959885</v>
       </c>
       <c r="P485" t="n">
-        <v>-0.0716110298201208</v>
+        <v>-0.071611053161444</v>
       </c>
     </row>
     <row r="486">
@@ -35917,7 +35917,7 @@
         <v>-0.01432845906674785</v>
       </c>
       <c r="M487" t="n">
-        <v>-0.2582028788511306</v>
+        <v>-0.2582028208492824</v>
       </c>
       <c r="N487" t="n">
         <v>-0.3780641775181033</v>
@@ -35981,10 +35981,10 @@
         <v>-0.2055404932885623</v>
       </c>
       <c r="O488" t="n">
-        <v>2.231184178120908</v>
+        <v>2.231183827557246</v>
       </c>
       <c r="P488" t="n">
-        <v>0.4783839461138786</v>
+        <v>0.4783838926486805</v>
       </c>
     </row>
     <row r="489">
@@ -36097,10 +36097,10 @@
         <v>-0.3109135567365433</v>
       </c>
       <c r="O490" t="n">
-        <v>0.1097444841458581</v>
+        <v>0.1097445807463893</v>
       </c>
       <c r="P490" t="n">
-        <v>0.03531935166075084</v>
+        <v>0.03531938170141879</v>
       </c>
     </row>
     <row r="491">
@@ -36149,10 +36149,10 @@
         <v>-0.3938169001291165</v>
       </c>
       <c r="M491" t="n">
-        <v>-0.3861827676708481</v>
+        <v>-0.3861827304792415</v>
       </c>
       <c r="N491" t="n">
-        <v>-0.4924001483533371</v>
+        <v>-0.4924001992207543</v>
       </c>
       <c r="O491" t="n">
         <v>-0.559542504080639</v>
@@ -36387,10 +36387,10 @@
         <v>-0.414207174890716</v>
       </c>
       <c r="O495" t="n">
-        <v>-0.03532236590235271</v>
+        <v>-0.03532225223059626</v>
       </c>
       <c r="P495" t="n">
-        <v>-0.01191553809259682</v>
+        <v>-0.01191549928264002</v>
       </c>
     </row>
     <row r="496">
@@ -36555,16 +36555,16 @@
         <v>-0.3799796565049585</v>
       </c>
       <c r="M498" t="n">
-        <v>-0.3993300693228833</v>
+        <v>-0.3993300314692119</v>
       </c>
       <c r="N498" t="n">
-        <v>-0.3487254115649945</v>
+        <v>-0.3487253670645353</v>
       </c>
       <c r="O498" t="n">
-        <v>-0.0381990598896299</v>
+        <v>-0.03819915694208964</v>
       </c>
       <c r="P498" t="n">
-        <v>-0.01289868058046906</v>
+        <v>-0.01289871378228535</v>
       </c>
     </row>
     <row r="499">

--- a/GICS_SubIndustry_Leaderboard.xlsx
+++ b/GICS_SubIndustry_Leaderboard.xlsx
@@ -613,19 +613,19 @@
         <v>0.1264466031910535</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0.9734455967577998</v>
+        <v>0.9734455777706591</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>1.658100088776258</v>
+        <v>1.658100070731195</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>4.63834889236929</v>
+        <v>4.638348924136558</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>4.968314935843672</v>
+        <v>4.968314529676612</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.6486070595102955</v>
+        <v>0.6486070098155311</v>
       </c>
     </row>
     <row r="3">
@@ -669,19 +669,19 @@
         <v>0.4119001830992179</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>0.7093011072044556</v>
+        <v>0.7093010643790878</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>0.8919108420181242</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>1.087250522989273</v>
+        <v>1.087250369246161</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>1.632274745421007</v>
+        <v>1.632274729063797</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>0.3796680244804529</v>
+        <v>0.3796680210728132</v>
       </c>
     </row>
     <row r="4">
@@ -725,7 +725,7 @@
         <v>0.05197439672237791</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0.3279617260320851</v>
+        <v>0.3279617367929258</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0.8265727491546303</v>
@@ -734,10 +734,10 @@
         <v>1.766390959753313</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>5.53046185844618</v>
+        <v>5.530461884894403</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.7156510448600314</v>
+        <v>0.7156510501361302</v>
       </c>
     </row>
     <row r="5">
@@ -781,19 +781,19 @@
         <v>0.4447616959674809</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.3126901574276534</v>
+        <v>0.312690147288337</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0.7366834344641364</v>
+        <v>0.73668340971628</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>1.004662218087438</v>
+        <v>1.004662230194709</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.5671440434033781</v>
+        <v>0.5671440033211501</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0.149033042585945</v>
+        <v>0.1490330370024291</v>
       </c>
     </row>
     <row r="6">
@@ -840,16 +840,16 @@
         <v>0.2063795932233158</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.8289471065465104</v>
+        <v>0.8289470867569635</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>1.810768545247723</v>
+        <v>1.810768653275881</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>2.943659268115632</v>
+        <v>2.943659450494714</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.5762920861679066</v>
+        <v>0.576292113077163</v>
       </c>
     </row>
     <row r="7">
@@ -893,13 +893,13 @@
         <v>0.313729128153714</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.8576402823790313</v>
+        <v>0.8576403017869358</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.4988906427521488</v>
+        <v>0.4988906283825678</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.5034330291729526</v>
+        <v>0.5034330080671638</v>
       </c>
       <c r="O7" s="5" t="n">
         <v>1.828043588401687</v>
@@ -958,10 +958,10 @@
         <v>0.7864102406570395</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>1.092662839664121</v>
+        <v>1.092662413613029</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.2790860255302279</v>
+        <v>0.2790859387259859</v>
       </c>
     </row>
     <row r="9">
@@ -1008,16 +1008,16 @@
         <v>0.472570603905262</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.6467576555209564</v>
+        <v>0.6467576553164555</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>1.056313876968401</v>
+        <v>1.05631387274781</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>2.251247948430847</v>
+        <v>2.25124856851845</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.3661228289890815</v>
+        <v>0.366122875197432</v>
       </c>
     </row>
     <row r="10">
@@ -1067,7 +1067,7 @@
         <v>0.464424508532032</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0.8322127886331152</v>
+        <v>0.8322125950288799</v>
       </c>
       <c r="O10" s="5" t="n">
         <v>2.619988281681814</v>
@@ -1117,19 +1117,19 @@
         <v>0.1107046877208739</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.5392299444331704</v>
+        <v>0.5392299863046508</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.4240206698350456</v>
+        <v>0.4240207240293392</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.5734115811543996</v>
+        <v>0.5734116159281004</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>-0.08889379009829998</v>
+        <v>-0.08889381581310091</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-0.03117019694151349</v>
+        <v>-0.031170206820891</v>
       </c>
     </row>
     <row r="12">
@@ -1182,10 +1182,10 @@
         <v>1.265100748111234</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>4.682371137782013</v>
+        <v>4.682371461951211</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.7640904529535678</v>
+        <v>0.764090492437744</v>
       </c>
     </row>
     <row r="13">
@@ -1288,16 +1288,16 @@
         <v>0.3314362456940749</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.5069995515270656</v>
+        <v>0.5069994744180117</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.7606173386839561</v>
+        <v>0.7606173203583211</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>0.9931324043468763</v>
+        <v>0.9931324796372044</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2523153169833388</v>
+        <v>0.2523153354982793</v>
       </c>
     </row>
     <row r="15">
@@ -1397,19 +1397,19 @@
         <v>0.3160438594975423</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.2817909339854199</v>
+        <v>0.2817909439714287</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.1238050384835327</v>
+        <v>0.1238050514021863</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.3353507947266334</v>
+        <v>0.335350814538196</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>0.2202951973907315</v>
+        <v>0.2202952457621725</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.06533092825999194</v>
+        <v>0.06533094352626798</v>
       </c>
     </row>
     <row r="17">
@@ -1459,13 +1459,13 @@
         <v>0.5027803570900253</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.2222463279697615</v>
+        <v>0.2222464066080978</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1.923381370994232</v>
+        <v>1.923382045800512</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.4298654038956351</v>
+        <v>0.4298655139145888</v>
       </c>
     </row>
     <row r="18">
@@ -1509,19 +1509,19 @@
         <v>0.1404650909528324</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.1642590838478542</v>
+        <v>0.1642590475235444</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.340692733729723</v>
+        <v>0.3406926911799784</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.4300102882059045</v>
+        <v>0.4300101919115606</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.6547486951146959</v>
+        <v>0.6547488378031361</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.1819081335832468</v>
+        <v>0.181908166229242</v>
       </c>
     </row>
     <row r="19">
@@ -1627,13 +1627,13 @@
         <v>0.1555626649456391</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>-0.04296128348072425</v>
+        <v>-0.04296117920089926</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.1735142537759247</v>
+        <v>0.1735142141474681</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0.05471898384975049</v>
+        <v>0.05471897178931695</v>
       </c>
     </row>
     <row r="21">
@@ -1683,13 +1683,13 @@
         <v>0.3382932993261842</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.2855321637657864</v>
+        <v>0.2855322695399887</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>2.524416012314875</v>
+        <v>2.524414819757526</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0.5218168504740031</v>
+        <v>0.52181667882816</v>
       </c>
     </row>
     <row r="22">
@@ -1736,16 +1736,16 @@
         <v>0.272169394253771</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0.203968450046236</v>
+        <v>0.2039684404268085</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0.2775560611464418</v>
+        <v>0.2775560869338565</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>3.085507188989801</v>
+        <v>3.085507233799864</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.5274440894678653</v>
+        <v>0.5274440943060915</v>
       </c>
     </row>
     <row r="23">
@@ -1789,19 +1789,19 @@
         <v>0.1599721144734034</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.2910386819659276</v>
+        <v>0.2910386735567436</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>0.2443484275286665</v>
+        <v>0.2443484098962646</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>0.2025224151742297</v>
+        <v>0.2025223670030324</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>1.096543711357129</v>
+        <v>1.096543728752536</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0.2630370200383129</v>
+        <v>0.2630370239316401</v>
       </c>
     </row>
     <row r="24">
@@ -1848,7 +1848,7 @@
         <v>0.1693374116089366</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.07796079354333241</v>
+        <v>0.07796092324858006</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>0.01642823276177507</v>
@@ -1907,13 +1907,13 @@
         <v>0.446956082603209</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0.5271113764165301</v>
+        <v>0.5271113402788818</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>2.351778339032057</v>
+        <v>2.351778245334124</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0.4550807717494396</v>
+        <v>0.4550807584235031</v>
       </c>
     </row>
     <row r="26">
@@ -1957,19 +1957,19 @@
         <v>0.05714207997716622</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.0955901756002154</v>
+        <v>0.09559019581188458</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.3639817524980002</v>
+        <v>0.3639817311806988</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0.4045288258669616</v>
+        <v>0.4045287623826621</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>1.449397285855657</v>
+        <v>1.449397221322918</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.3359533448850567</v>
+        <v>0.3359533392571248</v>
       </c>
     </row>
     <row r="27">
@@ -2016,16 +2016,16 @@
         <v>0.06418291796169939</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>0.3676890475716778</v>
+        <v>0.3676890232739692</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>0.3617256465240318</v>
+        <v>0.3617255816532589</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.4975810337964354</v>
+        <v>0.4975811101126548</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>0.1436984041214904</v>
+        <v>0.1436984243180118</v>
       </c>
     </row>
     <row r="28">
@@ -2069,10 +2069,10 @@
         <v>0.132886945136413</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.3871418317128721</v>
+        <v>0.3871419195551167</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.09859148995969802</v>
+        <v>0.09859160015527402</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>0.2141618380484327</v>
@@ -2128,16 +2128,16 @@
         <v>0.2124478504506307</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>0.2366303945387396</v>
+        <v>0.236630426545852</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>0.2447647084912533</v>
+        <v>0.244764691268852</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>0.6176516525717967</v>
+        <v>0.6176517340322827</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>0.1736495983978323</v>
+        <v>0.1736496175940313</v>
       </c>
     </row>
     <row r="30">
@@ -2178,22 +2178,22 @@
         <v>-0.04386998722680091</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.1120690890967945</v>
+        <v>0.1120691255763044</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.16506729486151</v>
+        <v>0.1650672029207284</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.1860063442041381</v>
+        <v>0.1860062994967779</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>0.3777072134155077</v>
+        <v>0.3777071650771857</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>1.244829647248357</v>
+        <v>1.244829742091903</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.290434466205552</v>
+        <v>0.2904344933333838</v>
       </c>
     </row>
     <row r="31">
@@ -2240,10 +2240,10 @@
         <v>-0.005733256131019937</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>0.3525922153623227</v>
+        <v>0.3525921256952782</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>0.2828821467222291</v>
+        <v>0.2828822273849125</v>
       </c>
       <c r="O31" s="5" t="n">
         <v>0.6439991794234468</v>
@@ -2293,19 +2293,19 @@
         <v>0.01335020144235533</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.05794382119371169</v>
+        <v>0.05794384395648303</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>0.3120192974357755</v>
+        <v>0.312019256767811</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0.5405551658029337</v>
+        <v>0.5405551794022198</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>1.517380076044304</v>
+        <v>1.517379981021776</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>0.3528175962005496</v>
+        <v>0.3528175782804082</v>
       </c>
     </row>
     <row r="33">
@@ -2355,7 +2355,7 @@
         <v>0.4573290641433352</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0.3794758030653085</v>
+        <v>0.3794756847314473</v>
       </c>
       <c r="O33" s="5" t="n">
         <v>1.181847784012425</v>
@@ -2411,13 +2411,13 @@
         <v>0.346297348644435</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0.5229528872291822</v>
+        <v>0.5229528257188631</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>3.224312328795572</v>
+        <v>3.224312132324756</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.5392935218153712</v>
+        <v>0.539293507199325</v>
       </c>
     </row>
     <row r="35">
@@ -2470,10 +2470,10 @@
         <v>0.0551957758525512</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>0.6111026614151305</v>
+        <v>0.6111025125228349</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>0.171965765481134</v>
+        <v>0.1719657293646145</v>
       </c>
     </row>
     <row r="36">
@@ -2520,16 +2520,16 @@
         <v>0.04424696871688279</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>0.2324109804734781</v>
+        <v>0.2324109593767924</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0.4160852131818257</v>
+        <v>0.4160852728489653</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>0.3985823843922102</v>
+        <v>0.3985823145453077</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>0.09383761579559662</v>
+        <v>0.09383759726006782</v>
       </c>
     </row>
     <row r="37">
@@ -2582,10 +2582,10 @@
         <v>0.5533186909886846</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>1.152195767477341</v>
+        <v>1.15219585542863</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>0.2909100923111765</v>
+        <v>0.2909101101991784</v>
       </c>
     </row>
     <row r="38">
@@ -2629,19 +2629,19 @@
         <v>0.1328658371658232</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.1531577656036375</v>
+        <v>0.153157753459167</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.1918400526550054</v>
+        <v>0.1918400678359965</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0.2247033791406839</v>
+        <v>0.2247033657460828</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>1.403004242213422</v>
+        <v>1.403004299520169</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.3339245491883954</v>
+        <v>0.3339245543882641</v>
       </c>
     </row>
     <row r="39">
@@ -2688,16 +2688,16 @@
         <v>0.01011758210515486</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>0.3907494934723993</v>
+        <v>0.3907495254947052</v>
       </c>
       <c r="N39" s="5" t="n">
         <v>0.5126891712090439</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0.2817420693816468</v>
+        <v>0.2817419414035932</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>0.07575753061370534</v>
+        <v>0.07575749563202712</v>
       </c>
     </row>
     <row r="40">
@@ -2738,10 +2738,10 @@
         <v>-0.07462123611090006</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.08632191291063795</v>
+        <v>0.08632194289155179</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.1250202603808857</v>
+        <v>0.125020258501184</v>
       </c>
       <c r="M40" s="5" t="n">
         <v>0.2529989770027483</v>
@@ -2750,10 +2750,10 @@
         <v>0.2428714419605818</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>0.5940005554907634</v>
+        <v>0.5940004550123434</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.1627005204811049</v>
+        <v>0.1627004938225237</v>
       </c>
     </row>
     <row r="41">
@@ -2800,16 +2800,16 @@
         <v>0.07505650087700196</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.2977711936486624</v>
+        <v>0.2977711877248008</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.3069813161266951</v>
+        <v>0.3069813428250653</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.2762258295959133</v>
+        <v>0.2762258532994756</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>0.08097896091262785</v>
+        <v>0.08097896913370617</v>
       </c>
     </row>
     <row r="42">
@@ -2853,19 +2853,19 @@
         <v>0.02013669054050635</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.03895489076615302</v>
+        <v>0.03895487476815543</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>0.2351107357814906</v>
+        <v>0.2351106772560166</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0.4699929103354986</v>
+        <v>0.4699928725009311</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>0.4736602064226304</v>
+        <v>0.4736603047950607</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>0.124545154862368</v>
+        <v>0.1245451740892291</v>
       </c>
     </row>
     <row r="43">
@@ -2912,16 +2912,16 @@
         <v>0.2277329447337089</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>0.04929028951922909</v>
+        <v>0.04929017674431413</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>-0.08359919215463352</v>
+        <v>-0.08359910613606414</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>-0.2467624450023983</v>
+        <v>-0.2467625612315604</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>-0.09013424071011167</v>
+        <v>-0.09013428750939811</v>
       </c>
     </row>
     <row r="44">
@@ -2974,10 +2974,10 @@
         <v>0.1247843396453128</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>0.1315465161444644</v>
+        <v>0.1315468265398596</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.04205538912503592</v>
+        <v>0.04205548440736573</v>
       </c>
     </row>
     <row r="45">
@@ -3021,7 +3021,7 @@
         <v>0.01077750201394279</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.1072021862887651</v>
+        <v>0.1072021510013453</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>0.3382170561713138</v>
@@ -3030,10 +3030,10 @@
         <v>0.2853490689768592</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.5658960473826217</v>
+        <v>0.5658959858344457</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>0.1607868126666818</v>
+        <v>0.1607867968223373</v>
       </c>
     </row>
     <row r="46">
@@ -3080,10 +3080,10 @@
         <v>-0.04971348504603135</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>0.2931833344102035</v>
+        <v>0.2931834350794018</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>0.2347926059017087</v>
+        <v>0.2347926976851742</v>
       </c>
       <c r="O46" s="5" t="n">
         <v>0.2590728569980931</v>
@@ -3136,16 +3136,16 @@
         <v>0.181318843929641</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>0.2835468748003356</v>
+        <v>0.283546826574549</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>0.0681314686392025</v>
+        <v>0.06813150390726952</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>1.124969524744018</v>
+        <v>1.124969673320046</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>0.2842638098850137</v>
+        <v>0.2842638398567855</v>
       </c>
     </row>
     <row r="48">
@@ -3189,19 +3189,19 @@
         <v>0.185487843752643</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.02581541931429066</v>
+        <v>-0.02581540208700212</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>0.0539392487523756</v>
+        <v>0.05393926894469214</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>0.3315880869643745</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>0.9650511880541865</v>
+        <v>0.9650510490556716</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>0.2398543631692958</v>
+        <v>0.2398543371048992</v>
       </c>
     </row>
     <row r="49">
@@ -3245,19 +3245,19 @@
         <v>0.09349315999224743</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.1072121768416322</v>
+        <v>0.1072121638789134</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>0.2382538060291639</v>
+        <v>0.2382538394402091</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>0.1965475568270559</v>
+        <v>0.1965474772642055</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>1.207638764699622</v>
+        <v>1.207638701541768</v>
       </c>
       <c r="P49" s="5" t="n">
-        <v>0.2978836333623771</v>
+        <v>0.2978836248024113</v>
       </c>
     </row>
     <row r="50">
@@ -3301,19 +3301,19 @@
         <v>0.009676065013408675</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>0.06357742496821284</v>
+        <v>0.06357740669731329</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.2498095219228432</v>
+        <v>0.2498094964603779</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>0.3905394038110404</v>
+        <v>0.3905393558224244</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>1.744562523407583</v>
+        <v>1.744562377112238</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.330395687930399</v>
+        <v>0.3303956735466971</v>
       </c>
     </row>
     <row r="51">
@@ -3357,19 +3357,19 @@
         <v>0.07616002310971512</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0.007162278484369256</v>
+        <v>0.007162288172222531</v>
       </c>
       <c r="M51" s="5" t="n">
         <v>0.2315523068321061</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>0.2267583653707351</v>
+        <v>0.2267583782975035</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>0.4387025948773211</v>
+        <v>0.4387026515921867</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>0.116263520296985</v>
+        <v>0.1162635341206298</v>
       </c>
     </row>
     <row r="52">
@@ -3416,16 +3416,16 @@
         <v>-0.009222402356332338</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>0.1687382493157318</v>
+        <v>0.1687382801973333</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>0.05474488348149133</v>
+        <v>0.05474488464891403</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>0.3297310781375417</v>
+        <v>0.3297309608855626</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>0.09486267751510979</v>
+        <v>0.09486264271690255</v>
       </c>
     </row>
     <row r="53">
@@ -3472,16 +3472,16 @@
         <v>0.05460583930690666</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>0.0857537603175452</v>
+        <v>0.08575377952414294</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>0.1430549953367131</v>
+        <v>0.1430550088996898</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0.9498665705575238</v>
+        <v>0.9498665398099704</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>0.2445164626386533</v>
+        <v>0.2445164525362145</v>
       </c>
     </row>
     <row r="54">
@@ -3534,10 +3534,10 @@
         <v>0.1914009119586844</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>0.5093947722838765</v>
+        <v>0.5093953259634265</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.1470991215157949</v>
+        <v>0.1470992617762621</v>
       </c>
     </row>
     <row r="55">
@@ -3584,10 +3584,10 @@
         <v>0.04837668921236216</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>0.2557832014950986</v>
+        <v>0.2557832493002841</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>0.3256974787254666</v>
+        <v>0.3256974380211656</v>
       </c>
       <c r="O55" s="5" t="n">
         <v>0.0766467852737196</v>
@@ -3637,19 +3637,19 @@
         <v>0.03227847709557904</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0.05904740536621766</v>
+        <v>0.05904737250027459</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.2827473774742945</v>
+        <v>0.2827474040929501</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>0.1044867133375591</v>
+        <v>0.1044867239342608</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>0.3795667071893698</v>
+        <v>0.3795666610131962</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.09317224543663112</v>
+        <v>0.09317223036781867</v>
       </c>
     </row>
     <row r="57">
@@ -3696,16 +3696,16 @@
         <v>0.07024558221169915</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>0.103062811976973</v>
+        <v>0.1030628467879378</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>0.1422730837777888</v>
+        <v>0.1422730536607827</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>0.7820482807019232</v>
+        <v>0.7820480790421215</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>0.2084877378265908</v>
+        <v>0.2084876965036866</v>
       </c>
     </row>
     <row r="58">
@@ -3749,19 +3749,19 @@
         <v>0.1631088363226633</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0.1312256709343106</v>
+        <v>0.1312256751224395</v>
       </c>
       <c r="M58" s="5" t="n">
         <v>0.06133528432314509</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>-0.06845787736091358</v>
+        <v>-0.06845787420481723</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>0.1307328847622939</v>
+        <v>0.1307329067701749</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>0.02527600088245616</v>
+        <v>0.02527600790927001</v>
       </c>
     </row>
     <row r="59">
@@ -3811,13 +3811,13 @@
         <v>0.1437567539872041</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>0.06790112757426779</v>
+        <v>0.06790109429622625</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>0.9661529802820215</v>
+        <v>0.9661529011992236</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>0.2367506325900491</v>
+        <v>0.2367506196326863</v>
       </c>
     </row>
     <row r="60">
@@ -3864,16 +3864,16 @@
         <v>0.02432479302234125</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0.223376434003134</v>
+        <v>0.2233764548260239</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>0.1393015965147455</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>1.096644127916081</v>
+        <v>1.096643923515288</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>0.2790417594237972</v>
+        <v>0.2790417198494253</v>
       </c>
     </row>
     <row r="61">
@@ -3923,13 +3923,13 @@
         <v>0.08030236886935294</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>0.2129001068137979</v>
+        <v>0.212900165616498</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>-0.3105119483550386</v>
+        <v>-0.3105119703658182</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>-0.1240483294226159</v>
+        <v>-0.1240483375020749</v>
       </c>
     </row>
     <row r="62">
@@ -3982,10 +3982,10 @@
         <v>0.3001188406273414</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>0.2588110716766623</v>
+        <v>0.2588111569045748</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>0.07974247165471882</v>
+        <v>0.07974249602273753</v>
       </c>
     </row>
     <row r="63">
@@ -4029,19 +4029,19 @@
         <v>0.2322670096707464</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.05277720530695259</v>
+        <v>0.05277722309123611</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>-0.006633015103428434</v>
+        <v>-0.006633032522708859</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>-0.1115382633412919</v>
+        <v>-0.1115382467665606</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>0.1589027021968768</v>
+        <v>0.1589025761829331</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>0.04557427873776097</v>
+        <v>0.04557423461093704</v>
       </c>
     </row>
     <row r="64">
@@ -4088,7 +4088,7 @@
         <v>-0.01576912650447754</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>0.4472003952678065</v>
+        <v>0.4472004764871712</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>0.2820479284530613</v>
@@ -4141,19 +4141,19 @@
         <v>0.1163850061971331</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>0.1235361774361216</v>
+        <v>0.1235361914671704</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>-0.01032495212703077</v>
+        <v>-0.01032496583457413</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>0.02090756397556311</v>
+        <v>0.02090763227707859</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>1.354791886510964</v>
+        <v>1.354791857012675</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>0.3292106815887999</v>
+        <v>0.3292106775487218</v>
       </c>
     </row>
     <row r="66">
@@ -4206,10 +4206,10 @@
         <v>0.2990028454187386</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>-0.3388986316127057</v>
+        <v>-0.3388986865824536</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>-0.1288571989914634</v>
+        <v>-0.1288572231362737</v>
       </c>
     </row>
     <row r="67">
@@ -4253,19 +4253,19 @@
         <v>0.06790393296284501</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.03163707988219093</v>
+        <v>-0.03163708474529957</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.1151888925786985</v>
+        <v>0.115188873520443</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>0.1357395275862977</v>
+        <v>0.1357395230110762</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0.3666107928573886</v>
+        <v>0.366610761053249</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>0.09967799655587355</v>
+        <v>0.0996779857791977</v>
       </c>
     </row>
     <row r="68">
@@ -4306,22 +4306,22 @@
         <v>-0.07631276313325006</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>0.001306261380989038</v>
+        <v>0.00130627409481241</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>0.02485724694973739</v>
+        <v>0.02485726888643243</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.1625903519705023</v>
+        <v>0.1625903569812071</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>0.1598341246925811</v>
+        <v>0.1598340855925466</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>0.5472249169790493</v>
+        <v>0.5472247782135676</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>0.1508387125181821</v>
+        <v>0.1508386778221986</v>
       </c>
     </row>
     <row r="69">
@@ -4368,7 +4368,7 @@
         <v>0.03760148711018215</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>0.1784146778269257</v>
+        <v>0.1784146523200085</v>
       </c>
       <c r="N69" s="5" t="n">
         <v>0.2071542602262829</v>
@@ -4421,19 +4421,19 @@
         <v>0.0133275677731623</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.03534476510085238</v>
+        <v>-0.03534475417556589</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.1512610232300547</v>
+        <v>0.1512610383072776</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>0.1967247348198656</v>
+        <v>0.1967246812272768</v>
       </c>
       <c r="O70" s="5" t="n">
-        <v>0.1305290292287589</v>
+        <v>0.1305290735775987</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.03113410033262259</v>
+        <v>0.03113410766512853</v>
       </c>
     </row>
     <row r="71">
@@ -4480,16 +4480,16 @@
         <v>0.04173860645068461</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0.194213397978574</v>
+        <v>0.1942134335528638</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>0.04160123184073949</v>
+        <v>0.04160129728247519</v>
       </c>
       <c r="O71" s="5" t="n">
-        <v>0.2294357552168371</v>
+        <v>0.2294356556552962</v>
       </c>
       <c r="P71" s="5" t="n">
-        <v>0.07062965960987244</v>
+        <v>0.07062963388722554</v>
       </c>
     </row>
     <row r="72">
@@ -4542,10 +4542,10 @@
         <v>-0.01756752518177174</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>0.04940651546724117</v>
+        <v>0.0494067613346294</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.0162048237344965</v>
+        <v>0.01620490309732436</v>
       </c>
     </row>
     <row r="73">
@@ -4589,19 +4589,19 @@
         <v>0.01648084060286211</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.03530241049048358</v>
+        <v>-0.03530244441103788</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0.111637902639807</v>
+        <v>0.1116379309820974</v>
       </c>
       <c r="N73" s="5" t="n">
         <v>0.2112476273355627</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>0.6795833074564953</v>
+        <v>0.6795833512203387</v>
       </c>
       <c r="P73" s="5" t="n">
-        <v>0.1812020719055902</v>
+        <v>0.1812020828187077</v>
       </c>
     </row>
     <row r="74">
@@ -4651,7 +4651,7 @@
         <v>0.1708253360349338</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>0.1113368672335916</v>
+        <v>0.1113368206200662</v>
       </c>
       <c r="O74" s="5" t="n">
         <v>1.1905314524776</v>
@@ -4760,16 +4760,16 @@
         <v>-0.02629911737097934</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.1376600299741817</v>
+        <v>0.1376599684401507</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>0.06110531460413599</v>
+        <v>0.06110540211220472</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>0.9490399646214452</v>
+        <v>0.9490400272547337</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>0.2483337568924805</v>
+        <v>0.2483337709924675</v>
       </c>
     </row>
     <row r="77">
@@ -4813,19 +4813,19 @@
         <v>0.08741279835402867</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.04314344690887691</v>
+        <v>-0.04314348187649542</v>
       </c>
       <c r="M77" s="5" t="n">
         <v>0.09001594948729985</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>0.03357823696844912</v>
+        <v>0.03357817210388373</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>-0.109243516637249</v>
+        <v>-0.1092434508969898</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>-0.04003715942344536</v>
+        <v>-0.04003713720109991</v>
       </c>
     </row>
     <row r="78">
@@ -4872,16 +4872,16 @@
         <v>0.1757035010407252</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>-0.06813548708462813</v>
+        <v>-0.06813549122380849</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>-0.1194891219216872</v>
+        <v>-0.1194891248547965</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>1.018970113556517</v>
+        <v>1.018970144732966</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.137147740002369</v>
+        <v>0.1371477504807445</v>
       </c>
     </row>
     <row r="79">
@@ -5043,13 +5043,13 @@
         <v>0.139144158902181</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0.08063778591625359</v>
+        <v>0.08063772700432381</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>0.2628045986951763</v>
+        <v>0.2628046803683965</v>
       </c>
       <c r="P81" s="5" t="n">
-        <v>0.08088149784300813</v>
+        <v>0.08088152114760783</v>
       </c>
     </row>
     <row r="82">
@@ -5096,16 +5096,16 @@
         <v>0.06017608221734377</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>0.5040672411237901</v>
+        <v>0.5040671569547506</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>0.5947314390773323</v>
+        <v>0.5947315080797199</v>
       </c>
       <c r="O82" s="5" t="n">
-        <v>0.2142865944835993</v>
+        <v>0.2142866190603884</v>
       </c>
       <c r="P82" s="5" t="n">
-        <v>0.06228076875993649</v>
+        <v>0.06228077229466616</v>
       </c>
     </row>
     <row r="83">
@@ -5152,16 +5152,16 @@
         <v>0.03909738127964485</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>0.1473100620913464</v>
+        <v>0.1473101079266502</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>0.1086093254651637</v>
+        <v>0.1086094416398534</v>
       </c>
       <c r="O83" s="5" t="n">
-        <v>0.3505412260636438</v>
+        <v>0.3505412627925441</v>
       </c>
       <c r="P83" s="5" t="n">
-        <v>0.0966798816125185</v>
+        <v>0.09667989388632431</v>
       </c>
     </row>
     <row r="84">
@@ -5214,10 +5214,10 @@
         <v>-0.01345237958823753</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>-0.03317933747312996</v>
+        <v>-0.03317952045762562</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>-0.01118440368790907</v>
+        <v>-0.01118446607036239</v>
       </c>
     </row>
     <row r="85">
@@ -5267,13 +5267,13 @@
         <v>0.008971751644566095</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>-0.151214299866901</v>
+        <v>-0.1512142431712132</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>-0.106606467459609</v>
+        <v>-0.1066064039089505</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>-0.05581591628876775</v>
+        <v>-0.05581589353654182</v>
       </c>
     </row>
     <row r="86">
@@ -5317,19 +5317,19 @@
         <v>0.06632691868513585</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>0.07814922384205387</v>
+        <v>0.07814922424625713</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.02161163179200808</v>
+        <v>0.02161164464767061</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>-0.03039054966804298</v>
+        <v>-0.03039055162589784</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>0.5859435453958002</v>
+        <v>0.5859436124135374</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>0.1509651069003539</v>
+        <v>0.1509651174290128</v>
       </c>
     </row>
     <row r="87">
@@ -5373,19 +5373,19 @@
         <v>0.06324174739639971</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>-0.06035120432668156</v>
+        <v>-0.06035118653677768</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>0.101705627783135</v>
+        <v>0.1017055999523382</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0.01488594813022659</v>
+        <v>0.01488594976502039</v>
       </c>
       <c r="O87" s="5" t="n">
-        <v>0.03867871410270907</v>
+        <v>0.03867870542619364</v>
       </c>
       <c r="P87" s="5" t="n">
-        <v>0.007871294402537948</v>
+        <v>0.007871294341006724</v>
       </c>
     </row>
     <row r="88">
@@ -5491,13 +5491,13 @@
         <v>0.1010604404885671</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>0.2037340466094767</v>
+        <v>0.2037339989316425</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>1.238773447729827</v>
+        <v>1.238773605390092</v>
       </c>
       <c r="P89" s="5" t="n">
-        <v>0.2811160290661188</v>
+        <v>0.2811160605267724</v>
       </c>
     </row>
     <row r="90">
@@ -5541,19 +5541,19 @@
         <v>0.02757138676314683</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.08582899491523904</v>
+        <v>-0.08582900171990349</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>0.08725711242464458</v>
+        <v>0.08725712303095479</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>0.09812097479518977</v>
+        <v>0.09812095056487298</v>
       </c>
       <c r="O90" s="5" t="n">
-        <v>1.172835712978332</v>
+        <v>1.172835703622193</v>
       </c>
       <c r="P90" s="5" t="n">
-        <v>0.2527687802090168</v>
+        <v>0.2527687751866961</v>
       </c>
     </row>
     <row r="91">
@@ -5653,19 +5653,19 @@
         <v>-0.001247197760422281</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>0.03439200562824216</v>
+        <v>0.03439197100585108</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>0.05020976632102576</v>
+        <v>0.05020984777062117</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>0.01230147420596077</v>
+        <v>0.01230151474630317</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>0.1298455537132594</v>
+        <v>0.1298455480091632</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>0.04055502316525628</v>
+        <v>0.0405550229651249</v>
       </c>
     </row>
     <row r="93">
@@ -5709,19 +5709,19 @@
         <v>0.1329755033681498</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.05296031147208472</v>
+        <v>-0.05296031479553964</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>-0.06440489170853776</v>
+        <v>-0.06440488380723788</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>-0.05798726459391943</v>
+        <v>-0.05798726827608763</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>0.04892356077626041</v>
+        <v>0.04892354441078504</v>
       </c>
       <c r="P93" s="5" t="n">
-        <v>0.01182130294484638</v>
+        <v>0.01182129938108231</v>
       </c>
     </row>
     <row r="94">
@@ -5765,19 +5765,19 @@
         <v>-0.1088740624807552</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-0.001742648474484946</v>
+        <v>-0.001742671877281388</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>0.03051415963989675</v>
+        <v>0.03051411855979632</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>0.253082546646795</v>
+        <v>0.2530825494519881</v>
       </c>
       <c r="O94" s="5" t="n">
-        <v>0.8615331504763931</v>
+        <v>0.8615333778261777</v>
       </c>
       <c r="P94" s="5" t="n">
-        <v>0.2178332334557342</v>
+        <v>0.217833264320987</v>
       </c>
     </row>
     <row r="95">
@@ -5821,19 +5821,19 @@
         <v>0.05756048349781304</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.06917265291521328</v>
+        <v>-0.06917263643831302</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>0.009806052887508715</v>
+        <v>0.00980606183192978</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>-0.006283918192320215</v>
+        <v>-0.006283955127663762</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>-0.1368158005744196</v>
+        <v>-0.1368157881500962</v>
       </c>
       <c r="P95" s="5" t="n">
-        <v>-0.05212622833638803</v>
+        <v>-0.05212622593706147</v>
       </c>
     </row>
     <row r="96">
@@ -5877,19 +5877,19 @@
         <v>0.04716533211532744</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.06383054771276699</v>
+        <v>-0.06383053705192787</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>0.03100650406167641</v>
+        <v>0.03100649417342764</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>-0.02594338394044928</v>
+        <v>-0.02594337056467531</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>0.1301620383956958</v>
+        <v>0.1301620777960065</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>0.03801603761718586</v>
+        <v>0.0380160489215689</v>
       </c>
     </row>
     <row r="97">
@@ -5939,13 +5939,13 @@
         <v>-0.1840159264162897</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>-0.2731700343262908</v>
+        <v>-0.2731700783558952</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>0.03686059578692591</v>
+        <v>0.03686041658204986</v>
       </c>
       <c r="P97" s="5" t="n">
-        <v>0.01213891575038106</v>
+        <v>0.01213885743966903</v>
       </c>
     </row>
     <row r="98">
@@ -5989,19 +5989,19 @@
         <v>-0.02582943340484732</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>-0.06084898844904837</v>
+        <v>-0.0608490013448943</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>0.01565804425522904</v>
+        <v>0.01565803296341886</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>0.09807949046085281</v>
+        <v>0.09807951565996216</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>0.4101739128864025</v>
+        <v>0.4101738825498085</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>0.1200395683698238</v>
+        <v>0.1200395603229269</v>
       </c>
     </row>
     <row r="99">
@@ -6054,10 +6054,10 @@
         <v>-0.05439277304811962</v>
       </c>
       <c r="O99" s="5" t="n">
-        <v>-0.2101337060254957</v>
+        <v>-0.210133655815647</v>
       </c>
       <c r="P99" s="5" t="n">
-        <v>-0.07561860928899866</v>
+        <v>-0.07561858970211877</v>
       </c>
     </row>
     <row r="100">
@@ -6101,19 +6101,19 @@
         <v>-0.02304086766090032</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>-0.07312618347722404</v>
+        <v>-0.07312619305384999</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>-0.004031535358364032</v>
+        <v>-0.004031544062732739</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>0.05940728338301025</v>
+        <v>0.05940728894203516</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>0.8092625478248566</v>
+        <v>0.8092624811941883</v>
       </c>
       <c r="P100" s="5" t="n">
-        <v>0.1955039898540017</v>
+        <v>0.1955039779541807</v>
       </c>
     </row>
     <row r="101">
@@ -6157,19 +6157,19 @@
         <v>0.09598250293112412</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>0.04447615414530656</v>
+        <v>0.0444761703960023</v>
       </c>
       <c r="M101" s="5" t="n">
         <v>-0.1913427183137145</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>-0.1384400256253932</v>
+        <v>-0.1384400415054449</v>
       </c>
       <c r="O101" s="5" t="n">
-        <v>-0.0164349118869602</v>
+        <v>-0.0164349273724039</v>
       </c>
       <c r="P101" s="5" t="n">
-        <v>-0.030047169246114</v>
+        <v>-0.03004717637054399</v>
       </c>
     </row>
     <row r="102">
@@ -6216,16 +6216,16 @@
         <v>0.029592939724777</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>-0.07052456564661699</v>
+        <v>-0.07052459109779372</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>0.1635798032572574</v>
+        <v>0.1635798183548257</v>
       </c>
       <c r="O102" s="5" t="n">
-        <v>1.397714076439346</v>
+        <v>1.397714279833025</v>
       </c>
       <c r="P102" s="5" t="n">
-        <v>0.336104394908074</v>
+        <v>0.3361044307256011</v>
       </c>
     </row>
     <row r="103">
@@ -6325,19 +6325,19 @@
         <v>-0.02775084215111612</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>-0.0942783797273099</v>
+        <v>-0.09427845458239015</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>-0.03543816990672854</v>
+        <v>-0.03543808500979007</v>
       </c>
       <c r="N104" s="5" t="n">
         <v>0.0342535565374793</v>
       </c>
       <c r="O104" s="5" t="n">
-        <v>0.5396413465534378</v>
+        <v>0.5396414547070458</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.1547106954685153</v>
+        <v>0.154710722506441</v>
       </c>
     </row>
     <row r="105">
@@ -6390,10 +6390,10 @@
         <v>-0.003500922302226817</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>0.4308779254166711</v>
+        <v>0.4308779913200389</v>
       </c>
       <c r="P105" s="5" t="n">
-        <v>0.1260333491841259</v>
+        <v>0.126033369959213</v>
       </c>
     </row>
     <row r="106">
@@ -6443,13 +6443,13 @@
         <v>-0.1215833921395003</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>-0.2434898475115453</v>
+        <v>-0.2434898305684353</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>-0.1025608483673768</v>
+        <v>-0.1025608639139494</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>-0.03623485183048641</v>
+        <v>-0.03623485933474063</v>
       </c>
     </row>
     <row r="107">
@@ -6493,19 +6493,19 @@
         <v>0.001665417631730214</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>-0.1148734684875837</v>
+        <v>-0.1148734937603964</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>-0.02342891235194466</v>
+        <v>-0.02342892313937002</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>-0.07421578321342805</v>
+        <v>-0.07421579354560331</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>0.4330056917068787</v>
+        <v>0.4330056373100887</v>
       </c>
       <c r="P107" s="5" t="n">
-        <v>0.1038500969685554</v>
+        <v>0.1038500841934716</v>
       </c>
     </row>
     <row r="108">
@@ -6549,19 +6549,19 @@
         <v>-0.08014618488538294</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>-0.109254754600164</v>
+        <v>-0.1092547283760883</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.0008414154171743626</v>
+        <v>0.0008414229696174502</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>0.0514991329383799</v>
+        <v>0.05149907556743569</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>0.07705994684451145</v>
+        <v>0.07705992773778728</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.0161985526911928</v>
+        <v>0.01619855191160002</v>
       </c>
     </row>
     <row r="109">
@@ -6608,16 +6608,16 @@
         <v>-0.09648714361539118</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>-0.02501844112875118</v>
+        <v>-0.02501846474164254</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>-0.08799119775369452</v>
+        <v>-0.08799116460694362</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>-0.5175633080208921</v>
+        <v>-0.517563295160864</v>
       </c>
       <c r="P109" s="5" t="n">
-        <v>-0.2167829963606057</v>
+        <v>-0.216782988822968</v>
       </c>
     </row>
     <row r="110">
@@ -6664,16 +6664,16 @@
         <v>-0.1053202026626017</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>-0.1052598525785461</v>
+        <v>-0.1052598023069765</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>-0.1862966504759879</v>
+        <v>-0.1862966481499158</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>0.3066867939498845</v>
+        <v>0.3066867587992091</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>0.07965600670046939</v>
+        <v>0.07965599840881847</v>
       </c>
     </row>
     <row r="111">
@@ -6720,16 +6720,16 @@
         <v>-0.08077480814765045</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>-0.04018907458451008</v>
+        <v>-0.04018908995460635</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>-0.1228810736495928</v>
+        <v>-0.1228810896974212</v>
       </c>
       <c r="O111" s="5" t="n">
-        <v>0.5607167912390594</v>
+        <v>0.5607167432562699</v>
       </c>
       <c r="P111" s="5" t="n">
-        <v>0.1455661743660359</v>
+        <v>0.1455661620146778</v>
       </c>
     </row>
     <row r="112">
@@ -6776,10 +6776,10 @@
         <v>-0.1305804170972452</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>-0.07467780712726158</v>
+        <v>-0.07467772781145832</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>-0.1348892374947659</v>
+        <v>-0.134889168165405</v>
       </c>
       <c r="O112" s="5" t="n">
         <v>-0.2658134440373598</v>
@@ -6829,19 +6829,19 @@
         <v>0.002646807201709012</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>-0.1293643378893085</v>
+        <v>-0.1293643180054515</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>-0.1005124675158415</v>
+        <v>-0.1005124490457907</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>-0.1216003519965445</v>
+        <v>-0.1216003294288245</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>0.315014375332666</v>
+        <v>0.3150143831523446</v>
       </c>
       <c r="P113" s="5" t="n">
-        <v>0.08999782386825943</v>
+        <v>0.08999782516239563</v>
       </c>
     </row>
     <row r="114">
@@ -6941,19 +6941,19 @@
         <v>0.013801193808057</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>-0.1404407635733881</v>
+        <v>-0.1404407726789801</v>
       </c>
       <c r="M115" s="5" t="n">
         <v>-0.1422875882435121</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>-0.1793566816068599</v>
+        <v>-0.1793566807793419</v>
       </c>
       <c r="O115" s="5" t="n">
-        <v>0.2025139090779836</v>
+        <v>0.2025138943976265</v>
       </c>
       <c r="P115" s="5" t="n">
-        <v>0.05506061110203142</v>
+        <v>0.0550606054675625</v>
       </c>
     </row>
     <row r="116">
@@ -7000,16 +7000,16 @@
         <v>-0.05836144371172799</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>-0.129728522992215</v>
+        <v>-0.1297285521660755</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>-0.1286379931223457</v>
+        <v>-0.128637995653474</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>-0.04447142686257229</v>
+        <v>-0.04447145388582056</v>
       </c>
       <c r="P116" s="5" t="n">
-        <v>-0.01546856111000109</v>
+        <v>-0.01546857013372852</v>
       </c>
     </row>
     <row r="117">
@@ -7059,13 +7059,13 @@
         <v>-0.09715294141095593</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>-0.1764063514540465</v>
+        <v>-0.1764064398829947</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>0.03677299894452368</v>
+        <v>0.03677288902781928</v>
       </c>
       <c r="P117" s="5" t="n">
-        <v>0.01183646803263738</v>
+        <v>0.01183643339531482</v>
       </c>
     </row>
     <row r="118">
@@ -7109,19 +7109,19 @@
         <v>-0.1973735718218957</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>-0.2141544638884171</v>
+        <v>-0.2141544346321113</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.01949852724961304</v>
+        <v>0.01949855911589926</v>
       </c>
       <c r="N118" s="5" t="n">
         <v>0.1205641742313664</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>2.169422354127264</v>
+        <v>2.169422272508235</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>0.4089179600875239</v>
+        <v>0.4089179380853151</v>
       </c>
     </row>
     <row r="119">
@@ -7168,16 +7168,16 @@
         <v>-0.08940619542534427</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>-0.05913373352463621</v>
+        <v>-0.05913368034949307</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>-0.1239501901412909</v>
+        <v>-0.1239501681996435</v>
       </c>
       <c r="O119" s="5" t="n">
-        <v>-0.04530121672549122</v>
+        <v>-0.04530116847985843</v>
       </c>
       <c r="P119" s="5" t="n">
-        <v>-0.0163350741650566</v>
+        <v>-0.01633505676598901</v>
       </c>
     </row>
     <row r="120">
@@ -7227,13 +7227,13 @@
         <v>-0.1758845841709403</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>-0.2074739615367785</v>
+        <v>-0.2074739792208116</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>0.07702187969479141</v>
+        <v>0.07702195715691734</v>
       </c>
       <c r="P120" s="5" t="n">
-        <v>0.01939580111314382</v>
+        <v>0.01939583012987933</v>
       </c>
     </row>
     <row r="121">
@@ -7336,16 +7336,16 @@
         <v>-0.2409920999731826</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>-0.1154544698511696</v>
+        <v>-0.1154545080821896</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>-0.03609828041315472</v>
+        <v>-0.03609832089249604</v>
       </c>
       <c r="O122" s="5" t="n">
-        <v>1.084659628047389</v>
+        <v>1.084659859234274</v>
       </c>
       <c r="P122" s="5" t="n">
-        <v>0.2301413768230874</v>
+        <v>0.2301414234261198</v>
       </c>
     </row>
     <row r="123">
@@ -7389,19 +7389,19 @@
         <v>-0.06313209977981959</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>-0.1742044003755691</v>
+        <v>-0.17420442969798</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>-0.1387245155067387</v>
+        <v>-0.1387244836127675</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>-0.1102071976139623</v>
+        <v>-0.1102071686206472</v>
       </c>
       <c r="O123" s="5" t="n">
-        <v>0.4281070501008528</v>
+        <v>0.4281070938347982</v>
       </c>
       <c r="P123" s="5" t="n">
-        <v>0.122882493930303</v>
+        <v>0.1228825037353406</v>
       </c>
     </row>
     <row r="124">
@@ -7504,16 +7504,16 @@
         <v>-0.2446128271929352</v>
       </c>
       <c r="M125" s="5" t="n">
-        <v>-0.1660789439867357</v>
+        <v>-0.1660789640281208</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>-0.1302005243134944</v>
+        <v>-0.1302005573746977</v>
       </c>
       <c r="O125" s="5" t="n">
-        <v>0.9887925395686313</v>
+        <v>0.9887926628915872</v>
       </c>
       <c r="P125" s="5" t="n">
-        <v>0.1222590532973033</v>
+        <v>0.1222590696324923</v>
       </c>
     </row>
     <row r="126">
@@ -7622,10 +7622,10 @@
         <v>-0.3117313282983062</v>
       </c>
       <c r="O127" s="5" t="n">
-        <v>2.026751457412403</v>
+        <v>2.026751414810581</v>
       </c>
       <c r="P127" s="5" t="n">
-        <v>0.2003311488593111</v>
+        <v>0.2003311363766462</v>
       </c>
     </row>
     <row r="128">
@@ -7890,10 +7890,10 @@
         <v>6.679436974010909</v>
       </c>
       <c r="O3" t="n">
-        <v>13.48236449505806</v>
+        <v>13.48237304861109</v>
       </c>
       <c r="P3" t="n">
-        <v>1.43751047787187</v>
+        <v>1.437510957751406</v>
       </c>
     </row>
     <row r="4">
@@ -7997,13 +7997,13 @@
         <v>1.704746148232404</v>
       </c>
       <c r="N5" t="n">
-        <v>2.13303615986701</v>
+        <v>2.13303647003268</v>
       </c>
       <c r="O5" t="n">
-        <v>3.417244364817237</v>
+        <v>3.417243748270988</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6407804589889423</v>
+        <v>0.6407803826504681</v>
       </c>
     </row>
     <row r="6">
@@ -8049,19 +8049,19 @@
         <v>-0.1300116026680964</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6529912254678392</v>
+        <v>0.6529910449795042</v>
       </c>
       <c r="M6" t="n">
-        <v>1.832996927623431</v>
+        <v>1.832996662547522</v>
       </c>
       <c r="N6" t="n">
-        <v>4.646660204576894</v>
+        <v>4.646660731116989</v>
       </c>
       <c r="O6" t="n">
-        <v>13.82792628357542</v>
+        <v>13.82792537586166</v>
       </c>
       <c r="P6" t="n">
-        <v>1.456745331410348</v>
+        <v>1.45674528127923</v>
       </c>
     </row>
     <row r="7">
@@ -8174,10 +8174,10 @@
         <v>2.567907586332034</v>
       </c>
       <c r="O8" t="n">
-        <v>7.664732991419683</v>
+        <v>7.664731172094051</v>
       </c>
       <c r="P8" t="n">
-        <v>1.053927271588772</v>
+        <v>1.053927127835053</v>
       </c>
     </row>
     <row r="9">
@@ -8223,19 +8223,19 @@
         <v>-0.03737386381643937</v>
       </c>
       <c r="L9" t="n">
-        <v>1.082392722762775</v>
+        <v>1.08239256655978</v>
       </c>
       <c r="M9" t="n">
         <v>2.07749177057058</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95530310724666</v>
+        <v>3.955302664989853</v>
       </c>
       <c r="O9" t="n">
-        <v>12.74680212317172</v>
+        <v>12.74680297406974</v>
       </c>
       <c r="P9" t="n">
-        <v>1.395524188427818</v>
+        <v>1.39552423785378</v>
       </c>
     </row>
     <row r="10">
@@ -8287,13 +8287,13 @@
         <v>1.526353945548596</v>
       </c>
       <c r="N10" t="n">
-        <v>1.398244166248835</v>
+        <v>1.39824436787096</v>
       </c>
       <c r="O10" t="n">
-        <v>2.501797391879059</v>
+        <v>2.501796962012823</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5185543433822761</v>
+        <v>0.5185542812451132</v>
       </c>
     </row>
     <row r="11">
@@ -8580,10 +8580,10 @@
         <v>1.061417634864106</v>
       </c>
       <c r="O15" t="n">
-        <v>1.696620237556533</v>
+        <v>1.696620542772665</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3918953901637572</v>
+        <v>0.3918954426775059</v>
       </c>
     </row>
     <row r="16">
@@ -8629,19 +8629,19 @@
         <v>0.4209901146188719</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7082804528084607</v>
+        <v>0.7082803243323574</v>
       </c>
       <c r="M16" t="n">
         <v>0.9898196837435391</v>
       </c>
       <c r="N16" t="n">
-        <v>1.341481984993731</v>
+        <v>1.341481743622424</v>
       </c>
       <c r="O16" t="n">
-        <v>1.860022758930047</v>
+        <v>1.860022578871807</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4194600140408811</v>
+        <v>0.4194599842526008</v>
       </c>
     </row>
     <row r="17">
@@ -8806,10 +8806,10 @@
         <v>0.3646858196514238</v>
       </c>
       <c r="M19" t="n">
-        <v>1.049435082735856</v>
+        <v>1.049434881562774</v>
       </c>
       <c r="N19" t="n">
-        <v>2.077559565604582</v>
+        <v>2.077559792426256</v>
       </c>
       <c r="O19" t="n">
         <v>3.911445831314191</v>
@@ -8870,10 +8870,10 @@
         <v>0.7833807602647949</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5004610296611962</v>
+        <v>0.5004609261435018</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1448315077000857</v>
+        <v>0.1448314813725506</v>
       </c>
     </row>
     <row r="21">
@@ -8983,7 +8983,7 @@
         <v>1.047150067967367</v>
       </c>
       <c r="N22" t="n">
-        <v>2.164071942848404</v>
+        <v>2.164072148139363</v>
       </c>
       <c r="O22" t="n">
         <v>2.598994957518313</v>
@@ -9044,10 +9044,10 @@
         <v>0.6548060241336471</v>
       </c>
       <c r="O23" t="n">
-        <v>1.65920335745686</v>
+        <v>1.65920279146648</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3854276475217568</v>
+        <v>0.3854275492293149</v>
       </c>
     </row>
     <row r="24">
@@ -9099,13 +9099,13 @@
         <v>0.7875979990880129</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8588519491099829</v>
+        <v>0.8588517292519513</v>
       </c>
       <c r="O24" t="n">
-        <v>1.340181239776441</v>
+        <v>1.340181065546919</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3276486692367206</v>
+        <v>0.3276486362883329</v>
       </c>
     </row>
     <row r="25">
@@ -9160,10 +9160,10 @@
         <v>1.934760870689353</v>
       </c>
       <c r="O25" t="n">
-        <v>2.39569024143366</v>
+        <v>2.395690970949991</v>
       </c>
       <c r="P25" t="n">
-        <v>0.50305897847966</v>
+        <v>0.5030590861166855</v>
       </c>
     </row>
     <row r="26">
@@ -9267,19 +9267,19 @@
         <v>0.2748827672081726</v>
       </c>
       <c r="L27" t="n">
-        <v>1.075968905565658</v>
+        <v>1.07596907305158</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6149652754285451</v>
+        <v>0.6149653767877017</v>
       </c>
       <c r="N27" t="n">
         <v>0.3370553376730621</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.1529099663065473</v>
+        <v>-0.1529100778529739</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.0538139864563566</v>
+        <v>-0.05381402798821633</v>
       </c>
     </row>
     <row r="28">
@@ -9502,16 +9502,16 @@
         <v>0.5209992771689507</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6544534921027096</v>
+        <v>0.6544536000993244</v>
       </c>
       <c r="N31" t="n">
         <v>0.7211841591030015</v>
       </c>
       <c r="O31" t="n">
-        <v>2.108816015705135</v>
+        <v>2.108816778347858</v>
       </c>
       <c r="P31" t="n">
-        <v>0.4594806459050509</v>
+        <v>0.4594807652497572</v>
       </c>
     </row>
     <row r="32">
@@ -9563,13 +9563,13 @@
         <v>0.7369847078951164</v>
       </c>
       <c r="N32" t="n">
-        <v>0.9085331369883911</v>
+        <v>0.9085333009222138</v>
       </c>
       <c r="O32" t="n">
-        <v>0.107430275131505</v>
+        <v>0.1074304959126502</v>
       </c>
       <c r="P32" t="n">
-        <v>0.03459918204610712</v>
+        <v>0.03459925079986448</v>
       </c>
     </row>
     <row r="33">
@@ -9740,10 +9740,10 @@
         <v>0.7864102406570395</v>
       </c>
       <c r="O35" t="n">
-        <v>1.092662839664121</v>
+        <v>1.092662413613029</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2790860255302279</v>
+        <v>0.2790859387259859</v>
       </c>
     </row>
     <row r="36">
@@ -9853,13 +9853,13 @@
         <v>0.4597709067870221</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8572214486104932</v>
+        <v>0.857221624589207</v>
       </c>
       <c r="O37" t="n">
-        <v>0.5056821132348193</v>
+        <v>0.5056819975705373</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1461578425846195</v>
+        <v>0.1461578132358998</v>
       </c>
     </row>
     <row r="38">
@@ -9914,10 +9914,10 @@
         <v>0.4963797129902412</v>
       </c>
       <c r="O38" t="n">
-        <v>1.989195941988775</v>
+        <v>1.989195728233403</v>
       </c>
       <c r="P38" t="n">
-        <v>0.4405161379581763</v>
+        <v>0.4405161036213987</v>
       </c>
     </row>
     <row r="39">
@@ -10085,7 +10085,7 @@
         <v>0.464424508532032</v>
       </c>
       <c r="N41" t="n">
-        <v>0.8322127886331152</v>
+        <v>0.8322125950288799</v>
       </c>
       <c r="O41" t="n">
         <v>2.619988281681814</v>
@@ -10140,16 +10140,16 @@
         <v>0.4351687906852153</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5970794839463738</v>
+        <v>0.5970793297282662</v>
       </c>
       <c r="N42" t="n">
-        <v>0.7072888748317931</v>
+        <v>0.7072890510685188</v>
       </c>
       <c r="O42" t="n">
-        <v>0.5781322561644866</v>
+        <v>0.5781324067451428</v>
       </c>
       <c r="P42" t="n">
-        <v>0.1642541613456896</v>
+        <v>0.1642541983755708</v>
       </c>
     </row>
     <row r="43">
@@ -10198,7 +10198,7 @@
         <v>0.2083075949739193</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5691756497960314</v>
+        <v>0.5691757520213794</v>
       </c>
       <c r="N43" t="n">
         <v>1.066681801848552</v>
@@ -10253,19 +10253,19 @@
         <v>0.1074745738446292</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2373210326688049</v>
+        <v>0.2373211135154816</v>
       </c>
       <c r="M44" t="n">
         <v>0.6725532653806028</v>
       </c>
       <c r="N44" t="n">
-        <v>0.7678686891300033</v>
+        <v>0.7678685240869232</v>
       </c>
       <c r="O44" t="n">
-        <v>2.614861980838965</v>
+        <v>2.614861635813813</v>
       </c>
       <c r="P44" t="n">
-        <v>0.5347250202701312</v>
+        <v>0.5347249714421951</v>
       </c>
     </row>
     <row r="45">
@@ -10372,16 +10372,16 @@
         <v>0.3576035549361085</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4898615847580414</v>
+        <v>0.4898614093580471</v>
       </c>
       <c r="N46" t="n">
-        <v>0.5449888346952552</v>
+        <v>0.5449887403851019</v>
       </c>
       <c r="O46" t="n">
-        <v>3.204875594846096</v>
+        <v>3.204875245557781</v>
       </c>
       <c r="P46" t="n">
-        <v>0.6140527239947218</v>
+        <v>0.6140526793029697</v>
       </c>
     </row>
     <row r="47">
@@ -10436,10 +10436,10 @@
         <v>1.216800995103654</v>
       </c>
       <c r="O47" t="n">
-        <v>7.999242660966431</v>
+        <v>7.999241895784309</v>
       </c>
       <c r="P47" t="n">
-        <v>1.080025475908879</v>
+        <v>1.080025416955831</v>
       </c>
     </row>
     <row r="48">
@@ -10485,7 +10485,7 @@
         <v>0.1588344475663799</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3730674098298923</v>
+        <v>0.3730674984874713</v>
       </c>
       <c r="M48" t="n">
         <v>0.4652694881446495</v>
@@ -10494,10 +10494,10 @@
         <v>0.5557666154226251</v>
       </c>
       <c r="O48" t="n">
-        <v>2.944142069166853</v>
+        <v>2.944141337628432</v>
       </c>
       <c r="P48" t="n">
-        <v>0.5799773095559535</v>
+        <v>0.5799772118740276</v>
       </c>
     </row>
     <row r="49">
@@ -10610,10 +10610,10 @@
         <v>1.240973747854169</v>
       </c>
       <c r="O50" t="n">
-        <v>4.016480873068667</v>
+        <v>4.016481501322419</v>
       </c>
       <c r="P50" t="n">
-        <v>0.7118526792736652</v>
+        <v>0.7118527507366323</v>
       </c>
     </row>
     <row r="51">
@@ -10662,16 +10662,16 @@
         <v>0.2869312401729278</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3933563106894491</v>
+        <v>0.3933564218574623</v>
       </c>
       <c r="N51" t="n">
-        <v>0.5579573919465786</v>
+        <v>0.557957252962022</v>
       </c>
       <c r="O51" t="n">
-        <v>1.467700548851763</v>
+        <v>1.467700897542499</v>
       </c>
       <c r="P51" t="n">
-        <v>0.3513385076292386</v>
+        <v>0.3513385712781276</v>
       </c>
     </row>
     <row r="52">
@@ -10717,19 +10717,19 @@
         <v>0.126865436250994</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3445162105689237</v>
+        <v>0.3445161115465409</v>
       </c>
       <c r="M52" t="n">
-        <v>0.6012877169548874</v>
+        <v>0.6012875764989747</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4359935140131956</v>
+        <v>0.4359934010579922</v>
       </c>
       <c r="O52" t="n">
-        <v>0.5766658700875982</v>
+        <v>0.576665733917856</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1638934448205172</v>
+        <v>0.1638934113137189</v>
       </c>
     </row>
     <row r="53">
@@ -10778,16 +10778,16 @@
         <v>0.3218151607304434</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3118651389908724</v>
+        <v>0.3118650013009467</v>
       </c>
       <c r="N53" t="n">
         <v>0.5889921807229168</v>
       </c>
       <c r="O53" t="n">
-        <v>0.7175557634189005</v>
+        <v>0.7175556454098011</v>
       </c>
       <c r="P53" t="n">
-        <v>0.1975774653725673</v>
+        <v>0.197577437945017</v>
       </c>
     </row>
     <row r="54">
@@ -10894,7 +10894,7 @@
         <v>0.1409289408147147</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2908345200376417</v>
+        <v>0.2908344036733637</v>
       </c>
       <c r="N55" t="n">
         <v>0.5724667585741585</v>
@@ -10952,16 +10952,16 @@
         <v>0.3212582508940127</v>
       </c>
       <c r="M56" t="n">
-        <v>0.2448211315770301</v>
+        <v>0.2448213138660691</v>
       </c>
       <c r="N56" t="n">
-        <v>0.4576784661227271</v>
+        <v>0.457678341142868</v>
       </c>
       <c r="O56" t="n">
-        <v>0.114125418410981</v>
+        <v>0.1141254914213907</v>
       </c>
       <c r="P56" t="n">
-        <v>0.03667993831405369</v>
+        <v>0.03667996095914794</v>
       </c>
     </row>
     <row r="57">
@@ -11010,10 +11010,10 @@
         <v>0.1579473453927676</v>
       </c>
       <c r="M57" t="n">
-        <v>0.6172268010528967</v>
+        <v>0.6172266533760966</v>
       </c>
       <c r="N57" t="n">
-        <v>0.6799990969403258</v>
+        <v>0.6799989375769546</v>
       </c>
       <c r="O57" t="n">
         <v>0.7480167765885775</v>
@@ -11129,13 +11129,13 @@
         <v>0.4668623076296718</v>
       </c>
       <c r="N59" t="n">
-        <v>0.6003683799691319</v>
+        <v>0.6003681904052782</v>
       </c>
       <c r="O59" t="n">
-        <v>0.7432747119466343</v>
+        <v>0.7432745994816587</v>
       </c>
       <c r="P59" t="n">
-        <v>0.2035254455028059</v>
+        <v>0.2035254196215412</v>
       </c>
     </row>
     <row r="60">
@@ -11181,7 +11181,7 @@
         <v>0.4270310256599397</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2319413904971739</v>
+        <v>0.2319414703852443</v>
       </c>
       <c r="M60" t="n">
         <v>0.1282334396660763</v>
@@ -11190,10 +11190,10 @@
         <v>0.3414415699410962</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.05938848093048055</v>
+        <v>-0.05938829464351314</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.02020151336552434</v>
+        <v>-0.02020144868289575</v>
       </c>
     </row>
     <row r="61">
@@ -11242,16 +11242,16 @@
         <v>0.1725504290294095</v>
       </c>
       <c r="M61" t="n">
-        <v>0.4346287277906973</v>
+        <v>0.4346285695630663</v>
       </c>
       <c r="N61" t="n">
         <v>0.3780069514871625</v>
       </c>
       <c r="O61" t="n">
-        <v>0.2310357147082136</v>
+        <v>0.231035831213243</v>
       </c>
       <c r="P61" t="n">
-        <v>0.07174191905480565</v>
+        <v>0.07174195286463436</v>
       </c>
     </row>
     <row r="62">
@@ -11297,7 +11297,7 @@
         <v>0.347713090342147</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2736120490920313</v>
+        <v>0.2736119297291315</v>
       </c>
       <c r="M62" t="n">
         <v>0.3850707005950704</v>
@@ -11306,10 +11306,10 @@
         <v>0.07180996512202564</v>
       </c>
       <c r="O62" t="n">
-        <v>-0.3373899525840073</v>
+        <v>-0.3373898879678457</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.1281950330726465</v>
+        <v>-0.1281950047338626</v>
       </c>
     </row>
     <row r="63">
@@ -11355,7 +11355,7 @@
         <v>0.08461549348110786</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2745989847338772</v>
+        <v>0.274598886136048</v>
       </c>
       <c r="M63" t="n">
         <v>0.6207230068043164</v>
@@ -11364,10 +11364,10 @@
         <v>0.4696102109034916</v>
       </c>
       <c r="O63" t="n">
-        <v>0.7875050852091201</v>
+        <v>0.787504891292615</v>
       </c>
       <c r="P63" t="n">
-        <v>0.2136191723201186</v>
+        <v>0.2136191284338478</v>
       </c>
     </row>
     <row r="64">
@@ -11422,10 +11422,10 @@
         <v>0.648742888541662</v>
       </c>
       <c r="O64" t="n">
-        <v>1.159948818540995</v>
+        <v>1.159948977230332</v>
       </c>
       <c r="P64" t="n">
-        <v>0.2926506040208239</v>
+        <v>0.292650635677417</v>
       </c>
     </row>
     <row r="65">
@@ -11480,10 +11480,10 @@
         <v>0.844323986344663</v>
       </c>
       <c r="O65" t="n">
-        <v>0.4512245493846418</v>
+        <v>0.4512246713931263</v>
       </c>
       <c r="P65" t="n">
-        <v>0.1321697287674437</v>
+        <v>0.1321697604956622</v>
       </c>
     </row>
     <row r="66">
@@ -11529,19 +11529,19 @@
         <v>0.1115833896680236</v>
       </c>
       <c r="L66" t="n">
-        <v>0.315145788296213</v>
+        <v>0.3151456466108802</v>
       </c>
       <c r="M66" t="n">
-        <v>0.4414587184736023</v>
+        <v>0.4414585482649973</v>
       </c>
       <c r="N66" t="n">
-        <v>0.4542947676610085</v>
+        <v>0.4542945944075247</v>
       </c>
       <c r="O66" t="n">
-        <v>1.698919493989254</v>
+        <v>1.698919195638623</v>
       </c>
       <c r="P66" t="n">
-        <v>0.3922908747579756</v>
+        <v>0.3922908234546203</v>
       </c>
     </row>
     <row r="67">
@@ -11593,13 +11593,13 @@
         <v>0.5112523113109544</v>
       </c>
       <c r="N67" t="n">
-        <v>0.8129973646398967</v>
+        <v>0.8129972133016266</v>
       </c>
       <c r="O67" t="n">
-        <v>0.6923301807323121</v>
+        <v>0.6923303125958395</v>
       </c>
       <c r="P67" t="n">
-        <v>0.1916856230521373</v>
+        <v>0.1916856540035179</v>
       </c>
     </row>
     <row r="68">
@@ -11709,13 +11709,13 @@
         <v>0.4067527182756163</v>
       </c>
       <c r="N69" t="n">
-        <v>0.4966616517963054</v>
+        <v>0.4966617794274946</v>
       </c>
       <c r="O69" t="n">
-        <v>0.2508245923221262</v>
+        <v>0.2508244140299554</v>
       </c>
       <c r="P69" t="n">
-        <v>0.07745416365640745</v>
+        <v>0.07745411246307143</v>
       </c>
     </row>
     <row r="70">
@@ -11767,13 +11767,13 @@
         <v>0.4304001426102013</v>
       </c>
       <c r="N70" t="n">
-        <v>0.5302237086809072</v>
+        <v>0.5302238288697811</v>
       </c>
       <c r="O70" t="n">
-        <v>1.68873450617062</v>
+        <v>1.688733949572943</v>
       </c>
       <c r="P70" t="n">
-        <v>0.39053729141199</v>
+        <v>0.3905371954598016</v>
       </c>
     </row>
     <row r="71">
@@ -11822,7 +11822,7 @@
         <v>0.2060150050758003</v>
       </c>
       <c r="M71" t="n">
-        <v>0.2760260569765189</v>
+        <v>0.2760261915175113</v>
       </c>
       <c r="N71" t="n">
         <v>0.3882114147541134</v>
@@ -11883,13 +11883,13 @@
         <v>0.5027803570900253</v>
       </c>
       <c r="N72" t="n">
-        <v>0.2222463279697615</v>
+        <v>0.2222464066080978</v>
       </c>
       <c r="O72" t="n">
-        <v>1.923381370994232</v>
+        <v>1.923382045800512</v>
       </c>
       <c r="P72" t="n">
-        <v>0.4298654038956351</v>
+        <v>0.4298655139145888</v>
       </c>
     </row>
     <row r="73">
@@ -11935,19 +11935,19 @@
         <v>0.1991505023460569</v>
       </c>
       <c r="L73" t="n">
-        <v>0.6049158529039811</v>
+        <v>0.6049160187110423</v>
       </c>
       <c r="M73" t="n">
-        <v>0.2629124606921402</v>
+        <v>0.2629125633624743</v>
       </c>
       <c r="N73" t="n">
         <v>0.09877683283924399</v>
       </c>
       <c r="O73" t="n">
-        <v>0.06933131949001914</v>
+        <v>0.06933124588236317</v>
       </c>
       <c r="P73" t="n">
-        <v>0.02259601427877445</v>
+        <v>0.02259599081523356</v>
       </c>
     </row>
     <row r="74">
@@ -12002,10 +12002,10 @@
         <v>0.4918967902991302</v>
       </c>
       <c r="O74" t="n">
-        <v>0.4125145335002922</v>
+        <v>0.412514901585205</v>
       </c>
       <c r="P74" t="n">
-        <v>0.1220123614741164</v>
+        <v>0.1220124589352463</v>
       </c>
     </row>
     <row r="75">
@@ -12054,16 +12054,16 @@
         <v>0.1604371086961003</v>
       </c>
       <c r="M75" t="n">
-        <v>0.3044663613544414</v>
+        <v>0.3044664598255193</v>
       </c>
       <c r="N75" t="n">
         <v>0.2862467388917629</v>
       </c>
       <c r="O75" t="n">
-        <v>0.03660550462567969</v>
+        <v>0.03660569117395829</v>
       </c>
       <c r="P75" t="n">
-        <v>0.01205590591966632</v>
+        <v>0.01205596662976771</v>
       </c>
     </row>
     <row r="76">
@@ -12118,10 +12118,10 @@
         <v>0.388967580800198</v>
       </c>
       <c r="O76" t="n">
-        <v>0.9587729035267052</v>
+        <v>0.9587726641874237</v>
       </c>
       <c r="P76" t="n">
-        <v>0.2512037265475311</v>
+        <v>0.2512036755866782</v>
       </c>
     </row>
     <row r="77">
@@ -12173,7 +12173,7 @@
         <v>0.4169196191077573</v>
       </c>
       <c r="N77" t="n">
-        <v>0.813945802536119</v>
+        <v>0.8139455896481234</v>
       </c>
       <c r="O77" t="n">
         <v>1.408132552529266</v>
@@ -12286,16 +12286,16 @@
         <v>0.05692703764779128</v>
       </c>
       <c r="M79" t="n">
-        <v>0.4989158733335077</v>
+        <v>0.4989157460211815</v>
       </c>
       <c r="N79" t="n">
         <v>1.008318902332786</v>
       </c>
       <c r="O79" t="n">
-        <v>6.080347394735076</v>
+        <v>6.080346684560581</v>
       </c>
       <c r="P79" t="n">
-        <v>0.9202223587537985</v>
+        <v>0.9202222945529472</v>
       </c>
     </row>
     <row r="80">
@@ -12408,10 +12408,10 @@
         <v>0.3570678065225157</v>
       </c>
       <c r="O81" t="n">
-        <v>0.2100920853317754</v>
+        <v>0.2100919990756327</v>
       </c>
       <c r="P81" t="n">
-        <v>0.06562926812924519</v>
+        <v>0.06562924280966453</v>
       </c>
     </row>
     <row r="82">
@@ -12463,7 +12463,7 @@
         <v>0.34884727475944</v>
       </c>
       <c r="N82" t="n">
-        <v>0.4151390795146346</v>
+        <v>0.4151389801954564</v>
       </c>
       <c r="O82" t="n">
         <v>0.4656127502698306</v>
@@ -12524,10 +12524,10 @@
         <v>-0.001362079971687136</v>
       </c>
       <c r="O83" t="n">
-        <v>0.2110834745000023</v>
+        <v>0.211083563293579</v>
       </c>
       <c r="P83" t="n">
-        <v>0.06592020051691039</v>
+        <v>0.06592022656710061</v>
       </c>
     </row>
     <row r="84">
@@ -12573,19 +12573,19 @@
         <v>-0.07790548166915867</v>
       </c>
       <c r="L84" t="n">
-        <v>0.103985943645923</v>
+        <v>0.1039860346970083</v>
       </c>
       <c r="M84" t="n">
         <v>0.4276654028666518</v>
       </c>
       <c r="N84" t="n">
-        <v>0.895459449746258</v>
+        <v>0.8954595839476545</v>
       </c>
       <c r="O84" t="n">
-        <v>2.101164755910948</v>
+        <v>2.1011651151452</v>
       </c>
       <c r="P84" t="n">
-        <v>0.458282329119958</v>
+        <v>0.4582823854283651</v>
       </c>
     </row>
     <row r="85">
@@ -12637,7 +12637,7 @@
         <v>0.3050683325982841</v>
       </c>
       <c r="N85" t="n">
-        <v>0.5489273340400254</v>
+        <v>0.5489274717851567</v>
       </c>
       <c r="O85" t="n">
         <v>0.7616492615638468</v>
@@ -12698,10 +12698,10 @@
         <v>0.2897783248220951</v>
       </c>
       <c r="O86" t="n">
-        <v>1.608840915547437</v>
+        <v>1.608841520229458</v>
       </c>
       <c r="P86" t="n">
-        <v>0.3766256766237019</v>
+        <v>0.3766257829826505</v>
       </c>
     </row>
     <row r="87">
@@ -12814,10 +12814,10 @@
         <v>0.4496647273181913</v>
       </c>
       <c r="O88" t="n">
-        <v>0.6362864183966708</v>
+        <v>0.6362866005059438</v>
       </c>
       <c r="P88" t="n">
-        <v>0.1783829277504001</v>
+        <v>0.1783829714661473</v>
       </c>
     </row>
     <row r="89">
@@ -12918,10 +12918,10 @@
         <v>0.0709989430307183</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2843567157611671</v>
+        <v>0.2843568656657363</v>
       </c>
       <c r="L90" t="n">
-        <v>0.1672134590478493</v>
+        <v>0.1672133352411842</v>
       </c>
       <c r="M90" t="n">
         <v>0.2586934336309059</v>
@@ -12930,10 +12930,10 @@
         <v>0.2322160303700607</v>
       </c>
       <c r="O90" t="n">
-        <v>0.6385127438639249</v>
+        <v>0.6385126218770467</v>
       </c>
       <c r="P90" t="n">
-        <v>0.1789171200869994</v>
+        <v>0.1789170908303004</v>
       </c>
     </row>
     <row r="91">
@@ -12988,10 +12988,10 @@
         <v>0.2252183446721026</v>
       </c>
       <c r="O91" t="n">
-        <v>0.6823875519900078</v>
+        <v>0.6823873276321057</v>
       </c>
       <c r="P91" t="n">
-        <v>0.1893472756803984</v>
+        <v>0.1893472228111945</v>
       </c>
     </row>
     <row r="92">
@@ -13040,16 +13040,16 @@
         <v>0.3044488624778559</v>
       </c>
       <c r="M92" t="n">
-        <v>0.287287018335779</v>
+        <v>0.2872871360192084</v>
       </c>
       <c r="N92" t="n">
-        <v>0.4631158519314058</v>
+        <v>0.4631160039588427</v>
       </c>
       <c r="O92" t="n">
-        <v>1.791401349960739</v>
+        <v>1.791401073279937</v>
       </c>
       <c r="P92" t="n">
-        <v>0.4080154751778875</v>
+        <v>0.4080154286575421</v>
       </c>
     </row>
     <row r="93">
@@ -13104,10 +13104,10 @@
         <v>0.2819495242476091</v>
       </c>
       <c r="O93" t="n">
-        <v>-0.09829641315533522</v>
+        <v>-0.0982964791015033</v>
       </c>
       <c r="P93" t="n">
-        <v>-0.033901816021213</v>
+        <v>-0.03390183957310444</v>
       </c>
     </row>
     <row r="94">
@@ -13159,13 +13159,13 @@
         <v>0.251197006309231</v>
       </c>
       <c r="N94" t="n">
-        <v>0.4144210954174619</v>
+        <v>0.4144212718255622</v>
       </c>
       <c r="O94" t="n">
-        <v>-0.1346379477218224</v>
+        <v>-0.1346380137541611</v>
       </c>
       <c r="P94" t="n">
-        <v>-0.0470591401028897</v>
+        <v>-0.04705916434126678</v>
       </c>
     </row>
     <row r="95">
@@ -13220,10 +13220,10 @@
         <v>0.5491392823779448</v>
       </c>
       <c r="O95" t="n">
-        <v>0.02649240488182047</v>
+        <v>0.0264923318133703</v>
       </c>
       <c r="P95" t="n">
-        <v>0.008753946439431726</v>
+        <v>0.008753922504171285</v>
       </c>
     </row>
     <row r="96">
@@ -13275,13 +13275,13 @@
         <v>0.1709792022826837</v>
       </c>
       <c r="N96" t="n">
-        <v>-0.04807708319289139</v>
+        <v>-0.04807697387233956</v>
       </c>
       <c r="O96" t="n">
-        <v>0.1462635671199797</v>
+        <v>0.1462634878630666</v>
       </c>
       <c r="P96" t="n">
-        <v>0.04655364911565374</v>
+        <v>0.04655362499478666</v>
       </c>
     </row>
     <row r="97">
@@ -13336,10 +13336,10 @@
         <v>0.2925211957741289</v>
       </c>
       <c r="O97" t="n">
-        <v>0.1680010064346713</v>
+        <v>0.1680012704771183</v>
       </c>
       <c r="P97" t="n">
-        <v>0.05312778811822305</v>
+        <v>0.05312786747615039</v>
       </c>
     </row>
     <row r="98">
@@ -13391,7 +13391,7 @@
         <v>0.359406819306697</v>
       </c>
       <c r="N98" t="n">
-        <v>0.4372242075736115</v>
+        <v>0.4372240728665548</v>
       </c>
       <c r="O98" t="n">
         <v>0.07462227487603634</v>
@@ -13510,10 +13510,10 @@
         <v>0.3248948740110196</v>
       </c>
       <c r="O100" t="n">
-        <v>1.151455329302251</v>
+        <v>1.151454834370358</v>
       </c>
       <c r="P100" t="n">
-        <v>0.2909540304189215</v>
+        <v>0.2909539314263367</v>
       </c>
     </row>
     <row r="101">
@@ -13562,16 +13562,16 @@
         <v>0.1819873818230484</v>
       </c>
       <c r="M101" t="n">
-        <v>0.3242768607757198</v>
+        <v>0.3242769561001735</v>
       </c>
       <c r="N101" t="n">
-        <v>0.3859514154851558</v>
+        <v>0.3859513110750123</v>
       </c>
       <c r="O101" t="n">
-        <v>1.892688500223942</v>
+        <v>1.89268804539302</v>
       </c>
       <c r="P101" t="n">
-        <v>0.4248436886468721</v>
+        <v>0.4248436139685925</v>
       </c>
     </row>
     <row r="102">
@@ -13675,19 +13675,19 @@
         <v>0.1790935150652453</v>
       </c>
       <c r="L103" t="n">
-        <v>0.03046308139455189</v>
+        <v>0.03046315030370605</v>
       </c>
       <c r="M103" t="n">
-        <v>0.1156219346058416</v>
+        <v>0.1156220153751077</v>
       </c>
       <c r="N103" t="n">
         <v>0.5890265404229613</v>
       </c>
       <c r="O103" t="n">
-        <v>1.744469511405606</v>
+        <v>1.744469267006956</v>
       </c>
       <c r="P103" t="n">
-        <v>0.4000798443247633</v>
+        <v>0.4000798027651065</v>
       </c>
     </row>
     <row r="104">
@@ -13742,10 +13742,10 @@
         <v>0.2616038537891479</v>
       </c>
       <c r="O104" t="n">
-        <v>0.6156602915418039</v>
+        <v>0.6156605181370405</v>
       </c>
       <c r="P104" t="n">
-        <v>0.1734106270788187</v>
+        <v>0.1734106819354921</v>
       </c>
     </row>
     <row r="105">
@@ -13797,13 +13797,13 @@
         <v>0.3382932993261842</v>
       </c>
       <c r="N105" t="n">
-        <v>0.2855321637657864</v>
+        <v>0.2855322695399887</v>
       </c>
       <c r="O105" t="n">
-        <v>2.524416012314875</v>
+        <v>2.524414819757526</v>
       </c>
       <c r="P105" t="n">
-        <v>0.5218168504740031</v>
+        <v>0.52181667882816</v>
       </c>
     </row>
     <row r="106">
@@ -13852,7 +13852,7 @@
         <v>0.09305686807827618</v>
       </c>
       <c r="M106" t="n">
-        <v>0.5932731315435242</v>
+        <v>0.5932732939822536</v>
       </c>
       <c r="N106" t="n">
         <v>0.5086176030072822</v>
@@ -13965,7 +13965,7 @@
         <v>0.1401461276085945</v>
       </c>
       <c r="N108" t="n">
-        <v>-0.03784548376855712</v>
+        <v>-0.03784538452945896</v>
       </c>
       <c r="O108" t="n">
         <v>0.2007649404318697</v>
@@ -14133,13 +14133,13 @@
         <v>0.2478394278729938</v>
       </c>
       <c r="L111" t="n">
-        <v>0.3645825333124433</v>
+        <v>0.3645826497598699</v>
       </c>
       <c r="M111" t="n">
-        <v>0.1741743073592374</v>
+        <v>0.174174221141751</v>
       </c>
       <c r="N111" t="n">
-        <v>0.0297456324569183</v>
+        <v>0.02974556614522283</v>
       </c>
       <c r="O111" t="n">
         <v>0.5847249125768266</v>
@@ -14191,19 +14191,19 @@
         <v>0.3010895470866641</v>
       </c>
       <c r="L112" t="n">
-        <v>0.03606512430334741</v>
+        <v>0.03606504318881587</v>
       </c>
       <c r="M112" t="n">
-        <v>0.03927916933190878</v>
+        <v>0.0392790877133351</v>
       </c>
       <c r="N112" t="n">
         <v>0.4006863759849693</v>
       </c>
       <c r="O112" t="n">
-        <v>-0.01872440084149241</v>
+        <v>-0.01872425531681399</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.006280833222551019</v>
+        <v>-0.006280784099193859</v>
       </c>
     </row>
     <row r="113">
@@ -14258,10 +14258,10 @@
         <v>0.0650439392656994</v>
       </c>
       <c r="O113" t="n">
-        <v>-0.2358187128344946</v>
+        <v>-0.2358186167516528</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.08574895325626275</v>
+        <v>-0.08574891493907444</v>
       </c>
     </row>
     <row r="114">
@@ -14310,16 +14310,16 @@
         <v>0.2409275730366955</v>
       </c>
       <c r="M114" t="n">
-        <v>0.1585602923077745</v>
+        <v>0.158560376014224</v>
       </c>
       <c r="N114" t="n">
         <v>0.2379182457469533</v>
       </c>
       <c r="O114" t="n">
-        <v>1.29277984479354</v>
+        <v>1.292780008707656</v>
       </c>
       <c r="P114" t="n">
-        <v>0.3186234204384399</v>
+        <v>0.3186234518618651</v>
       </c>
     </row>
     <row r="115">
@@ -14365,7 +14365,7 @@
         <v>0.2674919940791123</v>
       </c>
       <c r="L115" t="n">
-        <v>0.1902119288285962</v>
+        <v>0.1902118510422237</v>
       </c>
       <c r="M115" t="n">
         <v>0.2313952967882587</v>
@@ -14374,10 +14374,10 @@
         <v>0.09004282965414268</v>
       </c>
       <c r="O115" t="n">
-        <v>0.7204013567494316</v>
+        <v>0.7204011942265698</v>
       </c>
       <c r="P115" t="n">
-        <v>0.1982384702458255</v>
+        <v>0.1982384325140969</v>
       </c>
     </row>
     <row r="116">
@@ -14432,10 +14432,10 @@
         <v>0.3993680139754689</v>
       </c>
       <c r="O116" t="n">
-        <v>2.519792649446351</v>
+        <v>2.519793361838103</v>
       </c>
       <c r="P116" t="n">
-        <v>0.5211511146158376</v>
+        <v>0.5211512172407686</v>
       </c>
     </row>
     <row r="117">
@@ -14484,7 +14484,7 @@
         <v>0.1693374116089366</v>
       </c>
       <c r="M117" t="n">
-        <v>0.07796079354333241</v>
+        <v>0.07796092324858006</v>
       </c>
       <c r="N117" t="n">
         <v>0.01642823276177507</v>
@@ -14548,10 +14548,10 @@
         <v>0.3158747394645092</v>
       </c>
       <c r="O118" t="n">
-        <v>0.6864816402767755</v>
+        <v>0.6864817548232292</v>
       </c>
       <c r="P118" t="n">
-        <v>0.1903112525931623</v>
+        <v>0.1903112795419544</v>
       </c>
     </row>
     <row r="119">
@@ -14600,16 +14600,16 @@
         <v>0.2545143079147898</v>
       </c>
       <c r="M119" t="n">
-        <v>0.1555957279732088</v>
+        <v>0.155595812614775</v>
       </c>
       <c r="N119" t="n">
-        <v>0.1655904177287002</v>
+        <v>0.1655903316166938</v>
       </c>
       <c r="O119" t="n">
-        <v>0.4879297848853412</v>
+        <v>0.4879296445598287</v>
       </c>
       <c r="P119" t="n">
-        <v>0.1416355371070943</v>
+        <v>0.1416355012181703</v>
       </c>
     </row>
     <row r="120">
@@ -14658,16 +14658,16 @@
         <v>0.3652781397367928</v>
       </c>
       <c r="M120" t="n">
-        <v>0.2223280513708348</v>
+        <v>0.2223281667888524</v>
       </c>
       <c r="N120" t="n">
-        <v>0.3418575769044143</v>
+        <v>0.3418577159992171</v>
       </c>
       <c r="O120" t="n">
-        <v>-0.1456442767133548</v>
+        <v>-0.1456443330998952</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.05111646457142616</v>
+        <v>-0.05111648544651737</v>
       </c>
     </row>
     <row r="121">
@@ -14780,10 +14780,10 @@
         <v>0.3396480199556242</v>
       </c>
       <c r="O122" t="n">
-        <v>1.625990683213384</v>
+        <v>1.625990931284819</v>
       </c>
       <c r="P122" t="n">
-        <v>0.3796356041333353</v>
+        <v>0.3796356475770248</v>
       </c>
     </row>
     <row r="123">
@@ -14838,10 +14838,10 @@
         <v>0.4134651558531039</v>
       </c>
       <c r="O123" t="n">
-        <v>2.425586763525614</v>
+        <v>2.425587795680576</v>
       </c>
       <c r="P123" t="n">
-        <v>0.5074572006730975</v>
+        <v>0.5074573520757995</v>
       </c>
     </row>
     <row r="124">
@@ -14954,10 +14954,10 @@
         <v>0.3129973769259873</v>
       </c>
       <c r="O125" t="n">
-        <v>0.9073468534237881</v>
+        <v>0.9073466853460195</v>
       </c>
       <c r="P125" t="n">
-        <v>0.2401566861975029</v>
+        <v>0.2401566497694538</v>
       </c>
     </row>
     <row r="126">
@@ -15003,7 +15003,7 @@
         <v>0.01136424239358913</v>
       </c>
       <c r="L126" t="n">
-        <v>0.1156599791171433</v>
+        <v>0.1156599085423038</v>
       </c>
       <c r="M126" t="n">
         <v>0.4507533463093081</v>
@@ -15012,10 +15012,10 @@
         <v>0.3982133781081538</v>
       </c>
       <c r="O126" t="n">
-        <v>0.4734299726777418</v>
+        <v>0.4734298495813898</v>
       </c>
       <c r="P126" t="n">
-        <v>0.1379150288919322</v>
+        <v>0.1379149972032432</v>
       </c>
     </row>
     <row r="127">
@@ -15122,16 +15122,16 @@
         <v>0.1715594274074719</v>
       </c>
       <c r="M128" t="n">
-        <v>0.3365558416451422</v>
+        <v>0.3365559775818117</v>
       </c>
       <c r="N128" t="n">
         <v>0.3766168042573335</v>
       </c>
       <c r="O128" t="n">
-        <v>0.4853597232933391</v>
+        <v>0.4853598911836758</v>
       </c>
       <c r="P128" t="n">
-        <v>0.1409778527157657</v>
+        <v>0.1409778957040388</v>
       </c>
     </row>
     <row r="129">
@@ -15235,10 +15235,10 @@
         <v>0.132886945136413</v>
       </c>
       <c r="L130" t="n">
-        <v>0.3871418317128721</v>
+        <v>0.3871419195551167</v>
       </c>
       <c r="M130" t="n">
-        <v>0.09859148995969802</v>
+        <v>0.09859160015527402</v>
       </c>
       <c r="N130" t="n">
         <v>0.2141618380484327</v>
@@ -15354,7 +15354,7 @@
         <v>0.03948637118247422</v>
       </c>
       <c r="M132" t="n">
-        <v>0.3766242799123629</v>
+        <v>0.3766243723338898</v>
       </c>
       <c r="N132" t="n">
         <v>0.4201504957944857</v>
@@ -15415,7 +15415,7 @@
         <v>0.1605336524287004</v>
       </c>
       <c r="N133" t="n">
-        <v>0.280100694297319</v>
+        <v>0.2801007911554869</v>
       </c>
       <c r="O133" t="n">
         <v>0.9421318094244509</v>
@@ -15528,10 +15528,10 @@
         <v>-0.005733256131019937</v>
       </c>
       <c r="M135" t="n">
-        <v>0.3525922153623227</v>
+        <v>0.3525921256952782</v>
       </c>
       <c r="N135" t="n">
-        <v>0.2828821467222291</v>
+        <v>0.2828822273849125</v>
       </c>
       <c r="O135" t="n">
         <v>0.6439991794234468</v>
@@ -15589,13 +15589,13 @@
         <v>0.3413663766804726</v>
       </c>
       <c r="N136" t="n">
-        <v>0.5444314197099207</v>
+        <v>0.5444313243542522</v>
       </c>
       <c r="O136" t="n">
-        <v>2.172103123891395</v>
+        <v>2.172103325020033</v>
       </c>
       <c r="P136" t="n">
-        <v>0.469317887969207</v>
+        <v>0.4693179190234622</v>
       </c>
     </row>
     <row r="137">
@@ -15644,16 +15644,16 @@
         <v>0.08887946474092456</v>
       </c>
       <c r="M137" t="n">
-        <v>0.3587538152309926</v>
+        <v>0.3587536742140487</v>
       </c>
       <c r="N137" t="n">
-        <v>0.3033007972535779</v>
+        <v>0.303300667512032</v>
       </c>
       <c r="O137" t="n">
-        <v>0.4136064018948102</v>
+        <v>0.4136065545272491</v>
       </c>
       <c r="P137" t="n">
-        <v>0.1223013907853019</v>
+        <v>0.1223014311783448</v>
       </c>
     </row>
     <row r="138">
@@ -15696,22 +15696,22 @@
         <v>-0.06552925345004978</v>
       </c>
       <c r="K138" t="n">
-        <v>0.1034248110606391</v>
+        <v>0.1034249204991688</v>
       </c>
       <c r="L138" t="n">
-        <v>0.2386751217978451</v>
+        <v>0.2386748459755004</v>
       </c>
       <c r="M138" t="n">
-        <v>0.2215403186367892</v>
+        <v>0.2215401845147087</v>
       </c>
       <c r="N138" t="n">
-        <v>0.2701765157925058</v>
+        <v>0.2701763707775398</v>
       </c>
       <c r="O138" t="n">
-        <v>0.2580766815172924</v>
+        <v>0.2580769660479294</v>
       </c>
       <c r="P138" t="n">
-        <v>0.07953245695211208</v>
+        <v>0.07953253833560758</v>
       </c>
     </row>
     <row r="139">
@@ -15760,7 +15760,7 @@
         <v>0.3046121948192828</v>
       </c>
       <c r="M139" t="n">
-        <v>0.03346469016075826</v>
+        <v>0.03346479350998677</v>
       </c>
       <c r="N139" t="n">
         <v>0.2720502258349469</v>
@@ -15818,10 +15818,10 @@
         <v>0.196715819235189</v>
       </c>
       <c r="M140" t="n">
-        <v>0.3557026036573177</v>
+        <v>0.3557027605764222</v>
       </c>
       <c r="N140" t="n">
-        <v>0.3984078157863067</v>
+        <v>0.3984078992667268</v>
       </c>
       <c r="O140" t="n">
         <v>0.7048490101766114</v>
@@ -15928,16 +15928,16 @@
         <v>0.1205200649431666</v>
       </c>
       <c r="M142" t="n">
-        <v>0.06820808682552992</v>
+        <v>0.06820818937177031</v>
       </c>
       <c r="N142" t="n">
-        <v>0.0519494331737167</v>
+        <v>0.05194953262210444</v>
       </c>
       <c r="O142" t="n">
-        <v>0.7082037356374333</v>
+        <v>0.7082038667539341</v>
       </c>
       <c r="P142" t="n">
-        <v>0.1953999199834122</v>
+        <v>0.1953999505684934</v>
       </c>
     </row>
     <row r="143">
@@ -16044,16 +16044,16 @@
         <v>0.05581863928111264</v>
       </c>
       <c r="M144" t="n">
-        <v>0.4029977868886829</v>
+        <v>0.4029979412966904</v>
       </c>
       <c r="N144" t="n">
-        <v>0.07939207868312792</v>
+        <v>0.07939198728985808</v>
       </c>
       <c r="O144" t="n">
-        <v>0.4145934545304439</v>
+        <v>0.4145929836179667</v>
       </c>
       <c r="P144" t="n">
-        <v>0.1225625461795543</v>
+        <v>0.1225624216140202</v>
       </c>
     </row>
     <row r="145">
@@ -16105,7 +16105,7 @@
         <v>0.4573290641433352</v>
       </c>
       <c r="N145" t="n">
-        <v>0.3794758030653085</v>
+        <v>0.3794756847314473</v>
       </c>
       <c r="O145" t="n">
         <v>1.181847784012425</v>
@@ -16160,16 +16160,16 @@
         <v>0.1909314389649075</v>
       </c>
       <c r="M146" t="n">
-        <v>0.1474699684677809</v>
+        <v>0.1474700819060741</v>
       </c>
       <c r="N146" t="n">
         <v>0.1990450473958838</v>
       </c>
       <c r="O146" t="n">
-        <v>1.564290117787073</v>
+        <v>1.564290401044532</v>
       </c>
       <c r="P146" t="n">
-        <v>0.3687444973496947</v>
+        <v>0.3687445477479279</v>
       </c>
     </row>
     <row r="147">
@@ -16215,19 +16215,19 @@
         <v>0.116804997096835</v>
       </c>
       <c r="L147" t="n">
-        <v>0.1647606476637706</v>
+        <v>0.1647605626524771</v>
       </c>
       <c r="M147" t="n">
         <v>0.306813108525291</v>
       </c>
       <c r="N147" t="n">
-        <v>0.2232417348422668</v>
+        <v>0.2232416410800591</v>
       </c>
       <c r="O147" t="n">
-        <v>1.297936429551763</v>
+        <v>1.29793609866512</v>
       </c>
       <c r="P147" t="n">
-        <v>0.3196112318437083</v>
+        <v>0.3196111685054677</v>
       </c>
     </row>
     <row r="148">
@@ -16279,13 +16279,13 @@
         <v>0.09885159384394715</v>
       </c>
       <c r="N148" t="n">
-        <v>0.6169153798859857</v>
+        <v>0.6169155155643002</v>
       </c>
       <c r="O148" t="n">
-        <v>1.167427546563049</v>
+        <v>1.167427302767963</v>
       </c>
       <c r="P148" t="n">
-        <v>0.2941408007631965</v>
+        <v>0.2941407522409778</v>
       </c>
     </row>
     <row r="149">
@@ -16334,10 +16334,10 @@
         <v>0.02044471903418876</v>
       </c>
       <c r="M149" t="n">
-        <v>0.3101851267440761</v>
+        <v>0.3101852246070014</v>
       </c>
       <c r="N149" t="n">
-        <v>0.5225205879156687</v>
+        <v>0.5225207200693351</v>
       </c>
       <c r="O149" t="n">
         <v>4.523203126623596</v>
@@ -16398,10 +16398,10 @@
         <v>0.06605028771384602</v>
       </c>
       <c r="O150" t="n">
-        <v>0.5287746845861681</v>
+        <v>0.5287745416633323</v>
       </c>
       <c r="P150" t="n">
-        <v>0.1519876613689211</v>
+        <v>0.1519876254697246</v>
       </c>
     </row>
     <row r="151">
@@ -16456,10 +16456,10 @@
         <v>0.3398139198254648</v>
       </c>
       <c r="O151" t="n">
-        <v>0.721596897571487</v>
+        <v>0.7215972369237005</v>
       </c>
       <c r="P151" t="n">
-        <v>0.1985159658224713</v>
+        <v>0.1985160445708745</v>
       </c>
     </row>
     <row r="152">
@@ -16511,13 +16511,13 @@
         <v>0.3732141690609219</v>
       </c>
       <c r="N152" t="n">
-        <v>0.2025348852757491</v>
+        <v>0.2025349616272578</v>
       </c>
       <c r="O152" t="n">
-        <v>0.2612003851808071</v>
+        <v>0.2612004691636254</v>
       </c>
       <c r="P152" t="n">
-        <v>0.0804251827205138</v>
+        <v>0.08042520670220377</v>
       </c>
     </row>
     <row r="153">
@@ -16563,19 +16563,19 @@
         <v>0.1147244671210259</v>
       </c>
       <c r="L153" t="n">
-        <v>0.1065635806588607</v>
+        <v>0.1065636855551635</v>
       </c>
       <c r="M153" t="n">
-        <v>0.2429598130737627</v>
+        <v>0.2429599454230529</v>
       </c>
       <c r="N153" t="n">
-        <v>0.3397053451425422</v>
+        <v>0.3397051913887184</v>
       </c>
       <c r="O153" t="n">
-        <v>0.6063397821425773</v>
+        <v>0.6063395610968292</v>
       </c>
       <c r="P153" t="n">
-        <v>0.1711498623611027</v>
+        <v>0.1711498086411047</v>
       </c>
     </row>
     <row r="154">
@@ -16627,13 +16627,13 @@
         <v>0.1091513544503528</v>
       </c>
       <c r="N154" t="n">
-        <v>-0.1759183543333518</v>
+        <v>-0.1759182862648684</v>
       </c>
       <c r="O154" t="n">
-        <v>-0.264858708422025</v>
+        <v>-0.2648588167591039</v>
       </c>
       <c r="P154" t="n">
-        <v>-0.09747978331601803</v>
+        <v>-0.09747982765053798</v>
       </c>
     </row>
     <row r="155">
@@ -16746,10 +16746,10 @@
         <v>0.04434126399125637</v>
       </c>
       <c r="O156" t="n">
-        <v>0.6934306382440929</v>
+        <v>0.6934304833823375</v>
       </c>
       <c r="P156" t="n">
-        <v>0.1919438695933469</v>
+        <v>0.1919438332595045</v>
       </c>
     </row>
     <row r="157">
@@ -16804,10 +16804,10 @@
         <v>0.4514921086902193</v>
       </c>
       <c r="O157" t="n">
-        <v>2.816227029461178</v>
+        <v>2.816227373715022</v>
       </c>
       <c r="P157" t="n">
-        <v>0.5627088358425807</v>
+        <v>0.5627088828321425</v>
       </c>
     </row>
     <row r="158">
@@ -16859,13 +16859,13 @@
         <v>0.2718079261735782</v>
       </c>
       <c r="N158" t="n">
-        <v>0.3256513753006371</v>
+        <v>0.3256512209249651</v>
       </c>
       <c r="O158" t="n">
-        <v>0.4073015337698627</v>
+        <v>0.4073016207589173</v>
       </c>
       <c r="P158" t="n">
-        <v>0.120630367341557</v>
+        <v>0.120630390431272</v>
       </c>
     </row>
     <row r="159">
@@ -16920,10 +16920,10 @@
         <v>0.3473745926562224</v>
       </c>
       <c r="O159" t="n">
-        <v>0.03142137246183485</v>
+        <v>0.03142145858641054</v>
       </c>
       <c r="P159" t="n">
-        <v>0.01036596627812014</v>
+        <v>0.01036599440026298</v>
       </c>
     </row>
     <row r="160">
@@ -16975,13 +16975,13 @@
         <v>0.4828728947040777</v>
       </c>
       <c r="N160" t="n">
-        <v>0.4893984996721186</v>
+        <v>0.4893983912591739</v>
       </c>
       <c r="O160" t="n">
-        <v>1.794497087422397</v>
+        <v>1.794496705771215</v>
       </c>
       <c r="P160" t="n">
-        <v>0.4085357915997065</v>
+        <v>0.4085357274773311</v>
       </c>
     </row>
     <row r="161">
@@ -17036,10 +17036,10 @@
         <v>0.3301184891235773</v>
       </c>
       <c r="O161" t="n">
-        <v>1.546381801859154</v>
+        <v>1.54638160617304</v>
       </c>
       <c r="P161" t="n">
-        <v>0.3655507358902932</v>
+        <v>0.3655507009100292</v>
       </c>
     </row>
     <row r="162">
@@ -17152,10 +17152,10 @@
         <v>0.1761291456167489</v>
       </c>
       <c r="O163" t="n">
-        <v>0.2133872536132233</v>
+        <v>0.2133871258077586</v>
       </c>
       <c r="P163" t="n">
-        <v>0.06659565334050344</v>
+        <v>0.06659561589250873</v>
       </c>
     </row>
     <row r="164">
@@ -17207,13 +17207,13 @@
         <v>0.1370762962757166</v>
       </c>
       <c r="N164" t="n">
-        <v>0.05811762786015651</v>
+        <v>0.058117724867361</v>
       </c>
       <c r="O164" t="n">
-        <v>0.780420266399444</v>
+        <v>0.7804201290739785</v>
       </c>
       <c r="P164" t="n">
-        <v>0.2120136464749105</v>
+        <v>0.2120136153136642</v>
       </c>
     </row>
     <row r="165">
@@ -17259,19 +17259,19 @@
         <v>0.1345556035212814</v>
       </c>
       <c r="L165" t="n">
-        <v>0.114628736536015</v>
+        <v>0.1146286275630855</v>
       </c>
       <c r="M165" t="n">
-        <v>0.2063686188000573</v>
+        <v>0.2063684911508232</v>
       </c>
       <c r="N165" t="n">
         <v>0.2745234051339471</v>
       </c>
       <c r="O165" t="n">
-        <v>0.7553586231276228</v>
+        <v>0.7553591636579189</v>
       </c>
       <c r="P165" t="n">
-        <v>0.2062998829637208</v>
+        <v>0.2063000067829712</v>
       </c>
     </row>
     <row r="166">
@@ -17320,16 +17320,16 @@
         <v>0.00956513594245223</v>
       </c>
       <c r="M166" t="n">
-        <v>0.3001505473116719</v>
+        <v>0.3001506348297507</v>
       </c>
       <c r="N166" t="n">
         <v>0.4206960103159278</v>
       </c>
       <c r="O166" t="n">
-        <v>0.2266850846273538</v>
+        <v>0.2266853183484776</v>
       </c>
       <c r="P166" t="n">
-        <v>0.0704778733144964</v>
+        <v>0.07047794130077878</v>
       </c>
     </row>
     <row r="167">
@@ -17436,16 +17436,16 @@
         <v>0.1154085090361445</v>
       </c>
       <c r="M168" t="n">
-        <v>0.282435981429513</v>
+        <v>0.28243608657133</v>
       </c>
       <c r="N168" t="n">
-        <v>0.2239696972637208</v>
+        <v>0.2239696014902224</v>
       </c>
       <c r="O168" t="n">
-        <v>1.068466154442847</v>
+        <v>1.068466291206573</v>
       </c>
       <c r="P168" t="n">
-        <v>0.2741370358232631</v>
+        <v>0.2741370639045742</v>
       </c>
     </row>
     <row r="169">
@@ -17500,10 +17500,10 @@
         <v>0.3127600568707212</v>
       </c>
       <c r="O169" t="n">
-        <v>-0.07748335499715475</v>
+        <v>-0.07748328992339137</v>
       </c>
       <c r="P169" t="n">
-        <v>-0.02652514756755564</v>
+        <v>-0.02652512467811474</v>
       </c>
     </row>
     <row r="170">
@@ -17668,16 +17668,16 @@
         <v>0.09987687493092778</v>
       </c>
       <c r="M172" t="n">
-        <v>0.1798712186162488</v>
+        <v>0.1798710953759475</v>
       </c>
       <c r="N172" t="n">
-        <v>0.4868944855449215</v>
+        <v>0.4868943876829728</v>
       </c>
       <c r="O172" t="n">
-        <v>1.683232824999578</v>
+        <v>1.683233781074029</v>
       </c>
       <c r="P172" t="n">
-        <v>0.3895882059148579</v>
+        <v>0.3895883709582602</v>
       </c>
     </row>
     <row r="173">
@@ -17726,7 +17726,7 @@
         <v>0.241341629812232</v>
       </c>
       <c r="M173" t="n">
-        <v>0.2757838123858554</v>
+        <v>0.2757837358651039</v>
       </c>
       <c r="N173" t="n">
         <v>0.3236674282447001</v>
@@ -17784,16 +17784,16 @@
         <v>0.2277329447337089</v>
       </c>
       <c r="M174" t="n">
-        <v>0.04929028951922909</v>
+        <v>0.04929017674431413</v>
       </c>
       <c r="N174" t="n">
-        <v>-0.08359919215463352</v>
+        <v>-0.08359910613606414</v>
       </c>
       <c r="O174" t="n">
-        <v>-0.2467624450023983</v>
+        <v>-0.2467625612315604</v>
       </c>
       <c r="P174" t="n">
-        <v>-0.09013424071011167</v>
+        <v>-0.09013428750939811</v>
       </c>
     </row>
     <row r="175">
@@ -17848,10 +17848,10 @@
         <v>0.3569465226267545</v>
       </c>
       <c r="O175" t="n">
-        <v>1.132588215260121</v>
+        <v>1.13258774907762</v>
       </c>
       <c r="P175" t="n">
-        <v>0.2871692862736384</v>
+        <v>0.2871691924821542</v>
       </c>
     </row>
     <row r="176">
@@ -17900,10 +17900,10 @@
         <v>0.009351771380804452</v>
       </c>
       <c r="M176" t="n">
-        <v>0.2257927408708809</v>
+        <v>0.2257926502775351</v>
       </c>
       <c r="N176" t="n">
-        <v>0.2878386362360486</v>
+        <v>0.2878384362429225</v>
       </c>
       <c r="O176" t="n">
         <v>0.6581339217598892</v>
@@ -17961,7 +17961,7 @@
         <v>0.3291208207278233</v>
       </c>
       <c r="N177" t="n">
-        <v>0.2992519003250576</v>
+        <v>0.2992518189164555</v>
       </c>
       <c r="O177" t="n">
         <v>0.08132162476375604</v>
@@ -18022,10 +18022,10 @@
         <v>0.6046581441848011</v>
       </c>
       <c r="O178" t="n">
-        <v>-0.01890762505710342</v>
+        <v>-0.01890772851742251</v>
       </c>
       <c r="P178" t="n">
-        <v>-0.006342686300482958</v>
+        <v>-0.006342721228932424</v>
       </c>
     </row>
     <row r="179">
@@ -18071,7 +18071,7 @@
         <v>0.1857855907829851</v>
       </c>
       <c r="L179" t="n">
-        <v>0.01457220575137153</v>
+        <v>0.01457227031641617</v>
       </c>
       <c r="M179" t="n">
         <v>0.3279494672732126</v>
@@ -18132,10 +18132,10 @@
         <v>0.05883167510598653</v>
       </c>
       <c r="M180" t="n">
-        <v>0.4247844323911643</v>
+        <v>0.4247842669767563</v>
       </c>
       <c r="N180" t="n">
-        <v>0.4928120170659971</v>
+        <v>0.4928119262723867</v>
       </c>
       <c r="O180" t="n">
         <v>1.180031603720503</v>
@@ -18196,10 +18196,10 @@
         <v>0.1247843396453128</v>
       </c>
       <c r="O181" t="n">
-        <v>0.1315465161444644</v>
+        <v>0.1315468265398596</v>
       </c>
       <c r="P181" t="n">
-        <v>0.04205538912503592</v>
+        <v>0.04205548440736573</v>
       </c>
     </row>
     <row r="182">
@@ -18309,13 +18309,13 @@
         <v>0.1420278815398077</v>
       </c>
       <c r="N183" t="n">
-        <v>0.0938557250194183</v>
+        <v>0.09385582119733016</v>
       </c>
       <c r="O183" t="n">
-        <v>0.5929865154353513</v>
+        <v>0.5929866174234391</v>
       </c>
       <c r="P183" t="n">
-        <v>0.1678956293752882</v>
+        <v>0.1678956542994245</v>
       </c>
     </row>
     <row r="184">
@@ -18370,10 +18370,10 @@
         <v>0.04126845748304975</v>
       </c>
       <c r="O184" t="n">
-        <v>0.9171738153471363</v>
+        <v>0.9171739524329052</v>
       </c>
       <c r="P184" t="n">
-        <v>0.2422828686934522</v>
+        <v>0.2422828983028866</v>
       </c>
     </row>
     <row r="185">
@@ -18422,10 +18422,10 @@
         <v>-0.04971348504603135</v>
       </c>
       <c r="M185" t="n">
-        <v>0.2931833344102035</v>
+        <v>0.2931834350794018</v>
       </c>
       <c r="N185" t="n">
-        <v>0.2347926059017087</v>
+        <v>0.2347926976851742</v>
       </c>
       <c r="O185" t="n">
         <v>0.2590728569980931</v>
@@ -18544,10 +18544,10 @@
         <v>0.3131468895236511</v>
       </c>
       <c r="O187" t="n">
-        <v>0.5672495467789309</v>
+        <v>0.56724923915209</v>
       </c>
       <c r="P187" t="n">
-        <v>0.1615717760665571</v>
+        <v>0.1615717000670287</v>
       </c>
     </row>
     <row r="188">
@@ -18599,13 +18599,13 @@
         <v>0.3384301000400687</v>
       </c>
       <c r="N188" t="n">
-        <v>0.6124976021606194</v>
+        <v>0.6124974745530305</v>
       </c>
       <c r="O188" t="n">
-        <v>2.005115788640022</v>
+        <v>2.005116010240574</v>
       </c>
       <c r="P188" t="n">
-        <v>0.4430689096394125</v>
+        <v>0.443068945110576</v>
       </c>
     </row>
     <row r="189">
@@ -18715,13 +18715,13 @@
         <v>0.4199242005845418</v>
       </c>
       <c r="N190" t="n">
-        <v>0.5379331714978886</v>
+        <v>0.5379329512784023</v>
       </c>
       <c r="O190" t="n">
-        <v>1.715047548362976</v>
+        <v>1.715047719946583</v>
       </c>
       <c r="P190" t="n">
-        <v>0.3950586938238365</v>
+        <v>0.3950587232118055</v>
       </c>
     </row>
     <row r="191">
@@ -18776,10 +18776,10 @@
         <v>0.3576799252470817</v>
       </c>
       <c r="O191" t="n">
-        <v>0.769436555988734</v>
+        <v>0.7694362522578937</v>
       </c>
       <c r="P191" t="n">
-        <v>0.2095161319163561</v>
+        <v>0.2095160627102632</v>
       </c>
     </row>
     <row r="192">
@@ -18825,13 +18825,13 @@
         <v>0.1027833762533781</v>
       </c>
       <c r="L192" t="n">
-        <v>0.1133851862992545</v>
+        <v>0.1133851085229416</v>
       </c>
       <c r="M192" t="n">
         <v>0.230315905018146</v>
       </c>
       <c r="N192" t="n">
-        <v>0.1568769460348305</v>
+        <v>0.1568767780922702</v>
       </c>
       <c r="O192" t="n">
         <v>0.8521519892875533</v>
@@ -18883,7 +18883,7 @@
         <v>0.005649756700369712</v>
       </c>
       <c r="L193" t="n">
-        <v>0.1804240051786952</v>
+        <v>0.1804241195868519</v>
       </c>
       <c r="M193" t="n">
         <v>0.1833235769198072</v>
@@ -18892,10 +18892,10 @@
         <v>0.3289336012759463</v>
       </c>
       <c r="O193" t="n">
-        <v>0.5495679853756079</v>
+        <v>0.5495680839518331</v>
       </c>
       <c r="P193" t="n">
-        <v>0.157186997237577</v>
+        <v>0.1571870217758409</v>
       </c>
     </row>
     <row r="194">
@@ -18944,16 +18944,16 @@
         <v>0.2398177926549032</v>
       </c>
       <c r="M194" t="n">
-        <v>0.2804445958677164</v>
+        <v>0.2804444994161432</v>
       </c>
       <c r="N194" t="n">
-        <v>0.09499447979535525</v>
+        <v>0.09499455033148929</v>
       </c>
       <c r="O194" t="n">
-        <v>1.3327652341409</v>
+        <v>1.332765394207186</v>
       </c>
       <c r="P194" t="n">
-        <v>0.3262447510765751</v>
+        <v>0.3262447814106844</v>
       </c>
     </row>
     <row r="195">
@@ -19008,10 +19008,10 @@
         <v>-0.1311083732338738</v>
       </c>
       <c r="O195" t="n">
-        <v>0.5662889817248362</v>
+        <v>0.5662888514206319</v>
       </c>
       <c r="P195" t="n">
-        <v>0.1613344189959753</v>
+        <v>0.1613343867910282</v>
       </c>
     </row>
     <row r="196">
@@ -19063,7 +19063,7 @@
         <v>0.19579360682012</v>
       </c>
       <c r="N196" t="n">
-        <v>0.1905390936950522</v>
+        <v>0.1905389565601214</v>
       </c>
       <c r="O196" t="n">
         <v>0.6944442622875568</v>
@@ -19179,7 +19179,7 @@
         <v>0.03303626274433702</v>
       </c>
       <c r="N198" t="n">
-        <v>-0.000833031265417894</v>
+        <v>-0.0008330915884555701</v>
       </c>
       <c r="O198" t="n">
         <v>0.5968157865664248</v>
@@ -19234,16 +19234,16 @@
         <v>0.1473004588208582</v>
       </c>
       <c r="M199" t="n">
-        <v>0.06012941779403258</v>
+        <v>0.06012948371355442</v>
       </c>
       <c r="N199" t="n">
         <v>-0.1219583165312976</v>
       </c>
       <c r="O199" t="n">
-        <v>0.1695642826498522</v>
+        <v>0.1695642024184445</v>
       </c>
       <c r="P199" t="n">
-        <v>0.05359742118236754</v>
+        <v>0.05359739709031675</v>
       </c>
     </row>
     <row r="200">
@@ -19295,13 +19295,13 @@
         <v>0.229843557050859</v>
       </c>
       <c r="N200" t="n">
-        <v>0.3165495034903156</v>
+        <v>0.3165494105007383</v>
       </c>
       <c r="O200" t="n">
-        <v>1.545358410456975</v>
+        <v>1.545358236665777</v>
       </c>
       <c r="P200" t="n">
-        <v>0.3653677729975191</v>
+        <v>0.3653677419227981</v>
       </c>
     </row>
     <row r="201">
@@ -19350,16 +19350,16 @@
         <v>-0.01209882318050493</v>
       </c>
       <c r="M201" t="n">
-        <v>0.4856321969322701</v>
+        <v>0.4856320285941911</v>
       </c>
       <c r="N201" t="n">
-        <v>0.3451388918100016</v>
+        <v>0.3451390298147767</v>
       </c>
       <c r="O201" t="n">
-        <v>-0.0226513604174432</v>
+        <v>-0.02265143327234942</v>
       </c>
       <c r="P201" t="n">
-        <v>-0.007608191247570728</v>
+        <v>-0.007608215906329874</v>
       </c>
     </row>
     <row r="202">
@@ -19463,7 +19463,7 @@
         <v>0.1750921791087157</v>
       </c>
       <c r="L203" t="n">
-        <v>0.09207451800685962</v>
+        <v>0.09207441624519674</v>
       </c>
       <c r="M203" t="n">
         <v>0.05406490504757167</v>
@@ -19527,13 +19527,13 @@
         <v>0.1410036369406189</v>
       </c>
       <c r="N204" t="n">
-        <v>0.09196094750676109</v>
+        <v>0.09196086654265567</v>
       </c>
       <c r="O204" t="n">
-        <v>0.1767109939950966</v>
+        <v>0.1767108999755984</v>
       </c>
       <c r="P204" t="n">
-        <v>0.05573909381475817</v>
+        <v>0.05573906569681952</v>
       </c>
     </row>
     <row r="205">
@@ -19643,13 +19643,13 @@
         <v>0.2456643454061298</v>
       </c>
       <c r="N206" t="n">
-        <v>0.3197136273466803</v>
+        <v>0.3197137168984401</v>
       </c>
       <c r="O206" t="n">
-        <v>1.394449117785113</v>
+        <v>1.39444882298621</v>
       </c>
       <c r="P206" t="n">
-        <v>0.3378328968388267</v>
+        <v>0.3378328419352186</v>
       </c>
     </row>
     <row r="207">
@@ -19698,16 +19698,16 @@
         <v>0.03716575920629928</v>
       </c>
       <c r="M207" t="n">
-        <v>0.2416881583784654</v>
+        <v>0.2416882818866728</v>
       </c>
       <c r="N207" t="n">
         <v>0.1906766598589649</v>
       </c>
       <c r="O207" t="n">
-        <v>1.259024686627274</v>
+        <v>1.259024277825688</v>
       </c>
       <c r="P207" t="n">
-        <v>0.3121203132844268</v>
+        <v>0.312120234135683</v>
       </c>
     </row>
     <row r="208">
@@ -19756,16 +19756,16 @@
         <v>0.07802146944344424</v>
       </c>
       <c r="M208" t="n">
-        <v>0.193955797535792</v>
+        <v>0.1939558987590704</v>
       </c>
       <c r="N208" t="n">
         <v>0.2550685210828412</v>
       </c>
       <c r="O208" t="n">
-        <v>1.242318408513117</v>
+        <v>1.242318230000713</v>
       </c>
       <c r="P208" t="n">
-        <v>0.308877777236676</v>
+        <v>0.3088777425031424</v>
       </c>
     </row>
     <row r="209">
@@ -19817,7 +19817,7 @@
         <v>0.1369746166194397</v>
       </c>
       <c r="N209" t="n">
-        <v>0.1743206693543891</v>
+        <v>0.1743205702944532</v>
       </c>
       <c r="O209" t="n">
         <v>-0.2818619915365803</v>
@@ -19875,13 +19875,13 @@
         <v>0.0006619719431697479</v>
       </c>
       <c r="N210" t="n">
-        <v>0.01976685408688073</v>
+        <v>0.01976696747825635</v>
       </c>
       <c r="O210" t="n">
-        <v>0.2570676497566491</v>
+        <v>0.2570677359086813</v>
       </c>
       <c r="P210" t="n">
-        <v>0.07924376922776299</v>
+        <v>0.0792437938827717</v>
       </c>
     </row>
     <row r="211">
@@ -19927,7 +19927,7 @@
         <v>0.2509361041280398</v>
       </c>
       <c r="L211" t="n">
-        <v>0.05270151385069655</v>
+        <v>0.0527016135293914</v>
       </c>
       <c r="M211" t="n">
         <v>-0.01654500338403231</v>
@@ -19988,16 +19988,16 @@
         <v>0.04100075320936614</v>
       </c>
       <c r="M212" t="n">
-        <v>0.1867947939404582</v>
+        <v>0.1867946853525124</v>
       </c>
       <c r="N212" t="n">
-        <v>0.2427847708794675</v>
+        <v>0.2427846518040275</v>
       </c>
       <c r="O212" t="n">
-        <v>0.6163963686774723</v>
+        <v>0.6163965701084115</v>
       </c>
       <c r="P212" t="n">
-        <v>0.17358879770124</v>
+        <v>0.1735888464510575</v>
       </c>
     </row>
     <row r="213">
@@ -20052,10 +20052,10 @@
         <v>0.2189067007073793</v>
       </c>
       <c r="O213" t="n">
-        <v>-0.06153326053301633</v>
+        <v>-0.06153314063009463</v>
       </c>
       <c r="P213" t="n">
-        <v>-0.02094679131641752</v>
+        <v>-0.02094674962027276</v>
       </c>
     </row>
     <row r="214">
@@ -20110,10 +20110,10 @@
         <v>0.1208328155755274</v>
       </c>
       <c r="O214" t="n">
-        <v>0.1145957292170499</v>
+        <v>0.1145956273449926</v>
       </c>
       <c r="P214" t="n">
-        <v>0.03682579059121505</v>
+        <v>0.03682575900320595</v>
       </c>
     </row>
     <row r="215">
@@ -20168,10 +20168,10 @@
         <v>0.1861160332175145</v>
       </c>
       <c r="O215" t="n">
-        <v>1.313661132098159</v>
+        <v>1.313660900261441</v>
       </c>
       <c r="P215" t="n">
-        <v>0.3226144105951485</v>
+        <v>0.3226143664183254</v>
       </c>
     </row>
     <row r="216">
@@ -20266,19 +20266,19 @@
         <v>0.03762660174979615</v>
       </c>
       <c r="L217" t="n">
-        <v>0.1159827988930544</v>
+        <v>0.1159827075385567</v>
       </c>
       <c r="M217" t="n">
         <v>0.2128717905420583</v>
       </c>
       <c r="N217" t="n">
-        <v>0.1838762414688098</v>
+        <v>0.1838761386606607</v>
       </c>
       <c r="O217" t="n">
-        <v>0.9090028110351316</v>
+        <v>0.9090029446941104</v>
       </c>
       <c r="P217" t="n">
-        <v>0.2405154835257564</v>
+        <v>0.2405155124773513</v>
       </c>
     </row>
     <row r="218">
@@ -20330,13 +20330,13 @@
         <v>0.3683135297550315</v>
       </c>
       <c r="N218" t="n">
-        <v>0.2000301844145773</v>
+        <v>0.2000300973000848</v>
       </c>
       <c r="O218" t="n">
-        <v>-0.2119033818433436</v>
+        <v>-0.2119034569874603</v>
       </c>
       <c r="P218" t="n">
-        <v>-0.07630947668720134</v>
+        <v>-0.07630950604481612</v>
       </c>
     </row>
     <row r="219">
@@ -20391,10 +20391,10 @@
         <v>0.3129343886278289</v>
       </c>
       <c r="O219" t="n">
-        <v>1.132185226236718</v>
+        <v>1.132184914641308</v>
       </c>
       <c r="P219" t="n">
-        <v>0.2870882036144371</v>
+        <v>0.2870881409165076</v>
       </c>
     </row>
     <row r="220">
@@ -20443,10 +20443,10 @@
         <v>0.07409554941998886</v>
       </c>
       <c r="M220" t="n">
-        <v>0.127162245649171</v>
+        <v>0.1271623476657628</v>
       </c>
       <c r="N220" t="n">
-        <v>0.1903757187863218</v>
+        <v>0.1903756050063081</v>
       </c>
       <c r="O220" t="n">
         <v>0.7898875812649861</v>
@@ -20501,16 +20501,16 @@
         <v>0.1219746790039735</v>
       </c>
       <c r="M221" t="n">
-        <v>0.1934585869921226</v>
+        <v>0.1934586581407023</v>
       </c>
       <c r="N221" t="n">
         <v>0.06301527823325404</v>
       </c>
       <c r="O221" t="n">
-        <v>0.1388329217573243</v>
+        <v>0.1388330513264637</v>
       </c>
       <c r="P221" t="n">
-        <v>0.04428731937148056</v>
+        <v>0.04428735897559388</v>
       </c>
     </row>
     <row r="222">
@@ -20617,16 +20617,16 @@
         <v>0.01772591931096934</v>
       </c>
       <c r="M223" t="n">
-        <v>0.2628098751513974</v>
+        <v>0.2628097520833355</v>
       </c>
       <c r="N223" t="n">
-        <v>0.2020602541401888</v>
+        <v>0.2020603656522852</v>
       </c>
       <c r="O223" t="n">
-        <v>0.8017637926178562</v>
+        <v>0.8017639178844331</v>
       </c>
       <c r="P223" t="n">
-        <v>0.2168375932221729</v>
+        <v>0.2168376214221468</v>
       </c>
     </row>
     <row r="224">
@@ -20794,13 +20794,13 @@
         <v>0.03730800384636956</v>
       </c>
       <c r="N226" t="n">
-        <v>-0.09645565520920107</v>
+        <v>-0.09645559371058254</v>
       </c>
       <c r="O226" t="n">
-        <v>0.6847644808509457</v>
+        <v>0.6847645877600801</v>
       </c>
       <c r="P226" t="n">
-        <v>0.1899071275709032</v>
+        <v>0.1899071527399876</v>
       </c>
     </row>
     <row r="227">
@@ -20846,7 +20846,7 @@
         <v>0.1219882162728141</v>
       </c>
       <c r="L227" t="n">
-        <v>0.1104708423316103</v>
+        <v>0.1104709712579102</v>
       </c>
       <c r="M227" t="n">
         <v>0.1328490628654622</v>
@@ -20855,10 +20855,10 @@
         <v>0.05444970906187296</v>
       </c>
       <c r="O227" t="n">
-        <v>0.8422718918666963</v>
+        <v>0.8422724241293382</v>
       </c>
       <c r="P227" t="n">
-        <v>0.2258892650288604</v>
+        <v>0.2258893830887043</v>
       </c>
     </row>
     <row r="228">
@@ -20913,10 +20913,10 @@
         <v>0.1914009119586844</v>
       </c>
       <c r="O228" t="n">
-        <v>0.5093947722838765</v>
+        <v>0.5093953259634265</v>
       </c>
       <c r="P228" t="n">
-        <v>0.1470991215157949</v>
+        <v>0.1470992617762621</v>
       </c>
     </row>
     <row r="229">
@@ -20971,10 +20971,10 @@
         <v>0.2456262175925708</v>
       </c>
       <c r="O229" t="n">
-        <v>0.7428856780468096</v>
+        <v>0.7428858150539095</v>
       </c>
       <c r="P229" t="n">
-        <v>0.2034359115110453</v>
+        <v>0.2034359430448136</v>
       </c>
     </row>
     <row r="230">
@@ -21023,16 +21023,16 @@
         <v>-0.04157297801754956</v>
       </c>
       <c r="M230" t="n">
-        <v>0.2506553323072107</v>
+        <v>0.2506554283741282</v>
       </c>
       <c r="N230" t="n">
         <v>0.3842700870643858</v>
       </c>
       <c r="O230" t="n">
-        <v>0.8376414283202234</v>
+        <v>0.8376412209148318</v>
       </c>
       <c r="P230" t="n">
-        <v>0.2248613317021673</v>
+        <v>0.2248612856208425</v>
       </c>
     </row>
     <row r="231">
@@ -21078,19 +21078,19 @@
         <v>0.06028289635291317</v>
       </c>
       <c r="L231" t="n">
-        <v>-0.1298983642557504</v>
+        <v>-0.1298984459117237</v>
       </c>
       <c r="M231" t="n">
-        <v>0.2600877919023672</v>
+        <v>0.2600877062736155</v>
       </c>
       <c r="N231" t="n">
-        <v>0.273955360306237</v>
+        <v>0.2739552727823846</v>
       </c>
       <c r="O231" t="n">
-        <v>0.3558693896341356</v>
+        <v>0.3558692904930398</v>
       </c>
       <c r="P231" t="n">
-        <v>0.1068088388509563</v>
+        <v>0.1068088118743551</v>
       </c>
     </row>
     <row r="232">
@@ -21194,19 +21194,19 @@
         <v>0.1232004708687486</v>
       </c>
       <c r="L233" t="n">
-        <v>0.1662688593879569</v>
+        <v>0.166268989218737</v>
       </c>
       <c r="M233" t="n">
-        <v>0.04613470019569488</v>
+        <v>0.04613459573439371</v>
       </c>
       <c r="N233" t="n">
-        <v>0.06113287131322243</v>
+        <v>0.06113297879128754</v>
       </c>
       <c r="O233" t="n">
-        <v>1.656726644661225</v>
+        <v>1.656726476233345</v>
       </c>
       <c r="P233" t="n">
-        <v>0.3849973968352807</v>
+        <v>0.384997367567161</v>
       </c>
     </row>
     <row r="234">
@@ -21255,16 +21255,16 @@
         <v>0.09408964807744624</v>
       </c>
       <c r="M234" t="n">
-        <v>0.06601449503732626</v>
+        <v>0.06601439323261937</v>
       </c>
       <c r="N234" t="n">
-        <v>0.6141646378898127</v>
+        <v>0.6141645211800166</v>
       </c>
       <c r="O234" t="n">
-        <v>1.623239449859513</v>
+        <v>1.623239758098526</v>
       </c>
       <c r="P234" t="n">
-        <v>0.3791536240228446</v>
+        <v>0.3791536780411608</v>
       </c>
     </row>
     <row r="235">
@@ -21316,13 +21316,13 @@
         <v>0.170567706709787</v>
       </c>
       <c r="N235" t="n">
-        <v>0.125065914859205</v>
+        <v>0.1250658391292521</v>
       </c>
       <c r="O235" t="n">
-        <v>0.03200140824842856</v>
+        <v>0.0320014719679329</v>
       </c>
       <c r="P235" t="n">
-        <v>0.01055532910310086</v>
+        <v>0.01055534990154916</v>
       </c>
     </row>
     <row r="236">
@@ -21374,13 +21374,13 @@
         <v>0.2217294449467351</v>
       </c>
       <c r="N236" t="n">
-        <v>0.222018883836528</v>
+        <v>0.2220187863920859</v>
       </c>
       <c r="O236" t="n">
-        <v>0.3570551969048568</v>
+        <v>0.3570549565647678</v>
       </c>
       <c r="P236" t="n">
-        <v>0.1071314066807361</v>
+        <v>0.1071313413215482</v>
       </c>
     </row>
     <row r="237">
@@ -21435,10 +21435,10 @@
         <v>0.4507864582905534</v>
       </c>
       <c r="O237" t="n">
-        <v>0.5454965421533795</v>
+        <v>0.5454966734449098</v>
       </c>
       <c r="P237" t="n">
-        <v>0.1561726169699746</v>
+        <v>0.156172649709327</v>
       </c>
     </row>
     <row r="238">
@@ -21548,13 +21548,13 @@
         <v>0.103410522341304</v>
       </c>
       <c r="N239" t="n">
-        <v>0.05633555802969381</v>
+        <v>0.05633547234051672</v>
       </c>
       <c r="O239" t="n">
-        <v>0.9472896536615603</v>
+        <v>0.9472897992588727</v>
       </c>
       <c r="P239" t="n">
-        <v>0.248753884283758</v>
+        <v>0.2487539154065384</v>
       </c>
     </row>
     <row r="240">
@@ -21603,16 +21603,16 @@
         <v>-0.04979720663114628</v>
       </c>
       <c r="M240" t="n">
-        <v>0.1234594687515576</v>
+        <v>0.1234593346356239</v>
       </c>
       <c r="N240" t="n">
-        <v>0.2101587304853085</v>
+        <v>0.210158808292604</v>
       </c>
       <c r="O240" t="n">
-        <v>0.09491491782411066</v>
+        <v>0.09491479043675977</v>
       </c>
       <c r="P240" t="n">
-        <v>0.03068698249599322</v>
+        <v>0.03068694252439763</v>
       </c>
     </row>
     <row r="241">
@@ -21667,10 +21667,10 @@
         <v>0.3405802974904892</v>
       </c>
       <c r="O241" t="n">
-        <v>1.130730245568527</v>
+        <v>1.1307309075379</v>
       </c>
       <c r="P241" t="n">
-        <v>0.2867953718659517</v>
+        <v>0.2867955051252788</v>
       </c>
     </row>
     <row r="242">
@@ -21777,16 +21777,16 @@
         <v>0.0204187880306792</v>
       </c>
       <c r="M243" t="n">
-        <v>0.1058427062319407</v>
+        <v>0.105842797634309</v>
       </c>
       <c r="N243" t="n">
-        <v>-0.01016383317819025</v>
+        <v>-0.0101637599467852</v>
       </c>
       <c r="O243" t="n">
-        <v>0.6797982560784548</v>
+        <v>0.6797981506264288</v>
       </c>
       <c r="P243" t="n">
-        <v>0.1887368033253418</v>
+        <v>0.1887367784503891</v>
       </c>
     </row>
     <row r="244">
@@ -21896,13 +21896,13 @@
         <v>0.05701577383428469</v>
       </c>
       <c r="N245" t="n">
-        <v>0.5947372327202638</v>
+        <v>0.5947373476293731</v>
       </c>
       <c r="O245" t="n">
-        <v>1.58507813928998</v>
+        <v>1.585078441232003</v>
       </c>
       <c r="P245" t="n">
-        <v>0.3724332305349658</v>
+        <v>0.3724332839692306</v>
       </c>
     </row>
     <row r="246">
@@ -21954,13 +21954,13 @@
         <v>-0.0436194084282826</v>
       </c>
       <c r="N246" t="n">
-        <v>0.0583619654102896</v>
+        <v>0.0583621239027905</v>
       </c>
       <c r="O246" t="n">
-        <v>-0.05366424144262272</v>
+        <v>-0.05366430480050921</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.01821795903498535</v>
+        <v>-0.018217980945333</v>
       </c>
     </row>
     <row r="247">
@@ -22015,10 +22015,10 @@
         <v>0.1498216000547989</v>
       </c>
       <c r="O247" t="n">
-        <v>-0.1422763644438678</v>
+        <v>-0.1422762752728675</v>
       </c>
       <c r="P247" t="n">
-        <v>-0.04987125085450717</v>
+        <v>-0.04987121792862259</v>
       </c>
     </row>
     <row r="248">
@@ -22070,13 +22070,13 @@
         <v>0.2301363871666562</v>
       </c>
       <c r="N248" t="n">
-        <v>0.1194719613570194</v>
+        <v>0.1194720773921085</v>
       </c>
       <c r="O248" t="n">
-        <v>0.6720804536957528</v>
+        <v>0.672080583129413</v>
       </c>
       <c r="P248" t="n">
-        <v>0.1869134648646065</v>
+        <v>0.1869134954904355</v>
       </c>
     </row>
     <row r="249">
@@ -22131,10 +22131,10 @@
         <v>0.1260266891124986</v>
       </c>
       <c r="O249" t="n">
-        <v>0.1237141159695418</v>
+        <v>0.123714210078089</v>
       </c>
       <c r="P249" t="n">
-        <v>0.03964550170324177</v>
+        <v>0.03964553072590382</v>
       </c>
     </row>
     <row r="250">
@@ -22189,10 +22189,10 @@
         <v>0.1498342767084204</v>
       </c>
       <c r="O250" t="n">
-        <v>0.7789926086092147</v>
+        <v>0.7789923286925027</v>
       </c>
       <c r="P250" t="n">
-        <v>0.2116896024905948</v>
+        <v>0.2116895389392368</v>
       </c>
     </row>
     <row r="251">
@@ -22238,19 +22238,19 @@
         <v>0.1626303802221378</v>
       </c>
       <c r="L251" t="n">
-        <v>0.1161751037751451</v>
+        <v>0.1161750160375112</v>
       </c>
       <c r="M251" t="n">
-        <v>0.0006117255692408285</v>
+        <v>0.0006118665898291464</v>
       </c>
       <c r="N251" t="n">
         <v>-0.03126834960008573</v>
       </c>
       <c r="O251" t="n">
-        <v>1.234128309936482</v>
+        <v>1.234127958426677</v>
       </c>
       <c r="P251" t="n">
-        <v>0.3072822684722571</v>
+        <v>0.3072821999112054</v>
       </c>
     </row>
     <row r="252">
@@ -22305,10 +22305,10 @@
         <v>-0.06074398751886811</v>
       </c>
       <c r="O252" t="n">
-        <v>0.0254454057775515</v>
+        <v>0.02544515243233825</v>
       </c>
       <c r="P252" t="n">
-        <v>0.00841086100761701</v>
+        <v>0.00841077796204992</v>
       </c>
     </row>
     <row r="253">
@@ -22363,10 +22363,10 @@
         <v>0.141287920126193</v>
       </c>
       <c r="O253" t="n">
-        <v>1.130428945210185</v>
+        <v>1.130429073995309</v>
       </c>
       <c r="P253" t="n">
-        <v>0.2867347150114972</v>
+        <v>0.286734740939341</v>
       </c>
     </row>
     <row r="254">
@@ -22479,10 +22479,10 @@
         <v>0.2535972849324526</v>
       </c>
       <c r="O255" t="n">
-        <v>0.0390206540478244</v>
+        <v>0.03902058531936348</v>
       </c>
       <c r="P255" t="n">
-        <v>0.0128412803653104</v>
+        <v>0.01284125803305503</v>
       </c>
     </row>
     <row r="256">
@@ -22589,7 +22589,7 @@
         <v>0.2865080466664063</v>
       </c>
       <c r="M257" t="n">
-        <v>0.02478911556973018</v>
+        <v>0.02478899548079738</v>
       </c>
       <c r="N257" t="n">
         <v>-0.005439130212272381</v>
@@ -22653,10 +22653,10 @@
         <v>-0.04315110824296298</v>
       </c>
       <c r="O258" t="n">
-        <v>-0.1296089968721699</v>
+        <v>-0.129608822569351</v>
       </c>
       <c r="P258" t="n">
-        <v>-0.04521673618016209</v>
+        <v>-0.0452166724458164</v>
       </c>
     </row>
     <row r="259">
@@ -22702,19 +22702,19 @@
         <v>0.006515100826709475</v>
       </c>
       <c r="L259" t="n">
-        <v>-0.05851329849237763</v>
+        <v>-0.058513362484368</v>
       </c>
       <c r="M259" t="n">
-        <v>0.1556248289716944</v>
+        <v>0.1556247325597238</v>
       </c>
       <c r="N259" t="n">
         <v>0.2904968869277798</v>
       </c>
       <c r="O259" t="n">
-        <v>-0.2569027728899685</v>
+        <v>-0.256902852619369</v>
       </c>
       <c r="P259" t="n">
-        <v>-0.0942356702336995</v>
+        <v>-0.09423570262786762</v>
       </c>
     </row>
     <row r="260">
@@ -22769,10 +22769,10 @@
         <v>0.3001188406273414</v>
       </c>
       <c r="O260" t="n">
-        <v>0.2588110716766623</v>
+        <v>0.2588111569045748</v>
       </c>
       <c r="P260" t="n">
-        <v>0.07974247165471882</v>
+        <v>0.07974249602273753</v>
       </c>
     </row>
     <row r="261">
@@ -22824,13 +22824,13 @@
         <v>0.2621157397919072</v>
       </c>
       <c r="N261" t="n">
-        <v>0.2263365404348299</v>
+        <v>0.2263364220011423</v>
       </c>
       <c r="O261" t="n">
-        <v>2.508166967768155</v>
+        <v>2.508166725466464</v>
       </c>
       <c r="P261" t="n">
-        <v>0.5194745078349599</v>
+        <v>0.5194744728526597</v>
       </c>
     </row>
     <row r="262">
@@ -22940,13 +22940,13 @@
         <v>0.1679369429929798</v>
       </c>
       <c r="N263" t="n">
-        <v>0.3203208227345082</v>
+        <v>0.3203206723977363</v>
       </c>
       <c r="O263" t="n">
-        <v>0.7969887962615927</v>
+        <v>0.7969885177796778</v>
       </c>
       <c r="P263" t="n">
-        <v>0.2157616964573215</v>
+        <v>0.215761633654544</v>
       </c>
     </row>
     <row r="264">
@@ -22995,16 +22995,16 @@
         <v>-0.03429121391887746</v>
       </c>
       <c r="M264" t="n">
-        <v>0.1874407080103564</v>
+        <v>0.1874406227411509</v>
       </c>
       <c r="N264" t="n">
-        <v>0.2146582475266536</v>
+        <v>0.214658069080776</v>
       </c>
       <c r="O264" t="n">
-        <v>1.101796404521774</v>
+        <v>1.101796671668419</v>
       </c>
       <c r="P264" t="n">
-        <v>0.2809442098381065</v>
+        <v>0.2809442641091313</v>
       </c>
     </row>
     <row r="265">
@@ -23059,10 +23059,10 @@
         <v>0.1239751050858469</v>
       </c>
       <c r="O265" t="n">
-        <v>1.068144342608625</v>
+        <v>1.068144477677366</v>
       </c>
       <c r="P265" t="n">
-        <v>0.2740709556762619</v>
+        <v>0.2740709834124235</v>
       </c>
     </row>
     <row r="266">
@@ -23117,10 +23117,10 @@
         <v>-0.05839918298841251</v>
       </c>
       <c r="O266" t="n">
-        <v>0.4975255386274064</v>
+        <v>0.4975256457495552</v>
       </c>
       <c r="P266" t="n">
-        <v>0.1440844402935566</v>
+        <v>0.1440844675733988</v>
       </c>
     </row>
     <row r="267">
@@ -23166,19 +23166,19 @@
         <v>0.02459453930106847</v>
       </c>
       <c r="L267" t="n">
-        <v>0.1222425372399241</v>
+        <v>0.1222424687923207</v>
       </c>
       <c r="M267" t="n">
-        <v>0.09678684205428234</v>
+        <v>0.09678690743193297</v>
       </c>
       <c r="N267" t="n">
-        <v>0.08974417744365071</v>
+        <v>0.08974430652514442</v>
       </c>
       <c r="O267" t="n">
-        <v>0.3209342795300605</v>
+        <v>0.3209341846997416</v>
       </c>
       <c r="P267" t="n">
-        <v>0.09722005462700611</v>
+        <v>0.09722002837040589</v>
       </c>
     </row>
     <row r="268">
@@ -23224,7 +23224,7 @@
         <v>0.1005676604432586</v>
       </c>
       <c r="L268" t="n">
-        <v>0.02761221722066853</v>
+        <v>0.02761211231781302</v>
       </c>
       <c r="M268" t="n">
         <v>0.1454515310438935</v>
@@ -23233,10 +23233,10 @@
         <v>-0.02025664424471718</v>
       </c>
       <c r="O268" t="n">
-        <v>-0.05316858793650658</v>
+        <v>-0.05316849887824937</v>
       </c>
       <c r="P268" t="n">
-        <v>-0.01804658265930714</v>
+        <v>-0.01804655187203907</v>
       </c>
     </row>
     <row r="269">
@@ -23285,16 +23285,16 @@
         <v>0.05520454250449802</v>
       </c>
       <c r="M269" t="n">
-        <v>0.006043384967651333</v>
+        <v>0.006043294089846052</v>
       </c>
       <c r="N269" t="n">
         <v>0.05907427421068823</v>
       </c>
       <c r="O269" t="n">
-        <v>1.182080867096531</v>
+        <v>1.182080439567071</v>
       </c>
       <c r="P269" t="n">
-        <v>0.2970506841700149</v>
+        <v>0.2970505994607473</v>
       </c>
     </row>
     <row r="270">
@@ -23349,10 +23349,10 @@
         <v>0.2990028454187386</v>
       </c>
       <c r="O270" t="n">
-        <v>-0.3388986316127057</v>
+        <v>-0.3388986865824536</v>
       </c>
       <c r="P270" t="n">
-        <v>-0.1288571989914634</v>
+        <v>-0.1288572231362737</v>
       </c>
     </row>
     <row r="271">
@@ -23404,13 +23404,13 @@
         <v>0.1933531153298682</v>
       </c>
       <c r="N271" t="n">
-        <v>0.112862902082697</v>
+        <v>0.112863001292381</v>
       </c>
       <c r="O271" t="n">
-        <v>0.4641406667563528</v>
+        <v>0.4641404950302743</v>
       </c>
       <c r="P271" t="n">
-        <v>0.1355186401738735</v>
+        <v>0.1355185957796485</v>
       </c>
     </row>
     <row r="272">
@@ -23462,7 +23462,7 @@
         <v>-0.06439469086821192</v>
       </c>
       <c r="N272" t="n">
-        <v>-0.1808457798994281</v>
+        <v>-0.1808458517964463</v>
       </c>
       <c r="O272" t="n">
         <v>0.5463435482282253</v>
@@ -23581,10 +23581,10 @@
         <v>0.1112364052717845</v>
       </c>
       <c r="O274" t="n">
-        <v>0.2673871402499923</v>
+        <v>0.2673872190087911</v>
       </c>
       <c r="P274" t="n">
-        <v>0.08218895895281841</v>
+        <v>0.08218898136951558</v>
       </c>
     </row>
     <row r="275">
@@ -23636,13 +23636,13 @@
         <v>0.2032338034165588</v>
       </c>
       <c r="N275" t="n">
-        <v>0.05378014993841029</v>
+        <v>0.05378023019305411</v>
       </c>
       <c r="O275" t="n">
-        <v>0.5002007985101877</v>
+        <v>0.5002009611657592</v>
       </c>
       <c r="P275" t="n">
-        <v>0.1447653195885781</v>
+        <v>0.1447653609613619</v>
       </c>
     </row>
     <row r="276">
@@ -23697,10 +23697,10 @@
         <v>0.2568158920349024</v>
       </c>
       <c r="O276" t="n">
-        <v>0.47176860220122</v>
+        <v>0.4717687548668525</v>
       </c>
       <c r="P276" t="n">
-        <v>0.1374871815199137</v>
+        <v>0.1374872208501892</v>
       </c>
     </row>
     <row r="277">
@@ -23755,10 +23755,10 @@
         <v>-0.1309335525301775</v>
       </c>
       <c r="O277" t="n">
-        <v>0.1555867581824333</v>
+        <v>0.15558666688262</v>
       </c>
       <c r="P277" t="n">
-        <v>0.04938338949661625</v>
+        <v>0.04938336186029235</v>
       </c>
     </row>
     <row r="278">
@@ -23813,10 +23813,10 @@
         <v>-0.01756752518177174</v>
       </c>
       <c r="O278" t="n">
-        <v>0.04940651546724117</v>
+        <v>0.0494067613346294</v>
       </c>
       <c r="P278" t="n">
-        <v>0.0162048237344965</v>
+        <v>0.01620490309732436</v>
       </c>
     </row>
     <row r="279">
@@ -23923,16 +23923,16 @@
         <v>-0.01037016734676655</v>
       </c>
       <c r="M280" t="n">
-        <v>0.164218903395368</v>
+        <v>0.1642188313168558</v>
       </c>
       <c r="N280" t="n">
         <v>0.4486988685485209</v>
       </c>
       <c r="O280" t="n">
-        <v>1.621487120335759</v>
+        <v>1.621486937609073</v>
       </c>
       <c r="P280" t="n">
-        <v>0.3788464631013391</v>
+        <v>0.378846431064555</v>
       </c>
     </row>
     <row r="281">
@@ -23984,7 +23984,7 @@
         <v>0.2428597946823041</v>
       </c>
       <c r="N281" t="n">
-        <v>0.1161970375231971</v>
+        <v>0.1161969442961464</v>
       </c>
       <c r="O281" t="n">
         <v>1.456321948515411</v>
@@ -24045,10 +24045,10 @@
         <v>0.1609591501995882</v>
       </c>
       <c r="O282" t="n">
-        <v>0.5708881298235946</v>
+        <v>0.5708878467112108</v>
       </c>
       <c r="P282" t="n">
-        <v>0.1624699969468182</v>
+        <v>0.1624699271116581</v>
       </c>
     </row>
     <row r="283">
@@ -24094,7 +24094,7 @@
         <v>-0.02275407219147441</v>
       </c>
       <c r="L283" t="n">
-        <v>0.005604874503073232</v>
+        <v>0.00560494695267888</v>
       </c>
       <c r="M283" t="n">
         <v>0.1117583469151695</v>
@@ -24103,10 +24103,10 @@
         <v>0.2384230041337383</v>
       </c>
       <c r="O283" t="n">
-        <v>1.464015307485622</v>
+        <v>1.464015089996257</v>
       </c>
       <c r="P283" t="n">
-        <v>0.3506654803093798</v>
+        <v>0.3506654405699912</v>
       </c>
     </row>
     <row r="284">
@@ -24158,13 +24158,13 @@
         <v>0.1442082928142023</v>
       </c>
       <c r="N284" t="n">
-        <v>0.1816726655229237</v>
+        <v>0.1816725346790731</v>
       </c>
       <c r="O284" t="n">
-        <v>1.206065133801025</v>
+        <v>1.206065361817221</v>
       </c>
       <c r="P284" t="n">
-        <v>0.3017855412807777</v>
+        <v>0.301785586131097</v>
       </c>
     </row>
     <row r="285">
@@ -24213,16 +24213,16 @@
         <v>0.04289254729552083</v>
       </c>
       <c r="M285" t="n">
-        <v>0.07333516479541213</v>
+        <v>0.07333524018940807</v>
       </c>
       <c r="N285" t="n">
         <v>0.1217461989481243</v>
       </c>
       <c r="O285" t="n">
-        <v>0.6659942160451595</v>
+        <v>0.6659945793264945</v>
       </c>
       <c r="P285" t="n">
-        <v>0.1854716243724499</v>
+        <v>0.1854717105391523</v>
       </c>
     </row>
     <row r="286">
@@ -24561,7 +24561,7 @@
         <v>-0.06383268434913347</v>
       </c>
       <c r="M291" t="n">
-        <v>0.1824455822623738</v>
+        <v>0.1824456778727448</v>
       </c>
       <c r="N291" t="n">
         <v>0.3521430571258757</v>
@@ -24616,13 +24616,13 @@
         <v>0.1801031230250274</v>
       </c>
       <c r="L292" t="n">
-        <v>0.0126668643270742</v>
+        <v>0.01266694386250244</v>
       </c>
       <c r="M292" t="n">
-        <v>-0.02399884880253667</v>
+        <v>-0.02399877492233315</v>
       </c>
       <c r="N292" t="n">
-        <v>-0.07141434245732414</v>
+        <v>-0.07141427558115865</v>
       </c>
     </row>
     <row r="293">
@@ -24677,10 +24677,10 @@
         <v>-0.2139876689328551</v>
       </c>
       <c r="O293" t="n">
-        <v>0.8393330860143693</v>
+        <v>0.8393332040685171</v>
       </c>
       <c r="P293" t="n">
-        <v>0.2252370688790712</v>
+        <v>0.2252370950922526</v>
       </c>
     </row>
     <row r="294">
@@ -24790,13 +24790,13 @@
         <v>0.05216786267512852</v>
       </c>
       <c r="N295" t="n">
-        <v>0.06601992346306607</v>
+        <v>0.06602002069344937</v>
       </c>
       <c r="O295" t="n">
-        <v>0.01459526358604535</v>
+        <v>0.01459499935848263</v>
       </c>
       <c r="P295" t="n">
-        <v>0.004841608854710744</v>
+        <v>0.004841521625552625</v>
       </c>
     </row>
     <row r="296">
@@ -24909,10 +24909,10 @@
         <v>-0.1451038291761866</v>
       </c>
       <c r="O297" t="n">
-        <v>0.3219780639437455</v>
+        <v>0.3219783146959478</v>
       </c>
       <c r="P297" t="n">
-        <v>0.09750898135734198</v>
+        <v>0.09750905074900706</v>
       </c>
     </row>
     <row r="298">
@@ -25025,10 +25025,10 @@
         <v>0.008074437951749669</v>
       </c>
       <c r="O299" t="n">
-        <v>0.3506740075978794</v>
+        <v>0.3506738163840177</v>
       </c>
       <c r="P299" t="n">
-        <v>0.1053933497476516</v>
+        <v>0.1053932975844256</v>
       </c>
     </row>
     <row r="300">
@@ -25080,13 +25080,13 @@
         <v>0.01982419803495938</v>
       </c>
       <c r="N300" t="n">
-        <v>0.1404131729069211</v>
+        <v>0.1404130825559029</v>
       </c>
       <c r="O300" t="n">
-        <v>0.7799213261485203</v>
+        <v>0.7799212161010087</v>
       </c>
       <c r="P300" t="n">
-        <v>0.2119004187346769</v>
+        <v>0.2119003937585491</v>
       </c>
     </row>
     <row r="301">
@@ -25138,13 +25138,13 @@
         <v>0.09160401081971536</v>
       </c>
       <c r="N301" t="n">
-        <v>0.1534605363447441</v>
+        <v>0.1534606079091172</v>
       </c>
       <c r="O301" t="n">
-        <v>0.2487097814408012</v>
+        <v>0.2487099491838158</v>
       </c>
       <c r="P301" t="n">
-        <v>0.07684659187642473</v>
+        <v>0.07684664009512421</v>
       </c>
     </row>
     <row r="302">
@@ -25199,10 +25199,10 @@
         <v>0.0356159880192326</v>
       </c>
       <c r="O302" t="n">
-        <v>0.6303913386875719</v>
+        <v>0.6303919061466914</v>
       </c>
       <c r="P302" t="n">
-        <v>0.1769660974948071</v>
+        <v>0.1769662340428149</v>
       </c>
     </row>
     <row r="303">
@@ -25257,10 +25257,10 @@
         <v>0.187237439748716</v>
       </c>
       <c r="O303" t="n">
-        <v>0.01406264572258409</v>
+        <v>0.01406285357750736</v>
       </c>
       <c r="P303" t="n">
-        <v>0.004665745536298171</v>
+        <v>0.004665814179232619</v>
       </c>
     </row>
     <row r="304">
@@ -25370,13 +25370,13 @@
         <v>0.0751532578803551</v>
       </c>
       <c r="N305" t="n">
-        <v>0.1832471112296736</v>
+        <v>0.1832472424224549</v>
       </c>
       <c r="O305" t="n">
-        <v>0.6223191134852284</v>
+        <v>0.6223189901743116</v>
       </c>
       <c r="P305" t="n">
-        <v>0.1750204586110915</v>
+        <v>0.1750204288403654</v>
       </c>
     </row>
     <row r="306">
@@ -25431,10 +25431,10 @@
         <v>0.01017131510620772</v>
       </c>
       <c r="O306" t="n">
-        <v>0.2199591014061466</v>
+        <v>0.2199589751993203</v>
       </c>
       <c r="P306" t="n">
-        <v>0.06851778975220912</v>
+        <v>0.06851775290555207</v>
       </c>
     </row>
     <row r="307">
@@ -25483,7 +25483,7 @@
         <v>0.01148382683838323</v>
       </c>
       <c r="M307" t="n">
-        <v>0.2050647096278027</v>
+        <v>0.2050646277653749</v>
       </c>
       <c r="N307" t="n">
         <v>0.08792653317052612</v>
@@ -25541,16 +25541,16 @@
         <v>0.03115215981725927</v>
       </c>
       <c r="M308" t="n">
-        <v>0.1131308928043453</v>
+        <v>0.1131308170933103</v>
       </c>
       <c r="N308" t="n">
-        <v>0.05415575300768682</v>
+        <v>0.05415561720566142</v>
       </c>
       <c r="O308" t="n">
-        <v>-0.04831484274470799</v>
+        <v>-0.04831473206108172</v>
       </c>
       <c r="P308" t="n">
-        <v>-0.01637151129810532</v>
+        <v>-0.0163714731651986</v>
       </c>
     </row>
     <row r="309">
@@ -25605,10 +25605,10 @@
         <v>0.0604174851925583</v>
       </c>
       <c r="O309" t="n">
-        <v>1.025140064439509</v>
+        <v>1.025139837374126</v>
       </c>
       <c r="P309" t="n">
-        <v>0.2651781663970509</v>
+        <v>0.2651781191117331</v>
       </c>
     </row>
     <row r="310">
@@ -25657,16 +25657,16 @@
         <v>0.01965420179673005</v>
       </c>
       <c r="M310" t="n">
-        <v>0.0127053290049326</v>
+        <v>0.01270525710515136</v>
       </c>
       <c r="N310" t="n">
         <v>-0.05818180665692185</v>
       </c>
       <c r="O310" t="n">
-        <v>0.8095993610033951</v>
+        <v>0.8095992462154569</v>
       </c>
       <c r="P310" t="n">
-        <v>0.2185989831876065</v>
+        <v>0.2185989574212277</v>
       </c>
     </row>
     <row r="311">
@@ -25709,22 +25709,22 @@
         <v>-0.0558187978588961</v>
       </c>
       <c r="K311" t="n">
-        <v>0.01481591868893828</v>
+        <v>0.01481598225805514</v>
       </c>
       <c r="L311" t="n">
-        <v>-0.05741662845054885</v>
+        <v>-0.05741651876707365</v>
       </c>
       <c r="M311" t="n">
-        <v>0.1108501760231884</v>
+        <v>0.1108500998534341</v>
       </c>
       <c r="N311" t="n">
-        <v>0.1214130338099078</v>
+        <v>0.1214129561846997</v>
       </c>
       <c r="O311" t="n">
-        <v>0.2933223909920475</v>
+        <v>0.2933222877432109</v>
       </c>
       <c r="P311" t="n">
-        <v>0.08952098330038893</v>
+        <v>0.08952095430741758</v>
       </c>
     </row>
     <row r="312">
@@ -25779,10 +25779,10 @@
         <v>-0.04162965383770012</v>
       </c>
       <c r="O312" t="n">
-        <v>0.0771364397850125</v>
+        <v>0.07713654107576895</v>
       </c>
       <c r="P312" t="n">
-        <v>0.0250779840837192</v>
+        <v>0.02507801621549555</v>
       </c>
     </row>
     <row r="313">
@@ -25831,16 +25831,16 @@
         <v>-0.0715150103908655</v>
       </c>
       <c r="M313" t="n">
-        <v>0.1520544970850066</v>
+        <v>0.1520543857618195</v>
       </c>
       <c r="N313" t="n">
         <v>0.117652727617878</v>
       </c>
       <c r="O313" t="n">
-        <v>0.3251605362259513</v>
+        <v>0.3251603889348307</v>
       </c>
       <c r="P313" t="n">
-        <v>0.09838897398659041</v>
+        <v>0.0983889332914083</v>
       </c>
     </row>
     <row r="314">
@@ -25889,16 +25889,16 @@
         <v>-0.006421312171082216</v>
       </c>
       <c r="M314" t="n">
-        <v>0.1075805152867861</v>
+        <v>0.1075806108965838</v>
       </c>
       <c r="N314" t="n">
         <v>0.138379519698709</v>
       </c>
       <c r="O314" t="n">
-        <v>0.4071767931563939</v>
+        <v>0.4071769474859561</v>
       </c>
       <c r="P314" t="n">
-        <v>0.1205972561599731</v>
+        <v>0.1205972971264619</v>
       </c>
     </row>
     <row r="315">
@@ -25944,7 +25944,7 @@
         <v>0.01190047882675715</v>
       </c>
       <c r="L315" t="n">
-        <v>-0.03602878994386882</v>
+        <v>-0.03602885639378628</v>
       </c>
       <c r="M315" t="n">
         <v>0.08926022521803589</v>
@@ -26011,10 +26011,10 @@
         <v>-0.01345237958823753</v>
       </c>
       <c r="O316" t="n">
-        <v>-0.03317933747312996</v>
+        <v>-0.03317952045762562</v>
       </c>
       <c r="P316" t="n">
-        <v>-0.01118440368790907</v>
+        <v>-0.01118446607036239</v>
       </c>
     </row>
     <row r="317">
@@ -26124,13 +26124,13 @@
         <v>0.06360248261861345</v>
       </c>
       <c r="N318" t="n">
-        <v>-0.01728793582124111</v>
+        <v>-0.01728804507214121</v>
       </c>
       <c r="O318" t="n">
-        <v>0.738488836652581</v>
+        <v>0.7384890076093715</v>
       </c>
       <c r="P318" t="n">
-        <v>0.2024230754088008</v>
+        <v>0.2024231148227982</v>
       </c>
     </row>
     <row r="319">
@@ -26176,19 +26176,19 @@
         <v>0.113347551551209</v>
       </c>
       <c r="L319" t="n">
-        <v>0.01281146556083868</v>
+        <v>0.01281153672045421</v>
       </c>
       <c r="M319" t="n">
         <v>0.04691505624355496</v>
       </c>
       <c r="N319" t="n">
-        <v>-0.1037545904035153</v>
+        <v>-0.1037546461259657</v>
       </c>
       <c r="O319" t="n">
-        <v>-0.04141837878383348</v>
+        <v>-0.04141844252712901</v>
       </c>
       <c r="P319" t="n">
-        <v>-0.01400124624678822</v>
+        <v>-0.01400126810227764</v>
       </c>
     </row>
     <row r="320">
@@ -26353,16 +26353,16 @@
         <v>-0.04114253135148582</v>
       </c>
       <c r="M322" t="n">
-        <v>0.0115862775748774</v>
+        <v>0.01158636803821467</v>
       </c>
       <c r="N322" t="n">
-        <v>-0.04832422111158163</v>
+        <v>-0.04832430117694964</v>
       </c>
       <c r="O322" t="n">
-        <v>0.3309759713807905</v>
+        <v>0.330975658169772</v>
       </c>
       <c r="P322" t="n">
-        <v>0.09999338050583817</v>
+        <v>0.09999329422076575</v>
       </c>
     </row>
     <row r="323">
@@ -26408,19 +26408,19 @@
         <v>0.2588892489235901</v>
       </c>
       <c r="L323" t="n">
-        <v>-0.0007654523013652659</v>
+        <v>-0.000765345595664102</v>
       </c>
       <c r="M323" t="n">
-        <v>-0.1056824706986076</v>
+        <v>-0.1056825561730232</v>
       </c>
       <c r="N323" t="n">
         <v>-0.250877917157156</v>
       </c>
       <c r="O323" t="n">
-        <v>-0.003623369733852466</v>
+        <v>-0.003623688022300731</v>
       </c>
       <c r="P323" t="n">
-        <v>-0.001209251611318352</v>
+        <v>-0.001209357964539137</v>
       </c>
     </row>
     <row r="324">
@@ -26527,16 +26527,16 @@
         <v>0.08816456914526283</v>
       </c>
       <c r="M325" t="n">
-        <v>-0.07772128214602803</v>
+        <v>-0.07772135982794526</v>
       </c>
       <c r="N325" t="n">
-        <v>0.03285817021355264</v>
+        <v>0.03285826764003397</v>
       </c>
       <c r="O325" t="n">
-        <v>1.173520704935183</v>
+        <v>1.173521136378005</v>
       </c>
       <c r="P325" t="n">
-        <v>0.2953523794588619</v>
+        <v>0.295352465167799</v>
       </c>
     </row>
     <row r="326">
@@ -26582,19 +26582,19 @@
         <v>0.006812275012557434</v>
       </c>
       <c r="L326" t="n">
-        <v>-0.01272005396245857</v>
+        <v>-0.01272011943789064</v>
       </c>
       <c r="M326" t="n">
-        <v>0.08294404395433963</v>
+        <v>0.08294396517546487</v>
       </c>
       <c r="N326" t="n">
         <v>0.07769169369432771</v>
       </c>
       <c r="O326" t="n">
-        <v>1.296932571753733</v>
+        <v>1.296932394553522</v>
       </c>
       <c r="P326" t="n">
-        <v>0.3194190456493529</v>
+        <v>0.3194190117198503</v>
       </c>
     </row>
     <row r="327">
@@ -26698,19 +26698,19 @@
         <v>0.2139276837749682</v>
       </c>
       <c r="L328" t="n">
-        <v>-0.07507401473567887</v>
+        <v>-0.07507393403764651</v>
       </c>
       <c r="M328" t="n">
         <v>-0.1040417878760731</v>
       </c>
       <c r="N328" t="n">
-        <v>-0.1132101955828911</v>
+        <v>-0.1132101214022871</v>
       </c>
       <c r="O328" t="n">
-        <v>-0.322946345887327</v>
+        <v>-0.3229462594054375</v>
       </c>
       <c r="P328" t="n">
-        <v>-0.1219059612865909</v>
+        <v>-0.1219059238994858</v>
       </c>
     </row>
     <row r="329">
@@ -26759,16 +26759,16 @@
         <v>0.05708751757485753</v>
       </c>
       <c r="M329" t="n">
-        <v>0.0197932047001943</v>
+        <v>0.01979328363378685</v>
       </c>
       <c r="N329" t="n">
-        <v>-0.02981419843727373</v>
+        <v>-0.02981426987825397</v>
       </c>
       <c r="O329" t="n">
-        <v>-0.1257975429837185</v>
+        <v>-0.1257977169971704</v>
       </c>
       <c r="P329" t="n">
-        <v>-0.04382509596779316</v>
+        <v>-0.04382515941126108</v>
       </c>
     </row>
     <row r="330">
@@ -26933,16 +26933,16 @@
         <v>-0.125523151181942</v>
       </c>
       <c r="M332" t="n">
-        <v>0.08747410072165018</v>
+        <v>0.08747402425961015</v>
       </c>
       <c r="N332" t="n">
         <v>0.1486846029805129</v>
       </c>
       <c r="O332" t="n">
-        <v>-0.04653912383910486</v>
+        <v>-0.04653900628335672</v>
       </c>
       <c r="P332" t="n">
-        <v>-0.01576011775167585</v>
+        <v>-0.01576007730147533</v>
       </c>
     </row>
     <row r="333">
@@ -26988,7 +26988,7 @@
         <v>0.09129367204012473</v>
       </c>
       <c r="L333" t="n">
-        <v>-0.01077408359674092</v>
+        <v>-0.0107739909909218</v>
       </c>
       <c r="M333" t="n">
         <v>0.03525714817554371</v>
@@ -26997,10 +26997,10 @@
         <v>-0.07812422846412737</v>
       </c>
       <c r="O333" t="n">
-        <v>0.4249027014362599</v>
+        <v>0.424902605366289</v>
       </c>
       <c r="P333" t="n">
-        <v>0.1252829448476911</v>
+        <v>0.1252829195580341</v>
       </c>
     </row>
     <row r="334">
@@ -27052,13 +27052,13 @@
         <v>0.1949682089650253</v>
       </c>
       <c r="N334" t="n">
-        <v>0.02018718544822495</v>
+        <v>0.02018731633169635</v>
       </c>
       <c r="O334" t="n">
-        <v>0.3200385886763499</v>
+        <v>0.3200382599841287</v>
       </c>
       <c r="P334" t="n">
-        <v>0.09697199984826432</v>
+        <v>0.0969719087988572</v>
       </c>
     </row>
     <row r="335">
@@ -27226,13 +27226,13 @@
         <v>0.1098320252501155</v>
       </c>
       <c r="N337" t="n">
-        <v>0.05003916656072271</v>
+        <v>0.05003904873686316</v>
       </c>
       <c r="O337" t="n">
-        <v>0.2582220571403602</v>
+        <v>0.258222141728002</v>
       </c>
       <c r="P337" t="n">
-        <v>0.07957403673319785</v>
+        <v>0.07957406092570007</v>
       </c>
     </row>
     <row r="338">
@@ -27342,7 +27342,7 @@
         <v>0.09306322601692796</v>
       </c>
       <c r="N339" t="n">
-        <v>0.08780728265093152</v>
+        <v>0.08780716301072489</v>
       </c>
       <c r="O339" t="n">
         <v>0.3792879217288727</v>
@@ -27452,10 +27452,10 @@
         <v>0.01793896662272765</v>
       </c>
       <c r="L341" t="n">
-        <v>-0.09499981272485924</v>
+        <v>-0.09499990169284911</v>
       </c>
       <c r="M341" t="n">
-        <v>0.03204876968168491</v>
+        <v>0.03204888538264772</v>
       </c>
       <c r="N341" t="n">
         <v>0.09408820931552597</v>
@@ -27519,10 +27519,10 @@
         <v>-0.04848993136385737</v>
       </c>
       <c r="O342" t="n">
-        <v>0.5605873814443378</v>
+        <v>0.5605875509237987</v>
       </c>
       <c r="P342" t="n">
-        <v>0.1599235436737518</v>
+        <v>0.1599235856629013</v>
       </c>
     </row>
     <row r="343">
@@ -27745,16 +27745,16 @@
         <v>-0.2929495001656348</v>
       </c>
       <c r="M346" t="n">
-        <v>0.2891057002963058</v>
+        <v>0.2891055631241739</v>
       </c>
       <c r="N346" t="n">
         <v>0.2106368979796431</v>
       </c>
       <c r="O346" t="n">
-        <v>0.7912895616908981</v>
+        <v>0.7912894292596597</v>
       </c>
       <c r="P346" t="n">
-        <v>0.2144750534611437</v>
+        <v>0.214475023532158</v>
       </c>
     </row>
     <row r="347">
@@ -27867,10 +27867,10 @@
         <v>0.1044107071041074</v>
       </c>
       <c r="O348" t="n">
-        <v>0.439966402810914</v>
+        <v>0.4399662317885098</v>
       </c>
       <c r="P348" t="n">
-        <v>0.129234452320766</v>
+        <v>0.1292344076150012</v>
       </c>
     </row>
     <row r="349">
@@ -27919,16 +27919,16 @@
         <v>0.01507454587174761</v>
       </c>
       <c r="M349" t="n">
-        <v>0.03730043830615459</v>
+        <v>0.03730036145567328</v>
       </c>
       <c r="N349" t="n">
         <v>-0.07882718741609362</v>
       </c>
       <c r="O349" t="n">
-        <v>0.309093739568987</v>
+        <v>0.3090936171696819</v>
       </c>
       <c r="P349" t="n">
-        <v>0.093931803607052</v>
+        <v>0.09393176951311033</v>
       </c>
     </row>
     <row r="350">
@@ -28035,16 +28035,16 @@
         <v>-0.07461314311119027</v>
       </c>
       <c r="M351" t="n">
-        <v>-0.07091054064309044</v>
+        <v>-0.07091059651133125</v>
       </c>
       <c r="N351" t="n">
         <v>-0.1348163096220562</v>
       </c>
       <c r="O351" t="n">
-        <v>0.5000045628941563</v>
+        <v>0.500004417269446</v>
       </c>
       <c r="P351" t="n">
-        <v>0.1447154032654723</v>
+        <v>0.1447153662213951</v>
       </c>
     </row>
     <row r="352">
@@ -28093,16 +28093,16 @@
         <v>0.1669805869763425</v>
       </c>
       <c r="M352" t="n">
-        <v>-0.07280577356400963</v>
+        <v>-0.07280570295080058</v>
       </c>
       <c r="N352" t="n">
         <v>0.21257839798643</v>
       </c>
       <c r="O352" t="n">
-        <v>3.473296395192242</v>
+        <v>3.473296806095776</v>
       </c>
       <c r="P352" t="n">
-        <v>0.6476914633922175</v>
+        <v>0.6476915138428745</v>
       </c>
     </row>
     <row r="353">
@@ -28151,7 +28151,7 @@
         <v>-0.03597660133048808</v>
       </c>
       <c r="M353" t="n">
-        <v>0.02417224856964273</v>
+        <v>0.02417235300253728</v>
       </c>
       <c r="N353" t="n">
         <v>-0.0384887955845743</v>
@@ -28206,7 +28206,7 @@
         <v>0.1126728480893255</v>
       </c>
       <c r="L354" t="n">
-        <v>-0.160526372347893</v>
+        <v>-0.1605264404314141</v>
       </c>
       <c r="M354" t="n">
         <v>-0.01633001000704204</v>
@@ -28322,13 +28322,13 @@
         <v>-0.01383920332841315</v>
       </c>
       <c r="L356" t="n">
-        <v>0.008647118056218428</v>
+        <v>0.008647013391866354</v>
       </c>
       <c r="M356" t="n">
-        <v>0.05082961085910243</v>
+        <v>0.050829724460842</v>
       </c>
       <c r="N356" t="n">
-        <v>-0.006906588041705741</v>
+        <v>-0.006906689503021202</v>
       </c>
       <c r="O356" t="n">
         <v>0.06942605279104974</v>
@@ -28438,19 +28438,19 @@
         <v>-0.1530881210986831</v>
       </c>
       <c r="L358" t="n">
-        <v>0.01340157961019517</v>
+        <v>0.01340150940180584</v>
       </c>
       <c r="M358" t="n">
         <v>0.08685784587840417</v>
       </c>
       <c r="N358" t="n">
-        <v>0.2468314875595878</v>
+        <v>0.2468315938371159</v>
       </c>
       <c r="O358" t="n">
-        <v>0.4156870908917405</v>
+        <v>0.4156868168666434</v>
       </c>
       <c r="P358" t="n">
-        <v>0.1228517597752146</v>
+        <v>0.1228516873275707</v>
       </c>
     </row>
     <row r="359">
@@ -28499,16 +28499,16 @@
         <v>-0.03770694992187318</v>
       </c>
       <c r="M359" t="n">
-        <v>-0.03417969191831716</v>
+        <v>-0.03417962669867658</v>
       </c>
       <c r="N359" t="n">
-        <v>-0.0262608925944825</v>
+        <v>-0.0262608263009807</v>
       </c>
       <c r="O359" t="n">
-        <v>-0.571127605230221</v>
+        <v>-0.5711275795101648</v>
       </c>
       <c r="P359" t="n">
-        <v>-0.2458761125160618</v>
+        <v>-0.2458760974407864</v>
       </c>
     </row>
     <row r="360">
@@ -28554,19 +28554,19 @@
         <v>-0.0322147897345425</v>
       </c>
       <c r="L360" t="n">
-        <v>-0.06933040327359996</v>
+        <v>-0.06933051097742304</v>
       </c>
       <c r="M360" t="n">
-        <v>0.01419508461239238</v>
+        <v>0.01419514856424797</v>
       </c>
       <c r="N360" t="n">
-        <v>0.1318369072321797</v>
+        <v>0.1318368275836443</v>
       </c>
       <c r="O360" t="n">
-        <v>0.7264201939439894</v>
+        <v>0.7264205645677209</v>
       </c>
       <c r="P360" t="n">
-        <v>0.1996341926525196</v>
+        <v>0.1996342784973737</v>
       </c>
     </row>
     <row r="361">
@@ -28618,13 +28618,13 @@
         <v>-0.1840159264162897</v>
       </c>
       <c r="N361" t="n">
-        <v>-0.2731700343262908</v>
+        <v>-0.2731700783558952</v>
       </c>
       <c r="O361" t="n">
-        <v>0.03686059578692591</v>
+        <v>0.03686041658204986</v>
       </c>
       <c r="P361" t="n">
-        <v>0.01213891575038106</v>
+        <v>0.01213885743966903</v>
       </c>
     </row>
     <row r="362">
@@ -28676,7 +28676,7 @@
         <v>0.0944478834912541</v>
       </c>
       <c r="N362" t="n">
-        <v>0.1230309775069898</v>
+        <v>0.1230310728610875</v>
       </c>
       <c r="O362" t="n">
         <v>0.4504954273642245</v>
@@ -28731,16 +28731,16 @@
         <v>-0.02600124010743932</v>
       </c>
       <c r="M363" t="n">
-        <v>-0.1072347825721688</v>
+        <v>-0.1072349700791979</v>
       </c>
       <c r="N363" t="n">
         <v>-0.2459691381764462</v>
       </c>
       <c r="O363" t="n">
-        <v>-0.02331028093473653</v>
+        <v>-0.02331061756058639</v>
       </c>
       <c r="P363" t="n">
-        <v>-0.007831262219231805</v>
+        <v>-0.007831376206194229</v>
       </c>
     </row>
     <row r="364">
@@ -28792,13 +28792,13 @@
         <v>0.02515135393458134</v>
       </c>
       <c r="N364" t="n">
-        <v>-0.005783205337094643</v>
+        <v>-0.005783134050531991</v>
       </c>
       <c r="O364" t="n">
-        <v>0.1011656573652531</v>
+        <v>0.1011654824689232</v>
       </c>
       <c r="P364" t="n">
-        <v>0.03264461852724554</v>
+        <v>0.03264456385616055</v>
       </c>
     </row>
     <row r="365">
@@ -28844,7 +28844,7 @@
         <v>-0.2280139678632949</v>
       </c>
       <c r="L365" t="n">
-        <v>-0.2362804556178106</v>
+        <v>-0.2362803900660917</v>
       </c>
       <c r="M365" t="n">
         <v>0.05289338443679492</v>
@@ -28905,16 +28905,16 @@
         <v>-0.03826741127594757</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.09709777756542803</v>
+        <v>-0.0970976865538572</v>
       </c>
       <c r="N366" t="n">
-        <v>-0.01414074622092021</v>
+        <v>-0.01414063771710605</v>
       </c>
       <c r="O366" t="n">
-        <v>0.8103952419184919</v>
+        <v>0.810394876018977</v>
       </c>
       <c r="P366" t="n">
-        <v>0.2187776079050736</v>
+        <v>0.218777525795901</v>
       </c>
     </row>
     <row r="367">
@@ -29143,10 +29143,10 @@
         <v>-0.05439277304811962</v>
       </c>
       <c r="O370" t="n">
-        <v>-0.2101337060254957</v>
+        <v>-0.210133655815647</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.07561860928899866</v>
+        <v>-0.07561858970211877</v>
       </c>
     </row>
     <row r="371">
@@ -29201,10 +29201,10 @@
         <v>0.09951822837110225</v>
       </c>
       <c r="O371" t="n">
-        <v>0.4771150856830553</v>
+        <v>0.4771149778140997</v>
       </c>
       <c r="P371" t="n">
-        <v>0.1388628975804838</v>
+        <v>0.138862869857987</v>
       </c>
     </row>
     <row r="372">
@@ -29314,13 +29314,13 @@
         <v>0.07153813390602926</v>
       </c>
       <c r="N373" t="n">
-        <v>0.04353608729540137</v>
+        <v>0.04353601499707183</v>
       </c>
       <c r="O373" t="n">
-        <v>0.4659835011707709</v>
+        <v>0.465983643853549</v>
       </c>
       <c r="P373" t="n">
-        <v>0.1359948456718012</v>
+        <v>0.1359948825268988</v>
       </c>
     </row>
     <row r="374">
@@ -29366,19 +29366,19 @@
         <v>-0.01500936686183141</v>
       </c>
       <c r="L374" t="n">
-        <v>-0.06032984334381175</v>
+        <v>-0.06032995484004167</v>
       </c>
       <c r="M374" t="n">
         <v>0.0005086955480833044</v>
       </c>
       <c r="N374" t="n">
-        <v>0.02215332177210061</v>
+        <v>0.02215325580742489</v>
       </c>
       <c r="O374" t="n">
-        <v>0.5027980454480763</v>
+        <v>0.502797902860866</v>
       </c>
       <c r="P374" t="n">
-        <v>0.1454255698808442</v>
+        <v>0.1454255336544104</v>
       </c>
     </row>
     <row r="375">
@@ -29430,7 +29430,7 @@
         <v>0.01251018479696597</v>
       </c>
       <c r="N375" t="n">
-        <v>-0.07984962493191683</v>
+        <v>-0.0798495614278758</v>
       </c>
       <c r="O375" t="n">
         <v>1.096316136625034</v>
@@ -29491,10 +29491,10 @@
         <v>-0.04045530967533684</v>
       </c>
       <c r="O376" t="n">
-        <v>0.05101395003046094</v>
+        <v>0.05101380533098299</v>
       </c>
       <c r="P376" t="n">
-        <v>0.01672341826377921</v>
+        <v>0.01672337160427984</v>
       </c>
     </row>
     <row r="377">
@@ -29543,16 +29543,16 @@
         <v>-0.04280884047533118</v>
       </c>
       <c r="M377" t="n">
-        <v>0.004840089028685712</v>
+        <v>0.004839976091779219</v>
       </c>
       <c r="N377" t="n">
-        <v>0.08168509649078071</v>
+        <v>0.08168522736188732</v>
       </c>
       <c r="O377" t="n">
-        <v>0.4884172792780284</v>
+        <v>0.4884167836894517</v>
       </c>
       <c r="P377" t="n">
-        <v>0.1417602025223619</v>
+        <v>0.1417600758008697</v>
       </c>
     </row>
     <row r="378">
@@ -29604,13 +29604,13 @@
         <v>0.01171476672977034</v>
       </c>
       <c r="N378" t="n">
-        <v>-0.01482730869577642</v>
+        <v>-0.0148272406867227</v>
       </c>
       <c r="O378" t="n">
-        <v>0.4435633250779181</v>
+        <v>0.443563179057493</v>
       </c>
       <c r="P378" t="n">
-        <v>0.1301739166563072</v>
+        <v>0.1301738785495663</v>
       </c>
     </row>
     <row r="379">
@@ -29662,13 +29662,13 @@
         <v>-0.09812148297659462</v>
       </c>
       <c r="N379" t="n">
-        <v>-0.2111070127338401</v>
+        <v>-0.211107062620053</v>
       </c>
       <c r="O379" t="n">
-        <v>-0.02476426497568096</v>
+        <v>-0.0247641887390635</v>
       </c>
       <c r="P379" t="n">
-        <v>-0.008323849214271095</v>
+        <v>-0.00832382337366977</v>
       </c>
     </row>
     <row r="380">
@@ -29714,10 +29714,10 @@
         <v>0.03373325686632556</v>
       </c>
       <c r="L380" t="n">
-        <v>-0.09530870910523725</v>
+        <v>-0.09530881618578202</v>
       </c>
       <c r="M380" t="n">
-        <v>-0.05887011914673768</v>
+        <v>-0.05887006120667504</v>
       </c>
       <c r="N380" t="n">
         <v>0.01489783122726807</v>
@@ -29836,13 +29836,13 @@
         <v>-0.005576404405541746</v>
       </c>
       <c r="N382" t="n">
-        <v>-0.08038103380595496</v>
+        <v>-0.08038097154432933</v>
       </c>
       <c r="O382" t="n">
-        <v>-0.2527414170008234</v>
+        <v>-0.2527413347810161</v>
       </c>
       <c r="P382" t="n">
-        <v>-0.09254805183289216</v>
+        <v>-0.09254801855100758</v>
       </c>
     </row>
     <row r="383">
@@ -29949,16 +29949,16 @@
         <v>-0.01480538265496101</v>
       </c>
       <c r="M384" t="n">
-        <v>-0.01850282853785845</v>
+        <v>-0.01850260026927164</v>
       </c>
       <c r="N384" t="n">
-        <v>-0.06401442062446494</v>
+        <v>-0.06401431682949388</v>
       </c>
       <c r="O384" t="n">
-        <v>0.008928012171617095</v>
+        <v>0.008928253377784801</v>
       </c>
       <c r="P384" t="n">
-        <v>0.002967191126089341</v>
+        <v>0.00296727105311767</v>
       </c>
     </row>
     <row r="385">
@@ -30013,10 +30013,10 @@
         <v>-0.05076409356472567</v>
       </c>
       <c r="O385" t="n">
-        <v>0.04413373490450256</v>
+        <v>0.04413349526233734</v>
       </c>
       <c r="P385" t="n">
-        <v>0.01449997936265568</v>
+        <v>0.01449990174903792</v>
       </c>
     </row>
     <row r="386">
@@ -30123,7 +30123,7 @@
         <v>-0.07592084679668942</v>
       </c>
       <c r="M387" t="n">
-        <v>-0.182099356188606</v>
+        <v>-0.1820994082678978</v>
       </c>
       <c r="N387" t="n">
         <v>0.03053226338155746</v>
@@ -30184,7 +30184,7 @@
         <v>0.01916124152727416</v>
       </c>
       <c r="N388" t="n">
-        <v>0.03133345500244888</v>
+        <v>0.03133357413040172</v>
       </c>
       <c r="O388" t="n">
         <v>0.438260760588228</v>
@@ -30294,7 +30294,7 @@
         <v>-0.02955776141393696</v>
       </c>
       <c r="L390" t="n">
-        <v>-0.07035615622240954</v>
+        <v>-0.07035608217849598</v>
       </c>
       <c r="M390" t="n">
         <v>0.001314701658805983</v>
@@ -30303,10 +30303,10 @@
         <v>-0.002705827166443187</v>
       </c>
       <c r="O390" t="n">
-        <v>0.4493867219005008</v>
+        <v>0.4493868118905986</v>
       </c>
       <c r="P390" t="n">
-        <v>0.1316916011501736</v>
+        <v>0.131691624571812</v>
       </c>
     </row>
     <row r="391">
@@ -30355,10 +30355,10 @@
         <v>-0.0864092929100474</v>
       </c>
       <c r="M391" t="n">
-        <v>-0.0004903591966027854</v>
+        <v>-0.0004904561921889039</v>
       </c>
       <c r="N391" t="n">
-        <v>0.07213382532473256</v>
+        <v>0.07213393692778691</v>
       </c>
       <c r="O391" t="n">
         <v>0.5029994283293975</v>
@@ -30535,10 +30535,10 @@
         <v>0.03659716555942882</v>
       </c>
       <c r="O394" t="n">
-        <v>0.5465578537125393</v>
+        <v>0.546557679645689</v>
       </c>
       <c r="P394" t="n">
-        <v>0.1564372090837889</v>
+        <v>0.1564371656976784</v>
       </c>
     </row>
     <row r="395">
@@ -30587,16 +30587,16 @@
         <v>-0.07554011094714264</v>
       </c>
       <c r="M395" t="n">
-        <v>-0.02707149212805748</v>
+        <v>-0.02707156007976286</v>
       </c>
       <c r="N395" t="n">
         <v>0.03390565661315725</v>
       </c>
       <c r="O395" t="n">
-        <v>0.3879611734837383</v>
+        <v>0.3879610351929907</v>
       </c>
       <c r="P395" t="n">
-        <v>0.1154731108350113</v>
+        <v>0.1154730737879579</v>
       </c>
     </row>
     <row r="396">
@@ -30645,16 +30645,16 @@
         <v>-0.2029118689170963</v>
       </c>
       <c r="M396" t="n">
-        <v>0.1379539346462324</v>
+        <v>0.137953854480692</v>
       </c>
       <c r="N396" t="n">
-        <v>0.2165233245922282</v>
+        <v>0.2165231413569035</v>
       </c>
       <c r="O396" t="n">
-        <v>2.99206619094622</v>
+        <v>2.992066684238043</v>
       </c>
       <c r="P396" t="n">
-        <v>0.5863508459141524</v>
+        <v>0.5863509112549086</v>
       </c>
     </row>
     <row r="397">
@@ -30709,10 +30709,10 @@
         <v>0.05835819891031524</v>
       </c>
       <c r="O397" t="n">
-        <v>0.3490607256590537</v>
+        <v>0.3490605988996198</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1049530704007544</v>
+        <v>0.1049530357931623</v>
       </c>
     </row>
     <row r="398">
@@ -30758,19 +30758,19 @@
         <v>-0.02775084215111612</v>
       </c>
       <c r="L398" t="n">
-        <v>-0.0942783797273099</v>
+        <v>-0.09427845458239015</v>
       </c>
       <c r="M398" t="n">
-        <v>-0.03543816990672854</v>
+        <v>-0.03543808500979007</v>
       </c>
       <c r="N398" t="n">
         <v>0.0342535565374793</v>
       </c>
       <c r="O398" t="n">
-        <v>0.5396413465534378</v>
+        <v>0.5396414547070458</v>
       </c>
       <c r="P398" t="n">
-        <v>0.1547106954685153</v>
+        <v>0.154710722506441</v>
       </c>
     </row>
     <row r="399">
@@ -30825,10 +30825,10 @@
         <v>-0.04359901016388246</v>
       </c>
       <c r="O399" t="n">
-        <v>0.315197997120803</v>
+        <v>0.3151983029943888</v>
       </c>
       <c r="P399" t="n">
-        <v>0.09562948928446291</v>
+        <v>0.09562957422074758</v>
       </c>
     </row>
     <row r="400">
@@ -30880,7 +30880,7 @@
         <v>0.02757815038376821</v>
       </c>
       <c r="N400" t="n">
-        <v>-0.005129019048795258</v>
+        <v>-0.005128954414953424</v>
       </c>
       <c r="O400" t="n">
         <v>0.8138380243570151</v>
@@ -30999,10 +30999,10 @@
         <v>-0.2082073752244762</v>
       </c>
       <c r="O402" t="n">
-        <v>1.978632521257164</v>
+        <v>1.978632045906738</v>
       </c>
       <c r="P402" t="n">
-        <v>0.4388172710727707</v>
+        <v>0.4388171945340196</v>
       </c>
     </row>
     <row r="403">
@@ -31057,10 +31057,10 @@
         <v>-0.3221954538206827</v>
       </c>
       <c r="O403" t="n">
-        <v>-0.4702805846758671</v>
+        <v>-0.4702805437265822</v>
       </c>
       <c r="P403" t="n">
-        <v>-0.1908756018052985</v>
+        <v>-0.1908755809558553</v>
       </c>
     </row>
     <row r="404">
@@ -31109,7 +31109,7 @@
         <v>-0.1299693948286368</v>
       </c>
       <c r="M404" t="n">
-        <v>0.1081893961231768</v>
+        <v>0.1081894811500481</v>
       </c>
       <c r="N404" t="n">
         <v>0.02700865686327703</v>
@@ -31231,10 +31231,10 @@
         <v>-0.1157328433945605</v>
       </c>
       <c r="O406" t="n">
-        <v>-0.07178841252235246</v>
+        <v>-0.0717886247356655</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.02452608181608429</v>
+        <v>-0.02452615615566045</v>
       </c>
     </row>
     <row r="407">
@@ -31286,13 +31286,13 @@
         <v>-0.01237829920143363</v>
       </c>
       <c r="N407" t="n">
-        <v>-0.05332931420432452</v>
+        <v>-0.05332940973808487</v>
       </c>
       <c r="O407" t="n">
-        <v>0.007300029561339905</v>
+        <v>0.0073001377238604</v>
       </c>
       <c r="P407" t="n">
-        <v>0.002427445925488936</v>
+        <v>0.002427481805257203</v>
       </c>
     </row>
     <row r="408">
@@ -31341,16 +31341,16 @@
         <v>-0.1026945286488098</v>
       </c>
       <c r="M408" t="n">
-        <v>-0.04439649382816935</v>
+        <v>-0.04439659497502246</v>
       </c>
       <c r="N408" t="n">
-        <v>-0.02808342543940434</v>
+        <v>-0.02808353006908093</v>
       </c>
       <c r="O408" t="n">
-        <v>0.5077155232555373</v>
+        <v>0.5077156491497614</v>
       </c>
       <c r="P408" t="n">
-        <v>0.146673569078954</v>
+        <v>0.1466736009946952</v>
       </c>
     </row>
     <row r="409">
@@ -31402,7 +31402,7 @@
         <v>-0.08596187080923134</v>
       </c>
       <c r="N409" t="n">
-        <v>0.07076100567761023</v>
+        <v>0.07076110889087195</v>
       </c>
       <c r="O409" t="n">
         <v>0.3011243804101011</v>
@@ -31457,16 +31457,16 @@
         <v>-0.2184011738195384</v>
       </c>
       <c r="M410" t="n">
-        <v>-0.1713967292465722</v>
+        <v>-0.1713968252901145</v>
       </c>
       <c r="N410" t="n">
         <v>-0.1940769733491873</v>
       </c>
       <c r="O410" t="n">
-        <v>-0.2806371382414367</v>
+        <v>-0.2806370658526991</v>
       </c>
       <c r="P410" t="n">
-        <v>-0.1039835059643057</v>
+        <v>-0.1039834759092371</v>
       </c>
     </row>
     <row r="411">
@@ -31512,19 +31512,19 @@
         <v>-0.07457153670334649</v>
       </c>
       <c r="L411" t="n">
-        <v>-0.07978383093065933</v>
+        <v>-0.07978388582999729</v>
       </c>
       <c r="M411" t="n">
-        <v>0.08447759288353973</v>
+        <v>0.08447751663552361</v>
       </c>
       <c r="N411" t="n">
         <v>-0.09709873758745513</v>
       </c>
       <c r="O411" t="n">
-        <v>0.1029148399221982</v>
+        <v>0.1029149976475232</v>
       </c>
       <c r="P411" t="n">
-        <v>0.0331911086241703</v>
+        <v>0.03319115787559923</v>
       </c>
     </row>
     <row r="412">
@@ -31695,10 +31695,10 @@
         <v>-0.0739846513837773</v>
       </c>
       <c r="O414" t="n">
-        <v>-0.3009465042178714</v>
+        <v>-0.3009465595667441</v>
       </c>
       <c r="P414" t="n">
-        <v>-0.1124963715677259</v>
+        <v>-0.1124963949909816</v>
       </c>
     </row>
     <row r="415">
@@ -31750,13 +31750,13 @@
         <v>-0.145045301302406</v>
       </c>
       <c r="N415" t="n">
-        <v>-0.2758726822892504</v>
+        <v>-0.2758725985168177</v>
       </c>
       <c r="O415" t="n">
-        <v>-0.1803574317590726</v>
+        <v>-0.1803575390888352</v>
       </c>
       <c r="P415" t="n">
-        <v>-0.06414585444670173</v>
+        <v>-0.06414589529581149</v>
       </c>
     </row>
     <row r="416">
@@ -31805,16 +31805,16 @@
         <v>-0.1607669989617612</v>
       </c>
       <c r="M416" t="n">
-        <v>-0.03291158598892074</v>
+        <v>-0.03291168812843859</v>
       </c>
       <c r="N416" t="n">
         <v>-0.01175764373115618</v>
       </c>
       <c r="O416" t="n">
-        <v>-0.1393199353955826</v>
+        <v>-0.1393198544962355</v>
       </c>
       <c r="P416" t="n">
-        <v>-0.04878085805458487</v>
+        <v>-0.04878082825140628</v>
       </c>
     </row>
     <row r="417">
@@ -31863,10 +31863,10 @@
         <v>-0.1305804170972452</v>
       </c>
       <c r="M417" t="n">
-        <v>-0.07467780712726158</v>
+        <v>-0.07467772781145832</v>
       </c>
       <c r="N417" t="n">
-        <v>-0.1348892374947659</v>
+        <v>-0.134889168165405</v>
       </c>
       <c r="O417" t="n">
         <v>-0.2658134440373598</v>
@@ -31927,10 +31927,10 @@
         <v>-0.01361598813356379</v>
       </c>
       <c r="O418" t="n">
-        <v>0.6357237182931792</v>
+        <v>0.6357238188505629</v>
       </c>
       <c r="P418" t="n">
-        <v>0.1782478348126026</v>
+        <v>0.1782478589571685</v>
       </c>
     </row>
     <row r="419">
@@ -31976,19 +31976,19 @@
         <v>-0.008640121081893271</v>
       </c>
       <c r="L419" t="n">
-        <v>-0.1115319146913838</v>
+        <v>-0.1115320026586167</v>
       </c>
       <c r="M419" t="n">
-        <v>-0.07339156528222079</v>
+        <v>-0.07339146960030707</v>
       </c>
       <c r="N419" t="n">
         <v>-0.05242602659284468</v>
       </c>
       <c r="O419" t="n">
-        <v>0.3017547725538361</v>
+        <v>0.3017548669742072</v>
       </c>
       <c r="P419" t="n">
-        <v>0.09188372542472822</v>
+        <v>0.0918837518239819</v>
       </c>
     </row>
     <row r="420">
@@ -32043,10 +32043,10 @@
         <v>0.1874852090514012</v>
       </c>
       <c r="O420" t="n">
-        <v>0.7416576544292777</v>
+        <v>0.7416581137939711</v>
       </c>
       <c r="P420" t="n">
-        <v>0.2031532012584669</v>
+        <v>0.2031533070362492</v>
       </c>
     </row>
     <row r="421">
@@ -32092,13 +32092,13 @@
         <v>-0.05833540051462305</v>
       </c>
       <c r="L421" t="n">
-        <v>-0.1105835322798723</v>
+        <v>-0.1105836205801061</v>
       </c>
       <c r="M421" t="n">
         <v>-0.07268881263974325</v>
       </c>
       <c r="N421" t="n">
-        <v>-0.0101760349526504</v>
+        <v>-0.01017614431490266</v>
       </c>
       <c r="O421" t="n">
         <v>0.323224783737168</v>
@@ -32153,7 +32153,7 @@
         <v>-0.07443335778264604</v>
       </c>
       <c r="M422" t="n">
-        <v>-0.01082843329956873</v>
+        <v>-0.0108283475731008</v>
       </c>
       <c r="N422" t="n">
         <v>-0.1069917567446719</v>
@@ -32217,10 +32217,10 @@
         <v>-0.06943589604935541</v>
       </c>
       <c r="O423" t="n">
-        <v>-0.1063308908179276</v>
+        <v>-0.1063308256363483</v>
       </c>
       <c r="P423" t="n">
-        <v>-0.03677979923544461</v>
+        <v>-0.03677977581730185</v>
       </c>
     </row>
     <row r="424">
@@ -32272,13 +32272,13 @@
         <v>-0.06017079437486328</v>
       </c>
       <c r="N424" t="n">
-        <v>-0.1720531933478174</v>
+        <v>-0.17205332067001</v>
       </c>
       <c r="O424" t="n">
-        <v>0.08792069576701866</v>
+        <v>0.08792047593360985</v>
       </c>
       <c r="P424" t="n">
-        <v>0.02848764625484557</v>
+        <v>0.02848757698020044</v>
       </c>
     </row>
     <row r="425">
@@ -32324,19 +32324,19 @@
         <v>-0.07254525122084166</v>
       </c>
       <c r="L425" t="n">
-        <v>-0.220625460013776</v>
+        <v>-0.2206254088966063</v>
       </c>
       <c r="M425" t="n">
         <v>-0.01446293483663486</v>
       </c>
       <c r="N425" t="n">
-        <v>0.03776778134316428</v>
+        <v>0.037767690712603</v>
       </c>
       <c r="O425" t="n">
-        <v>-0.0906263014434131</v>
+        <v>-0.09062644062732839</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.03117025723298206</v>
+        <v>-0.03117030666096521</v>
       </c>
     </row>
     <row r="426">
@@ -32382,13 +32382,13 @@
         <v>0.04989734503556487</v>
       </c>
       <c r="L426" t="n">
-        <v>-0.1641618724143425</v>
+        <v>-0.1641618062267215</v>
       </c>
       <c r="M426" t="n">
         <v>-0.1253282641310711</v>
       </c>
       <c r="N426" t="n">
-        <v>-0.1649354185841883</v>
+        <v>-0.1649353525190204</v>
       </c>
       <c r="O426" t="n">
         <v>0.191772285745029</v>
@@ -32440,13 +32440,13 @@
         <v>-0.008352239701498121</v>
       </c>
       <c r="L427" t="n">
-        <v>-0.08888496699660653</v>
+        <v>-0.08888505419739845</v>
       </c>
       <c r="M427" t="n">
         <v>-0.07835640453471748</v>
       </c>
       <c r="N427" t="n">
-        <v>-0.129693091114938</v>
+        <v>-0.1296930115505094</v>
       </c>
       <c r="O427" t="n">
         <v>0.2962015295837577</v>
@@ -32501,16 +32501,16 @@
         <v>-0.1411523121404048</v>
       </c>
       <c r="M428" t="n">
-        <v>-0.02211261906437167</v>
+        <v>-0.02211255315909644</v>
       </c>
       <c r="N428" t="n">
-        <v>0.02061068514358677</v>
+        <v>0.02061061335380132</v>
       </c>
       <c r="O428" t="n">
-        <v>0.131128442828693</v>
+        <v>0.1311285310079318</v>
       </c>
       <c r="P428" t="n">
-        <v>0.04192703699499689</v>
+        <v>0.04192706407012148</v>
       </c>
     </row>
     <row r="429">
@@ -32620,13 +32620,13 @@
         <v>-0.03810544551526807</v>
       </c>
       <c r="N430" t="n">
-        <v>-0.01543836601104775</v>
+        <v>-0.01543844625018975</v>
       </c>
       <c r="O430" t="n">
-        <v>0.6850421047610307</v>
+        <v>0.6850419872463882</v>
       </c>
       <c r="P430" t="n">
-        <v>0.1899724835953245</v>
+        <v>0.1899724559324758</v>
       </c>
     </row>
     <row r="431">
@@ -32675,16 +32675,16 @@
         <v>-0.1648700508407565</v>
       </c>
       <c r="M431" t="n">
-        <v>-0.009084314201432631</v>
+        <v>-0.009084405171778331</v>
       </c>
       <c r="N431" t="n">
-        <v>0.02441710289594989</v>
+        <v>0.024417005670474</v>
       </c>
       <c r="O431" t="n">
-        <v>0.08297836988853136</v>
+        <v>0.08297815257040497</v>
       </c>
       <c r="P431" t="n">
-        <v>0.02692783955111966</v>
+        <v>0.02692777086090525</v>
       </c>
     </row>
     <row r="432">
@@ -32730,13 +32730,13 @@
         <v>-0.08976255587290149</v>
       </c>
       <c r="L432" t="n">
-        <v>0.008588443912580512</v>
+        <v>0.008588508915363446</v>
       </c>
       <c r="M432" t="n">
         <v>-0.2104012944918504</v>
       </c>
       <c r="N432" t="n">
-        <v>-0.002979718988990299</v>
+        <v>-0.002979782509197171</v>
       </c>
       <c r="O432" t="n">
         <v>0.7937449194190636</v>
@@ -32791,16 +32791,16 @@
         <v>-0.244140922359631</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.03624454115487152</v>
+        <v>-0.03624443715956904</v>
       </c>
       <c r="N433" t="n">
         <v>-0.05821277003172576</v>
       </c>
       <c r="O433" t="n">
-        <v>0.3231655790668844</v>
+        <v>0.3231656770786921</v>
       </c>
       <c r="P433" t="n">
-        <v>0.09783750886097287</v>
+        <v>0.09783753596794464</v>
       </c>
     </row>
     <row r="434">
@@ -32907,16 +32907,16 @@
         <v>-0.1306054705956495</v>
       </c>
       <c r="M435" t="n">
-        <v>-0.002617261548089056</v>
+        <v>-0.002617181692122328</v>
       </c>
       <c r="N435" t="n">
-        <v>-0.2756220322478339</v>
+        <v>-0.2756221164928179</v>
       </c>
       <c r="O435" t="n">
-        <v>-0.3208854173367633</v>
+        <v>-0.3208854913824394</v>
       </c>
       <c r="P435" t="n">
-        <v>-0.1210159008748317</v>
+        <v>-0.1210159328208272</v>
       </c>
     </row>
     <row r="436">
@@ -33023,7 +33023,7 @@
         <v>0.1692222441290796</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.004694029982805437</v>
+        <v>-0.004693938249122009</v>
       </c>
       <c r="N437" t="n">
         <v>0.0463499427362204</v>
@@ -33084,7 +33084,7 @@
         <v>-0.04500033486715627</v>
       </c>
       <c r="N438" t="n">
-        <v>0.09823246529620255</v>
+        <v>0.09823234090807675</v>
       </c>
       <c r="O438" t="n">
         <v>0.4375700382143546</v>
@@ -33194,7 +33194,7 @@
         <v>-0.1347713076551653</v>
       </c>
       <c r="L440" t="n">
-        <v>-0.1927819074044703</v>
+        <v>-0.1927818589652039</v>
       </c>
       <c r="M440" t="n">
         <v>-0.06348661881963236</v>
@@ -33203,10 +33203,10 @@
         <v>0.07682959669398826</v>
       </c>
       <c r="O440" t="n">
-        <v>1.001901311713106</v>
+        <v>1.001901609634128</v>
       </c>
       <c r="P440" t="n">
-        <v>0.2603201738866849</v>
+        <v>0.2603202364065593</v>
       </c>
     </row>
     <row r="441">
@@ -33261,10 +33261,10 @@
         <v>-0.2534596261393961</v>
       </c>
       <c r="O441" t="n">
-        <v>-0.3832936295339218</v>
+        <v>-0.3832936914756966</v>
       </c>
       <c r="P441" t="n">
-        <v>-0.1488107210593936</v>
+        <v>-0.1488107495571136</v>
       </c>
     </row>
     <row r="442">
@@ -33374,13 +33374,13 @@
         <v>-0.190254122446768</v>
       </c>
       <c r="N443" t="n">
-        <v>-0.2067973552142012</v>
+        <v>-0.2067972699911221</v>
       </c>
       <c r="O443" t="n">
-        <v>0.1520337815743549</v>
+        <v>0.1520333321473804</v>
       </c>
       <c r="P443" t="n">
-        <v>0.04830680443181112</v>
+        <v>0.04830666811132445</v>
       </c>
     </row>
     <row r="444">
@@ -33493,10 +33493,10 @@
         <v>-0.08277088315191716</v>
       </c>
       <c r="O445" t="n">
-        <v>0.323195294074565</v>
+        <v>0.3231951119132248</v>
       </c>
       <c r="P445" t="n">
-        <v>0.09784572703268735</v>
+        <v>0.09784567665336197</v>
       </c>
     </row>
     <row r="446">
@@ -33551,10 +33551,10 @@
         <v>-0.1119509365554103</v>
       </c>
       <c r="O446" t="n">
-        <v>-0.3939381807491258</v>
+        <v>-0.3939383124389422</v>
       </c>
       <c r="P446" t="n">
-        <v>-0.1537364378559902</v>
+        <v>-0.1537364991502331</v>
       </c>
     </row>
     <row r="447">
@@ -33606,13 +33606,13 @@
         <v>0.1737955519042309</v>
       </c>
       <c r="N447" t="n">
-        <v>-0.03846375959581849</v>
+        <v>-0.03846382205726406</v>
       </c>
       <c r="O447" t="n">
-        <v>0.1961052054955692</v>
+        <v>0.1961054954574215</v>
       </c>
       <c r="P447" t="n">
-        <v>0.06150764623759009</v>
+        <v>0.06150773201507764</v>
       </c>
     </row>
     <row r="448">
@@ -33658,19 +33658,19 @@
         <v>0.07656792550557467</v>
       </c>
       <c r="L448" t="n">
-        <v>-0.1657339874087341</v>
+        <v>-0.1657339234436994</v>
       </c>
       <c r="M448" t="n">
-        <v>-0.1965320066035217</v>
+        <v>-0.1965320659330143</v>
       </c>
       <c r="N448" t="n">
         <v>-0.2461197581972182</v>
       </c>
       <c r="O448" t="n">
-        <v>-0.1042159456174431</v>
+        <v>-0.10421587187115</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.03602054990685499</v>
+        <v>-0.03602052345334061</v>
       </c>
     </row>
     <row r="449">
@@ -33719,7 +33719,7 @@
         <v>-0.1552673373089092</v>
       </c>
       <c r="M449" t="n">
-        <v>-0.0158571903391852</v>
+        <v>-0.01585730278460851</v>
       </c>
       <c r="N449" t="n">
         <v>-0.1497215029129065</v>
@@ -33783,10 +33783,10 @@
         <v>-0.1112855651012801</v>
       </c>
       <c r="O450" t="n">
-        <v>1.732262440670095</v>
+        <v>1.73226223899383</v>
       </c>
       <c r="P450" t="n">
-        <v>0.3980009634081458</v>
+        <v>0.3980009290113014</v>
       </c>
     </row>
     <row r="451">
@@ -33835,16 +33835,16 @@
         <v>-0.1185210566758993</v>
       </c>
       <c r="M451" t="n">
-        <v>-0.06108247947462486</v>
+        <v>-0.06108254472312191</v>
       </c>
       <c r="N451" t="n">
-        <v>-0.1811891648559792</v>
+        <v>-0.1811890159870201</v>
       </c>
       <c r="O451" t="n">
-        <v>-0.003766558049323798</v>
+        <v>-0.003766484591523178</v>
       </c>
       <c r="P451" t="n">
-        <v>-0.0012570989854368</v>
+        <v>-0.00125707443782519</v>
       </c>
     </row>
     <row r="452">
@@ -33899,10 +33899,10 @@
         <v>-0.1533885010266569</v>
       </c>
       <c r="O452" t="n">
-        <v>-0.1082937012633564</v>
+        <v>-0.1082938710013606</v>
       </c>
       <c r="P452" t="n">
-        <v>-0.03748550581704635</v>
+        <v>-0.03748556688921023</v>
       </c>
     </row>
     <row r="453">
@@ -33951,10 +33951,10 @@
         <v>-0.1964476078929189</v>
       </c>
       <c r="M453" t="n">
-        <v>-0.2620532210289429</v>
+        <v>-0.2620531616166024</v>
       </c>
       <c r="N453" t="n">
-        <v>-0.2207260838196853</v>
+        <v>-0.2207261500728741</v>
       </c>
       <c r="O453" t="n">
         <v>0.4940207320842009</v>
@@ -34128,7 +34128,7 @@
         <v>-0.0166431871589896</v>
       </c>
       <c r="N456" t="n">
-        <v>-0.2197310840059017</v>
+        <v>-0.21973113054823</v>
       </c>
       <c r="O456" t="n">
         <v>0.6136816566968477</v>
@@ -34189,10 +34189,10 @@
         <v>-0.1369633264909673</v>
       </c>
       <c r="O457" t="n">
-        <v>0.3054437715682592</v>
+        <v>0.3054438857601518</v>
       </c>
       <c r="P457" t="n">
-        <v>0.0929141701630305</v>
+        <v>0.0929142020300826</v>
       </c>
     </row>
     <row r="458">
@@ -34244,7 +34244,7 @@
         <v>-0.1341350884470486</v>
       </c>
       <c r="N458" t="n">
-        <v>-0.1807595095602756</v>
+        <v>-0.1807595590959794</v>
       </c>
       <c r="O458" t="n">
         <v>-0.0143746978779713</v>
@@ -34302,13 +34302,13 @@
         <v>-0.1484783326242579</v>
       </c>
       <c r="N459" t="n">
-        <v>-0.1320813996103776</v>
+        <v>-0.1320813126304321</v>
       </c>
       <c r="O459" t="n">
-        <v>0.22453273646142</v>
+        <v>0.2245326498905327</v>
       </c>
       <c r="P459" t="n">
-        <v>0.06985141805655037</v>
+        <v>0.06985139284475972</v>
       </c>
     </row>
     <row r="460">
@@ -34592,7 +34592,7 @@
         <v>-0.1163125111323879</v>
       </c>
       <c r="N464" t="n">
-        <v>-0.2371666849421388</v>
+        <v>-0.2371666227511792</v>
       </c>
       <c r="O464" t="n">
         <v>0.9848246401685454</v>
@@ -34653,10 +34653,10 @@
         <v>-0.03903034826828555</v>
       </c>
       <c r="O465" t="n">
-        <v>0.5608519760287423</v>
+        <v>0.5608518341310569</v>
       </c>
       <c r="P465" t="n">
-        <v>0.1599890942367339</v>
+        <v>0.1599890590850401</v>
       </c>
     </row>
     <row r="466">
@@ -34763,10 +34763,10 @@
         <v>-0.1461141666386647</v>
       </c>
       <c r="O467" t="n">
-        <v>0.7580336412873023</v>
+        <v>0.7580337646396549</v>
       </c>
       <c r="P467" t="n">
-        <v>0.2069123383096305</v>
+        <v>0.2069123665372801</v>
       </c>
     </row>
     <row r="468">
@@ -34870,19 +34870,19 @@
         <v>-0.05447092779532736</v>
       </c>
       <c r="L469" t="n">
-        <v>-0.1767725487787819</v>
+        <v>-0.1767724902661701</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.1408364854179968</v>
+        <v>-0.1408364216854243</v>
       </c>
       <c r="N469" t="n">
         <v>-0.2772210819550801</v>
       </c>
       <c r="O469" t="n">
-        <v>0.3750099871298098</v>
+        <v>0.3750098238917523</v>
       </c>
       <c r="P469" t="n">
-        <v>0.1119927375421224</v>
+        <v>0.1119926935377047</v>
       </c>
     </row>
     <row r="470">
@@ -34989,16 +34989,16 @@
         <v>-0.1303663402624157</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.2672451633516577</v>
+        <v>-0.2672452508732392</v>
       </c>
       <c r="N471" t="n">
-        <v>-0.2544852769705694</v>
+        <v>-0.2544852316724366</v>
       </c>
       <c r="O471" t="n">
-        <v>-0.002654785971090035</v>
+        <v>-0.002654867040834841</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.0008857129127837204</v>
+        <v>-0.0008857399839660163</v>
       </c>
     </row>
     <row r="472">
@@ -35053,10 +35053,10 @@
         <v>-0.4733471227628393</v>
       </c>
       <c r="O472" t="n">
-        <v>-0.313273283624937</v>
+        <v>-0.313273118200828</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.1177439446205605</v>
+        <v>-0.1177438737789838</v>
       </c>
     </row>
     <row r="473">
@@ -35166,13 +35166,13 @@
         <v>-0.3541260498366285</v>
       </c>
       <c r="N474" t="n">
-        <v>-0.4327945782117572</v>
+        <v>-0.4327946135798233</v>
       </c>
       <c r="O474" t="n">
-        <v>-0.1605798906937418</v>
+        <v>-0.1605797357694899</v>
       </c>
       <c r="P474" t="n">
-        <v>-0.05667837668383735</v>
+        <v>-0.05667831865036632</v>
       </c>
     </row>
     <row r="475">
@@ -35221,16 +35221,16 @@
         <v>-0.1416769167673785</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.1480825010150505</v>
+        <v>-0.148082427216089</v>
       </c>
       <c r="N475" t="n">
-        <v>-0.1954229176298453</v>
+        <v>-0.1954228518049033</v>
       </c>
       <c r="O475" t="n">
-        <v>-0.1154812891123685</v>
+        <v>-0.1154812095570494</v>
       </c>
       <c r="P475" t="n">
-        <v>-0.04007859769363553</v>
+        <v>-0.04007856891457551</v>
       </c>
     </row>
     <row r="476">
@@ -35276,7 +35276,7 @@
         <v>-0.1264924918162785</v>
       </c>
       <c r="L476" t="n">
-        <v>-0.1937616892433224</v>
+        <v>-0.1937617601861779</v>
       </c>
       <c r="M476" t="n">
         <v>-0.2150718464716694</v>
@@ -35285,10 +35285,10 @@
         <v>-0.2854937002009488</v>
       </c>
       <c r="O476" t="n">
-        <v>3.807505460532629</v>
+        <v>3.807505145227236</v>
       </c>
       <c r="P476" t="n">
-        <v>0.6877440881016206</v>
+        <v>0.6877440512041189</v>
       </c>
     </row>
     <row r="477">
@@ -35334,13 +35334,13 @@
         <v>-0.02858676291541518</v>
       </c>
       <c r="L477" t="n">
-        <v>-0.188271904967247</v>
+        <v>-0.1882719669527815</v>
       </c>
       <c r="M477" t="n">
         <v>-0.3672137075036622</v>
       </c>
       <c r="N477" t="n">
-        <v>-0.3998236047173797</v>
+        <v>-0.3998236724904243</v>
       </c>
       <c r="O477" t="n">
         <v>-0.2157136906187457</v>
@@ -35627,16 +35627,16 @@
         <v>0.05227728480897076</v>
       </c>
       <c r="M482" t="n">
-        <v>-0.2403785161674952</v>
+        <v>-0.2403785741160201</v>
       </c>
       <c r="N482" t="n">
-        <v>-0.3605535532241104</v>
+        <v>-0.3605535942876393</v>
       </c>
       <c r="O482" t="n">
-        <v>0.3471404243661311</v>
+        <v>0.3471406066187326</v>
       </c>
       <c r="P482" t="n">
-        <v>0.1044285448709483</v>
+        <v>0.1044285946764381</v>
       </c>
     </row>
     <row r="483">
@@ -35682,19 +35682,19 @@
         <v>-0.04604437496900116</v>
       </c>
       <c r="L483" t="n">
-        <v>-0.2473642320338044</v>
+        <v>-0.2473641812553805</v>
       </c>
       <c r="M483" t="n">
         <v>-0.3415416590720854</v>
       </c>
       <c r="N483" t="n">
-        <v>-0.3478272968613619</v>
+        <v>-0.3478273731157183</v>
       </c>
       <c r="O483" t="n">
-        <v>-0.1906365628460533</v>
+        <v>-0.1906366215674817</v>
       </c>
       <c r="P483" t="n">
-        <v>-0.06807450341596288</v>
+        <v>-0.06807452595383856</v>
       </c>
     </row>
     <row r="484">
@@ -35862,7 +35862,7 @@
         <v>-0.3395657982555849</v>
       </c>
       <c r="N486" t="n">
-        <v>-0.2168038237677236</v>
+        <v>-0.2168038766592414</v>
       </c>
       <c r="O486" t="n">
         <v>-0.1270497834306841</v>
@@ -35923,10 +35923,10 @@
         <v>-0.506035119707735</v>
       </c>
       <c r="O487" t="n">
-        <v>-0.5819903389939307</v>
+        <v>-0.5819904100736313</v>
       </c>
       <c r="P487" t="n">
-        <v>-0.2522976027057012</v>
+        <v>-0.2522976450862732</v>
       </c>
     </row>
     <row r="488">
@@ -36137,13 +36137,13 @@
         <v>-0.3183830404239893</v>
       </c>
       <c r="N491" t="n">
-        <v>-0.2208811638068223</v>
+        <v>-0.220881244765505</v>
       </c>
       <c r="O491" t="n">
-        <v>2.215858379933883</v>
+        <v>2.215858724751905</v>
       </c>
       <c r="P491" t="n">
-        <v>0.4760428713978506</v>
+        <v>0.476042924153715</v>
       </c>
     </row>
     <row r="492">
@@ -36369,13 +36369,13 @@
         <v>-0.404045499643763</v>
       </c>
       <c r="N495" t="n">
-        <v>-0.4242516025782721</v>
+        <v>-0.4242515211277229</v>
       </c>
       <c r="O495" t="n">
-        <v>-0.04882651843159358</v>
+        <v>-0.04882674073588467</v>
       </c>
       <c r="P495" t="n">
-        <v>-0.01654782626446516</v>
+        <v>-0.01654790288058183</v>
       </c>
     </row>
     <row r="496">
@@ -36601,7 +36601,7 @@
         <v>-0.4087793995833229</v>
       </c>
       <c r="N499" t="n">
-        <v>-0.3516698254692201</v>
+        <v>-0.3516698700835591</v>
       </c>
       <c r="O499" t="n">
         <v>-0.0591075805242578</v>
@@ -36717,7 +36717,7 @@
         <v>-0.3920680466740076</v>
       </c>
       <c r="N501" t="n">
-        <v>-0.4931361620110827</v>
+        <v>-0.4931361110205711</v>
       </c>
       <c r="O501" t="n">
         <v>-0.5893045976313481</v>

--- a/GICS_SubIndustry_Leaderboard.xlsx
+++ b/GICS_SubIndustry_Leaderboard.xlsx
@@ -613,19 +613,19 @@
         <v>0.003617067901606183</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0.947667436261823</v>
+        <v>0.9476674906248704</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>1.652007431255238</v>
+        <v>1.652007422913595</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>4.739988056844705</v>
+        <v>4.739988092281586</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>4.55636187987751</v>
+        <v>4.556361709208328</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.6178565738279537</v>
+        <v>0.6178565589740235</v>
       </c>
     </row>
     <row r="3">
@@ -669,19 +669,19 @@
         <v>0.4619714472465127</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>0.7609204580826875</v>
+        <v>0.7609204137337976</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.9493516218271356</v>
+        <v>0.9493515003644694</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>1.141287932399562</v>
+        <v>1.141287924520505</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>1.719757654692604</v>
+        <v>1.71975780061358</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>0.3944790371484376</v>
+        <v>0.3944790623330734</v>
       </c>
     </row>
     <row r="4">
@@ -731,13 +731,13 @@
         <v>0.7781944436254576</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>1.727621451250888</v>
+        <v>1.727621470606185</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>4.81816333758004</v>
+        <v>4.818163345326322</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.6613018881417234</v>
+        <v>0.6613018905015431</v>
       </c>
     </row>
     <row r="5">
@@ -781,19 +781,19 @@
         <v>0.4295949065906464</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.2907268627698257</v>
+        <v>0.2907268728008083</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0.707843875804576</v>
+        <v>0.7078438858978906</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.9771852746137504</v>
+        <v>0.9771852471681314</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.5477488146594005</v>
+        <v>0.5477488334244227</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0.144182396137551</v>
+        <v>0.144182399036342</v>
       </c>
     </row>
     <row r="6">
@@ -837,7 +837,7 @@
         <v>0.2309233640852492</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.8778116135142241</v>
+        <v>0.8778115937881573</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>0.5122139557347204</v>
@@ -846,10 +846,10 @@
         <v>0.5365688200321103</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>1.685310760930806</v>
+        <v>1.685310814983154</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.3472549614140627</v>
+        <v>0.3472549744578639</v>
       </c>
     </row>
     <row r="7">
@@ -896,16 +896,16 @@
         <v>0.1430691274457464</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.7321279278225211</v>
+        <v>0.7321279370432041</v>
       </c>
       <c r="N7" s="5" t="n">
         <v>1.720830698470702</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>2.58459393369038</v>
+        <v>2.584593953668216</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0.5271545031532346</v>
+        <v>0.5271545066941901</v>
       </c>
     </row>
     <row r="8">
@@ -955,7 +955,7 @@
         <v>0.7747932484367259</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.7241940597639631</v>
+        <v>0.724193910034578</v>
       </c>
       <c r="O8" s="5" t="n">
         <v>0.973035454602007</v>
@@ -1008,16 +1008,16 @@
         <v>0.4332576042065369</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.6095673298447762</v>
+        <v>0.6095673453519519</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>1.100947663000233</v>
+        <v>1.100947650332173</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>2.04536759251128</v>
+        <v>2.045367493304696</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.3371540823151256</v>
+        <v>0.3371540614014371</v>
       </c>
     </row>
     <row r="10">
@@ -1061,19 +1061,19 @@
         <v>-0.1143276311501024</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.05094514696628383</v>
+        <v>0.05094510890118801</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.531723758432867</v>
+        <v>0.5317237173707918</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>1.257116250502816</v>
+        <v>1.257116181521912</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>4.291782339284169</v>
+        <v>4.291782131758393</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.7264336380026117</v>
+        <v>0.7264336112470767</v>
       </c>
     </row>
     <row r="11">
@@ -1126,10 +1126,10 @@
         <v>0.5109795602312941</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>-0.07364745600316525</v>
+        <v>-0.07364742218120568</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-0.02583670385735828</v>
+        <v>-0.02583669204808145</v>
       </c>
     </row>
     <row r="12">
@@ -1235,13 +1235,13 @@
         <v>0.4886885653510517</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.7495165760497846</v>
+        <v>0.7495163815901094</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>0.8949503175221211</v>
+        <v>0.8949501625229516</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>0.2318297832942895</v>
+        <v>0.2318297492183374</v>
       </c>
     </row>
     <row r="14">
@@ -1291,7 +1291,7 @@
         <v>0.3954596669379673</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.7123698708375017</v>
+        <v>0.7123700483005675</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>2.416258542488575</v>
@@ -1400,16 +1400,16 @@
         <v>0.04576371472426222</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.4226481722295998</v>
+        <v>0.422648266540852</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.3854120850939</v>
+        <v>0.385411995655015</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>0.6607719570002715</v>
+        <v>0.6607718284750286</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.1842316601145804</v>
+        <v>0.1842316295658015</v>
       </c>
     </row>
     <row r="17">
@@ -1453,19 +1453,19 @@
         <v>0.2826735130820824</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.2632898854602426</v>
+        <v>0.2632898855200887</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>0.1074222632155033</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.3066163265647879</v>
+        <v>0.3066163168068233</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.1848724106012039</v>
+        <v>0.1848724276288458</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.05524680575979346</v>
+        <v>0.05524681086593045</v>
       </c>
     </row>
     <row r="18">
@@ -1518,10 +1518,10 @@
         <v>0.1941445114142084</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1.829076408285253</v>
+        <v>1.829076838141252</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.4143217680169287</v>
+        <v>0.4143218396486295</v>
       </c>
     </row>
     <row r="19">
@@ -1568,16 +1568,16 @@
         <v>0.06345284162161569</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>0.4656875270153677</v>
+        <v>0.4656875874549138</v>
       </c>
       <c r="N19" s="5" t="n">
         <v>0.5854756207375128</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.330471961678898</v>
+        <v>0.3304720316760754</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>0.09044560415493071</v>
+        <v>0.09044561952491843</v>
       </c>
     </row>
     <row r="20">
@@ -1624,10 +1624,10 @@
         <v>0.0965269571100148</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.4091954327419124</v>
+        <v>0.4091953851989432</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.3916074103460015</v>
+        <v>0.3916075098821206</v>
       </c>
       <c r="O20" s="5" t="n">
         <v>0.5240333639532965</v>
@@ -1677,19 +1677,19 @@
         <v>0.105030307916456</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.1128894622219984</v>
+        <v>0.112889482762425</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0.3855788415926968</v>
+        <v>0.3855788258508663</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.4235180922163297</v>
+        <v>0.4235181150678559</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>1.48972691491646</v>
+        <v>1.489726798690577</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0.3438150311086204</v>
+        <v>0.3438150101255047</v>
       </c>
     </row>
     <row r="22">
@@ -1736,16 +1736,16 @@
         <v>0.3738825310910323</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0.1625073945395056</v>
+        <v>0.1625074295587018</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>-0.03968706208883999</v>
+        <v>-0.03968706664437338</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0.1798693804704427</v>
+        <v>0.1798694591236305</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.0566253699657755</v>
+        <v>0.05662539345743345</v>
       </c>
     </row>
     <row r="23">
@@ -1789,19 +1789,19 @@
         <v>0.1297643909213688</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.1418516327160196</v>
+        <v>0.1418516685037089</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>0.3147510973526672</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>0.3940424156187877</v>
+        <v>0.3940424616846467</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0.6569120374816725</v>
+        <v>0.6569120259279346</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0.1822305405411799</v>
+        <v>0.1822305391091784</v>
       </c>
     </row>
     <row r="24">
@@ -1854,10 +1854,10 @@
         <v>0.2606005618520774</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>0.5100032668366818</v>
+        <v>0.5100032803804995</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.129974719193967</v>
+        <v>0.1299747241545098</v>
       </c>
     </row>
     <row r="25">
@@ -1901,19 +1901,19 @@
         <v>0.1501200053852361</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.2855612327479586</v>
+        <v>0.2855612303766992</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0.2374268332077914</v>
+        <v>0.2374268406458739</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0.1988956318924015</v>
+        <v>0.1988956164699217</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>1.040114945965817</v>
+        <v>1.040115010946182</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0.2510607411108341</v>
+        <v>0.251060750307216</v>
       </c>
     </row>
     <row r="26">
@@ -1963,13 +1963,13 @@
         <v>0.06983876918959964</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0.008624951476069009</v>
+        <v>0.008625065894428019</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>-0.03056088604337759</v>
+        <v>-0.0305612031449819</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>-0.01029253483689996</v>
+        <v>-0.01029264274735897</v>
       </c>
     </row>
     <row r="27">
@@ -2016,16 +2016,16 @@
         <v>0.2639160309754857</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>0.2002778817499108</v>
+        <v>0.2002778622765872</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>0.2747971368100193</v>
+        <v>0.2747971466945163</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>2.958438768790457</v>
+        <v>2.958438801231102</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>0.5181938126344382</v>
+        <v>0.5181938157309427</v>
       </c>
     </row>
     <row r="28">
@@ -2069,19 +2069,19 @@
         <v>0.1139348067354825</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.04016518494276544</v>
+        <v>0.04016519551501613</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2267038290499619</v>
+        <v>0.2267038496720045</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0.3964972010866314</v>
+        <v>0.3964971577494583</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>0.3993766440794549</v>
+        <v>0.3993766237070763</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.09486610909470432</v>
+        <v>0.09486610727220431</v>
       </c>
     </row>
     <row r="29">
@@ -2134,10 +2134,10 @@
         <v>0.5684729368920051</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>1.102868222191381</v>
+        <v>1.102868305375731</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>0.2810670255382897</v>
+        <v>0.2810670424520527</v>
       </c>
     </row>
     <row r="30">
@@ -2181,19 +2181,19 @@
         <v>0.1147139514352273</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.1451016431054982</v>
+        <v>0.14510159800165</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.165651806339382</v>
+        <v>0.165651836466832</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>0.3462216971355399</v>
+        <v>0.346221747455763</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>1.178817889393299</v>
+        <v>1.178817356636592</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.2778227572603223</v>
+        <v>0.2778226555181237</v>
       </c>
     </row>
     <row r="31">
@@ -2240,16 +2240,16 @@
         <v>0.1180383695164156</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>0.2813148212740209</v>
+        <v>0.2813149310281884</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>0.2299497268284356</v>
+        <v>0.2299498279593746</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>2.390135228361604</v>
+        <v>2.390134844200596</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>0.5022389125712272</v>
+        <v>0.5022388558280004</v>
       </c>
     </row>
     <row r="32">
@@ -2296,16 +2296,16 @@
         <v>0.08705807678778572</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>0.3133510835298897</v>
+        <v>0.3133510661084244</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0.3177626121946577</v>
+        <v>0.3177625511697975</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>0.2752600011383381</v>
+        <v>0.2752599658589006</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>0.08052664260931268</v>
+        <v>0.08052663504405687</v>
       </c>
     </row>
     <row r="33">
@@ -2355,13 +2355,13 @@
         <v>0.4051726191631482</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0.5114227358207636</v>
+        <v>0.5114227237455727</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>2.186245641981509</v>
+        <v>2.186245734516061</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>0.4342616255880937</v>
+        <v>0.4342616438062756</v>
       </c>
     </row>
     <row r="34">
@@ -2405,19 +2405,19 @@
         <v>0.115244261193689</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.1937444461221225</v>
+        <v>0.1937444652182334</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.2175756441294812</v>
+        <v>0.2175756852947731</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0.2202996027089843</v>
+        <v>0.2202996304615408</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>0.5804572397343902</v>
+        <v>0.5804572328990015</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.1645080184991369</v>
+        <v>0.1645080165377248</v>
       </c>
     </row>
     <row r="35">
@@ -2464,16 +2464,16 @@
         <v>0.03168333382445984</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.2791949701466671</v>
+        <v>0.2791949775567042</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>0.5285475958245043</v>
+        <v>0.5285476311003225</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>1.457250962073816</v>
+        <v>1.457251049190538</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>0.3432550424574775</v>
+        <v>0.3432550629757538</v>
       </c>
     </row>
     <row r="36">
@@ -2526,10 +2526,10 @@
         <v>0.03749201190382079</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>0.531013855537387</v>
+        <v>0.5310137890498644</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>0.1522985490774208</v>
+        <v>0.1522985318820211</v>
       </c>
     </row>
     <row r="37">
@@ -2576,16 +2576,16 @@
         <v>0.150421349217301</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>0.1879626314760982</v>
+        <v>0.1879626056747437</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>0.2179826283698115</v>
+        <v>0.2179826275482316</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>1.382554853394048</v>
+        <v>1.382554935941959</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>0.3296152194612603</v>
+        <v>0.3296152365293228</v>
       </c>
     </row>
     <row r="38">
@@ -2629,19 +2629,19 @@
         <v>-0.04140192001218895</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.06584227253296243</v>
+        <v>0.06584224227929869</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.3011605339917625</v>
+        <v>0.3011604772542092</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0.5066875600976853</v>
+        <v>0.5066875276195681</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>3.00795948862019</v>
+        <v>3.007959506163941</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.5160751626122553</v>
+        <v>0.5160751507579511</v>
       </c>
     </row>
     <row r="39">
@@ -2694,10 +2694,10 @@
         <v>0.1092920788983749</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0.09473566032774117</v>
+        <v>0.09473575794866318</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>0.03063073202127575</v>
+        <v>0.03063076265610465</v>
       </c>
     </row>
     <row r="40">
@@ -2744,16 +2744,16 @@
         <v>0.1164546776208894</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.2425731729542405</v>
+        <v>0.2425731961934109</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>0.2190138918156464</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>0.5971532361378387</v>
+        <v>0.5971533810325527</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.163989822816382</v>
+        <v>0.1639898591635112</v>
       </c>
     </row>
     <row r="41">
@@ -2800,16 +2800,16 @@
         <v>-0.05571178767117335</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.2850207331243997</v>
+        <v>0.2850206330906353</v>
       </c>
       <c r="N41" s="5" t="n">
         <v>0.2137122834487963</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.2014272545946354</v>
+        <v>0.2014273420368942</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>0.06307970346547931</v>
+        <v>0.06307972925649508</v>
       </c>
     </row>
     <row r="42">
@@ -2912,16 +2912,16 @@
         <v>-0.02754840238910486</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>0.05186386547429306</v>
+        <v>0.0518638811818426</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>0.324179245289243</v>
+        <v>0.3241792865676224</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>1.011596517956175</v>
+        <v>1.011596245225343</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>0.2493209774769437</v>
+        <v>0.2493209220101311</v>
       </c>
     </row>
     <row r="44">
@@ -2968,16 +2968,16 @@
         <v>0.02862059354531785</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.2223809179067325</v>
+        <v>0.2223809438773039</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>0.4584877866788657</v>
+        <v>0.4584878222449628</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>0.4578033816221975</v>
+        <v>0.4578033391481986</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.1202357152384368</v>
+        <v>0.1202356982966629</v>
       </c>
     </row>
     <row r="45">
@@ -3021,19 +3021,19 @@
         <v>0.08538146798376418</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.08735879624463978</v>
+        <v>0.08735876224926498</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.3174470593009259</v>
+        <v>0.3174470322789567</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.1437635788640082</v>
+        <v>0.1437635892747208</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.4042283671684233</v>
+        <v>0.4042284323851316</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>0.09890063534372855</v>
+        <v>0.09890064559223355</v>
       </c>
     </row>
     <row r="46">
@@ -3080,16 +3080,16 @@
         <v>0.2492432065907677</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>0.06767406597904113</v>
+        <v>0.06767418072980758</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>-0.06126147324335229</v>
+        <v>-0.06126138453439256</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>-0.2491735309507453</v>
+        <v>-0.2491736444484923</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>-0.09110609411106518</v>
+        <v>-0.09110613990833882</v>
       </c>
     </row>
     <row r="47">
@@ -3139,13 +3139,13 @@
         <v>0.2608284071806251</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>0.05438618622087255</v>
+        <v>0.05438614640860195</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>1.039601306168536</v>
+        <v>1.039601379839886</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>0.2668355853816936</v>
+        <v>0.2668355997316992</v>
       </c>
     </row>
     <row r="48">
@@ -3192,16 +3192,16 @@
         <v>0.003952615450468345</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>0.2270707237397053</v>
+        <v>0.2270707071459909</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>0.2379211570603933</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>0.4429019756981278</v>
+        <v>0.4429018187948872</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>0.1200189633315738</v>
+        <v>0.1200189264349179</v>
       </c>
     </row>
     <row r="49">
@@ -3254,10 +3254,10 @@
         <v>0.1491146483877435</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>0.2160991648899557</v>
+        <v>0.2160993056646425</v>
       </c>
       <c r="P49" s="5" t="n">
-        <v>0.06738967314701738</v>
+        <v>0.06738971433374652</v>
       </c>
     </row>
     <row r="50">
@@ -3286,34 +3286,34 @@
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.01738663960350684</v>
+        <v>-0.01733720239577463</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>-0.02160360981880475</v>
+        <v>-0.02155469483595522</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-0.06741278096649471</v>
+        <v>-0.06736634579562496</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.03934162457000306</v>
+        <v>-0.03929270958715353</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.06959081101628413</v>
+        <v>0.06964221920660878</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>0.08784154451172092</v>
+        <v>0.08789211562390464</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.2164632295565025</v>
+        <v>0.2165158432734998</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>0.1726902756836937</v>
+        <v>0.1727388469912648</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>1.133683623474227</v>
+        <v>1.133768996737659</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.2838991046797782</v>
+        <v>0.2839190068879929</v>
       </c>
     </row>
     <row r="51">
@@ -3357,19 +3357,19 @@
         <v>-0.01598852100676723</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0.07317817168566754</v>
+        <v>0.07317821800722846</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>0.2974149336338661</v>
+        <v>0.2974148756135503</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>0.2494542328387829</v>
+        <v>0.2494541789229217</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>0.4870062632191324</v>
+        <v>0.4870060952422618</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>0.141195646760092</v>
+        <v>0.1411956032665559</v>
       </c>
     </row>
     <row r="52">
@@ -3419,13 +3419,13 @@
         <v>0.2088032979949274</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>0.3800911568518153</v>
+        <v>0.3800911395040064</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>1.594069292210921</v>
+        <v>1.594069739058121</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>0.308784378321714</v>
+        <v>0.3087844316165107</v>
       </c>
     </row>
     <row r="53">
@@ -3469,13 +3469,13 @@
         <v>-0.09443569109858396</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.08082221139433288</v>
+        <v>0.08082228865901708</v>
       </c>
       <c r="M53" s="5" t="n">
         <v>0.3701434671134503</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>0.2918908554393311</v>
+        <v>0.2918907450507651</v>
       </c>
       <c r="O53" s="5" t="n">
         <v>1.003214464440757</v>
@@ -3531,13 +3531,13 @@
         <v>0.1651517839548264</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>0.1966950351788632</v>
+        <v>0.1966951512882893</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>0.4798355367016791</v>
+        <v>0.4798358030308265</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.1395616291083945</v>
+        <v>0.1395616974714999</v>
       </c>
     </row>
     <row r="55">
@@ -3584,16 +3584,16 @@
         <v>0.04905335761316745</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>0.0801842767381571</v>
+        <v>0.08018426782088825</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>0.132662979778893</v>
+        <v>0.132662984964478</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>0.9139515095320989</v>
+        <v>0.9139515435462986</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>0.2367045862496402</v>
+        <v>0.2367045936194095</v>
       </c>
     </row>
     <row r="56">
@@ -3696,16 +3696,16 @@
         <v>0.05930075241846477</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>0.09187835817967109</v>
+        <v>0.09187833443069475</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>0.1366003170819881</v>
+        <v>0.1366003183405737</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>0.7548779177187885</v>
+        <v>0.7548778736050311</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>0.2023905624247323</v>
+        <v>0.202390554442756</v>
       </c>
     </row>
     <row r="58">
@@ -3752,16 +3752,16 @@
         <v>0.02172094039627015</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>0.2202239435632081</v>
+        <v>0.2202239628651922</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>0.1246398614228011</v>
+        <v>0.1246398504123304</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>1.081749411485936</v>
+        <v>1.081749305972386</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>0.2762575176467931</v>
+        <v>0.2762574950850315</v>
       </c>
     </row>
     <row r="59">
@@ -3808,16 +3808,16 @@
         <v>0.05325601585820777</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0.2072150619323131</v>
+        <v>0.2072150258933587</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>0.05880789129692254</v>
+        <v>0.05880792483785802</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>0.2230855429359004</v>
+        <v>0.2230855522401375</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>0.06876543578270977</v>
+        <v>0.06876544020813546</v>
       </c>
     </row>
     <row r="60">
@@ -3864,16 +3864,16 @@
         <v>0.003265306685461322</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0.3079876882351431</v>
+        <v>0.3079877951536523</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0.2853813295186243</v>
+        <v>0.2853812262640059</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>-0.3427057424473642</v>
+        <v>-0.3427056344469837</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>-0.130532647548442</v>
+        <v>-0.1305325999275585</v>
       </c>
     </row>
     <row r="61">
@@ -3923,13 +3923,13 @@
         <v>0.509707566085756</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>0.5895480294120689</v>
+        <v>0.5895481650369206</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>0.2030975881331674</v>
+        <v>0.2030976143648965</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>0.05832926600929272</v>
+        <v>0.05832926988865478</v>
       </c>
     </row>
     <row r="62">
@@ -3976,16 +3976,16 @@
         <v>-0.0414349303212586</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1307426058426255</v>
+        <v>0.1307425851854394</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>0.01069696265207507</v>
+        <v>0.01069697556751039</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>0.2549985031506669</v>
+        <v>0.254998540851327</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>0.0742725261165053</v>
+        <v>0.07427253689568103</v>
       </c>
     </row>
     <row r="63">
@@ -4032,16 +4032,16 @@
         <v>0.03024943773814237</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>0.08476218382151401</v>
+        <v>0.0847621188748533</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>-0.01051434343571156</v>
+        <v>-0.01051445151357067</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>0.07186173933538487</v>
+        <v>0.07186161251319123</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>0.02340198801222226</v>
+        <v>0.0234019476494014</v>
       </c>
     </row>
     <row r="64">
@@ -4085,19 +4085,19 @@
         <v>0.2289720393921856</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0.03889289030275717</v>
+        <v>0.03889293539113994</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>-0.01986553399750539</v>
+        <v>-0.01986551596778961</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>-0.1276463601174461</v>
+        <v>-0.1276463807300919</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>0.1391493624182561</v>
+        <v>0.139149324592236</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.03920958950496924</v>
+        <v>0.03920957653265825</v>
       </c>
     </row>
     <row r="65">
@@ -4141,19 +4141,19 @@
         <v>0.02182736144429483</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.03732829162513115</v>
+        <v>-0.03732831578128856</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>0.1492763369524938</v>
+        <v>0.1492763710895473</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>0.1918682034379461</v>
+        <v>0.1918682707180805</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0.09173440004147891</v>
+        <v>0.09173441115195947</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>0.01965811087573222</v>
+        <v>0.01965811297697756</v>
       </c>
     </row>
     <row r="66">
@@ -4200,16 +4200,16 @@
         <v>-0.003511802126315966</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.1139506886724377</v>
+        <v>0.1139507563340345</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>0.2695803881623753</v>
+        <v>0.2695804760506062</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>0.2396843507205504</v>
+        <v>0.2396842669227746</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>0.07424590365002115</v>
+        <v>0.07424587944509087</v>
       </c>
     </row>
     <row r="67">
@@ -4256,16 +4256,16 @@
         <v>0.007099407117818091</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.07273117116263332</v>
+        <v>0.07273112581062791</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>0.183703481946507</v>
+        <v>0.1837035105738283</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>-0.3216792428776012</v>
+        <v>-0.3216792002390391</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>-0.1289816047644357</v>
+        <v>-0.1289815888691415</v>
       </c>
     </row>
     <row r="68">
@@ -4309,19 +4309,19 @@
         <v>0.06692651191287173</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>0.04052376614311012</v>
+        <v>0.04052375281032131</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.1139444813374255</v>
+        <v>0.1139444912957799</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>0.04816968391860965</v>
+        <v>0.04816969996002142</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>0.896012940507383</v>
+        <v>0.8960129886504269</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>0.2217811370567889</v>
+        <v>0.2217811463390284</v>
       </c>
     </row>
     <row r="69">
@@ -4371,13 +4371,13 @@
         <v>0.1543540911070634</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>0.06687917218548484</v>
+        <v>0.06687908496828915</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>0.8996369937537674</v>
+        <v>0.8996370520584859</v>
       </c>
       <c r="P69" s="5" t="n">
-        <v>0.2376130394673187</v>
+        <v>0.2376130528568902</v>
       </c>
     </row>
     <row r="70">
@@ -4424,16 +4424,16 @@
         <v>0.01637442802856339</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.1530037301514266</v>
+        <v>0.1530037501539614</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>0.1424810965265437</v>
+        <v>0.1424811182803021</v>
       </c>
       <c r="O70" s="5" t="n">
-        <v>0.5227773318682024</v>
+        <v>0.5227774093395594</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1451716553644394</v>
+        <v>0.1451716784377843</v>
       </c>
     </row>
     <row r="71">
@@ -4477,19 +4477,19 @@
         <v>0.1211572770201386</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>0.1027016497291638</v>
+        <v>0.10270162611638</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0.03865492877539568</v>
+        <v>0.03865489632417729</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>-0.09081397583842868</v>
+        <v>-0.09081398243242207</v>
       </c>
       <c r="O71" s="5" t="n">
-        <v>0.09787665151774561</v>
+        <v>0.09787664311922864</v>
       </c>
       <c r="P71" s="5" t="n">
-        <v>0.01533953890636482</v>
+        <v>0.01533953738608052</v>
       </c>
     </row>
     <row r="72">
@@ -4533,19 +4533,19 @@
         <v>0.09173955738489752</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>0.1016345450627706</v>
+        <v>0.1016345033289338</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>-0.02975454383418071</v>
+        <v>-0.02975451025530392</v>
       </c>
       <c r="N72" s="5" t="n">
         <v>-0.002479768407605887</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>1.298880275650247</v>
+        <v>1.29888055322284</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.3190133058768712</v>
+        <v>0.3190133587264813</v>
       </c>
     </row>
     <row r="73">
@@ -4589,19 +4589,19 @@
         <v>0.04770654277635807</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.05324667100329095</v>
+        <v>-0.05324667574816281</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0.09015744569522857</v>
+        <v>0.0901574465499289</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>0.1191779768897901</v>
+        <v>0.1191779491428518</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>0.3141665907681475</v>
+        <v>0.3141666025306797</v>
       </c>
       <c r="P73" s="5" t="n">
-        <v>0.08545439524456536</v>
+        <v>0.0854544018958897</v>
       </c>
     </row>
     <row r="74">
@@ -4651,13 +4651,13 @@
         <v>0.07425395703221715</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>0.01278630629496262</v>
+        <v>0.01278633801104356</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>-0.1278608563899356</v>
+        <v>-0.1278608860792481</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>-0.04778502706960112</v>
+        <v>-0.0477850386054414</v>
       </c>
     </row>
     <row r="75">
@@ -4704,16 +4704,16 @@
         <v>-0.02520811421372898</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>0.09688625500529757</v>
+        <v>0.09688619822812261</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>0.2796447116453362</v>
+        <v>0.2796448756092769</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>0.7196960975836467</v>
+        <v>0.7196961578577539</v>
       </c>
       <c r="P75" s="5" t="n">
-        <v>0.1959984822336549</v>
+        <v>0.195998492658765</v>
       </c>
     </row>
     <row r="76">
@@ -4760,16 +4760,16 @@
         <v>0.1312490064017531</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.06835775475078321</v>
+        <v>0.06835768004161058</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>-0.0274913522793756</v>
+        <v>-0.02749129037412079</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>-0.04576927840611023</v>
+        <v>-0.04576915920580071</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>-0.01549528998671257</v>
+        <v>-0.01549524899269206</v>
       </c>
     </row>
     <row r="77">
@@ -4816,16 +4816,16 @@
         <v>-0.02389264286288229</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>0.095858302619657</v>
+        <v>0.09585835279682292</v>
       </c>
       <c r="N77" s="5" t="n">
         <v>0.1968926741913725</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>1.22347911798717</v>
+        <v>1.223479041844943</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>0.2800150472486087</v>
+        <v>0.2800150143648888</v>
       </c>
     </row>
     <row r="78">
@@ -4878,10 +4878,10 @@
         <v>0.03616838017222879</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>0.2651194030081727</v>
+        <v>0.265119553613179</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.08154311962356786</v>
+        <v>0.08154316254067684</v>
       </c>
     </row>
     <row r="79">
@@ -4928,10 +4928,10 @@
         <v>-0.01265541172470136</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>0.1246728236309786</v>
+        <v>0.124672889668394</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>0.05692156538477278</v>
+        <v>0.05692162393458144</v>
       </c>
       <c r="O79" s="5" t="n">
         <v>0.2480969866004727</v>
@@ -4981,19 +4981,19 @@
         <v>0.05488554268223447</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.0757792095472834</v>
+        <v>0.07577921887106284</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>0.01825149422765242</v>
+        <v>0.01825149781114631</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>-0.03314817582430511</v>
+        <v>-0.03314819998951907</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>0.5522195428041288</v>
+        <v>0.5522195761880412</v>
       </c>
       <c r="P80" s="5" t="n">
-        <v>0.1445141984685215</v>
+        <v>0.1445142012697748</v>
       </c>
     </row>
     <row r="81">
@@ -5040,16 +5040,16 @@
         <v>0.02606353218025992</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0.1326835582152692</v>
+        <v>0.1326835257429391</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0.0938041825800795</v>
+        <v>0.09380413397458115</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>0.3330896114729909</v>
+        <v>0.3330896363603277</v>
       </c>
       <c r="P81" s="5" t="n">
-        <v>0.09218827934868329</v>
+        <v>0.09218828159677539</v>
       </c>
     </row>
     <row r="82">
@@ -5099,7 +5099,7 @@
         <v>0.04452956075084114</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>0.03344276806703003</v>
+        <v>0.03344280829218079</v>
       </c>
       <c r="O82" s="5" t="n">
         <v>0.2653388269346399</v>
@@ -5152,7 +5152,7 @@
         <v>-0.000604263593011393</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>0.1356404224265627</v>
+        <v>0.1356403809277392</v>
       </c>
       <c r="N83" s="5" t="n">
         <v>0.1659868584652346</v>
@@ -5205,19 +5205,19 @@
         <v>0.1508166784052325</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.04586518876811482</v>
+        <v>-0.04586519374389343</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>-0.05794765106427437</v>
+        <v>-0.0579476492531991</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>-0.05685259373282515</v>
+        <v>-0.0568525761504273</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>0.04769139145990401</v>
+        <v>0.04769137902377932</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>0.01135622538734471</v>
+        <v>0.0113562248234968</v>
       </c>
     </row>
     <row r="85">
@@ -5264,16 +5264,16 @@
         <v>-0.06800147620935082</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>0.07453053172537098</v>
+        <v>0.07453050136187356</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>0.1802978631822739</v>
+        <v>0.1802979006586031</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>0.5954480159589656</v>
+        <v>0.5954480977692557</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>0.1619098433530375</v>
+        <v>0.1619098644334633</v>
       </c>
     </row>
     <row r="86">
@@ -5317,19 +5317,19 @@
         <v>-0.1028177579058399</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>0.009492471638602193</v>
+        <v>0.009492484009112364</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.04107534162063875</v>
+        <v>0.0410753827674738</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>0.2761433884728858</v>
+        <v>0.2761433534324411</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>0.8209075005142102</v>
+        <v>0.8209073092854101</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>0.2082070795389078</v>
+        <v>0.2082070380048951</v>
       </c>
     </row>
     <row r="87">
@@ -5376,10 +5376,10 @@
         <v>-0.07387827227329724</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>0.3617409383864472</v>
+        <v>0.3617407853653756</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0.2349467735058022</v>
+        <v>0.2349467001939153</v>
       </c>
       <c r="O87" s="5" t="n">
         <v>0.5603064446776735</v>
@@ -5429,19 +5429,19 @@
         <v>0.07088007223434678</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>-0.0510040583312393</v>
+        <v>-0.05100407272220209</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>0.04467460802065722</v>
+        <v>0.04467459783462193</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>-0.01815153104192085</v>
+        <v>-0.01815156749641074</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>0.1427961294446319</v>
+        <v>0.1427961635948015</v>
       </c>
       <c r="P88" s="5" t="n">
-        <v>0.0420353946758034</v>
+        <v>0.04203540734350889</v>
       </c>
     </row>
     <row r="89">
@@ -5485,19 +5485,19 @@
         <v>0.01464779743865567</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0.03438928474790497</v>
+        <v>0.03438930560738555</v>
       </c>
       <c r="M89" s="5" t="n">
         <v>0.05009699991286418</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>0.0005552670901640466</v>
+        <v>0.0005552997965329709</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>0.1268615357402452</v>
+        <v>0.1268615608152158</v>
       </c>
       <c r="P89" s="5" t="n">
-        <v>0.03955777250488013</v>
+        <v>0.03955778006531787</v>
       </c>
     </row>
     <row r="90">
@@ -5597,19 +5597,19 @@
         <v>0.06696428520563413</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>-0.08613164455213207</v>
+        <v>-0.08613164494115891</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>0.07131603913788867</v>
+        <v>0.07131601239814836</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>-0.01955074634439072</v>
+        <v>-0.01955075526016423</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>0.006636904074926703</v>
+        <v>0.006636924802320032</v>
       </c>
       <c r="P91" s="5" t="n">
-        <v>-0.003324483737715683</v>
+        <v>-0.003324479042501355</v>
       </c>
     </row>
     <row r="92">
@@ -5656,16 +5656,16 @@
         <v>0.1647139378092003</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>-0.07840006002029988</v>
+        <v>-0.07840006131040475</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>-0.1265676548460219</v>
+        <v>-0.1265676468981373</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>0.9472487842386338</v>
+        <v>0.947248801444158</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>0.12110146827863</v>
+        <v>0.1211014748048087</v>
       </c>
     </row>
     <row r="93">
@@ -5712,16 +5712,16 @@
         <v>0.09317179833976474</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>-0.0148184124274261</v>
+        <v>-0.01481844946767868</v>
       </c>
       <c r="N93" s="5" t="n">
         <v>-0.1802603004961097</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>-0.1433955746295581</v>
+        <v>-0.1433954741227476</v>
       </c>
       <c r="P93" s="5" t="n">
-        <v>-0.06791721103567377</v>
+        <v>-0.0679171857094335</v>
       </c>
     </row>
     <row r="94">
@@ -5765,19 +5765,19 @@
         <v>0.0709557777684276</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-0.06652131048339929</v>
+        <v>-0.06652130020657218</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>0.01165445805329572</v>
+        <v>0.01165443668509121</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>-0.02292648557980752</v>
+        <v>-0.02292645903471846</v>
       </c>
       <c r="O94" s="5" t="n">
-        <v>-0.1302321657715643</v>
+        <v>-0.1302322431852419</v>
       </c>
       <c r="P94" s="5" t="n">
-        <v>-0.04914107359264204</v>
+        <v>-0.04914110246014901</v>
       </c>
     </row>
     <row r="95">
@@ -5824,16 +5824,16 @@
         <v>-0.109827545192278</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>0.05962140643671583</v>
+        <v>0.05962141474326727</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>0.07799835326331095</v>
+        <v>0.07799836616742295</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>1.068228447060821</v>
+        <v>1.068228357053164</v>
       </c>
       <c r="P95" s="5" t="n">
-        <v>0.2365294263021938</v>
+        <v>0.2365294108310065</v>
       </c>
     </row>
     <row r="96">
@@ -5880,16 +5880,16 @@
         <v>-0.006696399262230979</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>-0.1871357994532691</v>
+        <v>-0.1871357441718897</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>-0.2718418548609312</v>
+        <v>-0.2718418105006494</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>0.03200866191090457</v>
+        <v>0.03200875101744227</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>0.01055769673879015</v>
+        <v>0.0105577258235896</v>
       </c>
     </row>
     <row r="97">
@@ -5936,16 +5936,16 @@
         <v>-0.03079516158976159</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>0.07044555642221328</v>
+        <v>0.07044564994136526</v>
       </c>
       <c r="N97" s="5" t="n">
         <v>-0.07224504896442208</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>-0.2227651345969558</v>
+        <v>-0.2227650359903628</v>
       </c>
       <c r="P97" s="5" t="n">
-        <v>-0.08057263683400495</v>
+        <v>-0.08057259795189431</v>
       </c>
     </row>
     <row r="98">
@@ -5995,13 +5995,13 @@
         <v>-0.04172542472593121</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>0.02318233646908885</v>
+        <v>0.02318243262546793</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>0.5409506639429866</v>
+        <v>0.5409508820399012</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>0.1550379263154382</v>
+        <v>0.1550379808078157</v>
       </c>
     </row>
     <row r="99">
@@ -6045,19 +6045,19 @@
         <v>-0.05185303057677687</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.08742211089222036</v>
+        <v>-0.08742210279305079</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>-0.01486550505293595</v>
+        <v>-0.01486551512813572</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>0.06063198483888483</v>
+        <v>0.06063195669644034</v>
       </c>
       <c r="O99" s="5" t="n">
-        <v>0.3917200819573673</v>
+        <v>0.3917200634242197</v>
       </c>
       <c r="P99" s="5" t="n">
-        <v>0.1134246284962912</v>
+        <v>0.1134246245111905</v>
       </c>
     </row>
     <row r="100">
@@ -6104,16 +6104,16 @@
         <v>0.01665213669109419</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>-0.07995263850649822</v>
+        <v>-0.07995268892979254</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>0.1519293815811567</v>
+        <v>0.1519293372492562</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>1.309676502430605</v>
+        <v>1.309676410397927</v>
       </c>
       <c r="P100" s="5" t="n">
-        <v>0.3199868078457757</v>
+        <v>0.3199867910275161</v>
       </c>
     </row>
     <row r="101">
@@ -6269,19 +6269,19 @@
         <v>0.05097457215017315</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>0.0478147786436931</v>
+        <v>0.04781478003607856</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>-0.1886731063153543</v>
+        <v>-0.1886730942510748</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>-0.1417178460346876</v>
+        <v>-0.1417178190376714</v>
       </c>
       <c r="O103" s="5" t="n">
-        <v>-0.02882830845180362</v>
+        <v>-0.02882833147052874</v>
       </c>
       <c r="P103" s="5" t="n">
-        <v>-0.03303531299152493</v>
+        <v>-0.03303531521204803</v>
       </c>
     </row>
     <row r="104">
@@ -6328,16 +6328,16 @@
         <v>-0.1932271358168874</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>-0.2395991720401368</v>
+        <v>-0.2395991747294968</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>-0.01250503582477164</v>
+        <v>-0.01250511532833082</v>
       </c>
       <c r="O104" s="5" t="n">
-        <v>0.4048563928391163</v>
+        <v>0.4048564534148879</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.1189930270949224</v>
+        <v>0.1189930469563926</v>
       </c>
     </row>
     <row r="105">
@@ -6390,10 +6390,10 @@
         <v>-0.247287706796265</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>-0.1230467854093554</v>
+        <v>-0.1230467591426738</v>
       </c>
       <c r="P105" s="5" t="n">
-        <v>-0.04332463618747062</v>
+        <v>-0.04332462616728128</v>
       </c>
     </row>
     <row r="106">
@@ -6437,19 +6437,19 @@
         <v>-0.04520047216570665</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>-0.09776796544943227</v>
+        <v>-0.09776797048324734</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.03402970735675583</v>
+        <v>-0.03402970155750022</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>0.03005662345239214</v>
+        <v>0.03005663548281519</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>0.771885500124336</v>
+        <v>0.7718854448745246</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>0.1875404804673993</v>
+        <v>0.1875404694914624</v>
       </c>
     </row>
     <row r="107">
@@ -6496,16 +6496,16 @@
         <v>-0.1065691457434384</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>-0.106938630187696</v>
+        <v>-0.1069386000724477</v>
       </c>
       <c r="N107" s="5" t="n">
         <v>-0.1901873495272314</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>0.2891053910667852</v>
+        <v>0.2891053971671476</v>
       </c>
       <c r="P107" s="5" t="n">
-        <v>0.07485695402443855</v>
+        <v>0.07485695614440795</v>
       </c>
     </row>
     <row r="108">
@@ -6555,13 +6555,13 @@
         <v>-0.00223042411365823</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>0.04275098677680161</v>
+        <v>0.04275103914503878</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>0.08031712175533021</v>
+        <v>0.08031700914146536</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.01695355061435516</v>
+        <v>0.0169535154428295</v>
       </c>
     </row>
     <row r="109">
@@ -6608,16 +6608,16 @@
         <v>-0.07771109433632555</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>-0.03807603999069351</v>
+        <v>-0.0380760248170303</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>-0.118851943060909</v>
+        <v>-0.1188519370178728</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>0.6174358307528174</v>
+        <v>0.6174358322219257</v>
       </c>
       <c r="P109" s="5" t="n">
-        <v>0.1580119614226169</v>
+        <v>0.1580119653143813</v>
       </c>
     </row>
     <row r="110">
@@ -6667,13 +6667,13 @@
         <v>-0.04061945157033986</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>-0.1260818601592902</v>
+        <v>-0.1260819004134384</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>-0.516067470217239</v>
+        <v>-0.5160674836407406</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>-0.2158863358807963</v>
+        <v>-0.2158863437055162</v>
       </c>
     </row>
     <row r="111">
@@ -6717,19 +6717,19 @@
         <v>0.026775327730058</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>-0.1252855750683425</v>
+        <v>-0.1252855949926256</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>-0.09621737312718673</v>
+        <v>-0.09621738274243491</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>-0.1204948863119873</v>
+        <v>-0.1204949189146825</v>
       </c>
       <c r="O111" s="5" t="n">
-        <v>0.3326399444961803</v>
+        <v>0.3326397554503118</v>
       </c>
       <c r="P111" s="5" t="n">
-        <v>0.09470309174023279</v>
+        <v>0.09470304087418957</v>
       </c>
     </row>
     <row r="112">
@@ -6829,19 +6829,19 @@
         <v>-0.017048320432155</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>-0.1358773418916363</v>
+        <v>-0.1358773370106852</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>-0.04671057592573637</v>
+        <v>-0.04671053974255482</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>-0.08698701946561672</v>
+        <v>-0.0869870415566513</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>0.3630891923902875</v>
+        <v>0.3630891827220569</v>
       </c>
       <c r="P113" s="5" t="n">
-        <v>0.08404625117969503</v>
+        <v>0.08404625434113379</v>
       </c>
     </row>
     <row r="114">
@@ -6891,13 +6891,13 @@
         <v>-0.1065854367060414</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>-0.1691874519693053</v>
+        <v>-0.1691875181939719</v>
       </c>
       <c r="O114" s="5" t="n">
-        <v>-0.3023932824219434</v>
+        <v>-0.3023932357307411</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>-0.1131090608430564</v>
+        <v>-0.113109041056357</v>
       </c>
     </row>
     <row r="115">
@@ -6944,16 +6944,16 @@
         <v>-0.07788237278430681</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>-0.04729224452372013</v>
+        <v>-0.04729218910873897</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>-0.1167864903362424</v>
+        <v>-0.1167865377122277</v>
       </c>
       <c r="O115" s="5" t="n">
-        <v>-0.04422675786136673</v>
+        <v>-0.04422692840827699</v>
       </c>
       <c r="P115" s="5" t="n">
-        <v>-0.01581194198594878</v>
+        <v>-0.01581199899227599</v>
       </c>
     </row>
     <row r="116">
@@ -7000,16 +7000,16 @@
         <v>-0.2343138562258431</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>-0.06710986996087837</v>
+        <v>-0.06710991362849222</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>-0.2746845735125883</v>
+        <v>-0.2746846010444992</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>-0.4870026537207002</v>
+        <v>-0.4870027196046802</v>
       </c>
       <c r="P116" s="5" t="n">
-        <v>-0.2090642909005793</v>
+        <v>-0.2090643193549707</v>
       </c>
     </row>
     <row r="117">
@@ -7062,10 +7062,10 @@
         <v>-0.1656276019998317</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>0.07015678529462444</v>
+        <v>0.07015682442741078</v>
       </c>
       <c r="P117" s="5" t="n">
-        <v>0.01779836448213257</v>
+        <v>0.01779837906269038</v>
       </c>
     </row>
     <row r="118">
@@ -7112,16 +7112,16 @@
         <v>-0.1722178027859526</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>-0.1025403503319982</v>
+        <v>-0.1025403094148771</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>-0.1815577450405936</v>
+        <v>-0.1815577938900413</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>0.00358010066690817</v>
+        <v>0.003580034374389696</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>0.0007866142846453261</v>
+        <v>0.0007865913061015917</v>
       </c>
     </row>
     <row r="119">
@@ -7165,19 +7165,19 @@
         <v>0.008443841937212176</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>-0.1462061222600525</v>
+        <v>-0.1462061314097463</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>-0.1478550159298269</v>
+        <v>-0.1478550038422457</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>-0.1874809793387851</v>
+        <v>-0.1874809689294954</v>
       </c>
       <c r="O119" s="5" t="n">
-        <v>0.1461422037362812</v>
+        <v>0.1461420942507165</v>
       </c>
       <c r="P119" s="5" t="n">
-        <v>0.03834033903979914</v>
+        <v>0.03834030467723165</v>
       </c>
     </row>
     <row r="120">
@@ -7221,13 +7221,13 @@
         <v>-0.1815809841970754</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>-0.2056435248556833</v>
+        <v>-0.2056434949852167</v>
       </c>
       <c r="M120" s="5" t="n">
         <v>0.02831183189625697</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>0.06505943456145247</v>
+        <v>0.065059411955952</v>
       </c>
       <c r="O120" s="5" t="n">
         <v>2.183191424422632</v>
@@ -7280,16 +7280,16 @@
         <v>-0.08269422517060916</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>-0.153155167148694</v>
+        <v>-0.1531551529248393</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>-0.1514541486561416</v>
+        <v>-0.1514541633773639</v>
       </c>
       <c r="O121" s="5" t="n">
-        <v>-0.09433516590611102</v>
+        <v>-0.09433516904919836</v>
       </c>
       <c r="P121" s="5" t="n">
-        <v>-0.03271353940003507</v>
+        <v>-0.03271354004570959</v>
       </c>
     </row>
     <row r="122">
@@ -7336,16 +7336,16 @@
         <v>-0.2533538424532739</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>-0.1286023168241335</v>
+        <v>-0.128602287004033</v>
       </c>
       <c r="N122" s="5" t="n">
         <v>-0.04565292959490397</v>
       </c>
       <c r="O122" s="5" t="n">
-        <v>1.025839966753148</v>
+        <v>1.025839633980116</v>
       </c>
       <c r="P122" s="5" t="n">
-        <v>0.2209198121012478</v>
+        <v>0.2209197599206823</v>
       </c>
     </row>
     <row r="123">
@@ -7389,19 +7389,19 @@
         <v>-0.09404279730262828</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>-0.1873319827659207</v>
+        <v>-0.1873319657326371</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>-0.1524759775980741</v>
+        <v>-0.1524759906263695</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>-0.1256829943909701</v>
+        <v>-0.1256830032441041</v>
       </c>
       <c r="O123" s="5" t="n">
-        <v>0.3915242497059466</v>
+        <v>0.3915242355313837</v>
       </c>
       <c r="P123" s="5" t="n">
-        <v>0.1128284383791508</v>
+        <v>0.1128284314242511</v>
       </c>
     </row>
     <row r="124">
@@ -7504,16 +7504,16 @@
         <v>-0.2382021584669423</v>
       </c>
       <c r="M125" s="5" t="n">
-        <v>-0.1595708360993556</v>
+        <v>-0.1595708454163446</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>-0.1195491669955029</v>
+        <v>-0.1195491568440209</v>
       </c>
       <c r="O125" s="5" t="n">
-        <v>0.9552676458326772</v>
+        <v>0.955267907323216</v>
       </c>
       <c r="P125" s="5" t="n">
-        <v>0.1170769611762832</v>
+        <v>0.1170770035794964</v>
       </c>
     </row>
     <row r="126">
@@ -7622,10 +7622,10 @@
         <v>-0.3115379480135468</v>
       </c>
       <c r="O127" s="5" t="n">
-        <v>1.863872793925104</v>
+        <v>1.863872835757483</v>
       </c>
       <c r="P127" s="5" t="n">
-        <v>0.183647755990432</v>
+        <v>0.1836477683392225</v>
       </c>
     </row>
     <row r="128">
@@ -8049,10 +8049,10 @@
         <v>-0.05777370925993863</v>
       </c>
       <c r="L6" t="n">
-        <v>1.03613354532528</v>
+        <v>1.036133698058325</v>
       </c>
       <c r="M6" t="n">
-        <v>2.009127255901277</v>
+        <v>2.009126922320115</v>
       </c>
       <c r="N6" t="n">
         <v>3.989365479002857</v>
@@ -8113,7 +8113,7 @@
         <v>1.371035770866738</v>
       </c>
       <c r="N7" t="n">
-        <v>2.373802456215067</v>
+        <v>2.373802251070248</v>
       </c>
       <c r="O7" t="n">
         <v>2.667499132623044</v>
@@ -8165,19 +8165,19 @@
         <v>-0.1516209029779765</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6120240154489227</v>
+        <v>0.6120241914641111</v>
       </c>
       <c r="M8" t="n">
-        <v>1.762784873870795</v>
+        <v>1.762785132377175</v>
       </c>
       <c r="N8" t="n">
-        <v>4.623238693626198</v>
+        <v>4.623239229077736</v>
       </c>
       <c r="O8" t="n">
-        <v>12.3068166621131</v>
+        <v>12.30681516289301</v>
       </c>
       <c r="P8" t="n">
-        <v>1.369689210263453</v>
+        <v>1.369689121269321</v>
       </c>
     </row>
     <row r="9">
@@ -8232,10 +8232,10 @@
         <v>2.780769057304163</v>
       </c>
       <c r="O9" t="n">
-        <v>7.507914284215609</v>
+        <v>7.507914889740421</v>
       </c>
       <c r="P9" t="n">
-        <v>1.041460754055163</v>
+        <v>1.04146080248674</v>
       </c>
     </row>
     <row r="10">
@@ -8281,19 +8281,19 @@
         <v>0.471722431868294</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7690529142179929</v>
+        <v>0.7690527811713233</v>
       </c>
       <c r="M10" t="n">
         <v>1.060607966629657</v>
       </c>
       <c r="N10" t="n">
-        <v>1.411222008150446</v>
+        <v>1.411221760979882</v>
       </c>
       <c r="O10" t="n">
-        <v>2.000529763782501</v>
+        <v>2.000529572406159</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4423344599316297</v>
+        <v>0.4423344292671894</v>
       </c>
     </row>
     <row r="11">
@@ -8348,10 +8348,10 @@
         <v>2.675975389484893</v>
       </c>
       <c r="O11" t="n">
-        <v>1.589842594104086</v>
+        <v>1.589842308256058</v>
       </c>
       <c r="P11" t="n">
-        <v>0.373275872120659</v>
+        <v>0.3732758215965826</v>
       </c>
     </row>
     <row r="12">
@@ -8461,13 +8461,13 @@
         <v>1.425597035948844</v>
       </c>
       <c r="N13" t="n">
-        <v>1.362788878413986</v>
+        <v>1.362788674579952</v>
       </c>
       <c r="O13" t="n">
-        <v>2.32255983643413</v>
+        <v>2.322559634902833</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4921904985652561</v>
+        <v>0.4921904683954363</v>
       </c>
     </row>
     <row r="14">
@@ -8806,16 +8806,16 @@
         <v>0.8958220377930792</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9493835465651277</v>
+        <v>0.9493833912429892</v>
       </c>
       <c r="N19" t="n">
         <v>1.112044660267259</v>
       </c>
       <c r="O19" t="n">
-        <v>1.774207543004305</v>
+        <v>1.774208172143575</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4051186001046103</v>
+        <v>0.405118706322958</v>
       </c>
     </row>
     <row r="20">
@@ -8870,10 +8870,10 @@
         <v>0.7440570832316022</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4189281266919147</v>
+        <v>0.418928222171127</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1237079822031237</v>
+        <v>0.1237080074077714</v>
       </c>
     </row>
     <row r="21">
@@ -8922,10 +8922,10 @@
         <v>0.6178864222369906</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8380633522866219</v>
+        <v>0.8380631432207613</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9005971287809815</v>
+        <v>0.9005973523143727</v>
       </c>
       <c r="O21" t="n">
         <v>1.384535657291007</v>
@@ -8986,10 +8986,10 @@
         <v>1.966217225464943</v>
       </c>
       <c r="O22" t="n">
-        <v>2.277076453369596</v>
+        <v>2.277076219159206</v>
       </c>
       <c r="P22" t="n">
-        <v>0.485350195857293</v>
+        <v>0.4853501604716415</v>
       </c>
     </row>
     <row r="23">
@@ -9038,7 +9038,7 @@
         <v>0.2914782214242084</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9394945982894003</v>
+        <v>0.9394944079081047</v>
       </c>
       <c r="N23" t="n">
         <v>2.027045311962594</v>
@@ -9102,10 +9102,10 @@
         <v>1.867164712580105</v>
       </c>
       <c r="O24" t="n">
-        <v>2.071896015652625</v>
+        <v>2.07189632977436</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4536800719887206</v>
+        <v>0.453680121538194</v>
       </c>
     </row>
     <row r="25">
@@ -9160,10 +9160,10 @@
         <v>0.9231244225873458</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1033749291949533</v>
+        <v>0.1033748215669104</v>
       </c>
       <c r="P25" t="n">
-        <v>0.03333475648160733</v>
+        <v>0.03333472288293415</v>
       </c>
     </row>
     <row r="26">
@@ -9273,13 +9273,13 @@
         <v>0.6374273433948052</v>
       </c>
       <c r="N27" t="n">
-        <v>0.7074717715965104</v>
+        <v>0.7074716553712446</v>
       </c>
       <c r="O27" t="n">
-        <v>2.061605065913235</v>
+        <v>2.06160469224017</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4520549643620717</v>
+        <v>0.4520549052869745</v>
       </c>
     </row>
     <row r="28">
@@ -9441,7 +9441,7 @@
         <v>0.06634212300624487</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8863448770385642</v>
+        <v>0.8863447305241785</v>
       </c>
       <c r="M30" t="n">
         <v>0.6826482358934629</v>
@@ -9450,10 +9450,10 @@
         <v>0.6715376168282994</v>
       </c>
       <c r="O30" t="n">
-        <v>1.561326083618367</v>
+        <v>1.561325813491484</v>
       </c>
       <c r="P30" t="n">
-        <v>0.3682169218901403</v>
+        <v>0.3682168737910734</v>
       </c>
     </row>
     <row r="31">
@@ -9731,10 +9731,10 @@
         <v>0.1566404916723056</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2574469574026372</v>
+        <v>0.2574470395643436</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6997587084316561</v>
+        <v>0.6997585583026584</v>
       </c>
       <c r="N35" t="n">
         <v>0.7880567873867996</v>
@@ -9795,7 +9795,7 @@
         <v>0.2473771217058383</v>
       </c>
       <c r="N36" t="n">
-        <v>0.4873105274208971</v>
+        <v>0.4873106338596502</v>
       </c>
       <c r="O36" t="n">
         <v>1.966291345816307</v>
@@ -9853,7 +9853,7 @@
         <v>0.7747932484367259</v>
       </c>
       <c r="N37" t="n">
-        <v>0.7241940597639631</v>
+        <v>0.724193910034578</v>
       </c>
       <c r="O37" t="n">
         <v>0.973035454602007</v>
@@ -9969,13 +9969,13 @@
         <v>0.4423950170665902</v>
       </c>
       <c r="N39" t="n">
-        <v>0.8152627478562366</v>
+        <v>0.8152625777139924</v>
       </c>
       <c r="O39" t="n">
-        <v>0.4870770661537134</v>
+        <v>0.4870768377884267</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1414174085271271</v>
+        <v>0.1414173500992817</v>
       </c>
     </row>
     <row r="40">
@@ -10021,7 +10021,7 @@
         <v>0.1633285903631383</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3184003312073078</v>
+        <v>0.3184002292211834</v>
       </c>
       <c r="M40" t="n">
         <v>0.6764188380490883</v>
@@ -10198,7 +10198,7 @@
         <v>0.1767647788610305</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6901622313309097</v>
+        <v>0.690162412649548</v>
       </c>
       <c r="N43" t="n">
         <v>0.675940074933459</v>
@@ -10259,13 +10259,13 @@
         <v>0.5798031822779075</v>
       </c>
       <c r="N44" t="n">
-        <v>0.7009704855692465</v>
+        <v>0.70097030872155</v>
       </c>
       <c r="O44" t="n">
-        <v>0.5142564718276168</v>
+        <v>0.5142563316738633</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1483293882128003</v>
+        <v>0.1483293527844824</v>
       </c>
     </row>
     <row r="45">
@@ -10378,10 +10378,10 @@
         <v>1.234000569090719</v>
       </c>
       <c r="O46" t="n">
-        <v>3.816228932683596</v>
+        <v>3.816228635211842</v>
       </c>
       <c r="P46" t="n">
-        <v>0.6887643048179377</v>
+        <v>0.6887642700494014</v>
       </c>
     </row>
     <row r="47">
@@ -10494,10 +10494,10 @@
         <v>0.589777505500598</v>
       </c>
       <c r="O48" t="n">
-        <v>0.6830420497065317</v>
+        <v>0.6830421636599096</v>
       </c>
       <c r="P48" t="n">
-        <v>0.1895014859184301</v>
+        <v>0.1895015127642061</v>
       </c>
     </row>
     <row r="49">
@@ -10549,13 +10549,13 @@
         <v>0.4565991941443026</v>
       </c>
       <c r="N49" t="n">
-        <v>0.5538833720751337</v>
+        <v>0.5538834862962587</v>
       </c>
       <c r="O49" t="n">
-        <v>2.866627255257527</v>
+        <v>2.866627962509646</v>
       </c>
       <c r="P49" t="n">
-        <v>0.5695582425505987</v>
+        <v>0.5695583382475504</v>
       </c>
     </row>
     <row r="50">
@@ -10662,7 +10662,7 @@
         <v>0.1536026496271956</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4981327559844153</v>
+        <v>0.4981328535816103</v>
       </c>
       <c r="N51" t="n">
         <v>1.022895543875165</v>
@@ -10717,10 +10717,10 @@
         <v>0.1119518310023426</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3186453487913927</v>
+        <v>0.318645251674375</v>
       </c>
       <c r="M52" t="n">
-        <v>0.570476118801029</v>
+        <v>0.5704759810477356</v>
       </c>
       <c r="N52" t="n">
         <v>0.4017761975992817</v>
@@ -10784,10 +10784,10 @@
         <v>0.5450753048631929</v>
       </c>
       <c r="O53" t="n">
-        <v>1.347590402425102</v>
+        <v>1.347590081749631</v>
       </c>
       <c r="P53" t="n">
-        <v>0.329048333175932</v>
+        <v>0.3290482726609434</v>
       </c>
     </row>
     <row r="54">
@@ -10836,16 +10836,16 @@
         <v>0.08287569658966132</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5843655858948043</v>
+        <v>0.5843654867686843</v>
       </c>
       <c r="N54" t="n">
         <v>1.201917843095177</v>
       </c>
       <c r="O54" t="n">
-        <v>7.455019277464439</v>
+        <v>7.455019983207444</v>
       </c>
       <c r="P54" t="n">
-        <v>1.037221264588355</v>
+        <v>1.037221321270844</v>
       </c>
     </row>
     <row r="55">
@@ -10949,7 +10949,7 @@
         <v>0.400736708999945</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2292215153218278</v>
+        <v>0.2292214356101392</v>
       </c>
       <c r="M56" t="n">
         <v>0.1257424574800672</v>
@@ -10958,10 +10958,10 @@
         <v>0.3311297217276736</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.0631410511132805</v>
+        <v>-0.06314095850705381</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.02150621881848147</v>
+        <v>-0.02150618657790637</v>
       </c>
     </row>
     <row r="57">
@@ -11016,10 +11016,10 @@
         <v>0.8459395698109005</v>
       </c>
       <c r="O57" t="n">
-        <v>0.4544325358459682</v>
+        <v>0.4544326574342765</v>
       </c>
       <c r="P57" t="n">
-        <v>0.1330033494114322</v>
+        <v>0.1330033809838733</v>
       </c>
     </row>
     <row r="58">
@@ -11071,7 +11071,7 @@
         <v>0.2698319461132823</v>
       </c>
       <c r="N58" t="n">
-        <v>0.5355915097578132</v>
+        <v>0.5355913423583054</v>
       </c>
       <c r="O58" t="n">
         <v>0.8347142992507806</v>
@@ -11132,10 +11132,10 @@
         <v>0.4455510369431039</v>
       </c>
       <c r="O59" t="n">
-        <v>1.66954559139589</v>
+        <v>1.669546470422046</v>
       </c>
       <c r="P59" t="n">
-        <v>0.3872214029535881</v>
+        <v>0.3872215552146778</v>
       </c>
     </row>
     <row r="60">
@@ -11187,13 +11187,13 @@
         <v>0.3893456060753537</v>
       </c>
       <c r="N60" t="n">
-        <v>0.05508743150323636</v>
+        <v>0.05508751316780414</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.3228668486265434</v>
+        <v>-0.3228666468102305</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.1218715950595253</v>
+        <v>-0.1218715078188701</v>
       </c>
     </row>
     <row r="61">
@@ -11239,19 +11239,19 @@
         <v>0.02299047138662336</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1318952266645692</v>
+        <v>0.1318953006703241</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5808415264808915</v>
+        <v>0.5808416708351893</v>
       </c>
       <c r="N61" t="n">
         <v>0.6204094962116635</v>
       </c>
       <c r="O61" t="n">
-        <v>0.7420682866609638</v>
+        <v>0.742068461961563</v>
       </c>
       <c r="P61" t="n">
-        <v>0.2032477500082566</v>
+        <v>0.2032477903683361</v>
       </c>
     </row>
     <row r="62">
@@ -11361,13 +11361,13 @@
         <v>0.5267845572036145</v>
       </c>
       <c r="N63" t="n">
-        <v>0.3808928406996144</v>
+        <v>0.3808927308934107</v>
       </c>
       <c r="O63" t="n">
-        <v>0.2221372857461361</v>
+        <v>0.2221373717557453</v>
       </c>
       <c r="P63" t="n">
-        <v>0.06915334245551641</v>
+        <v>0.06915336753656653</v>
       </c>
     </row>
     <row r="64">
@@ -11419,7 +11419,7 @@
         <v>0.3954596669379673</v>
       </c>
       <c r="N64" t="n">
-        <v>0.7123698708375017</v>
+        <v>0.7123700483005675</v>
       </c>
       <c r="O64" t="n">
         <v>2.416258542488575</v>
@@ -11538,10 +11538,10 @@
         <v>0.4318695917104045</v>
       </c>
       <c r="O66" t="n">
-        <v>0.1084031908540262</v>
+        <v>0.1084032637004677</v>
       </c>
       <c r="P66" t="n">
-        <v>0.03490207039522386</v>
+        <v>0.03490209306715775</v>
       </c>
     </row>
     <row r="67">
@@ -11590,16 +11590,16 @@
         <v>0.1386405733420881</v>
       </c>
       <c r="M67" t="n">
-        <v>0.393139635364594</v>
+        <v>0.3931394817128653</v>
       </c>
       <c r="N67" t="n">
-        <v>0.3563481987761585</v>
+        <v>0.3563480531328467</v>
       </c>
       <c r="O67" t="n">
-        <v>0.1517362196410486</v>
+        <v>0.1517360096096771</v>
       </c>
       <c r="P67" t="n">
-        <v>0.04821653998956466</v>
+        <v>0.04821647627174253</v>
       </c>
     </row>
     <row r="68">
@@ -11764,10 +11764,10 @@
         <v>0.1949126202020932</v>
       </c>
       <c r="M70" t="n">
-        <v>0.2642791613460276</v>
+        <v>0.2642792946484567</v>
       </c>
       <c r="N70" t="n">
-        <v>0.3692006658510623</v>
+        <v>0.3692008221968954</v>
       </c>
       <c r="O70" t="n">
         <v>1.394901016147734</v>
@@ -11828,10 +11828,10 @@
         <v>0.4840352060361146</v>
       </c>
       <c r="O71" t="n">
-        <v>0.2480063710616074</v>
+        <v>0.2480065489232444</v>
       </c>
       <c r="P71" t="n">
-        <v>0.07664435450724505</v>
+        <v>0.07664440565381048</v>
       </c>
     </row>
     <row r="72">
@@ -11880,16 +11880,16 @@
         <v>0.04576371472426222</v>
       </c>
       <c r="M72" t="n">
-        <v>0.4226481722295998</v>
+        <v>0.422648266540852</v>
       </c>
       <c r="N72" t="n">
-        <v>0.3854120850939</v>
+        <v>0.385411995655015</v>
       </c>
       <c r="O72" t="n">
-        <v>0.6607719570002715</v>
+        <v>0.6607718284750286</v>
       </c>
       <c r="P72" t="n">
-        <v>0.1842316601145804</v>
+        <v>0.1842316295658015</v>
       </c>
     </row>
     <row r="73">
@@ -11938,16 +11938,16 @@
         <v>0.05809331327393763</v>
       </c>
       <c r="M73" t="n">
-        <v>0.4929663921784138</v>
+        <v>0.4929664960606992</v>
       </c>
       <c r="N73" t="n">
         <v>0.7926104616034477</v>
       </c>
       <c r="O73" t="n">
-        <v>0.6547518900114664</v>
+        <v>0.6547517623948751</v>
       </c>
       <c r="P73" t="n">
-        <v>0.1827990360976826</v>
+        <v>0.1827990056913549</v>
       </c>
     </row>
     <row r="74">
@@ -12002,10 +12002,10 @@
         <v>0.5343519578001705</v>
       </c>
       <c r="O74" t="n">
-        <v>0.79062671409812</v>
+        <v>0.790626530066068</v>
       </c>
       <c r="P74" t="n">
-        <v>0.2143252338007413</v>
+        <v>0.2143251921998928</v>
       </c>
     </row>
     <row r="75">
@@ -12051,13 +12051,13 @@
         <v>0.1237241916411698</v>
       </c>
       <c r="L75" t="n">
-        <v>0.6260403646127934</v>
+        <v>0.62604053260227</v>
       </c>
       <c r="M75" t="n">
         <v>0.2795353939224547</v>
       </c>
       <c r="N75" t="n">
-        <v>0.1058280726882748</v>
+        <v>0.1058281503835554</v>
       </c>
       <c r="O75" t="n">
         <v>0.1424811961034147</v>
@@ -12115,13 +12115,13 @@
         <v>0.4569917094561056</v>
       </c>
       <c r="N76" t="n">
-        <v>0.6323324604804117</v>
+        <v>0.6323326444662483</v>
       </c>
       <c r="O76" t="n">
-        <v>1.085307248198827</v>
+        <v>1.085307098065473</v>
       </c>
       <c r="P76" t="n">
-        <v>0.2775856278834297</v>
+        <v>0.2775855972231642</v>
       </c>
     </row>
     <row r="77">
@@ -12234,10 +12234,10 @@
         <v>0.3461646495098065</v>
       </c>
       <c r="O78" t="n">
-        <v>0.93801438297179</v>
+        <v>0.9380148599630125</v>
       </c>
       <c r="P78" t="n">
-        <v>0.2467680525149867</v>
+        <v>0.2467681548013567</v>
       </c>
     </row>
     <row r="79">
@@ -12286,10 +12286,10 @@
         <v>0.07759564031331201</v>
       </c>
       <c r="M79" t="n">
-        <v>0.3935375343551597</v>
+        <v>0.3935376829840072</v>
       </c>
       <c r="N79" t="n">
-        <v>0.9202185675901386</v>
+        <v>0.9202187086934119</v>
       </c>
       <c r="O79" t="n">
         <v>1.95876769228766</v>
@@ -12344,16 +12344,16 @@
         <v>0.1544519087830498</v>
       </c>
       <c r="M80" t="n">
-        <v>0.2977383980603301</v>
+        <v>0.2977383000971374</v>
       </c>
       <c r="N80" t="n">
-        <v>0.2357275954252054</v>
+        <v>0.2357276842499925</v>
       </c>
       <c r="O80" t="n">
-        <v>0.01660304201450491</v>
+        <v>0.01660292178213507</v>
       </c>
       <c r="P80" t="n">
-        <v>0.005503997767391189</v>
+        <v>0.005503958127489605</v>
       </c>
     </row>
     <row r="81">
@@ -12408,10 +12408,10 @@
         <v>0.1941445114142084</v>
       </c>
       <c r="O81" t="n">
-        <v>1.829076408285253</v>
+        <v>1.829076838141252</v>
       </c>
       <c r="P81" t="n">
-        <v>0.4143217680169287</v>
+        <v>0.4143218396486295</v>
       </c>
     </row>
     <row r="82">
@@ -12463,13 +12463,13 @@
         <v>0.1789412031372208</v>
       </c>
       <c r="N82" t="n">
-        <v>-0.04668988098236693</v>
+        <v>-0.04668998988129192</v>
       </c>
       <c r="O82" t="n">
-        <v>0.1537741503753962</v>
+        <v>0.1537742301320417</v>
       </c>
       <c r="P82" t="n">
-        <v>0.04883442857297782</v>
+        <v>0.04883445274047871</v>
       </c>
     </row>
     <row r="83">
@@ -12524,10 +12524,10 @@
         <v>0.2703222572869006</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.09161695284077287</v>
+        <v>-0.09161688590685324</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.03152219222198804</v>
+        <v>-0.03152216843466094</v>
       </c>
     </row>
     <row r="84">
@@ -12582,10 +12582,10 @@
         <v>0.3252391343426835</v>
       </c>
       <c r="O84" t="n">
-        <v>0.7141693665763329</v>
+        <v>0.7141694833247734</v>
       </c>
       <c r="P84" t="n">
-        <v>0.1967898847761469</v>
+        <v>0.1967899119464198</v>
       </c>
     </row>
     <row r="85">
@@ -12695,13 +12695,13 @@
         <v>0.3975739484241958</v>
       </c>
       <c r="N86" t="n">
-        <v>0.7980626665303228</v>
+        <v>0.7980624544586687</v>
       </c>
       <c r="O86" t="n">
-        <v>1.275644163216625</v>
+        <v>1.27564399337204</v>
       </c>
       <c r="P86" t="n">
-        <v>0.3153301783757787</v>
+        <v>0.3153301456521924</v>
       </c>
     </row>
     <row r="87">
@@ -12808,10 +12808,10 @@
         <v>0.3288694257022349</v>
       </c>
       <c r="M88" t="n">
-        <v>0.1246131218152722</v>
+        <v>0.1246130468808042</v>
       </c>
       <c r="N88" t="n">
-        <v>0.01354054272183358</v>
+        <v>0.01354060358543419</v>
       </c>
       <c r="O88" t="n">
         <v>0.183037772638567</v>
@@ -12866,10 +12866,10 @@
         <v>0.06945373703347979</v>
       </c>
       <c r="M89" t="n">
-        <v>0.4163109503210494</v>
+        <v>0.4163108552351109</v>
       </c>
       <c r="N89" t="n">
-        <v>0.4490746916428738</v>
+        <v>0.4490748907151119</v>
       </c>
       <c r="O89" t="n">
         <v>0.5974435799633564</v>
@@ -12930,10 +12930,10 @@
         <v>0.4480639063843337</v>
       </c>
       <c r="O90" t="n">
-        <v>0.3646877820615262</v>
+        <v>0.3646876054013928</v>
       </c>
       <c r="P90" t="n">
-        <v>0.1092031675488347</v>
+        <v>0.1092031196863636</v>
       </c>
     </row>
     <row r="91">
@@ -13040,16 +13040,16 @@
         <v>0.02822801969996402</v>
       </c>
       <c r="M92" t="n">
-        <v>0.1132021705625705</v>
+        <v>0.1132020899684973</v>
       </c>
       <c r="N92" t="n">
-        <v>0.593359478868893</v>
+        <v>0.5933596439824105</v>
       </c>
       <c r="O92" t="n">
-        <v>1.814089834402874</v>
+        <v>1.814089576888824</v>
       </c>
       <c r="P92" t="n">
-        <v>0.4118199650354617</v>
+        <v>0.411819921970799</v>
       </c>
     </row>
     <row r="93">
@@ -13104,10 +13104,10 @@
         <v>0.2031318931771302</v>
       </c>
       <c r="O93" t="n">
-        <v>0.6422363686103951</v>
+        <v>0.6422364767118098</v>
       </c>
       <c r="P93" t="n">
-        <v>0.1798094992216732</v>
+        <v>0.1798095251089482</v>
       </c>
     </row>
     <row r="94">
@@ -13159,13 +13159,13 @@
         <v>0.4401348720163158</v>
       </c>
       <c r="N94" t="n">
-        <v>1.030615386807944</v>
+        <v>1.030615265213036</v>
       </c>
       <c r="O94" t="n">
-        <v>5.591991527651815</v>
+        <v>5.591993449790572</v>
       </c>
       <c r="P94" t="n">
-        <v>0.8750184557734728</v>
+        <v>0.8750186380170977</v>
       </c>
     </row>
     <row r="95">
@@ -13214,7 +13214,7 @@
         <v>0.08571040542665509</v>
       </c>
       <c r="M95" t="n">
-        <v>0.3757882602515956</v>
+        <v>0.3757881592417931</v>
       </c>
       <c r="N95" t="n">
         <v>0.4845788837130152</v>
@@ -13394,10 +13394,10 @@
         <v>0.3271062522648918</v>
       </c>
       <c r="O98" t="n">
-        <v>1.111428280442207</v>
+        <v>1.111428039096675</v>
       </c>
       <c r="P98" t="n">
-        <v>0.2828979507101503</v>
+        <v>0.2828979018298572</v>
       </c>
     </row>
     <row r="99">
@@ -13446,10 +13446,10 @@
         <v>0.2950993209875228</v>
       </c>
       <c r="M99" t="n">
-        <v>0.2780605999437951</v>
+        <v>0.2780604831038531</v>
       </c>
       <c r="N99" t="n">
-        <v>0.4497332330905037</v>
+        <v>0.4497330827539385</v>
       </c>
       <c r="O99" t="n">
         <v>1.746332832757961</v>
@@ -13510,10 +13510,10 @@
         <v>0.3668593500798554</v>
       </c>
       <c r="O100" t="n">
-        <v>0.4495635318728806</v>
+        <v>0.4495636385090396</v>
       </c>
       <c r="P100" t="n">
-        <v>0.1317376174460774</v>
+        <v>0.1317376451979138</v>
       </c>
     </row>
     <row r="101">
@@ -13562,16 +13562,16 @@
         <v>0.2565482175992602</v>
       </c>
       <c r="M101" t="n">
-        <v>0.1731441923716144</v>
+        <v>0.1731441076114784</v>
       </c>
       <c r="N101" t="n">
         <v>0.2473248946158968</v>
       </c>
       <c r="O101" t="n">
-        <v>1.309681589465921</v>
+        <v>1.309681753737771</v>
       </c>
       <c r="P101" t="n">
-        <v>0.3218556678152515</v>
+        <v>0.321855699153434</v>
       </c>
     </row>
     <row r="102">
@@ -13617,19 +13617,19 @@
         <v>0.07159533455116684</v>
       </c>
       <c r="L102" t="n">
-        <v>0.1741521629314813</v>
+        <v>0.1741522584120356</v>
       </c>
       <c r="M102" t="n">
-        <v>0.3333790139958286</v>
+        <v>0.3333791371285286</v>
       </c>
       <c r="N102" t="n">
         <v>0.4185598213970803</v>
       </c>
       <c r="O102" t="n">
-        <v>0.5780146025639021</v>
+        <v>0.578014775023836</v>
       </c>
       <c r="P102" t="n">
-        <v>0.1642252279662226</v>
+        <v>0.1642252703786309</v>
       </c>
     </row>
     <row r="103">
@@ -13678,16 +13678,16 @@
         <v>0.3430449984980475</v>
       </c>
       <c r="M103" t="n">
-        <v>0.2331930914217362</v>
+        <v>0.2331929553657199</v>
       </c>
       <c r="N103" t="n">
-        <v>0.3856008848017851</v>
+        <v>0.3856009706837491</v>
       </c>
       <c r="O103" t="n">
-        <v>-0.1544894016276932</v>
+        <v>-0.1544892737120069</v>
       </c>
       <c r="P103" t="n">
-        <v>-0.05440242032185072</v>
+        <v>-0.05440237263596814</v>
       </c>
     </row>
     <row r="104">
@@ -13739,7 +13739,7 @@
         <v>0.1960392010101208</v>
       </c>
       <c r="N104" t="n">
-        <v>0.1605137748823731</v>
+        <v>0.1605138684464786</v>
       </c>
       <c r="O104" t="n">
         <v>0.9349294278954727</v>
@@ -13791,7 +13791,7 @@
         <v>0.2073152052266662</v>
       </c>
       <c r="L105" t="n">
-        <v>0.3869528571329826</v>
+        <v>0.3869527387765817</v>
       </c>
       <c r="M105" t="n">
         <v>0.1934230664962742</v>
@@ -13800,10 +13800,10 @@
         <v>0.0469731853731794</v>
       </c>
       <c r="O105" t="n">
-        <v>0.6234304006443807</v>
+        <v>0.6234307249584727</v>
       </c>
       <c r="P105" t="n">
-        <v>0.1752886933654965</v>
+        <v>0.1752887716283034</v>
       </c>
     </row>
     <row r="106">
@@ -13852,16 +13852,16 @@
         <v>0.3561923657645745</v>
       </c>
       <c r="M106" t="n">
-        <v>0.1460735859417903</v>
+        <v>0.1460736559801827</v>
       </c>
       <c r="N106" t="n">
-        <v>-0.03268424319531305</v>
+        <v>-0.03268414340745485</v>
       </c>
       <c r="O106" t="n">
-        <v>0.2059646105654891</v>
+        <v>0.2059646881152193</v>
       </c>
       <c r="P106" t="n">
-        <v>0.06441631135857318</v>
+        <v>0.06441633417438819</v>
       </c>
     </row>
     <row r="107">
@@ -13913,13 +13913,13 @@
         <v>0.2995575754098796</v>
       </c>
       <c r="N107" t="n">
-        <v>0.3569591189362151</v>
+        <v>0.356959016944834</v>
       </c>
       <c r="O107" t="n">
-        <v>1.76199843341717</v>
+        <v>1.761998644691567</v>
       </c>
       <c r="P107" t="n">
-        <v>0.4030542898708966</v>
+        <v>0.4030543256456502</v>
       </c>
     </row>
     <row r="108">
@@ -13971,13 +13971,13 @@
         <v>0.3336849873921583</v>
       </c>
       <c r="N108" t="n">
-        <v>0.3786678751300299</v>
+        <v>0.3786677256620781</v>
       </c>
       <c r="O108" t="n">
-        <v>0.05103969957365329</v>
+        <v>0.05103987331257698</v>
       </c>
       <c r="P108" t="n">
-        <v>0.01673172134094059</v>
+        <v>0.01673177736352005</v>
       </c>
     </row>
     <row r="109">
@@ -14029,13 +14029,13 @@
         <v>0.1467947840483919</v>
       </c>
       <c r="N109" t="n">
-        <v>0.4245189811037295</v>
+        <v>0.4245188500338</v>
       </c>
       <c r="O109" t="n">
-        <v>2.02227799575634</v>
+        <v>2.02227711079036</v>
       </c>
       <c r="P109" t="n">
-        <v>0.445810817285448</v>
+        <v>0.4458106761674443</v>
       </c>
     </row>
     <row r="110">
@@ -14084,16 +14084,16 @@
         <v>0.1444051203988981</v>
       </c>
       <c r="M110" t="n">
-        <v>0.4547126256174252</v>
+        <v>0.4547127597586751</v>
       </c>
       <c r="N110" t="n">
         <v>0.2901599845466962</v>
       </c>
       <c r="O110" t="n">
-        <v>0.01073494875025238</v>
+        <v>0.01073488399389211</v>
       </c>
       <c r="P110" t="n">
-        <v>0.003565587724000174</v>
+        <v>0.003565566291656497</v>
       </c>
     </row>
     <row r="111">
@@ -14139,19 +14139,19 @@
         <v>0.3012997564410334</v>
       </c>
       <c r="L111" t="n">
-        <v>0.02499517140513552</v>
+        <v>0.02499525165299632</v>
       </c>
       <c r="M111" t="n">
-        <v>0.02817487536288521</v>
+        <v>0.02817495610940224</v>
       </c>
       <c r="N111" t="n">
-        <v>0.3831195551156492</v>
+        <v>0.3831194089958092</v>
       </c>
       <c r="O111" t="n">
-        <v>-0.02404055813126904</v>
+        <v>-0.02404063088466968</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.008078607529562798</v>
+        <v>-0.008078632177327516</v>
       </c>
     </row>
     <row r="112">
@@ -14261,13 +14261,13 @@
         <v>0.06983876918959964</v>
       </c>
       <c r="N113" t="n">
-        <v>0.008624951476069009</v>
+        <v>0.008625065894428019</v>
       </c>
       <c r="O113" t="n">
-        <v>-0.03056088604337759</v>
+        <v>-0.0305612031449819</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.01029253483689996</v>
+        <v>-0.01029264274735897</v>
       </c>
     </row>
     <row r="114">
@@ -14319,13 +14319,13 @@
         <v>0.3283818275580246</v>
       </c>
       <c r="N114" t="n">
-        <v>0.4105701511527793</v>
+        <v>0.4105700183652785</v>
       </c>
       <c r="O114" t="n">
-        <v>0.05260136876137667</v>
+        <v>0.05260151664693868</v>
       </c>
       <c r="P114" t="n">
-        <v>0.01723503656601433</v>
+        <v>0.01723508420493136</v>
       </c>
     </row>
     <row r="115">
@@ -14438,10 +14438,10 @@
         <v>-0.1482734068621051</v>
       </c>
       <c r="O116" t="n">
-        <v>-0.2573962191873891</v>
+        <v>-0.2573962728605976</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.09443620254857676</v>
+        <v>-0.0944362243657364</v>
       </c>
     </row>
     <row r="117">
@@ -14493,13 +14493,13 @@
         <v>0.2916394121685844</v>
       </c>
       <c r="N117" t="n">
-        <v>0.3113781770471198</v>
+        <v>0.3113782835781975</v>
       </c>
       <c r="O117" t="n">
-        <v>0.9260674766743859</v>
+        <v>0.9260680511922199</v>
       </c>
       <c r="P117" t="n">
-        <v>0.2442008659983184</v>
+        <v>0.2442009897072959</v>
       </c>
     </row>
     <row r="118">
@@ -14545,19 +14545,19 @@
         <v>0.2448408733848559</v>
       </c>
       <c r="L118" t="n">
-        <v>0.1845153199787231</v>
+        <v>0.1845152425646528</v>
       </c>
       <c r="M118" t="n">
-        <v>0.2255015755311713</v>
+        <v>0.2255016583952572</v>
       </c>
       <c r="N118" t="n">
         <v>0.08866073159232668</v>
       </c>
       <c r="O118" t="n">
-        <v>0.7055735472334399</v>
+        <v>0.7055738682367767</v>
       </c>
       <c r="P118" t="n">
-        <v>0.1947860700786237</v>
+        <v>0.1947861450348933</v>
       </c>
     </row>
     <row r="119">
@@ -14606,10 +14606,10 @@
         <v>0.2062342405257518</v>
       </c>
       <c r="M119" t="n">
-        <v>0.2896503066374803</v>
+        <v>0.2896502102296958</v>
       </c>
       <c r="N119" t="n">
-        <v>0.3917821127192345</v>
+        <v>0.3917820004370975</v>
       </c>
       <c r="O119" t="n">
         <v>2.494209701646107</v>
@@ -14667,13 +14667,13 @@
         <v>0.3362893026430009</v>
       </c>
       <c r="N120" t="n">
-        <v>0.38013567469167</v>
+        <v>0.3801353847420836</v>
       </c>
       <c r="O120" t="n">
-        <v>0.474300561391146</v>
+        <v>0.4743003959585677</v>
       </c>
       <c r="P120" t="n">
-        <v>0.1381391003783803</v>
+        <v>0.138139057807845</v>
       </c>
     </row>
     <row r="121">
@@ -14725,7 +14725,7 @@
         <v>0.289487319413847</v>
       </c>
       <c r="N121" t="n">
-        <v>0.2437988945940406</v>
+        <v>0.2437990313050737</v>
       </c>
       <c r="O121" t="n">
         <v>0.5880709096241907</v>
@@ -14786,10 +14786,10 @@
         <v>0.257001282355481</v>
       </c>
       <c r="O122" t="n">
-        <v>0.1183832556758644</v>
+        <v>0.1183831319655828</v>
       </c>
       <c r="P122" t="n">
-        <v>0.03799888120154948</v>
+        <v>0.03799884292870104</v>
       </c>
     </row>
     <row r="123">
@@ -14838,10 +14838,10 @@
         <v>0.1171213537566831</v>
       </c>
       <c r="M123" t="n">
-        <v>0.0649680459839852</v>
+        <v>0.06496814821918684</v>
       </c>
       <c r="N123" t="n">
-        <v>0.04891915131163049</v>
+        <v>0.04891905213456549</v>
       </c>
       <c r="O123" t="n">
         <v>0.7008811349422823</v>
@@ -14954,16 +14954,16 @@
         <v>0.1159050324215716</v>
       </c>
       <c r="M125" t="n">
-        <v>0.3041362816418069</v>
+        <v>0.304136168087457</v>
       </c>
       <c r="N125" t="n">
-        <v>0.5670945444432562</v>
+        <v>0.5670948723711375</v>
       </c>
       <c r="O125" t="n">
-        <v>0.9338441713229584</v>
+        <v>0.9338444210127959</v>
       </c>
       <c r="P125" t="n">
-        <v>0.2458731468090303</v>
+        <v>0.245873200429664</v>
       </c>
     </row>
     <row r="126">
@@ -15064,16 +15064,16 @@
         <v>0.1860870689952767</v>
       </c>
       <c r="M127" t="n">
-        <v>0.3775857104958393</v>
+        <v>0.3775856106157092</v>
       </c>
       <c r="N127" t="n">
         <v>0.2017239625814886</v>
       </c>
       <c r="O127" t="n">
-        <v>0.2534111724345298</v>
+        <v>0.253411089749104</v>
       </c>
       <c r="P127" t="n">
-        <v>0.07819634144530574</v>
+        <v>0.07819631773637248</v>
       </c>
     </row>
     <row r="128">
@@ -15186,10 +15186,10 @@
         <v>0.2037386273058162</v>
       </c>
       <c r="O129" t="n">
-        <v>1.598985363019441</v>
+        <v>1.598985073516282</v>
       </c>
       <c r="P129" t="n">
-        <v>0.3748899725546424</v>
+        <v>0.3748899215045918</v>
       </c>
     </row>
     <row r="130">
@@ -15302,10 +15302,10 @@
         <v>0.3216582713707616</v>
       </c>
       <c r="O131" t="n">
-        <v>0.6188191148218811</v>
+        <v>0.6188190020813709</v>
       </c>
       <c r="P131" t="n">
-        <v>0.1741748520464674</v>
+        <v>0.1741748247885166</v>
       </c>
     </row>
     <row r="132">
@@ -15418,10 +15418,10 @@
         <v>0.1623395616318279</v>
       </c>
       <c r="O133" t="n">
-        <v>0.1999145303704279</v>
+        <v>0.199914655867566</v>
       </c>
       <c r="P133" t="n">
-        <v>0.06263333940742122</v>
+        <v>0.06263337645379274</v>
       </c>
     </row>
     <row r="134">
@@ -15473,13 +15473,13 @@
         <v>0.2641933769826887</v>
       </c>
       <c r="N134" t="n">
-        <v>0.309711460466908</v>
+        <v>0.309711612060076</v>
       </c>
       <c r="O134" t="n">
-        <v>0.3186564055973622</v>
+        <v>0.3186562519264848</v>
       </c>
       <c r="P134" t="n">
-        <v>0.09658899446844105</v>
+        <v>0.09658895187109251</v>
       </c>
     </row>
     <row r="135">
@@ -15589,13 +15589,13 @@
         <v>0.1527563888242172</v>
       </c>
       <c r="N136" t="n">
-        <v>0.2565346224532163</v>
+        <v>0.2565347164076119</v>
       </c>
       <c r="O136" t="n">
-        <v>0.9352861693609265</v>
+        <v>0.9352863922345052</v>
       </c>
       <c r="P136" t="n">
-        <v>0.2461827374686971</v>
+        <v>0.2461827853067897</v>
       </c>
     </row>
     <row r="137">
@@ -15650,10 +15650,10 @@
         <v>0.5263873894103159</v>
       </c>
       <c r="O137" t="n">
-        <v>2.120700555514021</v>
+        <v>2.120700753067725</v>
       </c>
       <c r="P137" t="n">
-        <v>0.4613380732768293</v>
+        <v>0.4613381041131472</v>
       </c>
     </row>
     <row r="138">
@@ -15705,13 +15705,13 @@
         <v>0.2140962505065047</v>
       </c>
       <c r="N138" t="n">
-        <v>0.03857234209123828</v>
+        <v>0.03857225170889911</v>
       </c>
       <c r="O138" t="n">
-        <v>-0.2580351148829224</v>
+        <v>-0.2580350226243219</v>
       </c>
       <c r="P138" t="n">
-        <v>-0.09469597625618242</v>
+        <v>-0.0946959387332571</v>
       </c>
     </row>
     <row r="139">
@@ -15766,10 +15766,10 @@
         <v>0.05214249540121352</v>
       </c>
       <c r="O139" t="n">
-        <v>0.4632210943820303</v>
+        <v>0.4632209614069851</v>
       </c>
       <c r="P139" t="n">
-        <v>0.1352808646927703</v>
+        <v>0.135280830301971</v>
       </c>
     </row>
     <row r="140">
@@ -15821,13 +15821,13 @@
         <v>0.2005223859735512</v>
       </c>
       <c r="N140" t="n">
-        <v>0.3292136586737537</v>
+        <v>0.3292137884545667</v>
       </c>
       <c r="O140" t="n">
-        <v>1.563160827890566</v>
+        <v>1.563160586598781</v>
       </c>
       <c r="P140" t="n">
-        <v>0.368543540330833</v>
+        <v>0.3685434973866784</v>
       </c>
     </row>
     <row r="141">
@@ -15882,10 +15882,10 @@
         <v>0.06588271313730876</v>
       </c>
       <c r="O141" t="n">
-        <v>0.7778241481754977</v>
+        <v>0.7778240128333491</v>
       </c>
       <c r="P141" t="n">
-        <v>0.2114242610387604</v>
+        <v>0.2114242302976685</v>
       </c>
     </row>
     <row r="142">
@@ -15934,16 +15934,16 @@
         <v>0.1180383695164156</v>
       </c>
       <c r="M142" t="n">
-        <v>0.2813148212740209</v>
+        <v>0.2813149310281884</v>
       </c>
       <c r="N142" t="n">
-        <v>0.2299497268284356</v>
+        <v>0.2299498279593746</v>
       </c>
       <c r="O142" t="n">
-        <v>2.390135228361604</v>
+        <v>2.390134844200596</v>
       </c>
       <c r="P142" t="n">
-        <v>0.5022389125712272</v>
+        <v>0.5022388558280004</v>
       </c>
     </row>
     <row r="143">
@@ -15998,10 +15998,10 @@
         <v>0.3791244825195716</v>
       </c>
       <c r="O143" t="n">
-        <v>0.677799966583027</v>
+        <v>0.6778000890000584</v>
       </c>
       <c r="P143" t="n">
-        <v>0.1882652421674711</v>
+        <v>0.1882652710672015</v>
       </c>
     </row>
     <row r="144">
@@ -16053,13 +16053,13 @@
         <v>0.0807538551745226</v>
       </c>
       <c r="N144" t="n">
-        <v>0.5889395864937825</v>
+        <v>0.5889394532758152</v>
       </c>
       <c r="O144" t="n">
-        <v>1.130653673093637</v>
+        <v>1.130653433556009</v>
       </c>
       <c r="P144" t="n">
-        <v>0.2867799570745733</v>
+        <v>0.2867799088527161</v>
       </c>
     </row>
     <row r="145">
@@ -16163,19 +16163,19 @@
         <v>0.1029774606393297</v>
       </c>
       <c r="L146" t="n">
-        <v>0.2153259421449381</v>
+        <v>0.2153258068333934</v>
       </c>
       <c r="M146" t="n">
-        <v>0.1985142637422315</v>
+        <v>0.1985141321483399</v>
       </c>
       <c r="N146" t="n">
-        <v>0.2406760134609842</v>
+        <v>0.2406762954915831</v>
       </c>
       <c r="O146" t="n">
-        <v>0.2223661572352653</v>
+        <v>0.2223658834677611</v>
       </c>
       <c r="P146" t="n">
-        <v>0.06922007894167215</v>
+        <v>0.06921999911896326</v>
       </c>
     </row>
     <row r="147">
@@ -16227,13 +16227,13 @@
         <v>0.2602046320863778</v>
       </c>
       <c r="N147" t="n">
-        <v>0.3968189781309421</v>
+        <v>0.3968190942103837</v>
       </c>
       <c r="O147" t="n">
-        <v>2.330621149643028</v>
+        <v>2.330621479629046</v>
       </c>
       <c r="P147" t="n">
-        <v>0.4933963258240948</v>
+        <v>0.4933963751442134</v>
       </c>
     </row>
     <row r="148">
@@ -16279,19 +16279,19 @@
         <v>0.0392493354817387</v>
       </c>
       <c r="L148" t="n">
-        <v>0.101663517378598</v>
+        <v>0.1016636246481879</v>
       </c>
       <c r="M148" t="n">
-        <v>0.1817877956849696</v>
+        <v>0.1817879191254748</v>
       </c>
       <c r="N148" t="n">
         <v>0.4867680992046464</v>
       </c>
       <c r="O148" t="n">
-        <v>1.649153599202407</v>
+        <v>1.649153289058769</v>
       </c>
       <c r="P148" t="n">
-        <v>0.3836801580563971</v>
+        <v>0.383680104059325</v>
       </c>
     </row>
     <row r="149">
@@ -16340,16 +16340,16 @@
         <v>0.08484700613599938</v>
       </c>
       <c r="M149" t="n">
-        <v>0.4106857670485509</v>
+        <v>0.4106856510079193</v>
       </c>
       <c r="N149" t="n">
-        <v>0.3598735079576911</v>
+        <v>0.3598734001259687</v>
       </c>
       <c r="O149" t="n">
-        <v>0.4274366965993892</v>
+        <v>0.4274364589738098</v>
       </c>
       <c r="P149" t="n">
-        <v>0.1259496039097903</v>
+        <v>0.1259495414307927</v>
       </c>
     </row>
     <row r="150">
@@ -16404,10 +16404,10 @@
         <v>0.2692276652833767</v>
       </c>
       <c r="O150" t="n">
-        <v>3.482020196607114</v>
+        <v>3.482019849512451</v>
       </c>
       <c r="P150" t="n">
-        <v>0.6487618745490877</v>
+        <v>0.648761831988186</v>
       </c>
     </row>
     <row r="151">
@@ -16456,16 +16456,16 @@
         <v>0.2426494431659505</v>
       </c>
       <c r="M151" t="n">
-        <v>0.5766255893213963</v>
+        <v>0.5766257346953227</v>
       </c>
       <c r="N151" t="n">
         <v>0.321941958399373</v>
       </c>
       <c r="O151" t="n">
-        <v>0.6916504441733029</v>
+        <v>0.6916502768137334</v>
       </c>
       <c r="P151" t="n">
-        <v>0.191526051992458</v>
+        <v>0.1915260126988214</v>
       </c>
     </row>
     <row r="152">
@@ -16514,16 +16514,16 @@
         <v>0.2256449059583625</v>
       </c>
       <c r="M152" t="n">
-        <v>0.1290026812781568</v>
+        <v>0.129002763971916</v>
       </c>
       <c r="N152" t="n">
-        <v>0.1292134242922245</v>
+        <v>0.1292135070168585</v>
       </c>
       <c r="O152" t="n">
-        <v>0.4381800337178696</v>
+        <v>0.4381798995312454</v>
       </c>
       <c r="P152" t="n">
-        <v>0.1287672969152263</v>
+        <v>0.128767261809404</v>
       </c>
     </row>
     <row r="153">
@@ -16572,10 +16572,10 @@
         <v>0.02968495654400582</v>
       </c>
       <c r="M153" t="n">
-        <v>0.5009006005532981</v>
+        <v>0.5009002945111549</v>
       </c>
       <c r="N153" t="n">
-        <v>0.4691917662676772</v>
+        <v>0.4691916196439034</v>
       </c>
     </row>
     <row r="154">
@@ -16621,19 +16621,19 @@
         <v>0.06741871060190463</v>
       </c>
       <c r="L154" t="n">
-        <v>0.08929925468462607</v>
+        <v>0.08929914048933862</v>
       </c>
       <c r="M154" t="n">
-        <v>0.1313687812587991</v>
+        <v>0.1313686580725735</v>
       </c>
       <c r="N154" t="n">
-        <v>0.4663856221929923</v>
+        <v>0.466385415250278</v>
       </c>
       <c r="O154" t="n">
-        <v>2.675913761858983</v>
+        <v>2.67591343675341</v>
       </c>
       <c r="P154" t="n">
-        <v>0.5433168743631969</v>
+        <v>0.5433168288651282</v>
       </c>
     </row>
     <row r="155">
@@ -16688,10 +16688,10 @@
         <v>0.1931897190398588</v>
       </c>
       <c r="O155" t="n">
-        <v>1.217867097518682</v>
+        <v>1.217867410739032</v>
       </c>
       <c r="P155" t="n">
-        <v>0.3041028360407514</v>
+        <v>0.3041028974317952</v>
       </c>
     </row>
     <row r="156">
@@ -16740,7 +16740,7 @@
         <v>0.1930006977359298</v>
       </c>
       <c r="M156" t="n">
-        <v>0.1959311626325313</v>
+        <v>0.1959312788283831</v>
       </c>
       <c r="N156" t="n">
         <v>0.3245480449716776</v>
@@ -16859,13 +16859,13 @@
         <v>0.4121447047673441</v>
       </c>
       <c r="N158" t="n">
-        <v>0.227701442924112</v>
+        <v>0.2277013545758475</v>
       </c>
       <c r="O158" t="n">
-        <v>-0.1984339979154052</v>
+        <v>-0.1984339225935279</v>
       </c>
       <c r="P158" t="n">
-        <v>-0.07107689993721988</v>
+        <v>-0.07107687084074732</v>
       </c>
     </row>
     <row r="159">
@@ -16911,7 +16911,7 @@
         <v>0.1352125421162649</v>
       </c>
       <c r="L159" t="n">
-        <v>0.2704434631521255</v>
+        <v>0.2704435433425829</v>
       </c>
       <c r="M159" t="n">
         <v>0.006397570175366685</v>
@@ -16920,10 +16920,10 @@
         <v>0.2318338405737497</v>
       </c>
       <c r="O159" t="n">
-        <v>0.2976562080931533</v>
+        <v>0.2976563754183432</v>
       </c>
       <c r="P159" t="n">
-        <v>0.09073659161651038</v>
+        <v>0.09073663849787961</v>
       </c>
     </row>
     <row r="160">
@@ -16969,19 +16969,19 @@
         <v>0.1284977519546822</v>
       </c>
       <c r="L160" t="n">
-        <v>0.09816217287944307</v>
+        <v>0.09816228024251084</v>
       </c>
       <c r="M160" t="n">
         <v>0.1885467596789343</v>
       </c>
       <c r="N160" t="n">
-        <v>0.2459173554819045</v>
+        <v>0.2459174936794817</v>
       </c>
       <c r="O160" t="n">
-        <v>0.7816447122985912</v>
+        <v>0.7816445710012185</v>
       </c>
       <c r="P160" t="n">
-        <v>0.2122914282792612</v>
+        <v>0.2122913962314203</v>
       </c>
     </row>
     <row r="161">
@@ -17036,10 +17036,10 @@
         <v>0.1092920788983749</v>
       </c>
       <c r="O161" t="n">
-        <v>0.09473566032774117</v>
+        <v>0.09473575794866318</v>
       </c>
       <c r="P161" t="n">
-        <v>0.03063073202127575</v>
+        <v>0.03063076265610465</v>
       </c>
     </row>
     <row r="162">
@@ -17091,13 +17091,13 @@
         <v>0.3245649873372489</v>
       </c>
       <c r="N162" t="n">
-        <v>0.03876669403430189</v>
+        <v>0.03876662618024951</v>
       </c>
       <c r="O162" t="n">
-        <v>0.7682107872543198</v>
+        <v>0.7682109838653615</v>
       </c>
       <c r="P162" t="n">
-        <v>0.2092367718875425</v>
+        <v>0.2092368167067262</v>
       </c>
     </row>
     <row r="163">
@@ -17149,13 +17149,13 @@
         <v>0.4498167719837021</v>
       </c>
       <c r="N163" t="n">
-        <v>0.492027759571775</v>
+        <v>0.4920276482951538</v>
       </c>
       <c r="O163" t="n">
-        <v>1.68325066060169</v>
+        <v>1.683250840547889</v>
       </c>
       <c r="P163" t="n">
-        <v>0.3895912847988066</v>
+        <v>0.3895913158620823</v>
       </c>
     </row>
     <row r="164">
@@ -17204,16 +17204,16 @@
         <v>-0.05571178767117335</v>
       </c>
       <c r="M164" t="n">
-        <v>0.2850207331243997</v>
+        <v>0.2850206330906353</v>
       </c>
       <c r="N164" t="n">
         <v>0.2137122834487963</v>
       </c>
       <c r="O164" t="n">
-        <v>0.2014272545946354</v>
+        <v>0.2014273420368942</v>
       </c>
       <c r="P164" t="n">
-        <v>0.06307970346547931</v>
+        <v>0.06307972925649508</v>
       </c>
     </row>
     <row r="165">
@@ -17259,13 +17259,13 @@
         <v>0.016225282919623</v>
       </c>
       <c r="L165" t="n">
-        <v>0.2015119375366701</v>
+        <v>0.2015120765807734</v>
       </c>
       <c r="M165" t="n">
         <v>0.1393668711721072</v>
       </c>
       <c r="N165" t="n">
-        <v>0.3699511167218152</v>
+        <v>0.3699510263409567</v>
       </c>
       <c r="O165" t="n">
         <v>0.70934935908913</v>
@@ -17323,13 +17323,13 @@
         <v>0.2679337894080467</v>
       </c>
       <c r="N166" t="n">
-        <v>0.2146431393886008</v>
+        <v>0.214643244057457</v>
       </c>
       <c r="O166" t="n">
-        <v>1.267588106533897</v>
+        <v>1.267587924136621</v>
       </c>
       <c r="P166" t="n">
-        <v>0.3137762003203461</v>
+        <v>0.3137761650950766</v>
       </c>
     </row>
     <row r="167">
@@ -17378,16 +17378,16 @@
         <v>0.0711696815507239</v>
       </c>
       <c r="M167" t="n">
-        <v>0.1516463712275227</v>
+        <v>0.1516465932037643</v>
       </c>
       <c r="N167" t="n">
         <v>0.3734700968419058</v>
       </c>
       <c r="O167" t="n">
-        <v>1.291809515188291</v>
+        <v>1.291809075651655</v>
       </c>
       <c r="P167" t="n">
-        <v>0.3184373755538468</v>
+        <v>0.3184372912679636</v>
       </c>
     </row>
     <row r="168">
@@ -17433,7 +17433,7 @@
         <v>0.1645875049441023</v>
       </c>
       <c r="L168" t="n">
-        <v>0.1896754527341864</v>
+        <v>0.1896753388812997</v>
       </c>
       <c r="M168" t="n">
         <v>0.1411555277469643</v>
@@ -17497,13 +17497,13 @@
         <v>0.1413291560129588</v>
       </c>
       <c r="N169" t="n">
-        <v>0.3010498543172988</v>
+        <v>0.3010497488324548</v>
       </c>
       <c r="O169" t="n">
-        <v>1.416946547662457</v>
+        <v>1.416946365647832</v>
       </c>
       <c r="P169" t="n">
-        <v>0.3420097835154021</v>
+        <v>0.3420097498275225</v>
       </c>
     </row>
     <row r="170">
@@ -17549,7 +17549,7 @@
         <v>0.07765576750975889</v>
       </c>
       <c r="L170" t="n">
-        <v>0.09657919009803106</v>
+        <v>0.09657910375225431</v>
       </c>
       <c r="M170" t="n">
         <v>0.241876447632682</v>
@@ -17558,10 +17558,10 @@
         <v>0.2355300046133646</v>
       </c>
       <c r="O170" t="n">
-        <v>0.1758485649166113</v>
+        <v>0.175848664197112</v>
       </c>
       <c r="P170" t="n">
-        <v>0.0554811084559137</v>
+        <v>0.0554811381617486</v>
       </c>
     </row>
     <row r="171">
@@ -17616,10 +17616,10 @@
         <v>0.3377794728835919</v>
       </c>
       <c r="O171" t="n">
-        <v>1.446055788087078</v>
+        <v>1.446055483969148</v>
       </c>
       <c r="P171" t="n">
-        <v>0.3473759339697151</v>
+        <v>0.3473758781299969</v>
       </c>
     </row>
     <row r="172">
@@ -17665,10 +17665,10 @@
         <v>0.2465675858821368</v>
       </c>
       <c r="L172" t="n">
-        <v>0.08723886275209924</v>
+        <v>0.08723874173744428</v>
       </c>
       <c r="M172" t="n">
-        <v>0.1174094640286971</v>
+        <v>0.1174093362046038</v>
       </c>
       <c r="N172" t="n">
         <v>0.03014403880237571</v>
@@ -17790,10 +17790,10 @@
         <v>0.09425157014100782</v>
       </c>
       <c r="O174" t="n">
-        <v>1.238658989112027</v>
+        <v>1.238659136454728</v>
       </c>
       <c r="P174" t="n">
-        <v>0.3081653686477908</v>
+        <v>0.308165397347802</v>
       </c>
     </row>
     <row r="175">
@@ -17842,16 +17842,16 @@
         <v>-0.009871726705055206</v>
       </c>
       <c r="M175" t="n">
-        <v>0.2024471289872161</v>
+        <v>0.2024470401192429</v>
       </c>
       <c r="N175" t="n">
         <v>0.2721561056775261</v>
       </c>
       <c r="O175" t="n">
-        <v>0.6836780585776276</v>
+        <v>0.6836784070445165</v>
       </c>
       <c r="P175" t="n">
-        <v>0.1896513015892591</v>
+        <v>0.1896513836623643</v>
       </c>
     </row>
     <row r="176">
@@ -17955,19 +17955,19 @@
         <v>0.3078543142547856</v>
       </c>
       <c r="L177" t="n">
-        <v>0.1561207585382389</v>
+        <v>0.15612083633771</v>
       </c>
       <c r="M177" t="n">
         <v>0.06827962408323196</v>
       </c>
       <c r="N177" t="n">
-        <v>-0.1243554324710965</v>
+        <v>-0.1243555217308914</v>
       </c>
       <c r="O177" t="n">
-        <v>0.1675854409073156</v>
+        <v>0.1675855202574357</v>
       </c>
       <c r="P177" t="n">
-        <v>0.05300287512132451</v>
+        <v>0.05300289897565391</v>
       </c>
     </row>
     <row r="178">
@@ -18193,13 +18193,13 @@
         <v>0.3067036698874797</v>
       </c>
       <c r="N181" t="n">
-        <v>0.6075961325165431</v>
+        <v>0.6075960026040741</v>
       </c>
       <c r="O181" t="n">
-        <v>1.903266792956197</v>
+        <v>1.903266157388195</v>
       </c>
       <c r="P181" t="n">
-        <v>0.4265784160542578</v>
+        <v>0.4265783119545519</v>
       </c>
     </row>
     <row r="182">
@@ -18248,16 +18248,16 @@
         <v>0.2492432065907677</v>
       </c>
       <c r="M182" t="n">
-        <v>0.06767406597904113</v>
+        <v>0.06767418072980758</v>
       </c>
       <c r="N182" t="n">
-        <v>-0.06126147324335229</v>
+        <v>-0.06126138453439256</v>
       </c>
       <c r="O182" t="n">
-        <v>-0.2491735309507453</v>
+        <v>-0.2491736444484923</v>
       </c>
       <c r="P182" t="n">
-        <v>-0.09110609411106518</v>
+        <v>-0.09110613990833882</v>
       </c>
     </row>
     <row r="183">
@@ -18364,16 +18364,16 @@
         <v>0.1366296958454063</v>
       </c>
       <c r="M184" t="n">
-        <v>0.2090473849292003</v>
+        <v>0.2090473128512915</v>
       </c>
       <c r="N184" t="n">
         <v>0.08023221341083997</v>
       </c>
       <c r="O184" t="n">
-        <v>0.1317263875203221</v>
+        <v>0.1317265138276327</v>
       </c>
       <c r="P184" t="n">
-        <v>0.04211060146882617</v>
+        <v>0.04211064023737898</v>
       </c>
     </row>
     <row r="185">
@@ -18428,10 +18428,10 @@
         <v>0.4216674246104768</v>
       </c>
       <c r="O185" t="n">
-        <v>0.8703746284063176</v>
+        <v>0.8703748383978498</v>
       </c>
       <c r="P185" t="n">
-        <v>0.2320912335996894</v>
+        <v>0.2320912797096526</v>
       </c>
     </row>
     <row r="186">
@@ -18486,10 +18486,10 @@
         <v>0.2300468632116535</v>
       </c>
       <c r="O186" t="n">
-        <v>-0.02443483692608406</v>
+        <v>-0.02443464557580166</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.008212201280937803</v>
+        <v>-0.008212136436862472</v>
       </c>
     </row>
     <row r="187">
@@ -18541,13 +18541,13 @@
         <v>0.277882867553358</v>
       </c>
       <c r="N187" t="n">
-        <v>0.208157756189987</v>
+        <v>0.2081576448724369</v>
       </c>
       <c r="O187" t="n">
-        <v>0.7487335379943936</v>
+        <v>0.7487336546038306</v>
       </c>
       <c r="P187" t="n">
-        <v>0.2047803615901154</v>
+        <v>0.2047803883692583</v>
       </c>
     </row>
     <row r="188">
@@ -18602,10 +18602,10 @@
         <v>0.2577620125051128</v>
       </c>
       <c r="O188" t="n">
-        <v>-0.06721558643818482</v>
+        <v>-0.06721545115034655</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.02292681735743707</v>
+        <v>-0.02292677012032973</v>
       </c>
     </row>
     <row r="189">
@@ -18660,10 +18660,10 @@
         <v>0.5275211498916528</v>
       </c>
       <c r="O189" t="n">
-        <v>1.48764646753896</v>
+        <v>1.487646318573054</v>
       </c>
       <c r="P189" t="n">
-        <v>0.3549696062206513</v>
+        <v>0.3549695791744343</v>
       </c>
     </row>
     <row r="190">
@@ -18712,16 +18712,16 @@
         <v>0.02383138305366628</v>
       </c>
       <c r="M190" t="n">
-        <v>0.3776872008158427</v>
+        <v>0.3776873607623821</v>
       </c>
       <c r="N190" t="n">
-        <v>0.4603528715221934</v>
+        <v>0.4603527816636972</v>
       </c>
       <c r="O190" t="n">
-        <v>1.09115498447926</v>
+        <v>1.091155168732883</v>
       </c>
       <c r="P190" t="n">
-        <v>0.2787787392223424</v>
+        <v>0.2787787767804717</v>
       </c>
     </row>
     <row r="191">
@@ -18776,10 +18776,10 @@
         <v>0.1491146483877435</v>
       </c>
       <c r="O191" t="n">
-        <v>0.2160991648899557</v>
+        <v>0.2160993056646425</v>
       </c>
       <c r="P191" t="n">
-        <v>0.06738967314701738</v>
+        <v>0.06738971433374652</v>
       </c>
     </row>
     <row r="192">
@@ -18834,10 +18834,10 @@
         <v>-0.130393575824004</v>
       </c>
       <c r="O192" t="n">
-        <v>0.4813128067107229</v>
+        <v>0.4813129235851068</v>
       </c>
       <c r="P192" t="n">
-        <v>0.1399406983389406</v>
+        <v>0.1399407283190732</v>
       </c>
     </row>
     <row r="193">
@@ -18889,13 +18889,13 @@
         <v>0.2634276351869664</v>
       </c>
       <c r="N193" t="n">
-        <v>0.1517828996634558</v>
+        <v>0.1517830192568095</v>
       </c>
       <c r="O193" t="n">
-        <v>0.72620693089491</v>
+        <v>0.7262071995230632</v>
       </c>
       <c r="P193" t="n">
-        <v>0.1995847940604143</v>
+        <v>0.1995848562859071</v>
       </c>
     </row>
     <row r="194">
@@ -18950,10 +18950,10 @@
         <v>-0.1860791295156639</v>
       </c>
       <c r="O194" t="n">
-        <v>-0.1317676627755773</v>
+        <v>-0.1317676086003066</v>
       </c>
       <c r="P194" t="n">
-        <v>-0.04600671229620701</v>
+        <v>-0.04600669245403599</v>
       </c>
     </row>
     <row r="195">
@@ -19005,7 +19005,7 @@
         <v>0.2092710089052725</v>
       </c>
       <c r="N195" t="n">
-        <v>0.1345971960776404</v>
+        <v>0.1345972782513598</v>
       </c>
       <c r="O195" t="n">
         <v>0.839086714120304</v>
@@ -19118,16 +19118,16 @@
         <v>-0.1016178651725964</v>
       </c>
       <c r="M197" t="n">
-        <v>0.00765136809860012</v>
+        <v>0.007651438098982055</v>
       </c>
       <c r="N197" t="n">
         <v>0.2945989693605298</v>
       </c>
       <c r="O197" t="n">
-        <v>1.173520246513696</v>
+        <v>1.173520083667682</v>
       </c>
       <c r="P197" t="n">
-        <v>0.295352288390424</v>
+        <v>0.295352256039991</v>
       </c>
     </row>
     <row r="198">
@@ -19176,16 +19176,16 @@
         <v>0.143273013608201</v>
       </c>
       <c r="M198" t="n">
-        <v>0.07569159405151016</v>
+        <v>0.07569147420876376</v>
       </c>
       <c r="N198" t="n">
         <v>-0.003876576809868748</v>
       </c>
       <c r="O198" t="n">
-        <v>0.4538501354243327</v>
+        <v>0.4538500259668374</v>
       </c>
       <c r="P198" t="n">
-        <v>0.1328520991911164</v>
+        <v>0.1328520707610525</v>
       </c>
     </row>
     <row r="199">
@@ -19292,16 +19292,16 @@
         <v>0.06512879583973263</v>
       </c>
       <c r="M200" t="n">
-        <v>0.1796764991664881</v>
+        <v>0.1796765991791625</v>
       </c>
       <c r="N200" t="n">
         <v>0.231135093737038</v>
       </c>
       <c r="O200" t="n">
-        <v>1.179971779411285</v>
+        <v>1.179971608645498</v>
       </c>
       <c r="P200" t="n">
-        <v>0.2966326618590556</v>
+        <v>0.2966326280022713</v>
       </c>
     </row>
     <row r="201">
@@ -19353,13 +19353,13 @@
         <v>0.4848896715891877</v>
       </c>
       <c r="N201" t="n">
-        <v>0.3331564890132372</v>
+        <v>0.3331567602629408</v>
       </c>
       <c r="O201" t="n">
-        <v>-0.04823735957963349</v>
+        <v>-0.04823742870448355</v>
       </c>
       <c r="P201" t="n">
-        <v>-0.01634481739284677</v>
+        <v>-0.01634484120656376</v>
       </c>
     </row>
     <row r="202">
@@ -19411,7 +19411,7 @@
         <v>0.2406075927790867</v>
       </c>
       <c r="N202" t="n">
-        <v>0.01452080230073727</v>
+        <v>0.01452072267619609</v>
       </c>
       <c r="O202" t="n">
         <v>0.8405436232250447</v>
@@ -19466,10 +19466,10 @@
         <v>0.2077823700128449</v>
       </c>
       <c r="M203" t="n">
-        <v>0.1300363353168914</v>
+        <v>0.1300364228672262</v>
       </c>
       <c r="N203" t="n">
-        <v>0.0880973098527329</v>
+        <v>0.0880972286803301</v>
       </c>
       <c r="O203" t="n">
         <v>0.1462936038515523</v>
@@ -19530,10 +19530,10 @@
         <v>0.238445292677953</v>
       </c>
       <c r="O204" t="n">
-        <v>0.7435112015960437</v>
+        <v>0.7435113385840753</v>
       </c>
       <c r="P204" t="n">
-        <v>0.2035798657727474</v>
+        <v>0.2035798972945855</v>
       </c>
     </row>
     <row r="205">
@@ -19588,10 +19588,10 @@
         <v>0.2805757900308177</v>
       </c>
       <c r="O205" t="n">
-        <v>0.503095945792934</v>
+        <v>0.5030960923853838</v>
       </c>
       <c r="P205" t="n">
-        <v>0.1455012509587472</v>
+        <v>0.145501288197849</v>
       </c>
     </row>
     <row r="206">
@@ -19637,13 +19637,13 @@
         <v>-0.09443569109858396</v>
       </c>
       <c r="L206" t="n">
-        <v>0.08082221139433288</v>
+        <v>0.08082228865901708</v>
       </c>
       <c r="M206" t="n">
         <v>0.3701434671134503</v>
       </c>
       <c r="N206" t="n">
-        <v>0.2918908554393311</v>
+        <v>0.2918907450507651</v>
       </c>
       <c r="O206" t="n">
         <v>1.003214464440757</v>
@@ -19698,16 +19698,16 @@
         <v>-0.01285821241565543</v>
       </c>
       <c r="M207" t="n">
-        <v>0.2137947545653796</v>
+        <v>0.2137948417270552</v>
       </c>
       <c r="N207" t="n">
-        <v>0.242996974252244</v>
+        <v>0.2429970656583487</v>
       </c>
       <c r="O207" t="n">
-        <v>1.165911190322761</v>
+        <v>1.165910912788719</v>
       </c>
       <c r="P207" t="n">
-        <v>0.2938389319580936</v>
+        <v>0.2938388766950761</v>
       </c>
     </row>
     <row r="208">
@@ -19756,7 +19756,7 @@
         <v>0.08991438545481922</v>
       </c>
       <c r="M208" t="n">
-        <v>0.061946372754907</v>
+        <v>0.06194627133870712</v>
       </c>
       <c r="N208" t="n">
         <v>0.5984128597259455</v>
@@ -19817,13 +19817,13 @@
         <v>0.1651517839548264</v>
       </c>
       <c r="N209" t="n">
-        <v>0.1966950351788632</v>
+        <v>0.1966951512882893</v>
       </c>
       <c r="O209" t="n">
-        <v>0.4798355367016791</v>
+        <v>0.4798358030308265</v>
       </c>
       <c r="P209" t="n">
-        <v>0.1395616291083945</v>
+        <v>0.1395616974714999</v>
       </c>
     </row>
     <row r="210">
@@ -19878,10 +19878,10 @@
         <v>0.3008685885656575</v>
       </c>
       <c r="O210" t="n">
-        <v>1.45628613382815</v>
+        <v>1.456285967339658</v>
       </c>
       <c r="P210" t="n">
-        <v>0.3492517360139333</v>
+        <v>0.3492517055295787</v>
       </c>
     </row>
     <row r="211">
@@ -19933,7 +19933,7 @@
         <v>0.1547036954798051</v>
       </c>
       <c r="N211" t="n">
-        <v>0.06768137375961358</v>
+        <v>0.06768149443506588</v>
       </c>
       <c r="O211" t="n">
         <v>0.4125434655375522</v>
@@ -19988,10 +19988,10 @@
         <v>0.01985066265114788</v>
       </c>
       <c r="M212" t="n">
-        <v>0.2209586364453811</v>
+        <v>0.2209587578916647</v>
       </c>
       <c r="N212" t="n">
-        <v>0.1612715083075864</v>
+        <v>0.1612716181701852</v>
       </c>
       <c r="O212" t="n">
         <v>1.217148615457643</v>
@@ -20052,10 +20052,10 @@
         <v>0.09540439254886057</v>
       </c>
       <c r="O213" t="n">
-        <v>0.07579527085299986</v>
+        <v>0.07579517464720142</v>
       </c>
       <c r="P213" t="n">
-        <v>0.0246523574903581</v>
+        <v>0.02465232694628705</v>
       </c>
     </row>
     <row r="214">
@@ -20101,13 +20101,13 @@
         <v>0.2372706164264886</v>
       </c>
       <c r="L214" t="n">
-        <v>0.04196611895068503</v>
+        <v>0.0419660202885177</v>
       </c>
       <c r="M214" t="n">
-        <v>-0.02657423199133802</v>
+        <v>-0.02657440420955715</v>
       </c>
       <c r="N214" t="n">
-        <v>0.04406503514278426</v>
+        <v>0.04406513420285707</v>
       </c>
       <c r="O214" t="n">
         <v>0.1157763391719153</v>
@@ -20165,13 +20165,13 @@
         <v>0.0489034796044101</v>
       </c>
       <c r="N215" t="n">
-        <v>0.0191596257842892</v>
+        <v>0.01915950974172209</v>
       </c>
       <c r="O215" t="n">
-        <v>0.637798348717624</v>
+        <v>0.6377980490404025</v>
       </c>
       <c r="P215" t="n">
-        <v>0.1787457583641032</v>
+        <v>0.178745686470174</v>
       </c>
     </row>
     <row r="216">
@@ -20223,13 +20223,13 @@
         <v>0.2497111250100912</v>
       </c>
       <c r="N216" t="n">
-        <v>0.264989555283945</v>
+        <v>0.2649894682711635</v>
       </c>
       <c r="O216" t="n">
-        <v>0.3476149691615855</v>
+        <v>0.3476150679124457</v>
       </c>
       <c r="P216" t="n">
-        <v>0.1045582119495541</v>
+        <v>0.1045582389295827</v>
       </c>
     </row>
     <row r="217">
@@ -20342,10 +20342,10 @@
         <v>0.2199496257589988</v>
       </c>
       <c r="O218" t="n">
-        <v>0.5569839866980058</v>
+        <v>0.5569841782040399</v>
       </c>
       <c r="P218" t="n">
-        <v>0.1590301015566751</v>
+        <v>0.1590301490761636</v>
       </c>
     </row>
     <row r="219">
@@ -20400,10 +20400,10 @@
         <v>0.1320903155600968</v>
       </c>
       <c r="O219" t="n">
-        <v>0.03288651924786423</v>
+        <v>0.03288626377227777</v>
       </c>
       <c r="P219" t="n">
-        <v>0.01084415236704706</v>
+        <v>0.01084406902584112</v>
       </c>
     </row>
     <row r="220">
@@ -20452,16 +20452,16 @@
         <v>0.06268779574238836</v>
       </c>
       <c r="M220" t="n">
-        <v>0.2124864703934646</v>
+        <v>0.2124866001499734</v>
       </c>
       <c r="N220" t="n">
-        <v>0.1634298693923908</v>
+        <v>0.1634299888615387</v>
       </c>
       <c r="O220" t="n">
-        <v>1.184408304552975</v>
+        <v>1.18440809397502</v>
       </c>
       <c r="P220" t="n">
-        <v>0.2975116710086001</v>
+        <v>0.2975116293150268</v>
       </c>
     </row>
     <row r="221">
@@ -20510,16 +20510,16 @@
         <v>-0.1807439286278568</v>
       </c>
       <c r="M221" t="n">
-        <v>0.1740477782039107</v>
+        <v>0.1740476952353385</v>
       </c>
       <c r="N221" t="n">
         <v>0.189077170886341</v>
       </c>
       <c r="O221" t="n">
-        <v>-0.02374583295871835</v>
+        <v>-0.02374594769422866</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.00797876909772921</v>
+        <v>-0.007978807960582257</v>
       </c>
     </row>
     <row r="222">
@@ -20574,10 +20574,10 @@
         <v>0.1388981223602495</v>
       </c>
       <c r="O222" t="n">
-        <v>1.099037377359774</v>
+        <v>1.099037626912824</v>
       </c>
       <c r="P222" t="n">
-        <v>0.28038346611445</v>
+        <v>0.2803835168557391</v>
       </c>
     </row>
     <row r="223">
@@ -20623,7 +20623,7 @@
         <v>0.1100814682579141</v>
       </c>
       <c r="L223" t="n">
-        <v>0.09909577402094438</v>
+        <v>0.09909590162659221</v>
       </c>
       <c r="M223" t="n">
         <v>0.121244764054057</v>
@@ -20632,10 +20632,10 @@
         <v>0.04674111504949829</v>
       </c>
       <c r="O223" t="n">
-        <v>0.7673357648903307</v>
+        <v>0.7673352699782667</v>
       </c>
       <c r="P223" t="n">
-        <v>0.209037270068313</v>
+        <v>0.2090371572115866</v>
       </c>
     </row>
     <row r="224">
@@ -20684,16 +20684,16 @@
         <v>0.07840706384264728</v>
       </c>
       <c r="M224" t="n">
-        <v>0.04981702468924953</v>
+        <v>0.04981692441227215</v>
       </c>
       <c r="N224" t="n">
-        <v>0.5752718475023926</v>
+        <v>0.5752717346125027</v>
       </c>
       <c r="O224" t="n">
-        <v>1.463540184025015</v>
+        <v>1.463539907926983</v>
       </c>
       <c r="P224" t="n">
-        <v>0.3505786607582524</v>
+        <v>0.3505786103034738</v>
       </c>
     </row>
     <row r="225">
@@ -20919,13 +20919,13 @@
         <v>0.1558352202330411</v>
       </c>
       <c r="N228" t="n">
-        <v>0.1729865877404491</v>
+        <v>0.1729867254637001</v>
       </c>
       <c r="O228" t="n">
-        <v>0.6356558712341371</v>
+        <v>0.6356561390307423</v>
       </c>
       <c r="P228" t="n">
-        <v>0.1782315440101863</v>
+        <v>0.1782316083118924</v>
       </c>
     </row>
     <row r="229">
@@ -20971,19 +20971,19 @@
         <v>0.1920832344693923</v>
       </c>
       <c r="L229" t="n">
-        <v>0.1796962469517689</v>
+        <v>0.1796961402894584</v>
       </c>
       <c r="M229" t="n">
-        <v>0.0195380777983365</v>
+        <v>0.01953815746517185</v>
       </c>
       <c r="N229" t="n">
-        <v>-0.1035371689003526</v>
+        <v>-0.1035372304938942</v>
       </c>
       <c r="O229" t="n">
-        <v>0.6370138650243784</v>
+        <v>0.6370137623303187</v>
       </c>
       <c r="P229" t="n">
-        <v>0.1785575271111097</v>
+        <v>0.1785575024664683</v>
       </c>
     </row>
     <row r="230">
@@ -21038,10 +21038,10 @@
         <v>0.1315824607354144</v>
       </c>
       <c r="O230" t="n">
-        <v>-0.3289303917975024</v>
+        <v>-0.3289304589681477</v>
       </c>
       <c r="P230" t="n">
-        <v>-0.124500591725583</v>
+        <v>-0.1245006209365925</v>
       </c>
     </row>
     <row r="231">
@@ -21096,10 +21096,10 @@
         <v>-0.02056954686702839</v>
       </c>
       <c r="O231" t="n">
-        <v>0.1960665402050144</v>
+        <v>0.1960667809997985</v>
       </c>
       <c r="P231" t="n">
-        <v>0.06149620801748346</v>
+        <v>0.06149627925174017</v>
       </c>
     </row>
     <row r="232">
@@ -21145,19 +21145,19 @@
         <v>0.2183387798385124</v>
       </c>
       <c r="L232" t="n">
-        <v>0.02172104622819848</v>
+        <v>0.02172096661574074</v>
       </c>
       <c r="M232" t="n">
-        <v>0.03410132005135313</v>
+        <v>0.03410140160485353</v>
       </c>
       <c r="N232" t="n">
         <v>-0.04719668605392169</v>
       </c>
       <c r="O232" t="n">
-        <v>-0.1363926035236784</v>
+        <v>-0.1363925466450491</v>
       </c>
       <c r="P232" t="n">
-        <v>-0.04770365439031532</v>
+        <v>-0.0477036334837051</v>
       </c>
     </row>
     <row r="233">
@@ -21209,13 +21209,13 @@
         <v>0.2124295948154775</v>
       </c>
       <c r="N233" t="n">
-        <v>0.2039122300411023</v>
+        <v>0.203912325344739</v>
       </c>
       <c r="O233" t="n">
-        <v>0.3464499378402914</v>
+        <v>0.3464500570468763</v>
       </c>
       <c r="P233" t="n">
-        <v>0.1042398183548519</v>
+        <v>0.1042398509424365</v>
       </c>
     </row>
     <row r="234">
@@ -21264,10 +21264,10 @@
         <v>0.04932699782858041</v>
       </c>
       <c r="M234" t="n">
-        <v>0.01280539618400467</v>
+        <v>0.01280530509351241</v>
       </c>
       <c r="N234" t="n">
-        <v>0.1251970659677639</v>
+        <v>0.1251971783967516</v>
       </c>
       <c r="O234" t="n">
         <v>1.092050939101084</v>
@@ -21322,7 +21322,7 @@
         <v>0.04948005945134715</v>
       </c>
       <c r="M235" t="n">
-        <v>0.1013305046740307</v>
+        <v>0.1013306043526481</v>
       </c>
       <c r="N235" t="n">
         <v>0.1643136681927213</v>
@@ -21380,16 +21380,16 @@
         <v>0.008622613479786434</v>
       </c>
       <c r="M236" t="n">
-        <v>0.09305902002236133</v>
+        <v>0.09305911036810643</v>
       </c>
       <c r="N236" t="n">
         <v>-0.02957217990910144</v>
       </c>
       <c r="O236" t="n">
-        <v>0.6436497239342742</v>
+        <v>0.6436496217911909</v>
       </c>
       <c r="P236" t="n">
-        <v>0.1801478613751006</v>
+        <v>0.1801478369287031</v>
       </c>
     </row>
     <row r="237">
@@ -21441,7 +21441,7 @@
         <v>0.1990654738936366</v>
       </c>
       <c r="N237" t="n">
-        <v>0.4098791220498164</v>
+        <v>0.4098789982253823</v>
       </c>
       <c r="O237" t="n">
         <v>3.992439442964922</v>
@@ -21496,16 +21496,16 @@
         <v>0.02038005824318967</v>
       </c>
       <c r="M238" t="n">
-        <v>0.1678527889998211</v>
+        <v>0.1678528779592154</v>
       </c>
       <c r="N238" t="n">
         <v>0.09981850815135118</v>
       </c>
       <c r="O238" t="n">
-        <v>0.6968660616760196</v>
+        <v>0.6968662494825781</v>
       </c>
       <c r="P238" t="n">
-        <v>0.1927493481080227</v>
+        <v>0.1927493921119166</v>
       </c>
     </row>
     <row r="239">
@@ -21673,13 +21673,13 @@
         <v>0.1715914601819788</v>
       </c>
       <c r="N241" t="n">
-        <v>0.1638902814024374</v>
+        <v>0.1638901785350497</v>
       </c>
       <c r="O241" t="n">
-        <v>0.8109705827385489</v>
+        <v>0.8109703336943686</v>
       </c>
       <c r="P241" t="n">
-        <v>0.2189067027796545</v>
+        <v>0.2189066469050798</v>
       </c>
     </row>
     <row r="242">
@@ -21792,10 +21792,10 @@
         <v>0.08893484300755872</v>
       </c>
       <c r="O243" t="n">
-        <v>0.3291068783329687</v>
+        <v>0.3291069735939121</v>
       </c>
       <c r="P243" t="n">
-        <v>0.0994782314256053</v>
+        <v>0.09947825769320207</v>
       </c>
     </row>
     <row r="244">
@@ -21844,16 +21844,16 @@
         <v>0.1335588229309694</v>
       </c>
       <c r="M244" t="n">
-        <v>0.09519188679088608</v>
+        <v>0.09519197959122971</v>
       </c>
       <c r="N244" t="n">
-        <v>0.05400093143437723</v>
+        <v>0.05400084548335093</v>
       </c>
       <c r="O244" t="n">
-        <v>0.9581968846134326</v>
+        <v>0.9581974779648035</v>
       </c>
       <c r="P244" t="n">
-        <v>0.2510810668169596</v>
+        <v>0.2510811931799073</v>
       </c>
     </row>
     <row r="245">
@@ -21905,13 +21905,13 @@
         <v>0.2210716721839965</v>
       </c>
       <c r="N245" t="n">
-        <v>0.06821379699214947</v>
+        <v>0.06821371572868884</v>
       </c>
       <c r="O245" t="n">
-        <v>0.5190150258887434</v>
+        <v>0.5190148615639585</v>
       </c>
       <c r="P245" t="n">
-        <v>0.1495310062121118</v>
+        <v>0.1495309647605925</v>
       </c>
     </row>
     <row r="246">
@@ -21960,16 +21960,16 @@
         <v>0.003265306685461322</v>
       </c>
       <c r="M246" t="n">
-        <v>0.3079876882351431</v>
+        <v>0.3079877951536523</v>
       </c>
       <c r="N246" t="n">
-        <v>0.2853813295186243</v>
+        <v>0.2853812262640059</v>
       </c>
       <c r="O246" t="n">
-        <v>-0.3427057424473642</v>
+        <v>-0.3427056344469837</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.130532647548442</v>
+        <v>-0.1305325999275585</v>
       </c>
     </row>
     <row r="247">
@@ -22076,16 +22076,16 @@
         <v>0.07283886634459336</v>
       </c>
       <c r="M248" t="n">
-        <v>0.0228561393987472</v>
+        <v>0.02285604700221411</v>
       </c>
       <c r="N248" t="n">
         <v>0.07415273933228472</v>
       </c>
       <c r="O248" t="n">
-        <v>1.250248259796698</v>
+        <v>1.250248483389346</v>
       </c>
       <c r="P248" t="n">
-        <v>0.3104188897561311</v>
+        <v>0.3104189331587524</v>
       </c>
     </row>
     <row r="249">
@@ -22140,10 +22140,10 @@
         <v>0.2260713382128554</v>
       </c>
       <c r="O249" t="n">
-        <v>2.735456846659793</v>
+        <v>2.735456212435057</v>
       </c>
       <c r="P249" t="n">
-        <v>0.5516052528937845</v>
+        <v>0.5516051650806533</v>
       </c>
     </row>
     <row r="250">
@@ -22189,7 +22189,7 @@
         <v>0.1931845531322893</v>
       </c>
       <c r="L250" t="n">
-        <v>0.02739560155555609</v>
+        <v>0.02739568641482659</v>
       </c>
       <c r="M250" t="n">
         <v>0.05113036332844412</v>
@@ -22198,10 +22198,10 @@
         <v>-0.05886050142876353</v>
       </c>
       <c r="O250" t="n">
-        <v>0.0232102361717641</v>
+        <v>0.0232101520024921</v>
       </c>
       <c r="P250" t="n">
-        <v>0.007677648251637414</v>
+        <v>0.00767762062111621</v>
       </c>
     </row>
     <row r="251">
@@ -22250,16 +22250,16 @@
         <v>0.03024943773814237</v>
       </c>
       <c r="M251" t="n">
-        <v>0.08476218382151401</v>
+        <v>0.0847621188748533</v>
       </c>
       <c r="N251" t="n">
-        <v>-0.01051434343571156</v>
+        <v>-0.01051445151357067</v>
       </c>
       <c r="O251" t="n">
-        <v>0.07186173933538487</v>
+        <v>0.07186161251319123</v>
       </c>
       <c r="P251" t="n">
-        <v>0.02340198801222226</v>
+        <v>0.0234019476494014</v>
       </c>
     </row>
     <row r="252">
@@ -22427,13 +22427,13 @@
         <v>0.03071674124187562</v>
       </c>
       <c r="N254" t="n">
-        <v>0.1308975278540712</v>
+        <v>0.1308974129929181</v>
       </c>
       <c r="O254" t="n">
-        <v>0.7292870012342325</v>
+        <v>0.7292871355202821</v>
       </c>
       <c r="P254" t="n">
-        <v>0.2002978430208648</v>
+        <v>0.2002978740901729</v>
       </c>
     </row>
     <row r="255">
@@ -22485,7 +22485,7 @@
         <v>0.1256042826563681</v>
       </c>
       <c r="N255" t="n">
-        <v>0.06680415725379496</v>
+        <v>0.06680403112832556</v>
       </c>
       <c r="O255" t="n">
         <v>0.1955565793099026</v>
@@ -22537,7 +22537,7 @@
         <v>-0.01669794150372583</v>
       </c>
       <c r="L256" t="n">
-        <v>0.06150933723533569</v>
+        <v>0.06150942987845753</v>
       </c>
       <c r="M256" t="n">
         <v>0.1841441002191813</v>
@@ -22546,10 +22546,10 @@
         <v>0.1390349577198746</v>
       </c>
       <c r="O256" t="n">
-        <v>0.5465758298388756</v>
+        <v>0.5465757315107138</v>
       </c>
       <c r="P256" t="n">
-        <v>0.1564416896103937</v>
+        <v>0.156441665102319</v>
       </c>
     </row>
     <row r="257">
@@ -22598,16 +22598,16 @@
         <v>-0.004014277780299613</v>
       </c>
       <c r="M257" t="n">
-        <v>0.1025122353813541</v>
+        <v>0.1025123141864459</v>
       </c>
       <c r="N257" t="n">
-        <v>0.2348605511824702</v>
+        <v>0.2348604523218771</v>
       </c>
       <c r="O257" t="n">
-        <v>0.002067599847642265</v>
+        <v>0.002067730047798477</v>
       </c>
       <c r="P257" t="n">
-        <v>0.000688725497505871</v>
+        <v>0.0006887688378363066</v>
       </c>
     </row>
     <row r="258">
@@ -22659,7 +22659,7 @@
         <v>-0.05301994827285816</v>
       </c>
       <c r="N258" t="n">
-        <v>0.04526052109521572</v>
+        <v>0.0452604430314989</v>
       </c>
       <c r="O258" t="n">
         <v>-0.07534197342223947</v>
@@ -22714,16 +22714,16 @@
         <v>-0.003511802126315966</v>
       </c>
       <c r="M259" t="n">
-        <v>0.1139506886724377</v>
+        <v>0.1139507563340345</v>
       </c>
       <c r="N259" t="n">
-        <v>0.2695803881623753</v>
+        <v>0.2695804760506062</v>
       </c>
       <c r="O259" t="n">
-        <v>0.2396843507205504</v>
+        <v>0.2396842669227746</v>
       </c>
       <c r="P259" t="n">
-        <v>0.07424590365002115</v>
+        <v>0.07424587944509087</v>
       </c>
     </row>
     <row r="260">
@@ -22778,10 +22778,10 @@
         <v>-0.04126342307739517</v>
       </c>
       <c r="O260" t="n">
-        <v>1.194573623080624</v>
+        <v>1.194574136963574</v>
       </c>
       <c r="P260" t="n">
-        <v>0.299521248382292</v>
+        <v>0.2995213498145632</v>
       </c>
     </row>
     <row r="261">
@@ -22827,19 +22827,19 @@
         <v>0.1253873816085762</v>
       </c>
       <c r="L261" t="n">
-        <v>0.3086428087010036</v>
+        <v>0.3086427174410447</v>
       </c>
       <c r="M261" t="n">
         <v>-0.05940167859925793</v>
       </c>
       <c r="N261" t="n">
-        <v>-0.171556912927199</v>
+        <v>-0.1715569860736683</v>
       </c>
       <c r="O261" t="n">
-        <v>0.5147690070613586</v>
+        <v>0.5147692516075715</v>
       </c>
       <c r="P261" t="n">
-        <v>0.1484589331723203</v>
+        <v>0.1484589949752015</v>
       </c>
     </row>
     <row r="262">
@@ -22888,16 +22888,16 @@
         <v>0.02359121814139242</v>
       </c>
       <c r="M262" t="n">
-        <v>0.2194892506810351</v>
+        <v>0.2194891678387196</v>
       </c>
       <c r="N262" t="n">
-        <v>0.08800821453801588</v>
+        <v>0.08800808265447557</v>
       </c>
       <c r="O262" t="n">
-        <v>0.946350207514228</v>
+        <v>0.9463499964871285</v>
       </c>
       <c r="P262" t="n">
-        <v>0.2485530366202466</v>
+        <v>0.2485529914967235</v>
       </c>
     </row>
     <row r="263">
@@ -23001,19 +23001,19 @@
         <v>0.08360625407235989</v>
       </c>
       <c r="L264" t="n">
-        <v>0.1246842922714393</v>
+        <v>0.1246841670699288</v>
       </c>
       <c r="M264" t="n">
-        <v>0.008833533075721878</v>
+        <v>0.008833633812352248</v>
       </c>
       <c r="N264" t="n">
         <v>0.02651412161417976</v>
       </c>
       <c r="O264" t="n">
-        <v>1.538187320582307</v>
+        <v>1.538187639417135</v>
       </c>
       <c r="P264" t="n">
-        <v>0.3640843408556564</v>
+        <v>0.3640843979722155</v>
       </c>
     </row>
     <row r="265">
@@ -23059,13 +23059,13 @@
         <v>0.1157340209446522</v>
       </c>
       <c r="L265" t="n">
-        <v>0.06369219598335052</v>
+        <v>0.06369226440607356</v>
       </c>
       <c r="M265" t="n">
         <v>0.03510489830040053</v>
       </c>
       <c r="N265" t="n">
-        <v>-0.001457351484990044</v>
+        <v>-0.001457291187165421</v>
       </c>
       <c r="O265" t="n">
         <v>0.5352085059386118</v>
@@ -23123,13 +23123,13 @@
         <v>0.1883411132535235</v>
       </c>
       <c r="N266" t="n">
-        <v>0.1037541714199663</v>
+        <v>0.1037542694238529</v>
       </c>
       <c r="O266" t="n">
-        <v>0.4449045679856845</v>
+        <v>0.4449049038833379</v>
       </c>
       <c r="P266" t="n">
-        <v>0.1305238305352205</v>
+        <v>0.1305239181396851</v>
       </c>
     </row>
     <row r="267">
@@ -23184,10 +23184,10 @@
         <v>0.2703156440268837</v>
       </c>
       <c r="O267" t="n">
-        <v>-0.2695214408831252</v>
+        <v>-0.2695215971159074</v>
       </c>
       <c r="P267" t="n">
-        <v>-0.09939195035544679</v>
+        <v>-0.09939201456199076</v>
       </c>
     </row>
     <row r="268">
@@ -23236,10 +23236,10 @@
         <v>-0.04242808526091979</v>
       </c>
       <c r="M268" t="n">
-        <v>0.1827291978211909</v>
+        <v>0.1827290908622297</v>
       </c>
       <c r="N268" t="n">
-        <v>0.08493174776329271</v>
+        <v>0.0849316577614545</v>
       </c>
       <c r="O268" t="n">
         <v>0.06891192404349011</v>
@@ -23349,13 +23349,13 @@
         <v>0.2004779512266375</v>
       </c>
       <c r="L270" t="n">
-        <v>0.01472580624639397</v>
+        <v>0.01472572654926152</v>
       </c>
       <c r="M270" t="n">
-        <v>-0.02201445794514412</v>
+        <v>-0.02201453197555414</v>
       </c>
       <c r="N270" t="n">
-        <v>-0.06681015802684864</v>
+        <v>-0.06681022543079007</v>
       </c>
     </row>
     <row r="271">
@@ -23468,10 +23468,10 @@
         <v>0.4122686828003796</v>
       </c>
       <c r="O272" t="n">
-        <v>0.4713327899824151</v>
+        <v>0.4713330354132856</v>
       </c>
       <c r="P272" t="n">
-        <v>0.1373748949030278</v>
+        <v>0.1373749581443051</v>
       </c>
     </row>
     <row r="273">
@@ -23517,7 +23517,7 @@
         <v>-0.01930650081760443</v>
       </c>
       <c r="L273" t="n">
-        <v>0.003905170438744499</v>
+        <v>0.003905098111600447</v>
       </c>
       <c r="M273" t="n">
         <v>0.1098791390483194</v>
@@ -23526,10 +23526,10 @@
         <v>0.2368910364380628</v>
       </c>
       <c r="O273" t="n">
-        <v>1.460624659074675</v>
+        <v>1.460624876333163</v>
       </c>
       <c r="P273" t="n">
-        <v>0.3500456608378026</v>
+        <v>0.3500457005714626</v>
       </c>
     </row>
     <row r="274">
@@ -23578,16 +23578,16 @@
         <v>0.02616815242913062</v>
       </c>
       <c r="M274" t="n">
-        <v>0.09915647979346143</v>
+        <v>0.09915657274843359</v>
       </c>
       <c r="N274" t="n">
         <v>0.1043121285284698</v>
       </c>
       <c r="O274" t="n">
-        <v>0.8808244856370988</v>
+        <v>0.8808240773729501</v>
       </c>
       <c r="P274" t="n">
-        <v>0.2343815543725867</v>
+        <v>0.2343814650582505</v>
       </c>
     </row>
     <row r="275">
@@ -23694,7 +23694,7 @@
         <v>-0.02670098373707253</v>
       </c>
       <c r="M276" t="n">
-        <v>0.1450069569926971</v>
+        <v>0.1450070278817737</v>
       </c>
       <c r="N276" t="n">
         <v>0.4372368263173372</v>
@@ -23752,10 +23752,10 @@
         <v>0.01933095996555556</v>
       </c>
       <c r="M277" t="n">
-        <v>0.1526490095440221</v>
+        <v>0.1526491416188527</v>
       </c>
       <c r="N277" t="n">
-        <v>0.08533745165613671</v>
+        <v>0.08533756875575405</v>
       </c>
       <c r="O277" t="n">
         <v>0.254312856632964</v>
@@ -23874,10 +23874,10 @@
         <v>-0.04449388488295414</v>
       </c>
       <c r="O279" t="n">
-        <v>-0.07218062308872986</v>
+        <v>-0.07218053612162167</v>
       </c>
       <c r="P279" t="n">
-        <v>-0.02466349483807218</v>
+        <v>-0.02466346436439915</v>
       </c>
     </row>
     <row r="280">
@@ -23926,7 +23926,7 @@
         <v>-0.05735145751083048</v>
       </c>
       <c r="M280" t="n">
-        <v>0.474494862651603</v>
+        <v>0.4744950015391183</v>
       </c>
     </row>
     <row r="281">
@@ -23978,13 +23978,13 @@
         <v>-0.0538073606806394</v>
       </c>
       <c r="N281" t="n">
-        <v>-0.1160969705222115</v>
+        <v>-0.1160968712181096</v>
       </c>
       <c r="O281" t="n">
-        <v>0.5495379755218364</v>
+        <v>0.5495376703374879</v>
       </c>
       <c r="P281" t="n">
-        <v>0.1571795269325018</v>
+        <v>0.1571794509629527</v>
       </c>
     </row>
     <row r="282">
@@ -24033,16 +24033,16 @@
         <v>-0.1267419084824186</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.117635751690403</v>
+        <v>-0.1176356782665136</v>
       </c>
       <c r="N282" t="n">
         <v>0.1181577756898771</v>
       </c>
       <c r="O282" t="n">
-        <v>0.8855332161809049</v>
+        <v>0.8855325456176368</v>
       </c>
       <c r="P282" t="n">
-        <v>0.2354108062415328</v>
+        <v>0.2354106597893784</v>
       </c>
     </row>
     <row r="283">
@@ -24097,10 +24097,10 @@
         <v>0.2523877382774282</v>
       </c>
       <c r="O283" t="n">
-        <v>0.4286325336371721</v>
+        <v>0.4286326803895393</v>
       </c>
       <c r="P283" t="n">
-        <v>0.1262639380865092</v>
+        <v>0.1262639766506346</v>
       </c>
     </row>
     <row r="284">
@@ -24155,10 +24155,10 @@
         <v>-0.05994972617888505</v>
       </c>
       <c r="O284" t="n">
-        <v>0.787499415301808</v>
+        <v>0.7874991917408358</v>
       </c>
       <c r="P284" t="n">
-        <v>0.2136178891320686</v>
+        <v>0.213617838536694</v>
       </c>
     </row>
     <row r="285">
@@ -24210,13 +24210,13 @@
         <v>0.06661412978847325</v>
       </c>
       <c r="N285" t="n">
-        <v>0.106793980084446</v>
+        <v>0.1067938994115614</v>
       </c>
       <c r="O285" t="n">
-        <v>0.6557842841555939</v>
+        <v>0.6557841036039254</v>
       </c>
       <c r="P285" t="n">
-        <v>0.1830449664078588</v>
+        <v>0.1830449234069371</v>
       </c>
     </row>
     <row r="286">
@@ -24265,7 +24265,7 @@
         <v>-0.03872433906220185</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.1279210211514831</v>
+        <v>-0.1279210737277794</v>
       </c>
       <c r="N286" t="n">
         <v>-0.1488704920475137</v>
@@ -24384,7 +24384,7 @@
         <v>0.08558485677868588</v>
       </c>
       <c r="N288" t="n">
-        <v>0.1506732626416536</v>
+        <v>0.1506731861252859</v>
       </c>
       <c r="O288" t="n">
         <v>0.5506296519558949</v>
@@ -24445,10 +24445,10 @@
         <v>0.278118577787918</v>
       </c>
       <c r="O289" t="n">
-        <v>1.056665293041155</v>
+        <v>1.056665508040258</v>
       </c>
       <c r="P289" t="n">
-        <v>0.27170937552668</v>
+        <v>0.271709419840545</v>
       </c>
     </row>
     <row r="290">
@@ -24500,13 +24500,13 @@
         <v>0.04170682517680846</v>
       </c>
       <c r="N290" t="n">
-        <v>-0.03483196138660327</v>
+        <v>-0.03483189217002802</v>
       </c>
       <c r="O290" t="n">
-        <v>-0.09762166157562946</v>
+        <v>-0.09762172207926989</v>
       </c>
       <c r="P290" t="n">
-        <v>-0.03366089659138594</v>
+        <v>-0.03366091818877015</v>
       </c>
     </row>
     <row r="291">
@@ -24552,13 +24552,13 @@
         <v>0.145804659109406</v>
       </c>
       <c r="L291" t="n">
-        <v>0.2562066894406878</v>
+        <v>0.2562067991709738</v>
       </c>
       <c r="M291" t="n">
-        <v>-0.09782623424215553</v>
+        <v>-0.09782617764629264</v>
       </c>
       <c r="N291" t="n">
-        <v>-0.2077183938960487</v>
+        <v>-0.2077183066002264</v>
       </c>
       <c r="O291" t="n">
         <v>0.7822843079833366</v>
@@ -24674,13 +24674,13 @@
         <v>0.1279683119523349</v>
       </c>
       <c r="N293" t="n">
-        <v>0.2865147680255566</v>
+        <v>0.2865149158201079</v>
       </c>
       <c r="O293" t="n">
-        <v>0.7271355790368514</v>
+        <v>0.7271358454046677</v>
       </c>
       <c r="P293" t="n">
-        <v>0.1997998691797278</v>
+        <v>0.1997999308595131</v>
       </c>
     </row>
     <row r="294">
@@ -24726,19 +24726,19 @@
         <v>0.1985082821579658</v>
       </c>
       <c r="L294" t="n">
-        <v>-0.02897871046542189</v>
+        <v>-0.02897861779396183</v>
       </c>
       <c r="M294" t="n">
-        <v>-0.05751927115677336</v>
+        <v>-0.05751918385291077</v>
       </c>
       <c r="N294" t="n">
         <v>-0.07844474217556108</v>
       </c>
       <c r="O294" t="n">
-        <v>0.4172455624644016</v>
+        <v>0.4172454637572438</v>
       </c>
       <c r="P294" t="n">
-        <v>0.1232636424124494</v>
+        <v>0.1232636163350669</v>
       </c>
     </row>
     <row r="295">
@@ -24790,7 +24790,7 @@
         <v>0.06987122701106618</v>
       </c>
       <c r="N295" t="n">
-        <v>0.1766079835523446</v>
+        <v>0.1766078531872315</v>
       </c>
       <c r="O295" t="n">
         <v>0.6657424613820382</v>
@@ -24842,19 +24842,19 @@
         <v>0.2859923666742503</v>
       </c>
       <c r="L296" t="n">
-        <v>0.0101520674366895</v>
+        <v>0.01015217530824453</v>
       </c>
       <c r="M296" t="n">
-        <v>-0.09591126202620592</v>
+        <v>-0.09591134843450511</v>
       </c>
       <c r="N296" t="n">
         <v>-0.2483953606372442</v>
       </c>
       <c r="O296" t="n">
-        <v>-0.004562957949250213</v>
+        <v>-0.004563272204174962</v>
       </c>
       <c r="P296" t="n">
-        <v>-0.001523305263754215</v>
+        <v>-0.001523410335275033</v>
       </c>
     </row>
     <row r="297">
@@ -24906,7 +24906,7 @@
         <v>0.09262932775993904</v>
       </c>
       <c r="N297" t="n">
-        <v>0.1256188673970329</v>
+        <v>0.125618957722019</v>
       </c>
       <c r="O297" t="n">
         <v>0.3323607999222657</v>
@@ -24964,7 +24964,7 @@
         <v>0.1067119836543249</v>
       </c>
       <c r="N298" t="n">
-        <v>0.04534749292100915</v>
+        <v>0.04534762723762786</v>
       </c>
       <c r="O298" t="n">
         <v>-0.04995201671112337</v>
@@ -25016,19 +25016,19 @@
         <v>0.2396676599388841</v>
       </c>
       <c r="L299" t="n">
-        <v>-0.05769157782848056</v>
+        <v>-0.05769149561386366</v>
       </c>
       <c r="M299" t="n">
-        <v>-0.08720367466947443</v>
+        <v>-0.08720375181497175</v>
       </c>
       <c r="N299" t="n">
         <v>-0.1128444336893839</v>
       </c>
       <c r="O299" t="n">
-        <v>-0.3011487983041734</v>
+        <v>-0.301148933964687</v>
       </c>
       <c r="P299" t="n">
-        <v>-0.1125819892673512</v>
+        <v>-0.1125820466890124</v>
       </c>
     </row>
     <row r="300">
@@ -25080,13 +25080,13 @@
         <v>0.0795983590049516</v>
       </c>
       <c r="N300" t="n">
-        <v>0.1448697552638052</v>
+        <v>0.1448696839774422</v>
       </c>
       <c r="O300" t="n">
-        <v>0.2610999142315598</v>
+        <v>0.2610998277361056</v>
       </c>
       <c r="P300" t="n">
-        <v>0.08039649200448151</v>
+        <v>0.08039646730398364</v>
       </c>
     </row>
     <row r="301">
@@ -25135,16 +25135,16 @@
         <v>-0.01567815418389507</v>
       </c>
       <c r="M301" t="n">
-        <v>0.01606721164116998</v>
+        <v>0.01606709697340003</v>
       </c>
       <c r="N301" t="n">
         <v>0.05646632887133873</v>
       </c>
       <c r="O301" t="n">
-        <v>1.010150625059166</v>
+        <v>1.010150849459654</v>
       </c>
       <c r="P301" t="n">
-        <v>0.26204895171944</v>
+        <v>0.2620489986818229</v>
       </c>
     </row>
     <row r="302">
@@ -25193,10 +25193,10 @@
         <v>-0.008958799897162417</v>
       </c>
       <c r="M302" t="n">
-        <v>0.1047518797719413</v>
+        <v>0.1047519751375623</v>
       </c>
       <c r="N302" t="n">
-        <v>0.1349640041241524</v>
+        <v>0.1349639034712173</v>
       </c>
       <c r="O302" t="n">
         <v>0.4317383984437098</v>
@@ -25254,13 +25254,13 @@
         <v>0.1274122953142118</v>
       </c>
       <c r="N303" t="n">
-        <v>0.0015283167454192</v>
+        <v>0.001528210693154453</v>
       </c>
       <c r="O303" t="n">
-        <v>0.2888369862043028</v>
+        <v>0.28883707401745</v>
       </c>
       <c r="P303" t="n">
-        <v>0.08825999246264993</v>
+        <v>0.08826001717835186</v>
       </c>
     </row>
     <row r="304">
@@ -25309,16 +25309,16 @@
         <v>-0.07659187409828649</v>
       </c>
       <c r="M304" t="n">
-        <v>0.03769130826692346</v>
+        <v>0.03769142430304506</v>
       </c>
       <c r="N304" t="n">
-        <v>0.03313114318998789</v>
+        <v>0.03313125820850171</v>
       </c>
       <c r="O304" t="n">
-        <v>0.5896345778784329</v>
+        <v>0.5896347140296228</v>
       </c>
       <c r="P304" t="n">
-        <v>0.1670758981851346</v>
+        <v>0.1670759315049029</v>
       </c>
     </row>
     <row r="305">
@@ -25367,16 +25367,16 @@
         <v>-0.01460358026258979</v>
       </c>
       <c r="M305" t="n">
-        <v>0.00561613226891633</v>
+        <v>0.005616061021987306</v>
       </c>
       <c r="N305" t="n">
-        <v>0.1212723100515347</v>
+        <v>0.1212722214739412</v>
       </c>
       <c r="O305" t="n">
-        <v>0.7590810949917426</v>
+        <v>0.7590812039960024</v>
       </c>
       <c r="P305" t="n">
-        <v>0.2071519874611689</v>
+        <v>0.2071520123955333</v>
       </c>
     </row>
     <row r="306">
@@ -25483,16 +25483,16 @@
         <v>0.1312490064017531</v>
       </c>
       <c r="M307" t="n">
-        <v>0.06835775475078321</v>
+        <v>0.06835768004161058</v>
       </c>
       <c r="N307" t="n">
-        <v>-0.0274913522793756</v>
+        <v>-0.02749129037412079</v>
       </c>
       <c r="O307" t="n">
-        <v>-0.04576927840611023</v>
+        <v>-0.04576915920580071</v>
       </c>
       <c r="P307" t="n">
-        <v>-0.01549528998671257</v>
+        <v>-0.01549524899269206</v>
       </c>
     </row>
     <row r="308">
@@ -25544,13 +25544,13 @@
         <v>0.2053827389354259</v>
       </c>
       <c r="N308" t="n">
-        <v>0.03738356918300512</v>
+        <v>0.03738363626487606</v>
       </c>
       <c r="O308" t="n">
-        <v>0.3144446983514788</v>
+        <v>0.3144445906526423</v>
       </c>
       <c r="P308" t="n">
-        <v>0.09542027009659337</v>
+        <v>0.09542024017889195</v>
       </c>
     </row>
     <row r="309">
@@ -25602,13 +25602,13 @@
         <v>0.09075571807960214</v>
       </c>
       <c r="N309" t="n">
-        <v>0.02961582187636513</v>
+        <v>0.02961588395794634</v>
       </c>
       <c r="O309" t="n">
-        <v>0.1378780727547728</v>
+        <v>0.1378779211078078</v>
       </c>
       <c r="P309" t="n">
-        <v>0.04399537853228064</v>
+        <v>0.04399533215392637</v>
       </c>
     </row>
     <row r="310">
@@ -25663,10 +25663,10 @@
         <v>0.03616838017222879</v>
       </c>
       <c r="O310" t="n">
-        <v>0.2651194030081727</v>
+        <v>0.265119553613179</v>
       </c>
       <c r="P310" t="n">
-        <v>0.08154311962356786</v>
+        <v>0.08154316254067684</v>
       </c>
     </row>
     <row r="311">
@@ -25721,10 +25721,10 @@
         <v>0.1129311936471802</v>
       </c>
       <c r="O311" t="n">
-        <v>0.6018388008344737</v>
+        <v>0.6018386636984547</v>
       </c>
       <c r="P311" t="n">
-        <v>0.1700549809394198</v>
+        <v>0.1700549475493172</v>
       </c>
     </row>
     <row r="312">
@@ -25831,16 +25831,16 @@
         <v>-0.1031623182190878</v>
       </c>
       <c r="M313" t="n">
-        <v>0.02721188441185518</v>
+        <v>0.02721179193854928</v>
       </c>
       <c r="N313" t="n">
         <v>0.03727942249294003</v>
       </c>
       <c r="O313" t="n">
-        <v>-0.02166892076464078</v>
+        <v>-0.02166866911899556</v>
       </c>
       <c r="P313" t="n">
-        <v>-0.007275782208921222</v>
+        <v>-0.00727569709298248</v>
       </c>
     </row>
     <row r="314">
@@ -25886,7 +25886,7 @@
         <v>0.00227367535658396</v>
       </c>
       <c r="L314" t="n">
-        <v>-0.08315168950372664</v>
+        <v>-0.08315176090598841</v>
       </c>
       <c r="M314" t="n">
         <v>0.1376158269361758</v>
@@ -25895,10 +25895,10 @@
         <v>0.09511214193637918</v>
       </c>
       <c r="O314" t="n">
-        <v>0.3115800719910964</v>
+        <v>0.3115802181100964</v>
       </c>
       <c r="P314" t="n">
-        <v>0.09462392567308053</v>
+        <v>0.09462396632261227</v>
       </c>
     </row>
     <row r="315">
@@ -26005,16 +26005,16 @@
         <v>-0.02971912262915311</v>
       </c>
       <c r="M316" t="n">
-        <v>0.02668162913639605</v>
+        <v>0.02668170194063246</v>
       </c>
       <c r="N316" t="n">
-        <v>-0.04489450916757165</v>
+        <v>-0.04489457217441084</v>
       </c>
       <c r="O316" t="n">
-        <v>0.5866218339535585</v>
+        <v>0.58662166008068</v>
       </c>
       <c r="P316" t="n">
-        <v>0.1663381344035615</v>
+        <v>0.1663380917984552</v>
       </c>
     </row>
     <row r="317">
@@ -26066,13 +26066,13 @@
         <v>0.1015031327407838</v>
       </c>
       <c r="N317" t="n">
-        <v>0.1000549610308077</v>
+        <v>0.1000551116915673</v>
       </c>
       <c r="O317" t="n">
-        <v>0.2864312368577546</v>
+        <v>0.2864313398760878</v>
       </c>
       <c r="P317" t="n">
-        <v>0.08758245360159189</v>
+        <v>0.08758248263305135</v>
       </c>
     </row>
     <row r="318">
@@ -26121,16 +26121,16 @@
         <v>-0.2840948645261058</v>
       </c>
       <c r="M318" t="n">
-        <v>0.3052496126188879</v>
+        <v>0.3052494737289022</v>
       </c>
       <c r="N318" t="n">
         <v>0.2105787310173093</v>
       </c>
       <c r="O318" t="n">
-        <v>0.8438324694796457</v>
+        <v>0.8438321923221139</v>
       </c>
       <c r="P318" t="n">
-        <v>0.2262353151811927</v>
+        <v>0.2262352537402581</v>
       </c>
     </row>
     <row r="319">
@@ -26176,19 +26176,19 @@
         <v>0.09094917939795577</v>
       </c>
       <c r="L319" t="n">
-        <v>-0.01408709792021523</v>
+        <v>-0.01408700562454213</v>
       </c>
       <c r="M319" t="n">
         <v>0.03178997075579382</v>
       </c>
       <c r="N319" t="n">
-        <v>-0.0784021501661506</v>
+        <v>-0.0784022308129374</v>
       </c>
       <c r="O319" t="n">
-        <v>0.414232937689345</v>
+        <v>0.4142327477801302</v>
       </c>
       <c r="P319" t="n">
-        <v>0.1224671743521963</v>
+        <v>0.1224671241089716</v>
       </c>
     </row>
     <row r="320">
@@ -26350,19 +26350,19 @@
         <v>0.1212370325571253</v>
       </c>
       <c r="L322" t="n">
-        <v>-0.005882967091722535</v>
+        <v>-0.005882897245568119</v>
       </c>
       <c r="M322" t="n">
         <v>0.02759114090748627</v>
       </c>
       <c r="N322" t="n">
-        <v>-0.1231585627189901</v>
+        <v>-0.1231585083802459</v>
       </c>
       <c r="O322" t="n">
-        <v>-0.05429165658245527</v>
+        <v>-0.05429171979188196</v>
       </c>
       <c r="P322" t="n">
-        <v>-0.01843497894312029</v>
+        <v>-0.01843500081179472</v>
       </c>
     </row>
     <row r="323">
@@ -26417,10 +26417,10 @@
         <v>0.1595971273489105</v>
       </c>
       <c r="O323" t="n">
-        <v>-0.03202727108015924</v>
+        <v>-0.03202766038011307</v>
       </c>
       <c r="P323" t="n">
-        <v>-0.01079180104818322</v>
+        <v>-0.01079193366168441</v>
       </c>
     </row>
     <row r="324">
@@ -26649,10 +26649,10 @@
         <v>-0.07832953499126605</v>
       </c>
       <c r="O327" t="n">
-        <v>0.3256004102208794</v>
+        <v>0.3256005348745141</v>
       </c>
       <c r="P327" t="n">
-        <v>0.09851049367756537</v>
+        <v>0.09851052811059668</v>
       </c>
     </row>
     <row r="328">
@@ -26698,19 +26698,19 @@
         <v>0.117670929882197</v>
       </c>
       <c r="L328" t="n">
-        <v>-0.05891919511803134</v>
+        <v>-0.05891927488950988</v>
       </c>
       <c r="M328" t="n">
-        <v>-0.007167947860364787</v>
+        <v>-0.007167859074165506</v>
       </c>
       <c r="N328" t="n">
-        <v>-0.06507420626105165</v>
+        <v>-0.0650741275296165</v>
       </c>
       <c r="O328" t="n">
-        <v>0.2805319256792411</v>
+        <v>0.2805320733772767</v>
       </c>
       <c r="P328" t="n">
-        <v>0.08591742877052733</v>
+        <v>0.0859174705208503</v>
       </c>
     </row>
     <row r="329">
@@ -26823,10 +26823,10 @@
         <v>-0.08598981965191588</v>
       </c>
       <c r="O330" t="n">
-        <v>-0.04797815011538353</v>
+        <v>-0.04797804304092146</v>
       </c>
       <c r="P330" t="n">
-        <v>-0.01625552706681865</v>
+        <v>-0.01625549018604533</v>
       </c>
     </row>
     <row r="331">
@@ -26854,37 +26854,37 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>16.68</v>
+        <v>16.69</v>
       </c>
       <c r="G331" t="n">
-        <v>-0.01037966417994873</v>
+        <v>-0.0100830409335555</v>
       </c>
       <c r="H331" t="n">
-        <v>-0.02083341728353272</v>
+        <v>-0.02053992738643551</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.07047360686517967</v>
+        <v>-0.07019499583996125</v>
       </c>
       <c r="J331" t="n">
-        <v>-0.02083341728353272</v>
+        <v>-0.02053992738643551</v>
       </c>
       <c r="K331" t="n">
-        <v>0.02907491961441266</v>
+        <v>0.0293833687563605</v>
       </c>
       <c r="L331" t="n">
-        <v>0.01231852116644072</v>
+        <v>0.01262194783954307</v>
       </c>
       <c r="M331" t="n">
-        <v>0.05256258270386405</v>
+        <v>0.05287813524933882</v>
       </c>
       <c r="N331" t="n">
-        <v>-0.02803427312388651</v>
+        <v>-0.02774304959880247</v>
       </c>
       <c r="O331" t="n">
-        <v>0.7095845547392274</v>
+        <v>0.7100969760206579</v>
       </c>
       <c r="P331" t="n">
-        <v>0.1957219320184014</v>
+        <v>0.1958413864117792</v>
       </c>
     </row>
     <row r="332">
@@ -26939,10 +26939,10 @@
         <v>0.03484215051777495</v>
       </c>
       <c r="O332" t="n">
-        <v>-0.1511831773106708</v>
+        <v>-0.1511833733310425</v>
       </c>
       <c r="P332" t="n">
-        <v>-0.05317149094065809</v>
+        <v>-0.05317156382551991</v>
       </c>
     </row>
     <row r="333">
@@ -26997,10 +26997,10 @@
         <v>0.07675880500549681</v>
       </c>
       <c r="O333" t="n">
-        <v>1.220650352424056</v>
+        <v>1.220650183104798</v>
       </c>
       <c r="P333" t="n">
-        <v>0.3046481247049828</v>
+        <v>0.3046480915462193</v>
       </c>
     </row>
     <row r="334">
@@ -27168,7 +27168,7 @@
         <v>0.08306831078085986</v>
       </c>
       <c r="N336" t="n">
-        <v>0.07354902640380434</v>
+        <v>0.07354879120431312</v>
       </c>
       <c r="O336" t="n">
         <v>0.3561291372459969</v>
@@ -27229,10 +27229,10 @@
         <v>0.0631970755880491</v>
       </c>
       <c r="O337" t="n">
-        <v>0.2495542535864141</v>
+        <v>0.2495543312879955</v>
       </c>
       <c r="P337" t="n">
-        <v>0.07708928558800898</v>
+        <v>0.07708930791371404</v>
       </c>
     </row>
     <row r="338">
@@ -27284,7 +27284,7 @@
         <v>0.01792500393032759</v>
       </c>
       <c r="N338" t="n">
-        <v>0.09270914259610041</v>
+        <v>0.09270922852760544</v>
       </c>
       <c r="O338" t="n">
         <v>0.4671124721859885</v>
@@ -27339,16 +27339,16 @@
         <v>-0.1183314982805421</v>
       </c>
       <c r="M339" t="n">
-        <v>0.1040372750649792</v>
+        <v>0.1040371877297515</v>
       </c>
       <c r="N339" t="n">
-        <v>-0.1233581904349916</v>
+        <v>-0.1233582454988132</v>
       </c>
       <c r="O339" t="n">
-        <v>-0.3219465202149281</v>
+        <v>-0.3219466519828882</v>
       </c>
       <c r="P339" t="n">
-        <v>-0.12147393784164</v>
+        <v>-0.1214739947504228</v>
       </c>
     </row>
     <row r="340">
@@ -27452,7 +27452,7 @@
         <v>0.00880218669496724</v>
       </c>
       <c r="L341" t="n">
-        <v>0.005110735543509604</v>
+        <v>0.00511083984091254</v>
       </c>
       <c r="M341" t="n">
         <v>0.04714544243750352</v>
@@ -27461,10 +27461,10 @@
         <v>-0.02464364961439769</v>
       </c>
       <c r="O341" t="n">
-        <v>0.0539249976361762</v>
+        <v>0.05392488296216857</v>
       </c>
       <c r="P341" t="n">
-        <v>0.01766124339817754</v>
+        <v>0.01766120648875247</v>
       </c>
     </row>
     <row r="342">
@@ -27513,10 +27513,10 @@
         <v>-0.07537969040409509</v>
       </c>
       <c r="M342" t="n">
-        <v>-0.0005570363781335352</v>
+        <v>-0.0005569760480379493</v>
       </c>
       <c r="N342" t="n">
-        <v>-0.03554837212455975</v>
+        <v>-0.03554848448380254</v>
       </c>
       <c r="O342" t="n">
         <v>0.5751974132422066</v>
@@ -27574,7 +27574,7 @@
         <v>0.02056380403812019</v>
       </c>
       <c r="N343" t="n">
-        <v>-0.03857761107046209</v>
+        <v>-0.03857751871711179</v>
       </c>
       <c r="O343" t="n">
         <v>0.3941243777224155</v>
@@ -27626,13 +27626,13 @@
         <v>-0.02611419006836013</v>
       </c>
       <c r="L344" t="n">
-        <v>-0.07145410581728429</v>
+        <v>-0.07145399835921906</v>
       </c>
       <c r="M344" t="n">
         <v>0.0118809654847476</v>
       </c>
       <c r="N344" t="n">
-        <v>0.1369847736675374</v>
+        <v>0.1369846931090153</v>
       </c>
       <c r="O344" t="n">
         <v>0.7400570037827221</v>
@@ -27751,10 +27751,10 @@
         <v>-0.01669957826497204</v>
       </c>
       <c r="O346" t="n">
-        <v>0.1039299581654443</v>
+        <v>0.1039301339244134</v>
       </c>
       <c r="P346" t="n">
-        <v>0.03350799302775109</v>
+        <v>0.03350804787672912</v>
       </c>
     </row>
     <row r="347">
@@ -27806,7 +27806,7 @@
         <v>0.03082531466076888</v>
       </c>
       <c r="N347" t="n">
-        <v>-0.07439941181901732</v>
+        <v>-0.07439947493585863</v>
       </c>
       <c r="O347" t="n">
         <v>1.050540449513141</v>
@@ -27867,10 +27867,10 @@
         <v>-0.01749770966291475</v>
       </c>
       <c r="O348" t="n">
-        <v>0.4619907538935426</v>
+        <v>0.4619904559364054</v>
       </c>
       <c r="P348" t="n">
-        <v>0.1349625774806626</v>
+        <v>0.1349625003779809</v>
       </c>
     </row>
     <row r="349">
@@ -27922,13 +27922,13 @@
         <v>-0.1082230519092247</v>
       </c>
       <c r="N349" t="n">
-        <v>-0.03206887878823694</v>
+        <v>-0.03206877843854095</v>
       </c>
       <c r="O349" t="n">
-        <v>0.01633902544325894</v>
+        <v>0.01633913608127013</v>
       </c>
       <c r="P349" t="n">
-        <v>0.005416945531840689</v>
+        <v>0.005416982014853078</v>
       </c>
     </row>
     <row r="350">
@@ -27977,16 +27977,16 @@
         <v>0.1632114344825788</v>
       </c>
       <c r="M350" t="n">
-        <v>-0.07580045614037489</v>
+        <v>-0.0758005265255044</v>
       </c>
       <c r="N350" t="n">
         <v>0.254425111282889</v>
       </c>
       <c r="O350" t="n">
-        <v>3.160219857109334</v>
+        <v>3.160219500558068</v>
       </c>
       <c r="P350" t="n">
-        <v>0.608318635793643</v>
+        <v>0.6083185898467072</v>
       </c>
     </row>
     <row r="351">
@@ -28038,7 +28038,7 @@
         <v>-0.01006525112733214</v>
       </c>
       <c r="N351" t="n">
-        <v>0.09359154215939403</v>
+        <v>0.0935916416395246</v>
       </c>
       <c r="O351" t="n">
         <v>0.4400954479543315</v>
@@ -28090,10 +28090,10 @@
         <v>0.08895578284147998</v>
       </c>
       <c r="L352" t="n">
-        <v>0.04732512204403161</v>
+        <v>0.04732504523965053</v>
       </c>
       <c r="M352" t="n">
-        <v>-0.07008843910593976</v>
+        <v>-0.07008849965483843</v>
       </c>
       <c r="N352" t="n">
         <v>-0.1525420761857381</v>
@@ -28209,16 +28209,16 @@
         <v>-0.1059881514987574</v>
       </c>
       <c r="M354" t="n">
-        <v>-0.003985212321943155</v>
+        <v>-0.003985312093962246</v>
       </c>
       <c r="N354" t="n">
-        <v>-0.198689390094301</v>
+        <v>-0.1986893255171244</v>
       </c>
       <c r="O354" t="n">
-        <v>0.2404151566068855</v>
+        <v>0.2404150018637807</v>
       </c>
       <c r="P354" t="n">
-        <v>0.07445695495835447</v>
+        <v>0.07445691027847157</v>
       </c>
     </row>
     <row r="355">
@@ -28325,10 +28325,10 @@
         <v>-0.04056769057257126</v>
       </c>
       <c r="M356" t="n">
-        <v>-0.1205865451744043</v>
+        <v>-0.1205864528230121</v>
       </c>
       <c r="N356" t="n">
-        <v>-0.2635757011877145</v>
+        <v>-0.2635756364267291</v>
       </c>
       <c r="O356" t="n">
         <v>-0.03736477977661257</v>
@@ -28447,10 +28447,10 @@
         <v>0.1756607385448039</v>
       </c>
       <c r="O358" t="n">
-        <v>0.3475168564963647</v>
+        <v>0.3475169406199308</v>
       </c>
       <c r="P358" t="n">
-        <v>0.1045314056330549</v>
+        <v>0.1045314286178307</v>
       </c>
     </row>
     <row r="359">
@@ -28496,19 +28496,19 @@
         <v>-0.1920313110793118</v>
       </c>
       <c r="L359" t="n">
-        <v>0.01267511022783818</v>
+        <v>0.01267504006977882</v>
       </c>
       <c r="M359" t="n">
         <v>0.08607871846841064</v>
       </c>
       <c r="N359" t="n">
-        <v>0.2395863553437314</v>
+        <v>0.2395862502223973</v>
       </c>
       <c r="O359" t="n">
-        <v>0.3878480741038943</v>
+        <v>0.3878478105611323</v>
       </c>
       <c r="P359" t="n">
-        <v>0.1154428115378907</v>
+        <v>0.1154427409329248</v>
       </c>
     </row>
     <row r="360">
@@ -28621,10 +28621,10 @@
         <v>0.006442334594128241</v>
       </c>
       <c r="O361" t="n">
-        <v>0.7880977281517363</v>
+        <v>0.7880971079081591</v>
       </c>
       <c r="P361" t="n">
-        <v>0.2137532816568981</v>
+        <v>0.2137531413172973</v>
       </c>
     </row>
     <row r="362">
@@ -28679,10 +28679,10 @@
         <v>-0.04294841261571214</v>
       </c>
       <c r="O362" t="n">
-        <v>0.04147961018294066</v>
+        <v>0.04147946789530543</v>
       </c>
       <c r="P362" t="n">
-        <v>0.01363965081280161</v>
+        <v>0.01363960465142555</v>
       </c>
     </row>
     <row r="363">
@@ -28731,7 +28731,7 @@
         <v>-0.04924414942948574</v>
       </c>
       <c r="M363" t="n">
-        <v>-0.1074029651615741</v>
+        <v>-0.1074030551343841</v>
       </c>
       <c r="N363" t="n">
         <v>-0.03151049370935222</v>
@@ -28789,16 +28789,16 @@
         <v>-0.006696399262230979</v>
       </c>
       <c r="M364" t="n">
-        <v>-0.1871357994532691</v>
+        <v>-0.1871357441718897</v>
       </c>
       <c r="N364" t="n">
-        <v>-0.2718418548609312</v>
+        <v>-0.2718418105006494</v>
       </c>
       <c r="O364" t="n">
-        <v>0.03200866191090457</v>
+        <v>0.03200875101744227</v>
       </c>
       <c r="P364" t="n">
-        <v>0.01055769673879015</v>
+        <v>0.0105577258235896</v>
       </c>
     </row>
     <row r="365">
@@ -28844,19 +28844,19 @@
         <v>-0.2329977172184646</v>
       </c>
       <c r="L365" t="n">
-        <v>-0.2407804858118965</v>
+        <v>-0.2407805509773624</v>
       </c>
       <c r="M365" t="n">
         <v>0.04668937843975085</v>
       </c>
       <c r="N365" t="n">
-        <v>0.6108972297899453</v>
+        <v>0.6108973764758996</v>
       </c>
       <c r="O365" t="n">
-        <v>-0.2887993336800868</v>
+        <v>-0.2887992764970571</v>
       </c>
       <c r="P365" t="n">
-        <v>-0.1073852652918317</v>
+        <v>-0.1073852413687131</v>
       </c>
     </row>
     <row r="366">
@@ -28963,16 +28963,16 @@
         <v>-0.04603637133713634</v>
       </c>
       <c r="M367" t="n">
-        <v>0.001451779280995602</v>
+        <v>0.001451891837092711</v>
       </c>
       <c r="N367" t="n">
-        <v>0.07720934742229701</v>
+        <v>0.07720941253701286</v>
       </c>
       <c r="O367" t="n">
-        <v>0.4987734742776104</v>
+        <v>0.4987732221729841</v>
       </c>
       <c r="P367" t="n">
-        <v>0.1444021527046455</v>
+        <v>0.1444020885390467</v>
       </c>
     </row>
     <row r="368">
@@ -29027,10 +29027,10 @@
         <v>-0.06206572432147006</v>
       </c>
       <c r="O368" t="n">
-        <v>0.05803368482262594</v>
+        <v>0.05803393230497322</v>
       </c>
       <c r="P368" t="n">
-        <v>0.01898196671757946</v>
+        <v>0.01898204616685506</v>
       </c>
     </row>
     <row r="369">
@@ -29082,13 +29082,13 @@
         <v>-0.01804536196602247</v>
       </c>
       <c r="N369" t="n">
-        <v>-0.07443110155373389</v>
+        <v>-0.07443100010347048</v>
       </c>
       <c r="O369" t="n">
-        <v>0.009467771811863868</v>
+        <v>0.00946789248777713</v>
       </c>
       <c r="P369" t="n">
-        <v>0.003146016140586072</v>
+        <v>0.003146056113979334</v>
       </c>
     </row>
     <row r="370">
@@ -29137,7 +29137,7 @@
         <v>-0.07441211160698069</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.1807639776350198</v>
+        <v>-0.1807640297993411</v>
       </c>
       <c r="N370" t="n">
         <v>0.03712096620190852</v>
@@ -29195,7 +29195,7 @@
         <v>-0.2110146652388432</v>
       </c>
       <c r="M371" t="n">
-        <v>0.121367595761757</v>
+        <v>0.1213674712652866</v>
       </c>
       <c r="N371" t="n">
         <v>0.1931275322665944</v>
@@ -29250,13 +29250,13 @@
         <v>0.0757704002926356</v>
       </c>
       <c r="L372" t="n">
-        <v>-0.1809365002832509</v>
+        <v>-0.180936566711457</v>
       </c>
       <c r="M372" t="n">
         <v>-0.0402459850664143</v>
       </c>
       <c r="N372" t="n">
-        <v>-0.02900066783799515</v>
+        <v>-0.02900057447918292</v>
       </c>
       <c r="O372" t="n">
         <v>0.1100545964816479</v>
@@ -29308,13 +29308,13 @@
         <v>-0.01438706897113962</v>
       </c>
       <c r="L373" t="n">
-        <v>-0.06756160757605256</v>
+        <v>-0.06756171821420009</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.007191223425188298</v>
+        <v>-0.007191286139382358</v>
       </c>
       <c r="N373" t="n">
-        <v>0.01329318201716534</v>
+        <v>0.01329311668833677</v>
       </c>
       <c r="O373" t="n">
         <v>0.5117200586380457</v>
@@ -29366,19 +29366,19 @@
         <v>-0.04312069762697668</v>
       </c>
       <c r="L374" t="n">
-        <v>-0.07054428902710497</v>
+        <v>-0.07054419183707017</v>
       </c>
       <c r="M374" t="n">
         <v>0.01459805190372787</v>
       </c>
       <c r="N374" t="n">
-        <v>0.02558905053507776</v>
+        <v>0.02558881386631606</v>
       </c>
       <c r="O374" t="n">
-        <v>0.4538429121778846</v>
+        <v>0.4538425554883134</v>
       </c>
       <c r="P374" t="n">
-        <v>0.1328502230501365</v>
+        <v>0.1328501304046632</v>
       </c>
     </row>
     <row r="375">
@@ -29433,10 +29433,10 @@
         <v>-0.0823300908451795</v>
       </c>
       <c r="O375" t="n">
-        <v>-0.5675721483863314</v>
+        <v>-0.5675721752333347</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.2437978879375156</v>
+        <v>-0.2437979035869555</v>
       </c>
     </row>
     <row r="376">
@@ -29485,16 +29485,16 @@
         <v>-0.07920107498812068</v>
       </c>
       <c r="M376" t="n">
-        <v>0.007395757912585621</v>
+        <v>0.007395660151705563</v>
       </c>
       <c r="N376" t="n">
-        <v>0.0740023690143925</v>
+        <v>0.07400225789871406</v>
       </c>
       <c r="O376" t="n">
-        <v>0.5327822637950415</v>
+        <v>0.5327823769558073</v>
       </c>
       <c r="P376" t="n">
-        <v>0.152993402242267</v>
+        <v>0.1529934306162934</v>
       </c>
     </row>
     <row r="377">
@@ -29543,16 +29543,16 @@
         <v>-0.03079516158976159</v>
       </c>
       <c r="M377" t="n">
-        <v>0.07044555642221328</v>
+        <v>0.07044564994136526</v>
       </c>
       <c r="N377" t="n">
         <v>-0.07224504896442208</v>
       </c>
       <c r="O377" t="n">
-        <v>-0.2227651345969558</v>
+        <v>-0.2227650359903628</v>
       </c>
       <c r="P377" t="n">
-        <v>-0.08057263683400495</v>
+        <v>-0.08057259795189431</v>
       </c>
     </row>
     <row r="378">
@@ -29662,13 +29662,13 @@
         <v>0.02358298043783846</v>
       </c>
       <c r="N379" t="n">
-        <v>0.01957220647442814</v>
+        <v>0.01957209528749093</v>
       </c>
       <c r="O379" t="n">
-        <v>0.09042320736555598</v>
+        <v>0.09042308018873646</v>
       </c>
       <c r="P379" t="n">
-        <v>0.02927564220331469</v>
+        <v>0.02927560218826786</v>
       </c>
     </row>
     <row r="380">
@@ -29778,13 +29778,13 @@
         <v>0.001283058604520271</v>
       </c>
       <c r="N381" t="n">
-        <v>-0.04872965696757237</v>
+        <v>-0.04872956181932953</v>
       </c>
       <c r="O381" t="n">
-        <v>0.01752844571642553</v>
+        <v>0.01752833685202493</v>
       </c>
       <c r="P381" t="n">
-        <v>0.005809005354851848</v>
+        <v>0.00580896948466747</v>
       </c>
     </row>
     <row r="382">
@@ -29894,13 +29894,13 @@
         <v>0.1393389949313317</v>
       </c>
       <c r="N383" t="n">
-        <v>0.2274542483585724</v>
+        <v>0.2274543415167043</v>
       </c>
       <c r="O383" t="n">
-        <v>2.982530323041523</v>
+        <v>2.982531303723967</v>
       </c>
       <c r="P383" t="n">
-        <v>0.5850867308557968</v>
+        <v>0.5850868609629127</v>
       </c>
     </row>
     <row r="384">
@@ -30010,13 +30010,13 @@
         <v>-0.04172542472593121</v>
       </c>
       <c r="N385" t="n">
-        <v>0.02318233646908885</v>
+        <v>0.02318243262546793</v>
       </c>
       <c r="O385" t="n">
-        <v>0.5409506639429866</v>
+        <v>0.5409508820399012</v>
       </c>
       <c r="P385" t="n">
-        <v>0.1550379263154382</v>
+        <v>0.1550379808078157</v>
       </c>
     </row>
     <row r="386">
@@ -30129,10 +30129,10 @@
         <v>0.07782591369518266</v>
       </c>
       <c r="O387" t="n">
-        <v>0.4672352116100538</v>
+        <v>0.4672351031122346</v>
       </c>
       <c r="P387" t="n">
-        <v>0.1363180717057224</v>
+        <v>0.1363180436965719</v>
       </c>
     </row>
     <row r="388">
@@ -30245,10 +30245,10 @@
         <v>0.05745905229585668</v>
       </c>
       <c r="O389" t="n">
-        <v>0.3076644459421138</v>
+        <v>0.307664566338582</v>
       </c>
       <c r="P389" t="n">
-        <v>0.09353353339127279</v>
+        <v>0.09353356695176096</v>
       </c>
     </row>
     <row r="390">
@@ -30471,16 +30471,16 @@
         <v>-0.2148417802495565</v>
       </c>
       <c r="M393" t="n">
-        <v>-0.1805525796634827</v>
+        <v>-0.1805526291082192</v>
       </c>
       <c r="N393" t="n">
         <v>0.0329292794692202</v>
       </c>
       <c r="O393" t="n">
-        <v>0.5298464689849145</v>
+        <v>0.5298462966498876</v>
       </c>
       <c r="P393" t="n">
-        <v>0.1522568080681572</v>
+        <v>0.1522567648014592</v>
       </c>
     </row>
     <row r="394">
@@ -30535,10 +30535,10 @@
         <v>-0.07682945876739966</v>
       </c>
       <c r="O394" t="n">
-        <v>-0.320822708221708</v>
+        <v>-0.3208228657787829</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.1209888467174021</v>
+        <v>-0.1209889146890685</v>
       </c>
     </row>
     <row r="395">
@@ -30587,16 +30587,16 @@
         <v>-0.08131773780087381</v>
       </c>
       <c r="M395" t="n">
-        <v>-0.01049187775958693</v>
+        <v>-0.0104917928716135</v>
       </c>
       <c r="N395" t="n">
-        <v>-0.01510582479538469</v>
+        <v>-0.0151057406972086</v>
       </c>
       <c r="O395" t="n">
-        <v>0.440755736436568</v>
+        <v>0.4407556464540601</v>
       </c>
       <c r="P395" t="n">
-        <v>0.1294407487792164</v>
+        <v>0.1294407252661136</v>
       </c>
     </row>
     <row r="396">
@@ -30651,10 +30651,10 @@
         <v>0.02787732595426706</v>
       </c>
       <c r="O396" t="n">
-        <v>0.2088704861182162</v>
+        <v>0.2088703586096341</v>
       </c>
       <c r="P396" t="n">
-        <v>0.0652705598436556</v>
+        <v>0.06527052238964526</v>
       </c>
     </row>
     <row r="397">
@@ -30709,10 +30709,10 @@
         <v>-0.1196103162914884</v>
       </c>
       <c r="O397" t="n">
-        <v>-0.01485289978596294</v>
+        <v>-0.01485280766800667</v>
       </c>
       <c r="P397" t="n">
-        <v>-0.004975682954492244</v>
+        <v>-0.004975651940645531</v>
       </c>
     </row>
     <row r="398">
@@ -30761,16 +30761,16 @@
         <v>-0.1716124913842184</v>
       </c>
       <c r="M398" t="n">
-        <v>-0.2986457644167909</v>
+        <v>-0.2986457203507743</v>
       </c>
       <c r="N398" t="n">
-        <v>-0.05793935111876347</v>
+        <v>-0.05793951012588183</v>
       </c>
       <c r="O398" t="n">
-        <v>0.2798663166933182</v>
+        <v>0.2798666101798881</v>
       </c>
       <c r="P398" t="n">
-        <v>0.08572924612168764</v>
+        <v>0.08572932911132591</v>
       </c>
     </row>
     <row r="399">
@@ -30819,16 +30819,16 @@
         <v>-0.03841918848203385</v>
       </c>
       <c r="M399" t="n">
-        <v>-0.004315799642950813</v>
+        <v>-0.004315719882503455</v>
       </c>
       <c r="N399" t="n">
-        <v>-0.05051326815482426</v>
+        <v>-0.0505133406855599</v>
       </c>
       <c r="O399" t="n">
-        <v>-0.1011367733755778</v>
+        <v>-0.1011369033810025</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.03491728393015792</v>
+        <v>-0.03491733045781287</v>
       </c>
     </row>
     <row r="400">
@@ -30883,10 +30883,10 @@
         <v>-0.2706975918300637</v>
       </c>
       <c r="O400" t="n">
-        <v>-0.1832069586970947</v>
+        <v>-0.1832069061637314</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.06523162769951285</v>
+        <v>-0.06523160765913416</v>
       </c>
     </row>
     <row r="401">
@@ -30932,19 +30932,19 @@
         <v>-0.002754280769227679</v>
       </c>
       <c r="L401" t="n">
-        <v>-0.1292452990981569</v>
+        <v>-0.1292454021619187</v>
       </c>
       <c r="M401" t="n">
-        <v>-0.09417358588511449</v>
+        <v>-0.09417353011848739</v>
       </c>
       <c r="N401" t="n">
         <v>-0.01011455460867816</v>
       </c>
       <c r="O401" t="n">
-        <v>0.4655775487286165</v>
+        <v>0.4655774027457276</v>
       </c>
       <c r="P401" t="n">
-        <v>0.1358899780850968</v>
+        <v>0.1358899403706122</v>
       </c>
     </row>
     <row r="402">
@@ -30996,13 +30996,13 @@
         <v>-0.0286202168983325</v>
       </c>
       <c r="N402" t="n">
-        <v>-0.01852413479587356</v>
+        <v>-0.01852392532292491</v>
       </c>
       <c r="O402" t="n">
-        <v>-0.1302977687344437</v>
+        <v>-0.1302978509738063</v>
       </c>
       <c r="P402" t="n">
-        <v>-0.04546865414532797</v>
+        <v>-0.0454686842322739</v>
       </c>
     </row>
     <row r="403">
@@ -31167,16 +31167,16 @@
         <v>-0.06624912268324512</v>
       </c>
       <c r="M405" t="n">
-        <v>-0.002081777698277221</v>
+        <v>-0.002081691213781101</v>
       </c>
       <c r="N405" t="n">
-        <v>-0.1047964285383871</v>
+        <v>-0.1047964981356073</v>
       </c>
       <c r="O405" t="n">
-        <v>0.07647880249174244</v>
+        <v>0.07647850057971617</v>
       </c>
       <c r="P405" t="n">
-        <v>0.02486932381025708</v>
+        <v>0.02486922799774871</v>
       </c>
     </row>
     <row r="406">
@@ -31225,7 +31225,7 @@
         <v>-0.1266623854775822</v>
       </c>
       <c r="M406" t="n">
-        <v>-0.06240168374939026</v>
+        <v>-0.0624016019151481</v>
       </c>
       <c r="N406" t="n">
         <v>-0.1726376444671839</v>
@@ -31283,16 +31283,16 @@
         <v>-0.1107712567708592</v>
       </c>
       <c r="M407" t="n">
-        <v>-0.05299806809795926</v>
+        <v>-0.0529979678615381</v>
       </c>
       <c r="N407" t="n">
         <v>-0.0344549565557476</v>
       </c>
       <c r="O407" t="n">
-        <v>0.5151295772172104</v>
+        <v>0.5151298337975658</v>
       </c>
       <c r="P407" t="n">
-        <v>0.1485500509515503</v>
+        <v>0.148550115785469</v>
       </c>
     </row>
     <row r="408">
@@ -31341,16 +31341,16 @@
         <v>-0.02324142657064066</v>
       </c>
       <c r="M408" t="n">
-        <v>-0.001982174973853335</v>
+        <v>-0.001982249054358509</v>
       </c>
       <c r="N408" t="n">
         <v>-0.3399510541251911</v>
       </c>
       <c r="O408" t="n">
-        <v>-0.4828576894641305</v>
+        <v>-0.4828577292452936</v>
       </c>
       <c r="P408" t="n">
-        <v>-0.197330630088831</v>
+        <v>-0.1973306506706072</v>
       </c>
     </row>
     <row r="409">
@@ -31402,13 +31402,13 @@
         <v>-0.0825479226471646</v>
       </c>
       <c r="N409" t="n">
-        <v>0.00475439462177496</v>
+        <v>0.004754469672823669</v>
       </c>
       <c r="O409" t="n">
-        <v>0.6208739304517625</v>
+        <v>0.6208740281092191</v>
       </c>
       <c r="P409" t="n">
-        <v>0.1746714471040374</v>
+        <v>0.1746714706953074</v>
       </c>
     </row>
     <row r="410">
@@ -31460,13 +31460,13 @@
         <v>-0.1762584453595423</v>
       </c>
       <c r="N410" t="n">
-        <v>-0.2046121972929351</v>
+        <v>-0.2046121082727582</v>
       </c>
       <c r="O410" t="n">
-        <v>-0.2855547575637426</v>
+        <v>-0.2855549012113365</v>
       </c>
       <c r="P410" t="n">
-        <v>-0.1060299218941436</v>
+        <v>-0.1060299818085367</v>
       </c>
     </row>
     <row r="411">
@@ -31570,19 +31570,19 @@
         <v>-0.08518298469401209</v>
       </c>
       <c r="L412" t="n">
-        <v>-0.08948023196203336</v>
+        <v>-0.08948017764117155</v>
       </c>
       <c r="M412" t="n">
-        <v>0.07305034294035995</v>
+        <v>0.07305041838494852</v>
       </c>
       <c r="N412" t="n">
         <v>-0.09332144549832011</v>
       </c>
       <c r="O412" t="n">
-        <v>0.05558188012379528</v>
+        <v>0.05558202614024221</v>
       </c>
       <c r="P412" t="n">
-        <v>0.01819425484499182</v>
+        <v>0.01819430179322112</v>
       </c>
     </row>
     <row r="413">
@@ -31747,16 +31747,16 @@
         <v>-0.1143572205853898</v>
       </c>
       <c r="M415" t="n">
-        <v>-0.07662328373435556</v>
+        <v>-0.07662337931191532</v>
       </c>
       <c r="N415" t="n">
-        <v>-0.01933364121288417</v>
+        <v>-0.01933353340742672</v>
       </c>
       <c r="O415" t="n">
-        <v>0.3321489367945447</v>
+        <v>0.332149036260337</v>
       </c>
       <c r="P415" t="n">
-        <v>0.1003164204849909</v>
+        <v>0.1003164478702776</v>
       </c>
     </row>
     <row r="416">
@@ -31869,10 +31869,10 @@
         <v>-0.1643117704902668</v>
       </c>
       <c r="O417" t="n">
-        <v>0.1758495040726991</v>
+        <v>0.1758492434533732</v>
       </c>
       <c r="P417" t="n">
-        <v>0.05548138946183978</v>
+        <v>0.05548131148165969</v>
       </c>
     </row>
     <row r="418">
@@ -31921,10 +31921,10 @@
         <v>0.2096674636504063</v>
       </c>
       <c r="M418" t="n">
-        <v>0.02973524949559669</v>
+        <v>0.02973515458870235</v>
       </c>
       <c r="N418" t="n">
-        <v>0.08301619360987522</v>
+        <v>0.08301629859229687</v>
       </c>
       <c r="O418" t="n">
         <v>0.5775510490801024</v>
@@ -31985,10 +31985,10 @@
         <v>0.09046156389664239</v>
       </c>
       <c r="O419" t="n">
-        <v>0.9966597707407248</v>
+        <v>0.9966596257243971</v>
       </c>
       <c r="P419" t="n">
-        <v>0.2592192548644965</v>
+        <v>0.259219224379023</v>
       </c>
     </row>
     <row r="420">
@@ -32037,16 +32037,16 @@
         <v>-0.1174328040044504</v>
       </c>
       <c r="M420" t="n">
-        <v>0.01249470466672298</v>
+        <v>0.01249462360081521</v>
       </c>
       <c r="N420" t="n">
-        <v>-0.2525373647769226</v>
+        <v>-0.2525374531381385</v>
       </c>
       <c r="O420" t="n">
-        <v>-0.3207108042730807</v>
+        <v>-0.3207108772511094</v>
       </c>
       <c r="P420" t="n">
-        <v>-0.1209405729120699</v>
+        <v>-0.1209406043920477</v>
       </c>
     </row>
     <row r="421">
@@ -32101,10 +32101,10 @@
         <v>-0.00403323743183337</v>
       </c>
       <c r="O421" t="n">
-        <v>0.1382747647812073</v>
+        <v>0.1382746751441681</v>
       </c>
       <c r="P421" t="n">
-        <v>0.04411668518031875</v>
+        <v>0.04411665777289664</v>
       </c>
     </row>
     <row r="422">
@@ -32150,19 +32150,19 @@
         <v>-0.0142714925573153</v>
       </c>
       <c r="L422" t="n">
-        <v>-0.09327556156302674</v>
+        <v>-0.09327564834360469</v>
       </c>
       <c r="M422" t="n">
-        <v>-0.0827977354488687</v>
+        <v>-0.0827978242466535</v>
       </c>
       <c r="N422" t="n">
-        <v>-0.1367999340337239</v>
+        <v>-0.1367998553844157</v>
       </c>
       <c r="O422" t="n">
-        <v>0.2531057204831064</v>
+        <v>0.2531053889879074</v>
       </c>
       <c r="P422" t="n">
-        <v>0.07810875009455742</v>
+        <v>0.07810865502731756</v>
       </c>
     </row>
     <row r="423">
@@ -32211,7 +32211,7 @@
         <v>-0.1239516254780598</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.02139926399666769</v>
+        <v>-0.02139918039984978</v>
       </c>
       <c r="N423" t="n">
         <v>-0.09604937899468935</v>
@@ -32269,16 +32269,16 @@
         <v>-0.1406100333424497</v>
       </c>
       <c r="M424" t="n">
-        <v>-0.172335474990899</v>
+        <v>-0.1723355361071107</v>
       </c>
       <c r="N424" t="n">
-        <v>-0.2392431296430709</v>
+        <v>-0.2392431812775159</v>
       </c>
       <c r="O424" t="n">
-        <v>-0.07521466980609792</v>
+        <v>-0.0752145935051951</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.02572779970050221</v>
+        <v>-0.02572777290587069</v>
       </c>
     </row>
     <row r="425">
@@ -32327,7 +32327,7 @@
         <v>-0.1253854830931004</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.08783975234039565</v>
+        <v>-0.08783965815040673</v>
       </c>
       <c r="N425" t="n">
         <v>-0.06720111983210963</v>
@@ -32385,10 +32385,10 @@
         <v>-0.2329964085770583</v>
       </c>
       <c r="M426" t="n">
-        <v>-0.08878336281254751</v>
+        <v>-0.08878325567899181</v>
       </c>
       <c r="N426" t="n">
-        <v>-0.1520782120301306</v>
+        <v>-0.152078304797177</v>
       </c>
       <c r="O426" t="n">
         <v>-0.1359151194639439</v>
@@ -32443,16 +32443,16 @@
         <v>-0.1393214061187161</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.1188564187590769</v>
+        <v>-0.1188564912629758</v>
       </c>
       <c r="N427" t="n">
-        <v>0.01822328552374941</v>
+        <v>0.01822318870620987</v>
       </c>
       <c r="O427" t="n">
-        <v>0.2782347186708514</v>
+        <v>0.2782345660938061</v>
       </c>
       <c r="P427" t="n">
-        <v>0.08526768046937994</v>
+        <v>0.08526763728822817</v>
       </c>
     </row>
     <row r="428">
@@ -32562,7 +32562,7 @@
         <v>-0.04771661055272258</v>
       </c>
       <c r="N429" t="n">
-        <v>0.1812475355845335</v>
+        <v>0.1812476778489218</v>
       </c>
       <c r="O429" t="n">
         <v>0.7629410276539172</v>
@@ -32678,13 +32678,13 @@
         <v>-0.1065854367060414</v>
       </c>
       <c r="N431" t="n">
-        <v>-0.1691874519693053</v>
+        <v>-0.1691875181939719</v>
       </c>
       <c r="O431" t="n">
-        <v>-0.3023932824219434</v>
+        <v>-0.3023932357307411</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.1131090608430564</v>
+        <v>-0.113109041056357</v>
       </c>
     </row>
     <row r="432">
@@ -32733,16 +32733,16 @@
         <v>-0.1337059464943315</v>
       </c>
       <c r="M432" t="n">
-        <v>-0.1001100857785241</v>
+        <v>-0.1001101700318601</v>
       </c>
       <c r="N432" t="n">
-        <v>-0.07987436562230787</v>
+        <v>-0.07987427753716159</v>
       </c>
       <c r="O432" t="n">
-        <v>0.325361636918857</v>
+        <v>0.3253614541605572</v>
       </c>
       <c r="P432" t="n">
-        <v>0.09844453344650539</v>
+        <v>0.09844448295717489</v>
       </c>
     </row>
     <row r="433">
@@ -32794,13 +32794,13 @@
         <v>-0.06020103848214564</v>
       </c>
       <c r="N433" t="n">
-        <v>0.09324394940486513</v>
+        <v>0.09324407465923623</v>
       </c>
       <c r="O433" t="n">
-        <v>0.4059557923001937</v>
+        <v>0.4059555851420824</v>
       </c>
       <c r="P433" t="n">
-        <v>0.1202730500028313</v>
+        <v>0.1202729949812671</v>
       </c>
     </row>
     <row r="434">
@@ -32910,7 +32910,7 @@
         <v>-0.02192242139416445</v>
       </c>
       <c r="N435" t="n">
-        <v>-0.1698336294734009</v>
+        <v>-0.1698337099816972</v>
       </c>
       <c r="O435" t="n">
         <v>-0.4645627920481465</v>
@@ -32965,16 +32965,16 @@
         <v>-0.001930377728021182</v>
       </c>
       <c r="M436" t="n">
-        <v>0.1674551068841041</v>
+        <v>0.1674551994632976</v>
       </c>
       <c r="N436" t="n">
         <v>-0.02647321076679643</v>
       </c>
       <c r="O436" t="n">
-        <v>0.152113679962192</v>
+        <v>0.1521138602862659</v>
       </c>
       <c r="P436" t="n">
-        <v>0.04833103870014677</v>
+        <v>0.04833109339362518</v>
       </c>
     </row>
     <row r="437">
@@ -33026,13 +33026,13 @@
         <v>0.0234704756286197</v>
       </c>
       <c r="N437" t="n">
-        <v>-0.2474675730480741</v>
+        <v>-0.2474676373565428</v>
       </c>
       <c r="O437" t="n">
-        <v>1.793052695047034</v>
+        <v>1.793052916517628</v>
       </c>
       <c r="P437" t="n">
-        <v>0.4082930730335055</v>
+        <v>0.4082931102562779</v>
       </c>
     </row>
     <row r="438">
@@ -33084,13 +33084,13 @@
         <v>-0.04584432269254746</v>
       </c>
       <c r="N438" t="n">
-        <v>-0.07097549702988726</v>
+        <v>-0.07097539942265108</v>
       </c>
       <c r="O438" t="n">
-        <v>0.304117623071013</v>
+        <v>0.3041175269028915</v>
       </c>
       <c r="P438" t="n">
-        <v>0.09254396207038784</v>
+        <v>0.09254393521496174</v>
       </c>
     </row>
     <row r="439">
@@ -33142,7 +33142,7 @@
         <v>-0.03062344408882511</v>
       </c>
       <c r="N439" t="n">
-        <v>0.005900322399552627</v>
+        <v>0.00590022657418765</v>
       </c>
       <c r="O439" t="n">
         <v>0.03966991005155251</v>
@@ -33255,16 +33255,16 @@
         <v>-0.1778262527633868</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.04713264255693161</v>
+        <v>-0.04713256668861554</v>
       </c>
       <c r="N441" t="n">
-        <v>-0.02169418042081883</v>
+        <v>-0.02169410044755493</v>
       </c>
       <c r="O441" t="n">
-        <v>1.004284225655647</v>
+        <v>1.004284057820043</v>
       </c>
       <c r="P441" t="n">
-        <v>0.2608200393022069</v>
+        <v>0.2608200041091779</v>
       </c>
     </row>
     <row r="442">
@@ -33377,10 +33377,10 @@
         <v>-0.2168759729602076</v>
       </c>
       <c r="O443" t="n">
-        <v>0.487775297559415</v>
+        <v>0.4877754180035856</v>
       </c>
       <c r="P443" t="n">
-        <v>0.1415960248650108</v>
+        <v>0.1415960556713165</v>
       </c>
     </row>
     <row r="444">
@@ -33429,16 +33429,16 @@
         <v>-0.2425899659378287</v>
       </c>
       <c r="M444" t="n">
-        <v>-0.0422374792782374</v>
+        <v>-0.04223755871200141</v>
       </c>
       <c r="N444" t="n">
-        <v>-0.01211576418922966</v>
+        <v>-0.01211593320667514</v>
       </c>
       <c r="O444" t="n">
-        <v>-0.1032981851184183</v>
+        <v>-0.103298254746682</v>
       </c>
       <c r="P444" t="n">
-        <v>-0.03569145262309092</v>
+        <v>-0.03569147758238445</v>
       </c>
     </row>
     <row r="445">
@@ -33484,13 +33484,13 @@
         <v>0.02657667388659402</v>
       </c>
       <c r="L445" t="n">
-        <v>-0.07210485270803291</v>
+        <v>-0.07210478347501714</v>
       </c>
       <c r="M445" t="n">
-        <v>-0.2253188772331997</v>
+        <v>-0.2253188289760814</v>
       </c>
       <c r="N445" t="n">
-        <v>-0.255028319274185</v>
+        <v>-0.2550282746474655</v>
       </c>
       <c r="O445" t="n">
         <v>-0.3809773899480108</v>
@@ -33545,16 +33545,16 @@
         <v>-0.1465416009711153</v>
       </c>
       <c r="M446" t="n">
-        <v>-0.1300226772069903</v>
+        <v>-0.1300225768526585</v>
       </c>
       <c r="N446" t="n">
         <v>-0.1326020410275709</v>
       </c>
       <c r="O446" t="n">
-        <v>0.3262576804603181</v>
+        <v>0.3262573306221601</v>
       </c>
       <c r="P446" t="n">
-        <v>0.09869202122038812</v>
+        <v>0.09869192461663046</v>
       </c>
     </row>
     <row r="447">
@@ -33603,16 +33603,16 @@
         <v>-0.1226257602492977</v>
       </c>
       <c r="M447" t="n">
-        <v>-0.06545465209521339</v>
+        <v>-0.0654547170398736</v>
       </c>
       <c r="N447" t="n">
-        <v>-0.1915161173594127</v>
+        <v>-0.1915162145704093</v>
       </c>
       <c r="O447" t="n">
-        <v>-0.01162074363704513</v>
+        <v>-0.01162081627940292</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.003888683470104515</v>
+        <v>-0.003888707873650699</v>
       </c>
     </row>
     <row r="448">
@@ -33661,16 +33661,16 @@
         <v>-0.1435442480302335</v>
       </c>
       <c r="M448" t="n">
-        <v>-0.2085120473688303</v>
+        <v>-0.208511960556389</v>
       </c>
       <c r="N448" t="n">
-        <v>-0.2112637770114789</v>
+        <v>-0.211263690801622</v>
       </c>
       <c r="O448" t="n">
-        <v>0.1037792847995898</v>
+        <v>0.1037792003830098</v>
       </c>
       <c r="P448" t="n">
-        <v>0.03346097035447526</v>
+        <v>0.03346094400825317</v>
       </c>
     </row>
     <row r="449">
@@ -33783,10 +33783,10 @@
         <v>-0.1588018059798723</v>
       </c>
       <c r="O450" t="n">
-        <v>-0.1220988794630116</v>
+        <v>-0.122098631464048</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.0424784996978631</v>
+        <v>-0.04247840953420956</v>
       </c>
     </row>
     <row r="451">
@@ -33835,7 +33835,7 @@
         <v>-0.1633646488634333</v>
       </c>
       <c r="M451" t="n">
-        <v>-0.2425367220231185</v>
+        <v>-0.242536785747246</v>
       </c>
       <c r="N451" t="n">
         <v>-0.1028444403169936</v>
@@ -33957,10 +33957,10 @@
         <v>-0.007805121152583805</v>
       </c>
       <c r="O453" t="n">
-        <v>0.5055480238443351</v>
+        <v>0.5055478947027119</v>
       </c>
       <c r="P453" t="n">
-        <v>0.1461238176582795</v>
+        <v>0.146123784887866</v>
       </c>
     </row>
     <row r="454">
@@ -34070,13 +34070,13 @@
         <v>-0.1392128728143731</v>
       </c>
       <c r="N455" t="n">
-        <v>-0.1390748818352304</v>
+        <v>-0.1390749676642642</v>
       </c>
       <c r="O455" t="n">
-        <v>0.0006222256931935899</v>
+        <v>0.0006223416360111589</v>
       </c>
       <c r="P455" t="n">
-        <v>0.0002073655609498015</v>
+        <v>0.0002074041925306247</v>
       </c>
     </row>
     <row r="456">
@@ -34128,13 +34128,13 @@
         <v>-0.1426790169146062</v>
       </c>
       <c r="N456" t="n">
-        <v>-0.1904778456140034</v>
+        <v>-0.1904779433128988</v>
       </c>
       <c r="O456" t="n">
-        <v>-0.05695770030499525</v>
+        <v>-0.0569578328900322</v>
       </c>
       <c r="P456" t="n">
-        <v>-0.01935822278586263</v>
+        <v>-0.0193582687429501</v>
       </c>
     </row>
     <row r="457">
@@ -34186,7 +34186,7 @@
         <v>-0.03742547325907886</v>
       </c>
       <c r="N457" t="n">
-        <v>-0.0254079287930089</v>
+        <v>-0.02540781992350472</v>
       </c>
       <c r="O457" t="n">
         <v>0.5862921642496619</v>
@@ -34296,13 +34296,13 @@
         <v>-0.03225400963480984</v>
       </c>
       <c r="L459" t="n">
-        <v>-0.1594910084644279</v>
+        <v>-0.1594909487234946</v>
       </c>
       <c r="M459" t="n">
         <v>-0.1228005599980595</v>
       </c>
       <c r="N459" t="n">
-        <v>-0.268813015658546</v>
+        <v>-0.2688130608695469</v>
       </c>
       <c r="O459" t="n">
         <v>0.392849671896967</v>
@@ -34476,7 +34476,7 @@
         <v>-0.1143937266125411</v>
       </c>
       <c r="N462" t="n">
-        <v>-0.222667004771405</v>
+        <v>-0.2226670692091168</v>
       </c>
       <c r="O462" t="n">
         <v>0.9512859937477904</v>
@@ -34534,13 +34534,13 @@
         <v>-0.3095348646457743</v>
       </c>
       <c r="N463" t="n">
-        <v>-0.2455262003063015</v>
+        <v>-0.2455262500643843</v>
       </c>
       <c r="O463" t="n">
-        <v>-0.2397152724735456</v>
+        <v>-0.2397152219460348</v>
       </c>
       <c r="P463" t="n">
-        <v>-0.08730552364437438</v>
+        <v>-0.08730550342555488</v>
       </c>
     </row>
     <row r="464">
@@ -34586,19 +34586,19 @@
         <v>-0.2090407002637167</v>
       </c>
       <c r="L464" t="n">
-        <v>-0.0121923184082372</v>
+        <v>-0.01219238207171114</v>
       </c>
       <c r="M464" t="n">
         <v>-0.2266700842004989</v>
       </c>
       <c r="N464" t="n">
-        <v>-0.01453909530560316</v>
+        <v>-0.01453903194425776</v>
       </c>
       <c r="O464" t="n">
-        <v>0.7470957357921482</v>
+        <v>0.7470955366427856</v>
       </c>
       <c r="P464" t="n">
-        <v>0.2044041258334743</v>
+        <v>0.2044040800706086</v>
       </c>
     </row>
     <row r="465">
@@ -34650,7 +34650,7 @@
         <v>-0.04747380045792238</v>
       </c>
       <c r="N465" t="n">
-        <v>0.01469488162721388</v>
+        <v>0.01469495438813229</v>
       </c>
       <c r="O465" t="n">
         <v>-0.08994052358283677</v>
@@ -34708,13 +34708,13 @@
         <v>-0.4280318068271582</v>
       </c>
       <c r="N466" t="n">
-        <v>-0.4552678077771017</v>
+        <v>-0.4552677573703187</v>
       </c>
       <c r="O466" t="n">
-        <v>-0.320994217556979</v>
+        <v>-0.3209940609179798</v>
       </c>
       <c r="P466" t="n">
-        <v>-0.1210628437489648</v>
+        <v>-0.121062776161997</v>
       </c>
     </row>
     <row r="467">
@@ -34760,19 +34760,19 @@
         <v>-0.1298107087934345</v>
       </c>
       <c r="L467" t="n">
-        <v>-0.2053102991157754</v>
+        <v>-0.2053102480159247</v>
       </c>
       <c r="M467" t="n">
-        <v>-0.205177723998351</v>
+        <v>-0.2051777751152462</v>
       </c>
       <c r="N467" t="n">
-        <v>-0.1558488413051456</v>
+        <v>-0.1558487836464378</v>
       </c>
       <c r="O467" t="n">
-        <v>0.7315950287384203</v>
+        <v>0.731595150045774</v>
       </c>
       <c r="P467" t="n">
-        <v>0.200831606137903</v>
+        <v>0.200831634179429</v>
       </c>
     </row>
     <row r="468">
@@ -34827,10 +34827,10 @@
         <v>-0.195049774315516</v>
       </c>
       <c r="O468" t="n">
-        <v>-0.1080223027002648</v>
+        <v>-0.1080223824235447</v>
       </c>
       <c r="P468" t="n">
-        <v>-0.03738786583794551</v>
+        <v>-0.03738789451676383</v>
       </c>
     </row>
     <row r="469">
@@ -34937,16 +34937,16 @@
         <v>-0.2313001660888863</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.1644104564554756</v>
+        <v>-0.1644105386134557</v>
       </c>
       <c r="N470" t="n">
-        <v>-0.1539990220356551</v>
+        <v>-0.1539991062537648</v>
       </c>
       <c r="O470" t="n">
-        <v>0.1799571232968673</v>
+        <v>0.1799569594658248</v>
       </c>
       <c r="P470" t="n">
-        <v>0.05670900602258211</v>
+        <v>0.05670895711635704</v>
       </c>
     </row>
     <row r="471">
@@ -35218,10 +35218,10 @@
         <v>-0.4213044472166358</v>
       </c>
       <c r="O475" t="n">
-        <v>-0.1538096907790325</v>
+        <v>-0.1538096125134598</v>
       </c>
       <c r="P475" t="n">
-        <v>-0.0541490977420771</v>
+        <v>-0.05414906858096147</v>
       </c>
     </row>
     <row r="476">
@@ -35270,16 +35270,16 @@
         <v>-0.2975381076859545</v>
       </c>
       <c r="M476" t="n">
-        <v>-0.1694537960235074</v>
+        <v>-0.1694537464491869</v>
       </c>
       <c r="N476" t="n">
         <v>-0.1223384068011343</v>
       </c>
       <c r="O476" t="n">
-        <v>-0.1716854689197305</v>
+        <v>-0.1716853703031914</v>
       </c>
       <c r="P476" t="n">
-        <v>-0.06085692586325941</v>
+        <v>-0.06085688859278127</v>
       </c>
     </row>
     <row r="477">
@@ -35386,16 +35386,16 @@
         <v>-0.1520119764799557</v>
       </c>
       <c r="M478" t="n">
-        <v>-0.2854838568081043</v>
+        <v>-0.28548381413654</v>
       </c>
       <c r="N478" t="n">
-        <v>-0.2730988569592696</v>
+        <v>-0.2730989011229364</v>
       </c>
       <c r="O478" t="n">
-        <v>-0.07151042840851285</v>
+        <v>-0.07151050046423502</v>
       </c>
       <c r="P478" t="n">
-        <v>-0.02442871206729869</v>
+        <v>-0.02442873730380379</v>
       </c>
     </row>
     <row r="479">
@@ -35447,13 +35447,13 @@
         <v>-0.2287706279921752</v>
       </c>
       <c r="N479" t="n">
-        <v>-0.2697869978208008</v>
+        <v>-0.2697868793647156</v>
       </c>
       <c r="O479" t="n">
-        <v>3.50561442008015</v>
+        <v>3.505613856343608</v>
       </c>
       <c r="P479" t="n">
-        <v>0.6516499467503249</v>
+        <v>0.6516498778662334</v>
       </c>
     </row>
     <row r="480">
@@ -35615,13 +35615,13 @@
         <v>-0.3637805691704273</v>
       </c>
       <c r="N482" t="n">
-        <v>-0.3970859711782163</v>
+        <v>-0.3970860392018907</v>
       </c>
       <c r="O482" t="n">
-        <v>-0.2100470330339932</v>
+        <v>-0.2100470914217512</v>
       </c>
       <c r="P482" t="n">
-        <v>-0.07558479935994389</v>
+        <v>-0.0755848221353641</v>
       </c>
     </row>
     <row r="483">
@@ -35734,10 +35734,10 @@
         <v>-0.223339730138542</v>
       </c>
       <c r="O484" t="n">
-        <v>-0.1519225600066165</v>
+        <v>-0.1519224973801564</v>
       </c>
       <c r="P484" t="n">
-        <v>-0.05344649019686798</v>
+        <v>-0.05344646689738641</v>
       </c>
     </row>
     <row r="485">
@@ -35957,19 +35957,19 @@
         <v>-0.05756790819266622</v>
       </c>
       <c r="L488" t="n">
-        <v>-0.2562073264124767</v>
+        <v>-0.256207276230674</v>
       </c>
       <c r="M488" t="n">
-        <v>-0.3492782925368609</v>
+        <v>-0.3492782157188472</v>
       </c>
       <c r="N488" t="n">
-        <v>-0.3555384522212524</v>
+        <v>-0.3555383768741589</v>
       </c>
       <c r="O488" t="n">
-        <v>-0.2339966861195769</v>
+        <v>-0.2339967925666366</v>
       </c>
       <c r="P488" t="n">
-        <v>-0.08502291799748529</v>
+        <v>-0.08502296038051538</v>
       </c>
     </row>
     <row r="489">
@@ -36024,10 +36024,10 @@
         <v>-0.4975654500032018</v>
       </c>
       <c r="O489" t="n">
-        <v>-0.5783607655857738</v>
+        <v>-0.578360800769975</v>
       </c>
       <c r="P489" t="n">
-        <v>-0.2501397389740753</v>
+        <v>-0.2501397598317445</v>
       </c>
     </row>
     <row r="490">
@@ -36076,16 +36076,16 @@
         <v>-0.3805916544947721</v>
       </c>
       <c r="M490" t="n">
-        <v>-0.3439414469183725</v>
+        <v>-0.3439413872781715</v>
       </c>
       <c r="N490" t="n">
         <v>-0.2341248700782279</v>
       </c>
       <c r="O490" t="n">
-        <v>2.099396768938797</v>
+        <v>2.099396103392734</v>
       </c>
       <c r="P490" t="n">
-        <v>0.4580051521590496</v>
+        <v>0.4580050477979185</v>
       </c>
     </row>
     <row r="491">
@@ -36134,16 +36134,16 @@
         <v>0.03274701231595389</v>
       </c>
       <c r="M491" t="n">
-        <v>-0.2544771521745034</v>
+        <v>-0.2544770953015035</v>
       </c>
       <c r="N491" t="n">
         <v>-0.333040235042808</v>
       </c>
       <c r="O491" t="n">
-        <v>0.2831510539810924</v>
+        <v>0.2831511382194309</v>
       </c>
       <c r="P491" t="n">
-        <v>0.08665728281642737</v>
+        <v>0.08665730659596127</v>
       </c>
     </row>
     <row r="492">
@@ -36198,10 +36198,10 @@
         <v>-0.3068800828580911</v>
       </c>
       <c r="O492" t="n">
-        <v>0.04173461197210471</v>
+        <v>0.04173487162623268</v>
       </c>
       <c r="P492" t="n">
-        <v>0.01372237249356179</v>
+        <v>0.01372245671756467</v>
       </c>
     </row>
     <row r="493">
@@ -36250,16 +36250,16 @@
         <v>-0.3619959016830117</v>
       </c>
       <c r="M493" t="n">
-        <v>-0.3822626115324107</v>
+        <v>-0.3822626488003666</v>
       </c>
       <c r="N493" t="n">
-        <v>-0.4812996038982829</v>
+        <v>-0.4812996564504868</v>
       </c>
       <c r="O493" t="n">
-        <v>-0.5912147957132936</v>
+        <v>-0.5912147304335829</v>
       </c>
       <c r="P493" t="n">
-        <v>-0.2578385544868055</v>
+        <v>-0.2578385149810689</v>
       </c>
     </row>
     <row r="494">
@@ -36540,16 +36540,16 @@
         <v>-0.4027033050277223</v>
       </c>
       <c r="M498" t="n">
-        <v>-0.4066408172042983</v>
+        <v>-0.4066408544391175</v>
       </c>
       <c r="N498" t="n">
         <v>-0.3527771683906143</v>
       </c>
       <c r="O498" t="n">
-        <v>-0.05069275435856002</v>
+        <v>-0.05069284966614984</v>
       </c>
       <c r="P498" t="n">
-        <v>-0.01719143666352574</v>
+        <v>-0.0171914695538673</v>
       </c>
     </row>
     <row r="499">
@@ -36717,13 +36717,13 @@
         <v>-0.4197840671293929</v>
       </c>
       <c r="N501" t="n">
-        <v>-0.4308552290009259</v>
+        <v>-0.4308551881250126</v>
       </c>
       <c r="O501" t="n">
-        <v>-0.1088742356044675</v>
+        <v>-0.108874135397023</v>
       </c>
       <c r="P501" t="n">
-        <v>-0.03769442887577301</v>
+        <v>-0.03769439280522702</v>
       </c>
     </row>
     <row r="502">
